--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="441">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194986343384</t>
+    <t xml:space="preserve">13.2194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
@@ -53,31 +53,31 @@
     <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.523736000061</t>
+    <t xml:space="preserve">12.5237331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8020391464233</t>
+    <t xml:space="preserve">12.802041053772</t>
   </si>
   <si>
     <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758527755737</t>
+    <t xml:space="preserve">12.175853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279714584351</t>
+    <t xml:space="preserve">11.8279733657837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809120178223</t>
+    <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755996704102</t>
+    <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
     <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280223846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.088565826416</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990644454956</t>
+    <t xml:space="preserve">10.4990634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.4364452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451730728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843265533447</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773714065552</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826837539673</t>
+    <t xml:space="preserve">11.3826856613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.6331586837769</t>
@@ -119,55 +119,55 @@
     <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549787521362</t>
+    <t xml:space="preserve">12.1549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148024559021</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
     <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628875732422</t>
+    <t xml:space="preserve">12.6628856658936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933132171631</t>
+    <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150081634521</t>
+    <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506172180176</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114627838135</t>
+    <t xml:space="preserve">11.9114637374878</t>
   </si>
   <si>
     <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227861404419</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236061096191</t>
+    <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841327667236</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163724899292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407119750977</t>
+    <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045267105103</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670269012451</t>
+    <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
     <t xml:space="preserve">11.5065040588379</t>
@@ -176,46 +176,46 @@
     <t xml:space="preserve">11.5788726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893991470337</t>
+    <t xml:space="preserve">11.289400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426874160767</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979511260986</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
     <t xml:space="preserve">11.6512384414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683443069458</t>
+    <t xml:space="preserve">11.8683433532715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.832160949707</t>
+    <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130805969238</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.0854463577271</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939973831177</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025493621826</t>
+    <t xml:space="preserve">12.3025522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275535583496</t>
+    <t xml:space="preserve">12.0275526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
     <t xml:space="preserve">12.447286605835</t>
@@ -224,112 +224,112 @@
     <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643905639648</t>
+    <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.9466257095337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729444503784</t>
+    <t xml:space="preserve">12.7729415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755735397339</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091287612915</t>
+    <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.243335723877</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157014846802</t>
+    <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.388069152832</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025430679321</t>
+    <t xml:space="preserve">13.4025449752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4531993865967</t>
+    <t xml:space="preserve">13.4532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242563247681</t>
+    <t xml:space="preserve">13.4242525100708</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689897537231</t>
+    <t xml:space="preserve">13.5689878463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966220855713</t>
+    <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459638595581</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387273788452</t>
+    <t xml:space="preserve">13.4387264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071495056152</t>
+    <t xml:space="preserve">13.2071504592896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038604736328</t>
+    <t xml:space="preserve">13.5038614273071</t>
   </si>
   <si>
     <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881495475769</t>
+    <t xml:space="preserve">12.8814926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985994338989</t>
+    <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262317657471</t>
+    <t xml:space="preserve">13.0262298583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347827911377</t>
+    <t xml:space="preserve">13.1347818374634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453092575073</t>
+    <t xml:space="preserve">12.8453102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275444030762</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
     <t xml:space="preserve">12.7439956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189933776855</t>
+    <t xml:space="preserve">13.0189924240112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571559906006</t>
+    <t xml:space="preserve">12.6571550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446565628052</t>
+    <t xml:space="preserve">12.2446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012367248535</t>
+    <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334735870361</t>
+    <t xml:space="preserve">11.9334754943848</t>
   </si>
   <si>
     <t xml:space="preserve">12.1143941879272</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466329574585</t>
+    <t xml:space="preserve">11.8466339111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0782108306885</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722888946533</t>
+    <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551849365234</t>
+    <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
     <t xml:space="preserve">11.9696588516235</t>
@@ -368,40 +368,40 @@
     <t xml:space="preserve">11.9768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.150577545166</t>
+    <t xml:space="preserve">12.1505784988403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229471206665</t>
+    <t xml:space="preserve">12.2229452133179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554164886475</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054847717285</t>
+    <t xml:space="preserve">12.3054819107056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329069137573</t>
+    <t xml:space="preserve">12.1329050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428657531738</t>
+    <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180326461792</t>
+    <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756025314331</t>
@@ -410,133 +410,133 @@
     <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158418655396</t>
+    <t xml:space="preserve">13.1158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807844161987</t>
+    <t xml:space="preserve">12.9807834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732799530029</t>
+    <t xml:space="preserve">12.9732789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881542205811</t>
+    <t xml:space="preserve">12.6881523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657773971558</t>
+    <t xml:space="preserve">12.9657764434814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432668685913</t>
+    <t xml:space="preserve">12.9432649612427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308488845825</t>
+    <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457250595093</t>
+    <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083393096924</t>
+    <t xml:space="preserve">13.1083383560181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093334197998</t>
+    <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559503555298</t>
+    <t xml:space="preserve">13.3559484481812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809181213379</t>
+    <t xml:space="preserve">13.2809190750122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.4309844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735483169556</t>
+    <t xml:space="preserve">13.5735464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435352325439</t>
+    <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358980178833</t>
+    <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
+    <t xml:space="preserve">13.1383543014526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205883026123</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685010910034</t>
+    <t xml:space="preserve">13.4685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184328079224</t>
+    <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434024810791</t>
+    <t xml:space="preserve">13.2433996200562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683673858643</t>
+    <t xml:space="preserve">13.1683664321899</t>
   </si>
   <si>
     <t xml:space="preserve">13.5060176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560821533203</t>
   </si>
   <si>
     <t xml:space="preserve">13.6185674667358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061513900757</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687685012817</t>
+    <t xml:space="preserve">14.0687665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936006546021</t>
+    <t xml:space="preserve">13.6936016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485795974731</t>
+    <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4159784317017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562187194824</t>
+    <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312528610229</t>
+    <t xml:space="preserve">14.0312509536743</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609966278076</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.445990562439</t>
+    <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986488342285</t>
+    <t xml:space="preserve">13.7986459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087404251099</t>
+    <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315212249756</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
     <t xml:space="preserve">14.3013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165142059326</t>
+    <t xml:space="preserve">14.616512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.6915454864502</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">14.9991836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066862106323</t>
+    <t xml:space="preserve">15.006688117981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9916801452637</t>
+    <t xml:space="preserve">14.9916791915894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9766750335693</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465272903442</t>
+    <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
     <t xml:space="preserve">14.894136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567506790161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606951713562</t>
+    <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568872451782</t>
+    <t xml:space="preserve">15.4568891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570209503174</t>
+    <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
     <t xml:space="preserve">16.3572883605957</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.707893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576885223389</t>
+    <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076202392578</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575538635254</t>
+    <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
     <t xml:space="preserve">16.5073528289795</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615779876709</t>
+    <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
     <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702861785889</t>
+    <t xml:space="preserve">16.6702842712402</t>
   </si>
   <si>
     <t xml:space="preserve">14.9723854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898036956787</t>
+    <t xml:space="preserve">15.5898008346558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354496002197</t>
+    <t xml:space="preserve">15.435450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441577911377</t>
+    <t xml:space="preserve">15.744158744812</t>
   </si>
   <si>
     <t xml:space="preserve">16.5159301757812</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">16.2072238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8246383666992</t>
+    <t xml:space="preserve">16.8246402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985118865967</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
     <t xml:space="preserve">15.1267404556274</t>
@@ -647,46 +647,46 @@
     <t xml:space="preserve">15.0495634078979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636781692505</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
     <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549690246582</t>
+    <t xml:space="preserve">14.3549661636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321451187134</t>
+    <t xml:space="preserve">14.4321441650391</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522134780884</t>
+    <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7717990875244</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.45152759552</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917324066162</t>
+    <t xml:space="preserve">13.6917333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721448898315</t>
+    <t xml:space="preserve">14.1721439361572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116638183594</t>
+    <t xml:space="preserve">13.611665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315952301025</t>
+    <t xml:space="preserve">13.5315933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120048522949</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
     <t xml:space="preserve">13.8518705368042</t>
@@ -695,25 +695,25 @@
     <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.291389465332</t>
+    <t xml:space="preserve">13.2913885116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123497009277</t>
+    <t xml:space="preserve">14.4123487472534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920743942261</t>
+    <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714580535889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.131254196167</t>
+    <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971116065979</t>
+    <t xml:space="preserve">12.9711151123047</t>
   </si>
   <si>
     <t xml:space="preserve">12.8910465240479</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309103012085</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
     <t xml:space="preserve">12.6508417129517</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302225112915</t>
+    <t xml:space="preserve">11.9302215576172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.690016746521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903596878052</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498119354248</t>
+    <t xml:space="preserve">11.4498100280762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099481582642</t>
+    <t xml:space="preserve">11.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096061706543</t>
+    <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
     <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491250991821</t>
@@ -791,34 +791,34 @@
     <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687126159668</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700853347778</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102910995483</t>
+    <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493280410767</t>
+    <t xml:space="preserve">12.8493270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990161895752</t>
+    <t xml:space="preserve">12.5990171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.348705291748</t>
+    <t xml:space="preserve">12.3487043380737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137090682983</t>
+    <t xml:space="preserve">11.0137100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.681206703186</t>
+    <t xml:space="preserve">11.6812076568604</t>
   </si>
   <si>
     <t xml:space="preserve">11.9315176010132</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321413040161</t>
+    <t xml:space="preserve">12.4321403503418</t>
   </si>
   <si>
     <t xml:space="preserve">12.5155792236328</t>
@@ -842,52 +842,52 @@
     <t xml:space="preserve">13.4333877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499517440796</t>
+    <t xml:space="preserve">13.3499507904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7658891677856</t>
+    <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683849334717</t>
+    <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
     <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518218994141</t>
+    <t xml:space="preserve">14.8518190383911</t>
   </si>
   <si>
     <t xml:space="preserve">14.4346351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021318435669</t>
+    <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186958312988</t>
+    <t xml:space="preserve">15.0186939239502</t>
   </si>
   <si>
     <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015071868896</t>
+    <t xml:space="preserve">14.601508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511972427368</t>
+    <t xml:space="preserve">14.3511981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843223571777</t>
+    <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174474716187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837015151978</t>
+    <t xml:space="preserve">13.6837005615234</t>
   </si>
   <si>
     <t xml:space="preserve">13.7671365737915</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677593231201</t>
+    <t xml:space="preserve">14.2677612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741510391235</t>
+    <t xml:space="preserve">13.5741519927979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255243301392</t>
+    <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2444791793823</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931058883667</t>
+    <t xml:space="preserve">13.9931077957153</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903612136841</t>
+    <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
     <t xml:space="preserve">14.3282699584961</t>
@@ -938,46 +938,46 @@
     <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8310174942017</t>
+    <t xml:space="preserve">14.8310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985990524292</t>
+    <t xml:space="preserve">14.9985980987549</t>
   </si>
   <si>
     <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148063659668</t>
+    <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661806106567</t>
+    <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337621688843</t>
+    <t xml:space="preserve">15.3337602615356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.417552947998</t>
+    <t xml:space="preserve">15.4175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499732971191</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851345062256</t>
+    <t xml:space="preserve">15.5851373672485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689291000366</t>
+    <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9202995300293</t>
+    <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0182361602783</t>
+    <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311819076538</t>
+    <t xml:space="preserve">15.9311809539795</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
@@ -1007,37 +1007,37 @@
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829610824585</t>
+    <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088497161865</t>
+    <t xml:space="preserve">15.4088487625122</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405731201172</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146835327148</t>
+    <t xml:space="preserve">16.7146854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8887920379639</t>
+    <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758491516113</t>
+    <t xml:space="preserve">16.97585105896</t>
   </si>
   <si>
     <t xml:space="preserve">17.585241317749</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557971954346</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111289978027</t>
+    <t xml:space="preserve">17.4111270904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886505126953</t>
+    <t xml:space="preserve">18.2886524200439</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359622955322</t>
+    <t xml:space="preserve">17.8359603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264984130859</t>
+    <t xml:space="preserve">17.9264965057373</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1112,19 +1112,16 @@
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778919219971</t>
+    <t xml:space="preserve">16.4778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8441257476807</t>
+    <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2062797546387</t>
+    <t xml:space="preserve">16.20627784729</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1136,28 +1133,28 @@
     <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589660644531</t>
+    <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630516052246</t>
+    <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535905838013</t>
+    <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819755554199</t>
+    <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955211639404</t>
+    <t xml:space="preserve">14.3955202102661</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5806798934937</t>
+    <t xml:space="preserve">13.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">14.1239080429077</t>
@@ -1166,19 +1163,19 @@
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996047973633</t>
+    <t xml:space="preserve">13.3996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901428222656</t>
+    <t xml:space="preserve">13.4901418685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333690643311</t>
+    <t xml:space="preserve">14.0333700180054</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -44750,7 +44747,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44776,7 +44773,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44828,7 +44825,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44854,7 +44851,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44880,7 +44877,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44906,7 +44903,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44932,7 +44929,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44958,7 +44955,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44984,7 +44981,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45010,7 +45007,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45036,7 +45033,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45062,7 +45059,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45088,7 +45085,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45114,7 +45111,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45140,7 +45137,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45166,7 +45163,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45192,7 +45189,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45218,7 +45215,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45244,7 +45241,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45270,7 +45267,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45296,7 +45293,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45322,7 +45319,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45348,7 +45345,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45374,7 +45371,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45426,7 +45423,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45452,7 +45449,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45712,7 +45709,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45946,7 +45943,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45972,7 +45969,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45998,7 +45995,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46024,7 +46021,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46050,7 +46047,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46076,7 +46073,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46102,7 +46099,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46128,7 +46125,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46154,7 +46151,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46180,7 +46177,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46206,7 +46203,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46232,7 +46229,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46258,7 +46255,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46336,7 +46333,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46362,7 +46359,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46544,7 +46541,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46570,7 +46567,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46596,7 +46593,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46622,7 +46619,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46648,7 +46645,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46674,7 +46671,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46700,7 +46697,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46726,7 +46723,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46752,7 +46749,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46778,7 +46775,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46804,7 +46801,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46830,7 +46827,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46856,7 +46853,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46882,7 +46879,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46908,7 +46905,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46934,7 +46931,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46960,7 +46957,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46986,7 +46983,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47012,7 +47009,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47038,7 +47035,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47064,7 +47061,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47116,7 +47113,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47142,7 +47139,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47168,7 +47165,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47194,7 +47191,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47220,7 +47217,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47246,7 +47243,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47272,7 +47269,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47298,7 +47295,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47324,7 +47321,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47350,7 +47347,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47376,7 +47373,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47402,7 +47399,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47506,7 +47503,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47532,7 +47529,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47558,7 +47555,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47584,7 +47581,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47610,7 +47607,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47636,7 +47633,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47662,7 +47659,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47688,7 +47685,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47714,7 +47711,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47766,7 +47763,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47792,7 +47789,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47818,7 +47815,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47844,7 +47841,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47870,7 +47867,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47896,7 +47893,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47922,7 +47919,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48000,7 +47997,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48026,7 +48023,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48052,7 +48049,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48078,7 +48075,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48104,7 +48101,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48130,7 +48127,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48156,7 +48153,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48182,7 +48179,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48234,7 +48231,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48260,7 +48257,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48286,7 +48283,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48338,7 +48335,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48598,7 +48595,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48624,7 +48621,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48650,7 +48647,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48676,7 +48673,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48702,7 +48699,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48728,7 +48725,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48754,7 +48751,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48780,7 +48777,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48806,7 +48803,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48832,7 +48829,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48858,7 +48855,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48884,7 +48881,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48910,7 +48907,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48936,7 +48933,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48962,7 +48959,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48988,7 +48985,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49014,7 +49011,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49040,7 +49037,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49066,7 +49063,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49092,7 +49089,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49118,7 +49115,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49144,7 +49141,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49170,7 +49167,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49196,7 +49193,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49222,7 +49219,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49248,7 +49245,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49274,7 +49271,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49300,7 +49297,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49326,7 +49323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49352,7 +49349,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49378,7 +49375,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49404,7 +49401,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49430,7 +49427,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49456,7 +49453,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49482,7 +49479,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49508,7 +49505,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49534,7 +49531,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49560,7 +49557,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49586,7 +49583,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49612,7 +49609,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49638,7 +49635,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49664,7 +49661,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49690,7 +49687,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49716,7 +49713,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49742,7 +49739,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49768,7 +49765,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49794,7 +49791,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49820,7 +49817,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49846,7 +49843,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49872,7 +49869,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49898,7 +49895,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49924,7 +49921,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49950,7 +49947,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49976,7 +49973,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50002,7 +49999,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50028,7 +50025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50054,7 +50051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50080,7 +50077,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50106,7 +50103,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50132,7 +50129,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50158,7 +50155,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50184,7 +50181,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50210,7 +50207,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50236,7 +50233,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50262,7 +50259,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50288,7 +50285,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50314,7 +50311,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50340,7 +50337,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50366,7 +50363,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50392,7 +50389,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50418,7 +50415,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50444,7 +50441,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50470,7 +50467,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50496,7 +50493,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50522,7 +50519,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50548,7 +50545,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50574,7 +50571,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50600,7 +50597,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50626,7 +50623,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50652,7 +50649,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50678,7 +50675,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50704,7 +50701,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50730,7 +50727,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50756,7 +50753,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50782,7 +50779,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50808,7 +50805,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50834,7 +50831,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50860,7 +50857,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50886,7 +50883,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50912,7 +50909,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50938,7 +50935,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50964,7 +50961,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50990,7 +50987,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51016,7 +51013,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51042,7 +51039,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51068,7 +51065,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51094,7 +51091,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51120,7 +51117,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51146,7 +51143,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51172,7 +51169,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51198,7 +51195,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51224,7 +51221,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51250,7 +51247,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51276,7 +51273,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51302,7 +51299,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51328,7 +51325,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51354,7 +51351,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51380,7 +51377,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51406,7 +51403,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51432,7 +51429,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51458,7 +51455,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51484,7 +51481,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51510,7 +51507,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51536,7 +51533,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51562,7 +51559,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51588,7 +51585,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51614,7 +51611,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51640,7 +51637,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51666,7 +51663,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51692,7 +51689,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51718,7 +51715,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51744,7 +51741,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51770,7 +51767,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51796,7 +51793,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51822,7 +51819,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51848,7 +51845,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51874,7 +51871,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51900,7 +51897,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51926,7 +51923,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51952,7 +51949,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51978,7 +51975,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52004,7 +52001,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52030,7 +52027,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52056,7 +52053,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52082,7 +52079,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52108,7 +52105,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52134,7 +52131,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52160,7 +52157,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52186,7 +52183,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52212,7 +52209,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52238,7 +52235,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52264,7 +52261,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52290,7 +52287,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52316,7 +52313,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52342,7 +52339,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52368,7 +52365,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52394,7 +52391,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52420,7 +52417,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52446,7 +52443,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52472,7 +52469,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52498,7 +52495,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52524,7 +52521,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52550,7 +52547,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52576,7 +52573,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52602,7 +52599,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52628,7 +52625,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52654,7 +52651,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52680,7 +52677,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52706,7 +52703,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52732,7 +52729,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52758,7 +52755,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52784,7 +52781,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52810,7 +52807,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52836,7 +52833,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52862,7 +52859,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52888,7 +52885,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52914,7 +52911,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52940,7 +52937,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52966,7 +52963,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -52992,7 +52989,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53018,7 +53015,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53044,7 +53041,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53070,7 +53067,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53096,7 +53093,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53122,7 +53119,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53148,7 +53145,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53174,7 +53171,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53200,7 +53197,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53226,7 +53223,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53252,7 +53249,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53278,7 +53275,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53304,7 +53301,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53330,7 +53327,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53356,7 +53353,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53382,7 +53379,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53408,7 +53405,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53434,7 +53431,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53460,7 +53457,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53486,7 +53483,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53512,7 +53509,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53538,7 +53535,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53564,7 +53561,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53590,7 +53587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53616,7 +53613,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53642,7 +53639,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53668,7 +53665,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53694,7 +53691,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53720,7 +53717,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53746,7 +53743,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53772,7 +53769,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53798,7 +53795,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53824,7 +53821,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53850,7 +53847,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53876,7 +53873,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53902,7 +53899,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53928,7 +53925,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53954,7 +53951,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53980,7 +53977,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54006,7 +54003,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54032,7 +54029,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54058,7 +54055,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54084,7 +54081,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54110,7 +54107,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54136,7 +54133,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54162,7 +54159,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54188,7 +54185,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54214,7 +54211,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54240,7 +54237,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54266,7 +54263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54292,7 +54289,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54318,7 +54315,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54344,7 +54341,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54370,7 +54367,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54396,7 +54393,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54422,7 +54419,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54448,7 +54445,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54474,7 +54471,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54500,7 +54497,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54526,7 +54523,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54552,7 +54549,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54578,7 +54575,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54604,7 +54601,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54630,7 +54627,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54656,7 +54653,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54682,7 +54679,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54708,7 +54705,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54734,7 +54731,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54760,7 +54757,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54786,7 +54783,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54812,7 +54809,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54838,7 +54835,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54864,7 +54861,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54890,7 +54887,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54916,7 +54913,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54942,7 +54939,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54968,7 +54965,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -54994,7 +54991,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55020,7 +55017,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55046,7 +55043,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55072,7 +55069,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55098,7 +55095,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55124,7 +55121,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55150,7 +55147,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55176,7 +55173,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55202,7 +55199,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55228,7 +55225,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55254,7 +55251,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55280,7 +55277,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55306,7 +55303,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55332,7 +55329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55358,7 +55355,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55384,7 +55381,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55410,7 +55407,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55436,7 +55433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55462,7 +55459,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55488,7 +55485,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55514,7 +55511,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55540,7 +55537,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55566,7 +55563,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55592,7 +55589,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55618,7 +55615,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55644,7 +55641,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55670,7 +55667,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55696,7 +55693,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55722,7 +55719,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55748,7 +55745,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55774,7 +55771,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55800,7 +55797,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55826,7 +55823,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55852,7 +55849,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55878,7 +55875,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55904,7 +55901,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55930,7 +55927,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55956,7 +55953,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55982,7 +55979,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56008,7 +56005,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56034,7 +56031,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56060,7 +56057,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56086,7 +56083,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56112,7 +56109,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56138,7 +56135,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56164,7 +56161,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56190,7 +56187,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56216,7 +56213,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56242,7 +56239,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56268,7 +56265,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56294,7 +56291,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56320,7 +56317,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56346,7 +56343,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56372,7 +56369,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56398,7 +56395,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56424,7 +56421,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56450,7 +56447,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56476,7 +56473,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56502,7 +56499,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56528,7 +56525,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56554,7 +56551,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56580,7 +56577,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56606,7 +56603,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56632,7 +56629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56658,7 +56655,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56684,7 +56681,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56710,7 +56707,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56736,7 +56733,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56762,7 +56759,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56788,7 +56785,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56814,7 +56811,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56840,7 +56837,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56866,7 +56863,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56892,7 +56889,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56918,7 +56915,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56944,7 +56941,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56970,7 +56967,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -56996,7 +56993,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57022,7 +57019,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57048,7 +57045,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57074,7 +57071,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57100,7 +57097,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57126,7 +57123,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57152,7 +57149,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57178,7 +57175,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57204,7 +57201,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57230,7 +57227,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57256,7 +57253,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57282,7 +57279,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57308,7 +57305,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57334,7 +57331,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57360,7 +57357,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57386,7 +57383,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57412,7 +57409,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57438,7 +57435,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57464,7 +57461,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57490,7 +57487,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57516,7 +57513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57542,7 +57539,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57568,7 +57565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57594,7 +57591,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57620,7 +57617,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57646,7 +57643,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57672,7 +57669,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57698,7 +57695,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57724,7 +57721,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57750,7 +57747,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57776,7 +57773,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57802,7 +57799,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57828,7 +57825,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57854,7 +57851,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57880,7 +57877,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57906,7 +57903,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57932,7 +57929,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57958,7 +57955,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57984,7 +57981,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58010,7 +58007,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58036,7 +58033,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58062,7 +58059,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58088,7 +58085,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58114,7 +58111,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58140,7 +58137,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58166,7 +58163,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58192,7 +58189,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58218,7 +58215,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58244,7 +58241,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58270,7 +58267,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58296,7 +58293,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58322,7 +58319,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58348,7 +58345,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58374,7 +58371,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58400,7 +58397,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58426,7 +58423,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58452,7 +58449,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58478,7 +58475,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58504,7 +58501,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58530,7 +58527,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58556,7 +58553,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58582,7 +58579,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58608,7 +58605,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58634,7 +58631,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58660,7 +58657,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58686,7 +58683,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58712,7 +58709,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58738,7 +58735,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58764,7 +58761,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58790,7 +58787,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58816,7 +58813,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58842,7 +58839,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58868,7 +58865,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58894,7 +58891,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58920,7 +58917,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58946,7 +58943,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58972,7 +58969,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -58998,7 +58995,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59024,7 +59021,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59050,7 +59047,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59076,7 +59073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59102,7 +59099,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59128,7 +59125,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59154,7 +59151,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59180,7 +59177,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59206,7 +59203,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59232,7 +59229,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59258,7 +59255,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59284,7 +59281,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59310,7 +59307,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59336,7 +59333,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59362,7 +59359,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59388,7 +59385,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59414,7 +59411,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59440,7 +59437,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59466,7 +59463,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59492,7 +59489,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59518,7 +59515,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59544,7 +59541,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59570,7 +59567,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59596,7 +59593,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59622,7 +59619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59648,7 +59645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59674,7 +59671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59700,7 +59697,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59726,7 +59723,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59752,7 +59749,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59778,7 +59775,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59804,7 +59801,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59830,7 +59827,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59856,7 +59853,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59882,7 +59879,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59908,7 +59905,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59934,7 +59931,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59960,7 +59957,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59986,7 +59983,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60012,7 +60009,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60038,7 +60035,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60064,7 +60061,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60090,7 +60087,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60116,7 +60113,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60142,7 +60139,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60168,7 +60165,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60194,7 +60191,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60220,7 +60217,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60246,7 +60243,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60272,7 +60269,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60298,7 +60295,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60324,7 +60321,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60350,7 +60347,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60376,7 +60373,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60402,7 +60399,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60428,7 +60425,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60454,7 +60451,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60480,7 +60477,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60506,7 +60503,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60532,7 +60529,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60558,7 +60555,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60584,7 +60581,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60610,7 +60607,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60636,7 +60633,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60662,7 +60659,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60688,7 +60685,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60714,7 +60711,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60740,7 +60737,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60766,7 +60763,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60792,7 +60789,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60818,7 +60815,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60844,7 +60841,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60870,7 +60867,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60896,7 +60893,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60922,7 +60919,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60948,7 +60945,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60974,7 +60971,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61000,7 +60997,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61026,7 +61023,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61052,7 +61049,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61078,7 +61075,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61104,7 +61101,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61130,7 +61127,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61156,7 +61153,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61182,7 +61179,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61208,7 +61205,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61234,7 +61231,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61260,7 +61257,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61286,7 +61283,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61312,7 +61309,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61338,7 +61335,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61364,7 +61361,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61390,7 +61387,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61416,7 +61413,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61442,7 +61439,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61468,7 +61465,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61494,7 +61491,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61520,7 +61517,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61546,7 +61543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61572,7 +61569,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61598,7 +61595,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61624,7 +61621,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61650,7 +61647,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61676,7 +61673,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61702,7 +61699,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61728,7 +61725,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61754,7 +61751,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61780,7 +61777,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61806,7 +61803,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61832,7 +61829,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61858,7 +61855,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61884,7 +61881,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61910,7 +61907,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61936,7 +61933,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61962,7 +61959,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -61988,7 +61985,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62014,7 +62011,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62040,7 +62037,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62066,7 +62063,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62092,7 +62089,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62118,7 +62115,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62144,7 +62141,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62170,7 +62167,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62196,7 +62193,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62222,7 +62219,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62248,7 +62245,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62274,7 +62271,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62300,7 +62297,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62326,7 +62323,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62352,7 +62349,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62378,7 +62375,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62404,7 +62401,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62430,7 +62427,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62456,7 +62453,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62482,7 +62479,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62508,7 +62505,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62534,7 +62531,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62560,7 +62557,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62586,7 +62583,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62612,7 +62609,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62638,7 +62635,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62664,7 +62661,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62690,7 +62687,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62716,7 +62713,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62742,7 +62739,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62768,7 +62765,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62794,7 +62791,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62820,7 +62817,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62846,7 +62843,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62872,7 +62869,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62898,7 +62895,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62924,7 +62921,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62950,7 +62947,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62976,7 +62973,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63002,7 +62999,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63028,7 +63025,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63054,7 +63051,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63080,7 +63077,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63106,7 +63103,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63132,7 +63129,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63158,7 +63155,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63184,7 +63181,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63210,7 +63207,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63236,7 +63233,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63262,7 +63259,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63288,7 +63285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63314,7 +63311,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63340,7 +63337,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63366,7 +63363,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63392,7 +63389,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63418,7 +63415,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63444,7 +63441,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63470,7 +63467,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63496,7 +63493,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63522,7 +63519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63548,7 +63545,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63574,7 +63571,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63600,7 +63597,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63626,7 +63623,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63652,7 +63649,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63678,7 +63675,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63704,7 +63701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63730,7 +63727,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63756,7 +63753,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63782,7 +63779,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63808,7 +63805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63834,7 +63831,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63860,7 +63857,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63886,7 +63883,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63912,7 +63909,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63938,7 +63935,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63964,7 +63961,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63990,7 +63987,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64016,7 +64013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64042,7 +64039,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64068,7 +64065,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64094,7 +64091,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64120,7 +64117,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64146,7 +64143,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64172,7 +64169,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64198,7 +64195,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64224,7 +64221,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64250,7 +64247,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64276,7 +64273,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64302,7 +64299,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64328,7 +64325,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64354,7 +64351,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64380,7 +64377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64406,7 +64403,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64432,7 +64429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64458,7 +64455,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64484,7 +64481,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64510,7 +64507,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64536,7 +64533,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64562,7 +64559,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64588,7 +64585,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64614,7 +64611,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64640,7 +64637,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64666,7 +64663,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64692,7 +64689,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64718,7 +64715,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64744,7 +64741,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64770,7 +64767,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64796,7 +64793,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64822,7 +64819,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64848,7 +64845,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64874,7 +64871,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64900,7 +64897,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64926,7 +64923,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64952,7 +64949,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64978,7 +64975,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65004,7 +65001,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65030,7 +65027,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65056,7 +65053,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65082,7 +65079,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65108,7 +65105,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65134,7 +65131,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65160,7 +65157,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65186,7 +65183,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65212,7 +65209,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65238,7 +65235,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65264,7 +65261,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65290,7 +65287,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65316,7 +65313,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65342,7 +65339,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65368,7 +65365,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65394,7 +65391,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65420,7 +65417,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65446,7 +65443,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65472,7 +65469,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65498,7 +65495,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65524,7 +65521,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65550,7 +65547,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65576,7 +65573,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65602,7 +65599,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65628,7 +65625,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65654,7 +65651,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65680,7 +65677,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65706,7 +65703,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65732,7 +65729,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65758,7 +65755,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65784,7 +65781,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65810,7 +65807,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65836,7 +65833,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65862,7 +65859,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65888,7 +65885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65914,7 +65911,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65940,7 +65937,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65966,7 +65963,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65992,7 +65989,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66018,7 +66015,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66044,7 +66041,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66070,7 +66067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66096,7 +66093,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66122,7 +66119,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66148,7 +66145,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66174,7 +66171,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66200,7 +66197,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66226,7 +66223,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66252,7 +66249,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66278,7 +66275,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66304,7 +66301,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66330,7 +66327,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66338,7 +66335,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.565625</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>1181</v>
@@ -66356,9 +66353,35 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494328704</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194995880127</t>
+    <t xml:space="preserve">13.2194986343384</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">13.149920463562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8577032089233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716144561768</t>
+    <t xml:space="preserve">12.8716154098511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237369537354</t>
+    <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
     <t xml:space="preserve">12.8020401000977</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.175853729248</t>
+    <t xml:space="preserve">12.1758546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279733657837</t>
+    <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809129714966</t>
+    <t xml:space="preserve">11.1809139251709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755996704102</t>
+    <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
     <t xml:space="preserve">9.39280223846436</t>
@@ -92,61 +92,61 @@
     <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364452362061</t>
+    <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
     <t xml:space="preserve">10.6451749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.714750289917</t>
+    <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
     <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773694992065</t>
+    <t xml:space="preserve">10.7773714065552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826856613159</t>
+    <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905916213989</t>
+    <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480226516724</t>
+    <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193716049194</t>
+    <t xml:space="preserve">12.4193706512451</t>
   </si>
   <si>
     <t xml:space="preserve">12.6628875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411916732788</t>
+    <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933094024658</t>
+    <t xml:space="preserve">12.5933103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150062561035</t>
+    <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506181716919</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583951950073</t>
+    <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227851867676</t>
@@ -155,100 +155,100 @@
     <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841327667236</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163724899292</t>
+    <t xml:space="preserve">11.7163705825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407119750977</t>
+    <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045267105103</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670269012451</t>
+    <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065021514893</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289400100708</t>
+    <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.542685508728</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512403488159</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.8321590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.193998336792</t>
+    <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025503158569</t>
+    <t xml:space="preserve">12.3025522232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275545120239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.295313835144</t>
+    <t xml:space="preserve">12.2953147888184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472875595093</t>
+    <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196552276611</t>
+    <t xml:space="preserve">12.5196561813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643896102905</t>
+    <t xml:space="preserve">12.6643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466238021851</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729434967041</t>
+    <t xml:space="preserve">12.7729444503784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755735397339</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538612365723</t>
+    <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091278076172</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.243335723877</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157014846802</t>
+    <t xml:space="preserve">13.3157005310059</t>
   </si>
   <si>
     <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.388069152832</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
     <t xml:space="preserve">13.4025440216064</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">13.4532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242534637451</t>
+    <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.5328044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689878463745</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554515838623</t>
+    <t xml:space="preserve">13.554518699646</t>
   </si>
   <si>
     <t xml:space="preserve">13.4966230392456</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459629058838</t>
+    <t xml:space="preserve">13.4459657669067</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387292861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071495056152</t>
+    <t xml:space="preserve">13.2071504592896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038614273071</t>
+    <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288589477539</t>
+    <t xml:space="preserve">13.2288608551025</t>
   </si>
   <si>
     <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985984802246</t>
+    <t xml:space="preserve">13.0985975265503</t>
   </si>
   <si>
     <t xml:space="preserve">12.9104404449463</t>
@@ -302,55 +302,55 @@
     <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.134783744812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.8453092575073</t>
   </si>
   <si>
     <t xml:space="preserve">13.1275453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439947128296</t>
+    <t xml:space="preserve">12.7439975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189924240112</t>
+    <t xml:space="preserve">13.0189933776855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571531295776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012338638306</t>
+    <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143970489502</t>
+    <t xml:space="preserve">12.1143960952759</t>
   </si>
   <si>
     <t xml:space="preserve">12.0709743499756</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492639541626</t>
+    <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466329574585</t>
+    <t xml:space="preserve">11.8466339111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913702011108</t>
+    <t xml:space="preserve">11.9913682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986047744751</t>
+    <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479484558105</t>
+    <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
     <t xml:space="preserve">12.1722888946533</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2301826477051</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554136276245</t>
+    <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.3054828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805170059204</t>
+    <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
     <t xml:space="preserve">12.3880186080933</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">12.0428657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180326461792</t>
+    <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756025314331</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158418655396</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
     <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732789993286</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657773971558</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432668685913</t>
+    <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
     <t xml:space="preserve">13.1308507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682336807251</t>
+    <t xml:space="preserve">12.8682327270508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845724105835</t>
+    <t xml:space="preserve">12.8457250595093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083402633667</t>
+    <t xml:space="preserve">13.1083383560181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933351516724</t>
+    <t xml:space="preserve">13.093334197998</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559503555298</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735454559326</t>
+    <t xml:space="preserve">13.5735464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435342788696</t>
+    <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.138352394104</t>
+    <t xml:space="preserve">13.1383543014526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234771728516</t>
+    <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058839797974</t>
+    <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934659957886</t>
@@ -473,73 +473,73 @@
     <t xml:space="preserve">13.4685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184337615967</t>
+    <t xml:space="preserve">13.3184328079224</t>
   </si>
   <si>
     <t xml:space="preserve">13.2434015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683654785156</t>
+    <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060186386108</t>
+    <t xml:space="preserve">13.5060176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185684204102</t>
+    <t xml:space="preserve">13.6185693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061513900757</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810527801514</t>
+    <t xml:space="preserve">13.5810499191284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687675476074</t>
+    <t xml:space="preserve">14.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6935997009277</t>
+    <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159784317017</t>
+    <t xml:space="preserve">13.4159774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562196731567</t>
+    <t xml:space="preserve">13.9562187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.03125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.460994720459</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.445990562439</t>
+    <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087413787842</t>
+    <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315183639526</t>
+    <t xml:space="preserve">14.6315202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013706207275</t>
+    <t xml:space="preserve">14.3013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165142059326</t>
+    <t xml:space="preserve">14.6165132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915483474731</t>
+    <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991827011108</t>
+    <t xml:space="preserve">14.9991855621338</t>
   </si>
   <si>
     <t xml:space="preserve">15.006688117981</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">14.991681098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766731262207</t>
+    <t xml:space="preserve">14.9766750335693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691696166992</t>
+    <t xml:space="preserve">14.9691724777222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941335678101</t>
+    <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
     <t xml:space="preserve">14.6390218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567525863647</t>
+    <t xml:space="preserve">15.1567535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069536209106</t>
+    <t xml:space="preserve">15.606951713562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568862915039</t>
+    <t xml:space="preserve">15.4568881988525</t>
   </si>
   <si>
     <t xml:space="preserve">15.757022857666</t>
@@ -581,127 +581,127 @@
     <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076259613037</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575576782227</t>
+    <t xml:space="preserve">16.9575538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073528289795</t>
+    <t xml:space="preserve">16.5073566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.807487487793</t>
+    <t xml:space="preserve">16.8074932098389</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571575164795</t>
+    <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615741729736</t>
+    <t xml:space="preserve">16.3615779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528659820557</t>
+    <t xml:space="preserve">16.052864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702842712402</t>
+    <t xml:space="preserve">16.6702880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723854064941</t>
+    <t xml:space="preserve">14.9723834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898036956787</t>
+    <t xml:space="preserve">15.5898027420044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354496002197</t>
+    <t xml:space="preserve">15.4354476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441558837891</t>
+    <t xml:space="preserve">15.7441568374634</t>
   </si>
   <si>
     <t xml:space="preserve">16.5159301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8246364593506</t>
+    <t xml:space="preserve">16.8246402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985137939453</t>
+    <t xml:space="preserve">15.898512840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267414093018</t>
+    <t xml:space="preserve">15.1267423629761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.0495624542236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636762619019</t>
+    <t xml:space="preserve">14.6636753082275</t>
   </si>
   <si>
     <t xml:space="preserve">15.2810935974121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549661636353</t>
+    <t xml:space="preserve">14.3549690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321460723877</t>
+    <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919057846069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522115707397</t>
+    <t xml:space="preserve">14.2522134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319372177124</t>
+    <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">13.771800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515266418457</t>
+    <t xml:space="preserve">13.45152759552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917333602905</t>
+    <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.1721448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116638183594</t>
+    <t xml:space="preserve">13.611665725708</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120067596436</t>
+    <t xml:space="preserve">14.0120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518714904785</t>
+    <t xml:space="preserve">13.8518705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113208770752</t>
+    <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2913885116577</t>
+    <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123497009277</t>
+    <t xml:space="preserve">14.4123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.092077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.131254196167</t>
+    <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
@@ -719,46 +719,46 @@
     <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302215576172</t>
+    <t xml:space="preserve">11.9302234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.690016746521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295375823975</t>
+    <t xml:space="preserve">11.1295385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896738052368</t>
+    <t xml:space="preserve">11.2896747589111</t>
   </si>
   <si>
     <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099472045898</t>
+    <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298805236816</t>
+    <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
     <t xml:space="preserve">11.369743347168</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9693984985352</t>
+    <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494689941406</t>
+    <t xml:space="preserve">11.0494680404663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491241455078</t>
+    <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288497924805</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889869689941</t>
+    <t xml:space="preserve">10.4889888763428</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089193344116</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">10.2487831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085754394531</t>
+    <t xml:space="preserve">10.0085773468018</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687126159668</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102920532227</t>
+    <t xml:space="preserve">12.0102910995483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493270874023</t>
+    <t xml:space="preserve">12.849328994751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990161895752</t>
+    <t xml:space="preserve">12.5990171432495</t>
   </si>
   <si>
     <t xml:space="preserve">12.3487043380737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137100219727</t>
+    <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
     <t xml:space="preserve">11.681206703186</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818313598633</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321413040161</t>
+    <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.932765007019</t>
+    <t xml:space="preserve">12.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">13.1830768585205</t>
@@ -848,82 +848,82 @@
     <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180702209473</t>
+    <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518190383911</t>
+    <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346361160278</t>
+    <t xml:space="preserve">14.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021318435669</t>
+    <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186939239502</t>
+    <t xml:space="preserve">15.0186967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849460601807</t>
+    <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511962890625</t>
+    <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0174474716187</t>
+    <t xml:space="preserve">14.0174493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837005615234</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671365737915</t>
+    <t xml:space="preserve">13.7671375274658</t>
   </si>
   <si>
     <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677602767944</t>
+    <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741519927979</t>
+    <t xml:space="preserve">13.5741500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255233764648</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444791793823</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093151092529</t>
+    <t xml:space="preserve">13.9093160629272</t>
   </si>
   <si>
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796432495117</t>
+    <t xml:space="preserve">14.5796422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606864929199</t>
+    <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6579399108887</t>
+    <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903612136841</t>
+    <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
     <t xml:space="preserve">14.3282709121704</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.831018447876</t>
+    <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4958515167236</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">14.9985980987549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472267150879</t>
+    <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148054122925</t>
+    <t xml:space="preserve">14.9148063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33376121521</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175539016724</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499742507935</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668927192688</t>
+    <t xml:space="preserve">15.6689291000366</t>
   </si>
   <si>
     <t xml:space="preserve">15.9202995300293</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878849029541</t>
+    <t xml:space="preserve">16.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794055938721</t>
+    <t xml:space="preserve">16.2794075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923503875732</t>
+    <t xml:space="preserve">16.1923484802246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1052951812744</t>
+    <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.018238067627</t>
+    <t xml:space="preserve">16.0182361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311809539795</t>
+    <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700162887573</t>
+    <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441295623779</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088506698608</t>
+    <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
     <t xml:space="preserve">16.3664588928223</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.627628326416</t>
+    <t xml:space="preserve">16.6276264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146854400635</t>
+    <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.97585105896</t>
+    <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
     <t xml:space="preserve">17.585241317749</t>
@@ -1040,40 +1040,37 @@
     <t xml:space="preserve">18.6299076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.107572555542</t>
+    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2816867828369</t>
+    <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
     <t xml:space="preserve">18.4557971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.759349822998</t>
+    <t xml:space="preserve">17.7593517303467</t>
   </si>
   <si>
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240718841553</t>
+    <t xml:space="preserve">17.3240737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111270904541</t>
+    <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4697246551514</t>
+    <t xml:space="preserve">18.4697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886524200439</t>
+    <t xml:space="preserve">18.2886505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1075744628906</t>
+    <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9264965057373</t>
+    <t xml:space="preserve">17.9264984130859</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1091,19 +1088,19 @@
     <t xml:space="preserve">17.6548843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021961212158</t>
+    <t xml:space="preserve">17.2021942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2927341461182</t>
+    <t xml:space="preserve">17.2927322387695</t>
   </si>
   <si>
     <t xml:space="preserve">16.4778938293457</t>
@@ -1112,7 +1109,7 @@
     <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -1127,43 +1124,43 @@
     <t xml:space="preserve">15.9346656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8400440216064</t>
+    <t xml:space="preserve">16.8400421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589679718018</t>
+    <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873558044434</t>
+    <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630506515503</t>
+    <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
     <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819765090942</t>
+    <t xml:space="preserve">15.4819774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955202102661</t>
+    <t xml:space="preserve">14.3955211639404</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580680847168</t>
+    <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239080429077</t>
+    <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3049840927124</t>
+    <t xml:space="preserve">14.3049831390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996057510376</t>
+    <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
     <t xml:space="preserve">13.4901418685913</t>
@@ -1172,7 +1169,7 @@
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333700180054</t>
+    <t xml:space="preserve">14.0333690643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1181,13 +1178,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1202,13 +1199,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1223,7 +1220,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1275,6 +1272,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -43600,7 +43600,7 @@
         <v>20</v>
       </c>
       <c r="G1613" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43626,7 +43626,7 @@
         <v>20</v>
       </c>
       <c r="G1614" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43678,7 +43678,7 @@
         <v>20</v>
       </c>
       <c r="G1616" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43704,7 +43704,7 @@
         <v>20</v>
       </c>
       <c r="G1617" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43730,7 +43730,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43756,7 +43756,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1619" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43782,7 +43782,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1620" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43808,7 +43808,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1621" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43834,7 +43834,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43860,7 +43860,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43886,7 +43886,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43912,7 +43912,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43938,7 +43938,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43964,7 +43964,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43990,7 +43990,7 @@
         <v>20</v>
       </c>
       <c r="G1628" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44016,7 +44016,7 @@
         <v>20</v>
       </c>
       <c r="G1629" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44042,7 +44042,7 @@
         <v>20</v>
       </c>
       <c r="G1630" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44068,7 +44068,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1631" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44094,7 +44094,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44120,7 +44120,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1633" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44146,7 +44146,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1634" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44172,7 +44172,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44198,7 +44198,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44224,7 +44224,7 @@
         <v>19.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44250,7 +44250,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44276,7 +44276,7 @@
         <v>19.5</v>
       </c>
       <c r="G1639" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44302,7 +44302,7 @@
         <v>19</v>
       </c>
       <c r="G1640" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44328,7 +44328,7 @@
         <v>19</v>
       </c>
       <c r="G1641" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44354,7 +44354,7 @@
         <v>19</v>
       </c>
       <c r="G1642" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44380,7 +44380,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44406,7 +44406,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44432,7 +44432,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1645" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44458,7 +44458,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1646" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44484,7 +44484,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1647" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44510,7 +44510,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1648" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44536,7 +44536,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44562,7 +44562,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44588,7 +44588,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44614,7 +44614,7 @@
         <v>19</v>
       </c>
       <c r="G1652" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44640,7 +44640,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44666,7 +44666,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1654" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44692,7 +44692,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44718,7 +44718,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44744,7 +44744,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44770,7 +44770,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44796,7 +44796,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44822,7 +44822,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44848,7 +44848,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44874,7 +44874,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44900,7 +44900,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44926,7 +44926,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44952,7 +44952,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44978,7 +44978,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45004,7 +45004,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45030,7 +45030,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45056,7 +45056,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45082,7 +45082,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45108,7 +45108,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45134,7 +45134,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45160,7 +45160,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45186,7 +45186,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45212,7 +45212,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45238,7 +45238,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45264,7 +45264,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45290,7 +45290,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45316,7 +45316,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45342,7 +45342,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45368,7 +45368,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45394,7 +45394,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45420,7 +45420,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45446,7 +45446,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45472,7 +45472,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1685" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45498,7 +45498,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45524,7 +45524,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45550,7 +45550,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1688" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45576,7 +45576,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1689" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45602,7 +45602,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45628,7 +45628,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1691" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45654,7 +45654,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1692" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45680,7 +45680,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1693" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45706,7 +45706,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45732,7 +45732,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1695" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45758,7 +45758,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45784,7 +45784,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1697" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45810,7 +45810,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45836,7 +45836,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45862,7 +45862,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45888,7 +45888,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1701" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45914,7 +45914,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45940,7 +45940,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45966,7 +45966,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45992,7 +45992,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46018,7 +46018,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46044,7 +46044,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46070,7 +46070,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46096,7 +46096,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46122,7 +46122,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46148,7 +46148,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46174,7 +46174,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46200,7 +46200,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46226,7 +46226,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46252,7 +46252,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46278,7 +46278,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1716" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46304,7 +46304,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46330,7 +46330,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46356,7 +46356,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46382,7 +46382,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46408,7 +46408,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1721" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46434,7 +46434,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46460,7 +46460,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46486,7 +46486,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46512,7 +46512,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1725" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46538,7 +46538,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46564,7 +46564,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46590,7 +46590,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46616,7 +46616,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46642,7 +46642,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46668,7 +46668,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46694,7 +46694,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46720,7 +46720,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46746,7 +46746,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46772,7 +46772,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46798,7 +46798,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46824,7 +46824,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46850,7 +46850,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46876,7 +46876,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46902,7 +46902,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46928,7 +46928,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46954,7 +46954,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46980,7 +46980,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47006,7 +47006,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47032,7 +47032,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47058,7 +47058,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47084,7 +47084,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1747" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47110,7 +47110,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47136,7 +47136,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47162,7 +47162,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47188,7 +47188,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47214,7 +47214,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47240,7 +47240,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47266,7 +47266,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47292,7 +47292,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47318,7 +47318,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47344,7 +47344,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47370,7 +47370,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47396,7 +47396,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47422,7 +47422,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1760" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47448,7 +47448,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47474,7 +47474,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1762" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47500,7 +47500,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47526,7 +47526,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47552,7 +47552,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47578,7 +47578,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47604,7 +47604,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47630,7 +47630,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47656,7 +47656,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47682,7 +47682,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47708,7 +47708,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47734,7 +47734,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1772" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47760,7 +47760,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47786,7 +47786,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47812,7 +47812,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47838,7 +47838,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47864,7 +47864,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47890,7 +47890,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47916,7 +47916,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47942,7 +47942,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47968,7 +47968,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47994,7 +47994,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48020,7 +48020,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48046,7 +48046,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48072,7 +48072,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48098,7 +48098,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48124,7 +48124,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48150,7 +48150,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48176,7 +48176,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48202,7 +48202,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48228,7 +48228,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48254,7 +48254,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48280,7 +48280,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48306,7 +48306,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48332,7 +48332,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48358,7 +48358,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48384,7 +48384,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1797" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48410,7 +48410,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48436,7 +48436,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1799" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48462,7 +48462,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48488,7 +48488,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1801" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48514,7 +48514,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48540,7 +48540,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48566,7 +48566,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48592,7 +48592,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48618,7 +48618,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48644,7 +48644,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48670,7 +48670,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48696,7 +48696,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48722,7 +48722,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48748,7 +48748,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48774,7 +48774,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48800,7 +48800,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48826,7 +48826,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48852,7 +48852,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48878,7 +48878,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48904,7 +48904,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48930,7 +48930,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48956,7 +48956,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48982,7 +48982,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49008,7 +49008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49034,7 +49034,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49060,7 +49060,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49086,7 +49086,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49112,7 +49112,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49138,7 +49138,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49164,7 +49164,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49190,7 +49190,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49216,7 +49216,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49242,7 +49242,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49268,7 +49268,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49294,7 +49294,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49320,7 +49320,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49346,7 +49346,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49372,7 +49372,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49398,7 +49398,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49424,7 +49424,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49450,7 +49450,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49476,7 +49476,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49502,7 +49502,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49528,7 +49528,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49554,7 +49554,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49580,7 +49580,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49606,7 +49606,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49632,7 +49632,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49658,7 +49658,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49684,7 +49684,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49710,7 +49710,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49736,7 +49736,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49762,7 +49762,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49788,7 +49788,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49814,7 +49814,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49840,7 +49840,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49866,7 +49866,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49892,7 +49892,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49918,7 +49918,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49944,7 +49944,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49970,7 +49970,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49996,7 +49996,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50022,7 +50022,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50048,7 +50048,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50074,7 +50074,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50100,7 +50100,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50126,7 +50126,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50152,7 +50152,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50178,7 +50178,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50204,7 +50204,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50230,7 +50230,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50256,7 +50256,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50282,7 +50282,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50308,7 +50308,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50334,7 +50334,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50360,7 +50360,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50386,7 +50386,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50412,7 +50412,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50438,7 +50438,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50464,7 +50464,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50490,7 +50490,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50516,7 +50516,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50542,7 +50542,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50568,7 +50568,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50594,7 +50594,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50620,7 +50620,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50646,7 +50646,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50672,7 +50672,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50698,7 +50698,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50724,7 +50724,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50750,7 +50750,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50776,7 +50776,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50802,7 +50802,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50828,7 +50828,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50854,7 +50854,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50880,7 +50880,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50906,7 +50906,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50932,7 +50932,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50958,7 +50958,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50984,7 +50984,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51010,7 +51010,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51036,7 +51036,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51062,7 +51062,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51088,7 +51088,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51114,7 +51114,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51140,7 +51140,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51166,7 +51166,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51192,7 +51192,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51218,7 +51218,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51244,7 +51244,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51270,7 +51270,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51296,7 +51296,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51322,7 +51322,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51348,7 +51348,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51374,7 +51374,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51400,7 +51400,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51426,7 +51426,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51452,7 +51452,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51478,7 +51478,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51504,7 +51504,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51530,7 +51530,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51556,7 +51556,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51582,7 +51582,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51608,7 +51608,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51634,7 +51634,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51660,7 +51660,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51686,7 +51686,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51712,7 +51712,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51738,7 +51738,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51764,7 +51764,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51790,7 +51790,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51816,7 +51816,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51842,7 +51842,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51868,7 +51868,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51894,7 +51894,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51920,7 +51920,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51946,7 +51946,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51972,7 +51972,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -51998,7 +51998,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52024,7 +52024,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52050,7 +52050,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52076,7 +52076,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52102,7 +52102,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52128,7 +52128,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52154,7 +52154,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52180,7 +52180,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52206,7 +52206,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52232,7 +52232,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52258,7 +52258,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52284,7 +52284,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52310,7 +52310,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52336,7 +52336,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52362,7 +52362,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52388,7 +52388,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52414,7 +52414,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52440,7 +52440,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52466,7 +52466,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52492,7 +52492,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52518,7 +52518,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52544,7 +52544,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52570,7 +52570,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52596,7 +52596,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52622,7 +52622,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52648,7 +52648,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52674,7 +52674,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52700,7 +52700,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52726,7 +52726,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52752,7 +52752,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52778,7 +52778,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52804,7 +52804,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52830,7 +52830,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52856,7 +52856,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52882,7 +52882,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52908,7 +52908,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52934,7 +52934,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52960,7 +52960,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -52986,7 +52986,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53012,7 +53012,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53038,7 +53038,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53064,7 +53064,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53090,7 +53090,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53116,7 +53116,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53142,7 +53142,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53168,7 +53168,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53194,7 +53194,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53220,7 +53220,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53246,7 +53246,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53272,7 +53272,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53298,7 +53298,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53324,7 +53324,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53350,7 +53350,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53376,7 +53376,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53402,7 +53402,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53428,7 +53428,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53454,7 +53454,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53480,7 +53480,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53506,7 +53506,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53532,7 +53532,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53558,7 +53558,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53584,7 +53584,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53610,7 +53610,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53636,7 +53636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53662,7 +53662,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53688,7 +53688,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53714,7 +53714,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53740,7 +53740,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53766,7 +53766,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53792,7 +53792,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53818,7 +53818,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53844,7 +53844,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53870,7 +53870,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53896,7 +53896,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53922,7 +53922,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53948,7 +53948,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53974,7 +53974,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54000,7 +54000,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54026,7 +54026,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54052,7 +54052,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54078,7 +54078,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54104,7 +54104,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54130,7 +54130,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54156,7 +54156,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54182,7 +54182,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54208,7 +54208,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54234,7 +54234,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54260,7 +54260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54286,7 +54286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54312,7 +54312,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54338,7 +54338,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54364,7 +54364,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54390,7 +54390,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54416,7 +54416,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54442,7 +54442,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54468,7 +54468,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54494,7 +54494,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54520,7 +54520,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54546,7 +54546,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54572,7 +54572,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54598,7 +54598,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54624,7 +54624,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54650,7 +54650,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54676,7 +54676,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54702,7 +54702,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54728,7 +54728,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54754,7 +54754,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54780,7 +54780,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54806,7 +54806,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54832,7 +54832,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54858,7 +54858,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54884,7 +54884,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54910,7 +54910,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54936,7 +54936,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54962,7 +54962,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -54988,7 +54988,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55014,7 +55014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55040,7 +55040,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55066,7 +55066,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55092,7 +55092,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55118,7 +55118,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55144,7 +55144,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55170,7 +55170,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55196,7 +55196,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55222,7 +55222,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55248,7 +55248,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55274,7 +55274,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55300,7 +55300,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55326,7 +55326,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55352,7 +55352,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55378,7 +55378,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55404,7 +55404,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55430,7 +55430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55456,7 +55456,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55482,7 +55482,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55508,7 +55508,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55534,7 +55534,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55560,7 +55560,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55586,7 +55586,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55612,7 +55612,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55638,7 +55638,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55664,7 +55664,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55690,7 +55690,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55716,7 +55716,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55742,7 +55742,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55768,7 +55768,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55794,7 +55794,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55820,7 +55820,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55846,7 +55846,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55872,7 +55872,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55898,7 +55898,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55924,7 +55924,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55950,7 +55950,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55976,7 +55976,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56002,7 +56002,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56028,7 +56028,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56054,7 +56054,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56080,7 +56080,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56106,7 +56106,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56132,7 +56132,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56158,7 +56158,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56184,7 +56184,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56210,7 +56210,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56236,7 +56236,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56262,7 +56262,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56288,7 +56288,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56314,7 +56314,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56340,7 +56340,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56366,7 +56366,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56392,7 +56392,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56418,7 +56418,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56444,7 +56444,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56470,7 +56470,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56496,7 +56496,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56522,7 +56522,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56548,7 +56548,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56574,7 +56574,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56600,7 +56600,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56626,7 +56626,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56652,7 +56652,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56678,7 +56678,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56704,7 +56704,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56730,7 +56730,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56756,7 +56756,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56782,7 +56782,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56808,7 +56808,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56834,7 +56834,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56860,7 +56860,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56886,7 +56886,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56912,7 +56912,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56938,7 +56938,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56964,7 +56964,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -56990,7 +56990,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57016,7 +57016,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57042,7 +57042,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57068,7 +57068,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57094,7 +57094,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57120,7 +57120,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57146,7 +57146,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57172,7 +57172,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57198,7 +57198,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57224,7 +57224,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57250,7 +57250,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57276,7 +57276,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57302,7 +57302,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57328,7 +57328,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57354,7 +57354,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57380,7 +57380,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57406,7 +57406,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57432,7 +57432,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57458,7 +57458,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57484,7 +57484,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57510,7 +57510,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57536,7 +57536,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57562,7 +57562,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57588,7 +57588,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57614,7 +57614,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57640,7 +57640,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57666,7 +57666,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57692,7 +57692,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57718,7 +57718,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57744,7 +57744,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57770,7 +57770,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57796,7 +57796,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57822,7 +57822,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57848,7 +57848,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57874,7 +57874,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57900,7 +57900,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57926,7 +57926,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57952,7 +57952,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57978,7 +57978,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58004,7 +58004,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58030,7 +58030,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58056,7 +58056,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58082,7 +58082,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58108,7 +58108,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58134,7 +58134,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58160,7 +58160,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58186,7 +58186,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58212,7 +58212,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58238,7 +58238,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58264,7 +58264,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58290,7 +58290,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58316,7 +58316,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58342,7 +58342,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58368,7 +58368,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58394,7 +58394,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58420,7 +58420,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58446,7 +58446,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58472,7 +58472,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58498,7 +58498,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58524,7 +58524,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58550,7 +58550,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58576,7 +58576,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58602,7 +58602,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58628,7 +58628,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58654,7 +58654,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58680,7 +58680,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58706,7 +58706,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58732,7 +58732,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58758,7 +58758,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58784,7 +58784,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58810,7 +58810,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58836,7 +58836,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58862,7 +58862,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58888,7 +58888,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58914,7 +58914,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58940,7 +58940,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58966,7 +58966,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -58992,7 +58992,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59018,7 +59018,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59044,7 +59044,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59070,7 +59070,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59096,7 +59096,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59122,7 +59122,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59148,7 +59148,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59174,7 +59174,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59200,7 +59200,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59226,7 +59226,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59252,7 +59252,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59278,7 +59278,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59304,7 +59304,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59330,7 +59330,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59356,7 +59356,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59382,7 +59382,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59408,7 +59408,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59434,7 +59434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59460,7 +59460,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59486,7 +59486,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59512,7 +59512,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59538,7 +59538,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59564,7 +59564,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59590,7 +59590,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59616,7 +59616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59642,7 +59642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59668,7 +59668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59694,7 +59694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59720,7 +59720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59746,7 +59746,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59772,7 +59772,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59798,7 +59798,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59824,7 +59824,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59850,7 +59850,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59876,7 +59876,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59902,7 +59902,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59928,7 +59928,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59954,7 +59954,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59980,7 +59980,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60006,7 +60006,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60032,7 +60032,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60058,7 +60058,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60084,7 +60084,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60110,7 +60110,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60136,7 +60136,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60162,7 +60162,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60188,7 +60188,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60214,7 +60214,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60240,7 +60240,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60266,7 +60266,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60292,7 +60292,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60318,7 +60318,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60344,7 +60344,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60370,7 +60370,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60396,7 +60396,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60422,7 +60422,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60448,7 +60448,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60474,7 +60474,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60500,7 +60500,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60526,7 +60526,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60552,7 +60552,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60578,7 +60578,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60604,7 +60604,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60630,7 +60630,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60656,7 +60656,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60682,7 +60682,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60708,7 +60708,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60734,7 +60734,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60760,7 +60760,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60786,7 +60786,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60812,7 +60812,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60838,7 +60838,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60864,7 +60864,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60890,7 +60890,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60916,7 +60916,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60942,7 +60942,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60968,7 +60968,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -60994,7 +60994,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61020,7 +61020,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61046,7 +61046,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61072,7 +61072,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61098,7 +61098,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61124,7 +61124,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61150,7 +61150,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61176,7 +61176,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61202,7 +61202,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61228,7 +61228,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61254,7 +61254,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61280,7 +61280,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61306,7 +61306,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61332,7 +61332,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61358,7 +61358,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61384,7 +61384,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61410,7 +61410,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61436,7 +61436,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61462,7 +61462,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61488,7 +61488,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61514,7 +61514,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61540,7 +61540,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61566,7 +61566,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61592,7 +61592,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61618,7 +61618,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61644,7 +61644,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61670,7 +61670,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61696,7 +61696,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61722,7 +61722,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61748,7 +61748,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61774,7 +61774,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61800,7 +61800,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61826,7 +61826,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61852,7 +61852,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61878,7 +61878,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61904,7 +61904,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61930,7 +61930,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61956,7 +61956,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -61982,7 +61982,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62008,7 +62008,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62034,7 +62034,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62060,7 +62060,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62086,7 +62086,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62112,7 +62112,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62138,7 +62138,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62164,7 +62164,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62190,7 +62190,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62216,7 +62216,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62242,7 +62242,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62268,7 +62268,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62294,7 +62294,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62320,7 +62320,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62346,7 +62346,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62372,7 +62372,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62398,7 +62398,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62424,7 +62424,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62450,7 +62450,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62476,7 +62476,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62502,7 +62502,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62528,7 +62528,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62554,7 +62554,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62580,7 +62580,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62606,7 +62606,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62632,7 +62632,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62658,7 +62658,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62684,7 +62684,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62710,7 +62710,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62736,7 +62736,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62762,7 +62762,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62788,7 +62788,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62814,7 +62814,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62840,7 +62840,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62866,7 +62866,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62892,7 +62892,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62918,7 +62918,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62944,7 +62944,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62970,7 +62970,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -62996,7 +62996,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63022,7 +63022,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63048,7 +63048,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63334,7 +63334,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66384,7 +66384,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6495023148</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>6352</v>
@@ -66405,6 +66405,32 @@
         <v>434</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.5909953704</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>240</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>438</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="439">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194986343384</t>
+    <t xml:space="preserve">13.2194967269897</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149920463562</t>
+    <t xml:space="preserve">13.149923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577032089233</t>
+    <t xml:space="preserve">12.857702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.871618270874</t>
   </si>
   <si>
     <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8020401000977</t>
+    <t xml:space="preserve">12.802041053772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167770385742</t>
+    <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758546829224</t>
+    <t xml:space="preserve">12.1758527755737</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809139251709</t>
+    <t xml:space="preserve">11.1809110641479</t>
   </si>
   <si>
     <t xml:space="preserve">10.5755987167358</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280223846436</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885648727417</t>
+    <t xml:space="preserve">10.0885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112087249756</t>
+    <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060224533081</t>
@@ -95,67 +95,67 @@
     <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147512435913</t>
+    <t xml:space="preserve">10.714750289917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773714065552</t>
+    <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1322088241577</t>
+    <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331596374512</t>
+    <t xml:space="preserve">11.6331586837769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905897140503</t>
+    <t xml:space="preserve">11.8905916213989</t>
   </si>
   <si>
     <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480236053467</t>
+    <t xml:space="preserve">12.148024559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193706512451</t>
+    <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628875732422</t>
+    <t xml:space="preserve">12.6628885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933103561401</t>
+    <t xml:space="preserve">12.5933132171631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150072097778</t>
+    <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114646911621</t>
+    <t xml:space="preserve">11.9114627838135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583961486816</t>
+    <t xml:space="preserve">11.758394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227851867676</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236061096191</t>
+    <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.9841327667236</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163705825806</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045276641846</t>
+    <t xml:space="preserve">11.9045267105103</t>
   </si>
   <si>
     <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065021514893</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893991470337</t>
+    <t xml:space="preserve">11.289400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426864624023</t>
+    <t xml:space="preserve">11.542688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979520797729</t>
+    <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512403488159</t>
+    <t xml:space="preserve">11.6512393951416</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321590423584</t>
+    <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
     <t xml:space="preserve">12.0130786895752</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578140258789</t>
+    <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939973831177</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
     <t xml:space="preserve">12.3025522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275545120239</t>
+    <t xml:space="preserve">12.0275535583496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472856521606</t>
+    <t xml:space="preserve">12.447286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196561813354</t>
+    <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643905639648</t>
+    <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.946626663208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729444503784</t>
+    <t xml:space="preserve">12.7729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">12.9755725860596</t>
@@ -236,97 +236,97 @@
     <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091268539429</t>
+    <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433347702026</t>
+    <t xml:space="preserve">13.2433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157005310059</t>
+    <t xml:space="preserve">13.3157033920288</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604387283325</t>
+    <t xml:space="preserve">13.4604396820068</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025440216064</t>
+    <t xml:space="preserve">13.4025449752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.453200340271</t>
   </si>
   <si>
     <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328044891357</t>
+    <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689897537231</t>
+    <t xml:space="preserve">13.5689907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554518699646</t>
+    <t xml:space="preserve">13.5545177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966230392456</t>
+    <t xml:space="preserve">13.4966220855713</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459657669067</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387292861938</t>
+    <t xml:space="preserve">13.4387273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071504592896</t>
+    <t xml:space="preserve">13.2071514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038604736328</t>
+    <t xml:space="preserve">13.5038595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288608551025</t>
+    <t xml:space="preserve">13.2288618087769</t>
   </si>
   <si>
     <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985975265503</t>
+    <t xml:space="preserve">13.0986003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104404449463</t>
+    <t xml:space="preserve">12.9104413986206</t>
   </si>
   <si>
     <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134783744812</t>
+    <t xml:space="preserve">13.1347846984863</t>
   </si>
   <si>
     <t xml:space="preserve">12.8453092575073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275453567505</t>
+    <t xml:space="preserve">13.1275472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439975738525</t>
+    <t xml:space="preserve">12.7439966201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189933776855</t>
+    <t xml:space="preserve">13.0189962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571531295776</t>
+    <t xml:space="preserve">12.657154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446556091309</t>
+    <t xml:space="preserve">12.2446584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012357711792</t>
+    <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334735870361</t>
+    <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
     <t xml:space="preserve">12.1143960952759</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">12.0709743499756</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492630004883</t>
+    <t xml:space="preserve">12.0492639541626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466339111328</t>
+    <t xml:space="preserve">11.8466320037842</t>
   </si>
   <si>
     <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913682937622</t>
+    <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986066818237</t>
+    <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479475021362</t>
+    <t xml:space="preserve">11.9479465484619</t>
   </si>
   <si>
     <t xml:space="preserve">12.1722888946533</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768934249878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597894668579</t>
   </si>
   <si>
     <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301826477051</t>
+    <t xml:space="preserve">12.2301816940308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229461669922</t>
+    <t xml:space="preserve">12.2229471206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554145812988</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.3054828643799</t>
@@ -389,55 +389,55 @@
     <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428657531738</t>
+    <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129854202271</t>
+    <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180316925049</t>
+    <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307161331177</t>
+    <t xml:space="preserve">12.8307151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158428192139</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
     <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732799530029</t>
+    <t xml:space="preserve">12.9732789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881532669067</t>
+    <t xml:space="preserve">12.6881513595581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657783508301</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308507919312</t>
+    <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682327270508</t>
+    <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
     <t xml:space="preserve">12.8457250595093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083383560181</t>
+    <t xml:space="preserve">13.1083393096924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093334197998</t>
+    <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559503555298</t>
@@ -455,46 +455,46 @@
     <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358980178833</t>
+    <t xml:space="preserve">13.2358961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383543014526</t>
+    <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058849334717</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934659957886</t>
+    <t xml:space="preserve">13.3934679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685020446777</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184328079224</t>
+    <t xml:space="preserve">13.318434715271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434015274048</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060176849365</t>
+    <t xml:space="preserve">13.5060205459595</t>
   </si>
   <si>
     <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185693740845</t>
+    <t xml:space="preserve">13.6185665130615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061504364014</t>
+    <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810499191284</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687685012817</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">13.4159774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562187194824</t>
+    <t xml:space="preserve">13.9562168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.03125</t>
+    <t xml:space="preserve">14.0312519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609956741333</t>
+    <t xml:space="preserve">13.4609966278076</t>
   </si>
   <si>
     <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986478805542</t>
+    <t xml:space="preserve">13.7986469268799</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315202713013</t>
+    <t xml:space="preserve">14.631519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013734817505</t>
+    <t xml:space="preserve">14.3013696670532</t>
   </si>
   <si>
     <t xml:space="preserve">14.6165132522583</t>
@@ -539,91 +539,91 @@
     <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991855621338</t>
+    <t xml:space="preserve">14.9991836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.006688117981</t>
+    <t xml:space="preserve">15.0066862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991681098938</t>
+    <t xml:space="preserve">14.9916791915894</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766750335693</t>
+    <t xml:space="preserve">14.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691724777222</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465272903442</t>
+    <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941354751587</t>
+    <t xml:space="preserve">14.8941345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390199661255</t>
   </si>
   <si>
     <t xml:space="preserve">15.1567535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606951713562</t>
+    <t xml:space="preserve">15.6069536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568881988525</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.757022857666</t>
+    <t xml:space="preserve">15.7570209503174</t>
   </si>
   <si>
     <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574211120605</t>
+    <t xml:space="preserve">16.6574230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575538635254</t>
+    <t xml:space="preserve">16.9575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">16.5073566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074932098389</t>
+    <t xml:space="preserve">16.8074913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072219848633</t>
+    <t xml:space="preserve">16.2072200775146</t>
   </si>
   <si>
     <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615779876709</t>
+    <t xml:space="preserve">16.3615741729736</t>
   </si>
   <si>
     <t xml:space="preserve">16.052864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702880859375</t>
+    <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723834991455</t>
+    <t xml:space="preserve">14.9723844528198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898027420044</t>
+    <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354476928711</t>
+    <t xml:space="preserve">15.435450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441568374634</t>
+    <t xml:space="preserve">15.7441577911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.5159301757812</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">15.898512840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267423629761</t>
+    <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495624542236</t>
+    <t xml:space="preserve">15.0495643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636753082275</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810935974121</t>
+    <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549690246582</t>
+    <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">14.4321451187134</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">13.8919057846069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522134780884</t>
+    <t xml:space="preserve">14.2522144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319381713867</t>
+    <t xml:space="preserve">13.9319372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.771800994873</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.45152759552</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">14.1721448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.611665725708</t>
+    <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315942764282</t>
+    <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120048522949</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
     <t xml:space="preserve">13.8518705368042</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.291389465332</t>
+    <t xml:space="preserve">13.2913904190063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123516082764</t>
+    <t xml:space="preserve">14.4123525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.092077255249</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714599609375</t>
   </si>
   <si>
     <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511837005615</t>
+    <t xml:space="preserve">13.0511827468872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
     <t xml:space="preserve">12.810977935791</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302234649658</t>
+    <t xml:space="preserve">11.9302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.690016746521</t>
+    <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707721710205</t>
+    <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903596878052</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295385360718</t>
+    <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896747589111</t>
+    <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498109817505</t>
+    <t xml:space="preserve">11.4498100280762</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096061706543</t>
+    <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
     <t xml:space="preserve">10.9694004058838</t>
@@ -773,34 +773,34 @@
     <t xml:space="preserve">11.0494680404663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491250991821</t>
+    <t xml:space="preserve">10.6491260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288507461548</t>
+    <t xml:space="preserve">10.3288516998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889888763428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089193344116</t>
+    <t xml:space="preserve">10.4089183807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687126159668</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700853347778</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102910995483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.849328994751</t>
+    <t xml:space="preserve">12.8493280410767</t>
   </si>
   <si>
     <t xml:space="preserve">12.5990171432495</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.5155782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9327640533447</t>
+    <t xml:space="preserve">12.932765007019</t>
   </si>
   <si>
     <t xml:space="preserve">13.1830768585205</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346342086792</t>
+    <t xml:space="preserve">14.4346351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021308898926</t>
+    <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352579116821</t>
+    <t xml:space="preserve">14.9352569580078</t>
   </si>
   <si>
     <t xml:space="preserve">15.0186967849731</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0174493789673</t>
+    <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837015151978</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">13.7671375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002626419067</t>
+    <t xml:space="preserve">13.6002616882324</t>
   </si>
   <si>
     <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741500854492</t>
+    <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255243301392</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417335510254</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.993106842041</t>
+    <t xml:space="preserve">13.9931077957153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093160629272</t>
+    <t xml:space="preserve">13.9093151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4120616912842</t>
+    <t xml:space="preserve">14.4120607376099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796422958374</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
     <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.657940864563</t>
+    <t xml:space="preserve">13.6579418182373</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903602600098</t>
+    <t xml:space="preserve">13.4903593063354</t>
   </si>
   <si>
     <t xml:space="preserve">14.3282709121704</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958515167236</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
     <t xml:space="preserve">14.9985980987549</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337621688843</t>
+    <t xml:space="preserve">15.33376121521</t>
   </si>
   <si>
     <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499723434448</t>
+    <t xml:space="preserve">15.2499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">15.0823888778687</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">15.5851345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689291000366</t>
+    <t xml:space="preserve">15.6689281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9202995300293</t>
+    <t xml:space="preserve">15.9202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0040912628174</t>
+    <t xml:space="preserve">16.0040893554688</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441286087036</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664588928223</t>
+    <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6276264190674</t>
+    <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7146835327148</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.585241317749</t>
+    <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299076080322</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">18.4557971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7593517303467</t>
+    <t xml:space="preserve">17.759349822998</t>
   </si>
   <si>
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111289978027</t>
@@ -1107,9 +1107,6 @@
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -44744,7 +44741,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44770,7 +44767,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44822,7 +44819,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44848,7 +44845,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44874,7 +44871,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44900,7 +44897,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44926,7 +44923,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44952,7 +44949,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44978,7 +44975,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45004,7 +45001,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45030,7 +45027,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45056,7 +45053,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45082,7 +45079,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45108,7 +45105,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45134,7 +45131,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45160,7 +45157,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45186,7 +45183,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45212,7 +45209,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45238,7 +45235,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45264,7 +45261,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45290,7 +45287,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45316,7 +45313,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45342,7 +45339,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45368,7 +45365,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45420,7 +45417,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45446,7 +45443,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45706,7 +45703,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45940,7 +45937,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45966,7 +45963,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45992,7 +45989,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46018,7 +46015,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46044,7 +46041,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46070,7 +46067,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46096,7 +46093,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46122,7 +46119,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46148,7 +46145,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46174,7 +46171,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46200,7 +46197,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46226,7 +46223,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46252,7 +46249,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46330,7 +46327,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46356,7 +46353,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46538,7 +46535,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46564,7 +46561,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46590,7 +46587,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46616,7 +46613,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46642,7 +46639,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46668,7 +46665,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46694,7 +46691,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46720,7 +46717,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46746,7 +46743,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46772,7 +46769,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46798,7 +46795,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46824,7 +46821,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46850,7 +46847,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46876,7 +46873,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46902,7 +46899,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46928,7 +46925,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46954,7 +46951,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46980,7 +46977,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47006,7 +47003,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47032,7 +47029,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47058,7 +47055,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47110,7 +47107,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47136,7 +47133,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47162,7 +47159,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47188,7 +47185,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47214,7 +47211,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47240,7 +47237,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47266,7 +47263,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47292,7 +47289,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47318,7 +47315,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47344,7 +47341,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47370,7 +47367,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47396,7 +47393,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47500,7 +47497,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47526,7 +47523,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47552,7 +47549,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47578,7 +47575,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47604,7 +47601,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47630,7 +47627,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47656,7 +47653,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47682,7 +47679,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47708,7 +47705,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47760,7 +47757,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47786,7 +47783,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47812,7 +47809,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47838,7 +47835,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47864,7 +47861,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47890,7 +47887,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47916,7 +47913,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47994,7 +47991,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48020,7 +48017,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48046,7 +48043,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48072,7 +48069,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48098,7 +48095,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48124,7 +48121,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48150,7 +48147,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48176,7 +48173,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48228,7 +48225,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48254,7 +48251,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48280,7 +48277,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48332,7 +48329,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48592,7 +48589,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48618,7 +48615,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48644,7 +48641,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48670,7 +48667,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48696,7 +48693,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48722,7 +48719,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48748,7 +48745,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48774,7 +48771,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48800,7 +48797,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48826,7 +48823,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48852,7 +48849,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48878,7 +48875,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48904,7 +48901,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48930,7 +48927,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48956,7 +48953,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48982,7 +48979,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49008,7 +49005,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49034,7 +49031,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49060,7 +49057,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49086,7 +49083,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49112,7 +49109,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49138,7 +49135,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49164,7 +49161,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49190,7 +49187,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49216,7 +49213,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49242,7 +49239,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49268,7 +49265,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49294,7 +49291,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49320,7 +49317,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49346,7 +49343,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49372,7 +49369,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49398,7 +49395,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49424,7 +49421,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49450,7 +49447,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49476,7 +49473,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49502,7 +49499,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49528,7 +49525,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49554,7 +49551,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49580,7 +49577,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49606,7 +49603,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49632,7 +49629,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49658,7 +49655,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49684,7 +49681,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49710,7 +49707,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49736,7 +49733,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49762,7 +49759,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49788,7 +49785,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49814,7 +49811,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49840,7 +49837,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49866,7 +49863,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49892,7 +49889,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49918,7 +49915,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49944,7 +49941,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49970,7 +49967,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49996,7 +49993,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50022,7 +50019,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50048,7 +50045,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50074,7 +50071,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50100,7 +50097,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50126,7 +50123,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50152,7 +50149,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50178,7 +50175,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50204,7 +50201,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50230,7 +50227,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50256,7 +50253,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50282,7 +50279,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50308,7 +50305,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50334,7 +50331,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50360,7 +50357,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50386,7 +50383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50412,7 +50409,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50438,7 +50435,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50464,7 +50461,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50490,7 +50487,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50516,7 +50513,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50542,7 +50539,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50568,7 +50565,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50594,7 +50591,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50620,7 +50617,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50646,7 +50643,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50672,7 +50669,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50698,7 +50695,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50724,7 +50721,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50750,7 +50747,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50776,7 +50773,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50802,7 +50799,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50828,7 +50825,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50854,7 +50851,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50880,7 +50877,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50906,7 +50903,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50932,7 +50929,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50958,7 +50955,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50984,7 +50981,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51010,7 +51007,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51036,7 +51033,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51062,7 +51059,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51088,7 +51085,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51114,7 +51111,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51140,7 +51137,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51166,7 +51163,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51192,7 +51189,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51218,7 +51215,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51244,7 +51241,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51270,7 +51267,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51296,7 +51293,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51322,7 +51319,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51348,7 +51345,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51374,7 +51371,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51400,7 +51397,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51426,7 +51423,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51452,7 +51449,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51478,7 +51475,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51504,7 +51501,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51530,7 +51527,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51556,7 +51553,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51582,7 +51579,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51608,7 +51605,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51634,7 +51631,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51660,7 +51657,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51686,7 +51683,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51712,7 +51709,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51738,7 +51735,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51764,7 +51761,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51790,7 +51787,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51816,7 +51813,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51842,7 +51839,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51868,7 +51865,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51894,7 +51891,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51920,7 +51917,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51946,7 +51943,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51972,7 +51969,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -51998,7 +51995,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52024,7 +52021,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52050,7 +52047,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52076,7 +52073,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52102,7 +52099,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52128,7 +52125,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52154,7 +52151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52180,7 +52177,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52206,7 +52203,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52232,7 +52229,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52258,7 +52255,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52284,7 +52281,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52310,7 +52307,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52336,7 +52333,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52362,7 +52359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52388,7 +52385,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52414,7 +52411,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52440,7 +52437,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52466,7 +52463,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52492,7 +52489,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52518,7 +52515,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52544,7 +52541,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52570,7 +52567,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52596,7 +52593,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52622,7 +52619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52648,7 +52645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52674,7 +52671,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52700,7 +52697,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52726,7 +52723,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52752,7 +52749,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52778,7 +52775,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52804,7 +52801,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52830,7 +52827,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52856,7 +52853,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52882,7 +52879,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52908,7 +52905,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52934,7 +52931,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52960,7 +52957,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -52986,7 +52983,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53012,7 +53009,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53038,7 +53035,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53064,7 +53061,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53090,7 +53087,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53116,7 +53113,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53142,7 +53139,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53168,7 +53165,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53194,7 +53191,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53220,7 +53217,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53246,7 +53243,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53272,7 +53269,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53298,7 +53295,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53324,7 +53321,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53350,7 +53347,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53376,7 +53373,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53402,7 +53399,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53428,7 +53425,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53454,7 +53451,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53480,7 +53477,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53506,7 +53503,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53532,7 +53529,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53558,7 +53555,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53584,7 +53581,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53610,7 +53607,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53636,7 +53633,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53662,7 +53659,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53688,7 +53685,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53714,7 +53711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53740,7 +53737,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53766,7 +53763,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53792,7 +53789,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53818,7 +53815,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53844,7 +53841,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53870,7 +53867,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53896,7 +53893,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53922,7 +53919,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53948,7 +53945,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53974,7 +53971,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54000,7 +53997,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54026,7 +54023,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54052,7 +54049,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54078,7 +54075,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54104,7 +54101,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54130,7 +54127,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54156,7 +54153,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54182,7 +54179,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54208,7 +54205,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54234,7 +54231,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54260,7 +54257,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54286,7 +54283,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54312,7 +54309,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54338,7 +54335,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54364,7 +54361,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54390,7 +54387,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54416,7 +54413,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54442,7 +54439,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54468,7 +54465,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54494,7 +54491,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54520,7 +54517,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54546,7 +54543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54572,7 +54569,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54598,7 +54595,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54624,7 +54621,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54650,7 +54647,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54676,7 +54673,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54702,7 +54699,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54728,7 +54725,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54754,7 +54751,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54780,7 +54777,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54806,7 +54803,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54832,7 +54829,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54858,7 +54855,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54884,7 +54881,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54910,7 +54907,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54936,7 +54933,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54962,7 +54959,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -54988,7 +54985,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55014,7 +55011,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55040,7 +55037,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55066,7 +55063,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55092,7 +55089,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55118,7 +55115,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55144,7 +55141,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55170,7 +55167,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55196,7 +55193,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55222,7 +55219,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55248,7 +55245,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55274,7 +55271,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55300,7 +55297,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55326,7 +55323,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55352,7 +55349,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55378,7 +55375,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55404,7 +55401,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55430,7 +55427,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55456,7 +55453,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55482,7 +55479,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55508,7 +55505,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55534,7 +55531,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55560,7 +55557,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55586,7 +55583,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55612,7 +55609,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55638,7 +55635,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55664,7 +55661,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55690,7 +55687,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55716,7 +55713,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55742,7 +55739,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55768,7 +55765,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55794,7 +55791,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55820,7 +55817,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55846,7 +55843,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55872,7 +55869,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55898,7 +55895,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55924,7 +55921,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55950,7 +55947,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55976,7 +55973,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56002,7 +55999,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56028,7 +56025,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56054,7 +56051,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56080,7 +56077,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56106,7 +56103,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56132,7 +56129,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56158,7 +56155,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56184,7 +56181,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56210,7 +56207,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56236,7 +56233,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56262,7 +56259,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56288,7 +56285,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56314,7 +56311,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56340,7 +56337,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56366,7 +56363,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56392,7 +56389,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56418,7 +56415,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56444,7 +56441,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56470,7 +56467,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56496,7 +56493,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56522,7 +56519,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56548,7 +56545,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56574,7 +56571,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56600,7 +56597,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56626,7 +56623,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56652,7 +56649,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56678,7 +56675,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56704,7 +56701,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56730,7 +56727,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56756,7 +56753,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56782,7 +56779,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56808,7 +56805,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56834,7 +56831,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56860,7 +56857,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56886,7 +56883,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56912,7 +56909,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56938,7 +56935,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56964,7 +56961,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -56990,7 +56987,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57016,7 +57013,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57042,7 +57039,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57068,7 +57065,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57094,7 +57091,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57120,7 +57117,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57146,7 +57143,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57172,7 +57169,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57198,7 +57195,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57224,7 +57221,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57250,7 +57247,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57276,7 +57273,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57302,7 +57299,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57328,7 +57325,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57354,7 +57351,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57380,7 +57377,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57406,7 +57403,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57432,7 +57429,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57458,7 +57455,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57484,7 +57481,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57510,7 +57507,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57536,7 +57533,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57562,7 +57559,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57588,7 +57585,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57614,7 +57611,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57640,7 +57637,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57666,7 +57663,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57692,7 +57689,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57718,7 +57715,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57744,7 +57741,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57770,7 +57767,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57796,7 +57793,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57822,7 +57819,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57848,7 +57845,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57874,7 +57871,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57900,7 +57897,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57926,7 +57923,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57952,7 +57949,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57978,7 +57975,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58004,7 +58001,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58030,7 +58027,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58056,7 +58053,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58082,7 +58079,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58108,7 +58105,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58134,7 +58131,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58160,7 +58157,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58186,7 +58183,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58212,7 +58209,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58238,7 +58235,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58264,7 +58261,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58290,7 +58287,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58316,7 +58313,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58342,7 +58339,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58368,7 +58365,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58394,7 +58391,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58420,7 +58417,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58446,7 +58443,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58472,7 +58469,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58498,7 +58495,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58524,7 +58521,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58550,7 +58547,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58576,7 +58573,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58602,7 +58599,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58628,7 +58625,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58654,7 +58651,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58680,7 +58677,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58706,7 +58703,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58732,7 +58729,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58758,7 +58755,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58784,7 +58781,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58810,7 +58807,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58836,7 +58833,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58862,7 +58859,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58888,7 +58885,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58914,7 +58911,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58940,7 +58937,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58966,7 +58963,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -58992,7 +58989,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59018,7 +59015,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59044,7 +59041,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59070,7 +59067,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59096,7 +59093,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59122,7 +59119,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59148,7 +59145,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59174,7 +59171,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59200,7 +59197,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59226,7 +59223,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59252,7 +59249,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59278,7 +59275,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59304,7 +59301,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59330,7 +59327,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59356,7 +59353,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59382,7 +59379,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59408,7 +59405,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59434,7 +59431,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59460,7 +59457,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59486,7 +59483,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59512,7 +59509,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59538,7 +59535,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59564,7 +59561,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59590,7 +59587,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59616,7 +59613,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59642,7 +59639,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59668,7 +59665,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59694,7 +59691,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59720,7 +59717,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59746,7 +59743,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59772,7 +59769,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59798,7 +59795,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59824,7 +59821,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59850,7 +59847,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59876,7 +59873,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59902,7 +59899,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59928,7 +59925,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59954,7 +59951,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59980,7 +59977,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60006,7 +60003,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60032,7 +60029,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60058,7 +60055,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60084,7 +60081,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60110,7 +60107,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60136,7 +60133,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60162,7 +60159,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60188,7 +60185,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60214,7 +60211,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60240,7 +60237,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60266,7 +60263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60292,7 +60289,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60318,7 +60315,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60344,7 +60341,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60370,7 +60367,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60396,7 +60393,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60422,7 +60419,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60448,7 +60445,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60474,7 +60471,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60500,7 +60497,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60526,7 +60523,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60552,7 +60549,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60578,7 +60575,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60604,7 +60601,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60630,7 +60627,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60656,7 +60653,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60682,7 +60679,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60708,7 +60705,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60734,7 +60731,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60760,7 +60757,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60786,7 +60783,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60812,7 +60809,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60838,7 +60835,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60864,7 +60861,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60890,7 +60887,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60916,7 +60913,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60942,7 +60939,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60968,7 +60965,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -60994,7 +60991,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61020,7 +61017,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61046,7 +61043,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61072,7 +61069,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61098,7 +61095,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61124,7 +61121,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61150,7 +61147,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61176,7 +61173,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61202,7 +61199,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61228,7 +61225,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61254,7 +61251,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61280,7 +61277,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61306,7 +61303,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61332,7 +61329,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61358,7 +61355,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61384,7 +61381,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61410,7 +61407,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61436,7 +61433,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61462,7 +61459,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61488,7 +61485,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61514,7 +61511,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61540,7 +61537,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61566,7 +61563,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61592,7 +61589,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61618,7 +61615,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61644,7 +61641,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61670,7 +61667,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61696,7 +61693,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61722,7 +61719,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61748,7 +61745,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61774,7 +61771,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61800,7 +61797,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61826,7 +61823,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61852,7 +61849,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61878,7 +61875,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61904,7 +61901,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61930,7 +61927,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61956,7 +61953,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -61982,7 +61979,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62008,7 +62005,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62034,7 +62031,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62060,7 +62057,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62086,7 +62083,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62112,7 +62109,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62138,7 +62135,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62164,7 +62161,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62190,7 +62187,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62216,7 +62213,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62242,7 +62239,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62268,7 +62265,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62294,7 +62291,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62320,7 +62317,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62346,7 +62343,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62372,7 +62369,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62398,7 +62395,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62424,7 +62421,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62450,7 +62447,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62476,7 +62473,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62502,7 +62499,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62528,7 +62525,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62554,7 +62551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62580,7 +62577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62606,7 +62603,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62632,7 +62629,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62658,7 +62655,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62684,7 +62681,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62710,7 +62707,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62736,7 +62733,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62762,7 +62759,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62788,7 +62785,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62814,7 +62811,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62840,7 +62837,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62866,7 +62863,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62892,7 +62889,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62918,7 +62915,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62944,7 +62941,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62970,7 +62967,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -62996,7 +62993,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63022,7 +63019,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63048,7 +63045,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63074,7 +63071,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63100,7 +63097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63126,7 +63123,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63152,7 +63149,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63178,7 +63175,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63204,7 +63201,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63230,7 +63227,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63256,7 +63253,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63282,7 +63279,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63308,7 +63305,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63334,7 +63331,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63360,7 +63357,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63386,7 +63383,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63412,7 +63409,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63438,7 +63435,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63464,7 +63461,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63490,7 +63487,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63516,7 +63513,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63542,7 +63539,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63568,7 +63565,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63594,7 +63591,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63620,7 +63617,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63646,7 +63643,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63672,7 +63669,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63698,7 +63695,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63724,7 +63721,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63750,7 +63747,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63776,7 +63773,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63802,7 +63799,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63828,7 +63825,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63854,7 +63851,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63880,7 +63877,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63906,7 +63903,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63932,7 +63929,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63958,7 +63955,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63984,7 +63981,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64010,7 +64007,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64036,7 +64033,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64062,7 +64059,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64088,7 +64085,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64114,7 +64111,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64140,7 +64137,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64166,7 +64163,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64192,7 +64189,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64218,7 +64215,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64244,7 +64241,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64270,7 +64267,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64296,7 +64293,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64322,7 +64319,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64348,7 +64345,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64374,7 +64371,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64400,7 +64397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64426,7 +64423,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64452,7 +64449,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64478,7 +64475,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64504,7 +64501,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64530,7 +64527,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64556,7 +64553,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64582,7 +64579,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64608,7 +64605,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64634,7 +64631,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64660,7 +64657,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64686,7 +64683,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64712,7 +64709,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64738,7 +64735,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64764,7 +64761,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64790,7 +64787,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64816,7 +64813,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64842,7 +64839,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64868,7 +64865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64894,7 +64891,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64920,7 +64917,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64946,7 +64943,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64972,7 +64969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -64998,7 +64995,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65024,7 +65021,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65050,7 +65047,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65076,7 +65073,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65102,7 +65099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65128,7 +65125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65154,7 +65151,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65180,7 +65177,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65206,7 +65203,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65232,7 +65229,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65258,7 +65255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65284,7 +65281,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65310,7 +65307,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65336,7 +65333,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65362,7 +65359,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65388,7 +65385,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65414,7 +65411,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65440,7 +65437,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65466,7 +65463,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65492,7 +65489,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65518,7 +65515,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65544,7 +65541,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65570,7 +65567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65596,7 +65593,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65622,7 +65619,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65648,7 +65645,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65674,7 +65671,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65700,7 +65697,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65726,7 +65723,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65752,7 +65749,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65778,7 +65775,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65804,7 +65801,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65830,7 +65827,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65856,7 +65853,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65882,7 +65879,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65908,7 +65905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65934,7 +65931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65960,7 +65957,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65986,7 +65983,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66012,7 +66009,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66038,7 +66035,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66064,7 +66061,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66090,7 +66087,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66116,7 +66113,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66142,7 +66139,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66168,7 +66165,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66194,7 +66191,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66220,7 +66217,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66246,7 +66243,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66272,7 +66269,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66298,7 +66295,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66324,7 +66321,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66350,7 +66347,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66376,7 +66373,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66402,7 +66399,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66410,7 +66407,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.5909953704</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>240</v>
@@ -66428,9 +66425,35 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
+        <v>437</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6417708333</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>640</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="G2492" t="s">
         <v>438</v>
       </c>
-      <c r="H2491" t="s">
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194976806641</t>
+    <t xml:space="preserve">13.2194995880127</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499223709106</t>
+    <t xml:space="preserve">13.1499214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577003479004</t>
+    <t xml:space="preserve">12.857702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237369537354</t>
+    <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.802041053772</t>
+    <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
     <t xml:space="preserve">12.5167779922485</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">12.1758527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279705047607</t>
+    <t xml:space="preserve">11.8279733657837</t>
   </si>
   <si>
     <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755987167358</t>
+    <t xml:space="preserve">10.5755977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885629653931</t>
+    <t xml:space="preserve">10.0885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112096786499</t>
+    <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060224533081</t>
@@ -95,49 +95,49 @@
     <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451740264893</t>
+    <t xml:space="preserve">10.6451749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147512435913</t>
+    <t xml:space="preserve">10.714750289917</t>
   </si>
   <si>
     <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773714065552</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322078704834</t>
   </si>
   <si>
     <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549797058105</t>
+    <t xml:space="preserve">12.1549816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148021697998</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193696975708</t>
+    <t xml:space="preserve">12.4193706512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628875732422</t>
+    <t xml:space="preserve">12.6628866195679</t>
   </si>
   <si>
     <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933103561401</t>
+    <t xml:space="preserve">12.5933122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150072097778</t>
+    <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0506181716919</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">11.9114637374878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583951950073</t>
+    <t xml:space="preserve">11.7583932876587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227880477905</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841327667236</t>
+    <t xml:space="preserve">11.984130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163715362549</t>
+    <t xml:space="preserve">11.7163696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407110214233</t>
+    <t xml:space="preserve">11.9407091140747</t>
   </si>
   <si>
     <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670278549194</t>
+    <t xml:space="preserve">11.7670269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065040588379</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788726806641</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426874160767</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979511260986</t>
@@ -191,64 +191,64 @@
     <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683452606201</t>
+    <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.8321590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.0854482650757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578159332275</t>
+    <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.193998336792</t>
+    <t xml:space="preserve">12.1939992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025503158569</t>
+    <t xml:space="preserve">12.3025522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275535583496</t>
+    <t xml:space="preserve">12.0275526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.2953128814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196552276611</t>
+    <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466257095337</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729444503784</t>
+    <t xml:space="preserve">12.7729434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755725860596</t>
+    <t xml:space="preserve">12.9755716323853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538602828979</t>
+    <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091278076172</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433338165283</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
     <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604396820068</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880681991577</t>
@@ -263,67 +263,67 @@
     <t xml:space="preserve">13.4242534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328044891357</t>
+    <t xml:space="preserve">13.5328063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689897537231</t>
+    <t xml:space="preserve">13.5689916610718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554518699646</t>
+    <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
     <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518867492676</t>
+    <t xml:space="preserve">13.3518877029419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459648132324</t>
+    <t xml:space="preserve">13.4459638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387273788452</t>
+    <t xml:space="preserve">13.4387292861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071504592896</t>
+    <t xml:space="preserve">13.2071485519409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038585662842</t>
+    <t xml:space="preserve">13.5038595199585</t>
   </si>
   <si>
     <t xml:space="preserve">13.2288608551025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814945220947</t>
+    <t xml:space="preserve">12.8814926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985975265503</t>
+    <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104413986206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262327194214</t>
+    <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347808837891</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
     <t xml:space="preserve">12.8453092575073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275453567505</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
     <t xml:space="preserve">12.7439966201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189943313599</t>
+    <t xml:space="preserve">13.0189924240112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446584701538</t>
+    <t xml:space="preserve">12.2446575164795</t>
   </si>
   <si>
     <t xml:space="preserve">12.2012338638306</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709743499756</t>
+    <t xml:space="preserve">12.0709733963013</t>
   </si>
   <si>
     <t xml:space="preserve">12.0492639541626</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782098770142</t>
+    <t xml:space="preserve">12.0782117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913702011108</t>
+    <t xml:space="preserve">11.9913682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986066818237</t>
+    <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479455947876</t>
+    <t xml:space="preserve">11.9479465484619</t>
   </si>
   <si>
     <t xml:space="preserve">12.172287940979</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696578979492</t>
+    <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
     <t xml:space="preserve">11.9768943786621</t>
@@ -371,28 +371,28 @@
     <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.150577545166</t>
+    <t xml:space="preserve">12.1505784988403</t>
   </si>
   <si>
     <t xml:space="preserve">12.2301816940308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229461669922</t>
+    <t xml:space="preserve">12.2229480743408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554155349731</t>
+    <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805170059204</t>
+    <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880176544189</t>
+    <t xml:space="preserve">12.3880186080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.0428647994995</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180307388306</t>
+    <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756044387817</t>
+    <t xml:space="preserve">12.5756015777588</t>
   </si>
   <si>
     <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158437728882</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.980785369873</t>
+    <t xml:space="preserve">12.9807834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732799530029</t>
+    <t xml:space="preserve">12.9732789993286</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881532669067</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">12.9657793045044</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432649612427</t>
+    <t xml:space="preserve">12.9432678222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308479309082</t>
+    <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845724105835</t>
+    <t xml:space="preserve">12.8457231521606</t>
   </si>
   <si>
     <t xml:space="preserve">13.1083402633667</t>
@@ -443,43 +443,43 @@
     <t xml:space="preserve">13.0933351516724</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559513092041</t>
+    <t xml:space="preserve">13.3559494018555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2809171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.4309844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735483169556</t>
+    <t xml:space="preserve">13.5735492706299</t>
   </si>
   <si>
     <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358980178833</t>
+    <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383543014526</t>
+    <t xml:space="preserve">13.138352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234800338745</t>
+    <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205883026123</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934659957886</t>
+    <t xml:space="preserve">13.3934679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4684991836548</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
     <t xml:space="preserve">13.318431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434034347534</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683673858643</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">13.5060186386108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185665130615</t>
+    <t xml:space="preserve">13.6185693740845</t>
   </si>
   <si>
     <t xml:space="preserve">13.80615234375</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687675476074</t>
+    <t xml:space="preserve">14.0687694549561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6935997009277</t>
   </si>
   <si>
     <t xml:space="preserve">13.6485795974731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159784317017</t>
+    <t xml:space="preserve">13.4159774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562196731567</t>
+    <t xml:space="preserve">13.9562187194824</t>
   </si>
   <si>
     <t xml:space="preserve">14.0312509536743</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">13.7986488342285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087404251099</t>
+    <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631519317627</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013715744019</t>
+    <t xml:space="preserve">14.3013696670532</t>
   </si>
   <si>
     <t xml:space="preserve">14.6165132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915473937988</t>
+    <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991798400879</t>
+    <t xml:space="preserve">14.9991836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.006685256958</t>
+    <t xml:space="preserve">15.006688117981</t>
   </si>
   <si>
     <t xml:space="preserve">14.9916791915894</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">14.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691686630249</t>
+    <t xml:space="preserve">14.9691677093506</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941354751587</t>
+    <t xml:space="preserve">14.8941345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390209197998</t>
+    <t xml:space="preserve">14.6390218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606954574585</t>
+    <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
     <t xml:space="preserve">15.4568881988525</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">15.7570219039917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572864532471</t>
+    <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
     <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.707893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575576782227</t>
+    <t xml:space="preserve">16.9575538635254</t>
   </si>
   <si>
     <t xml:space="preserve">16.5073547363281</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">16.2072200775146</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571537017822</t>
+    <t xml:space="preserve">16.0571556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615741729736</t>
+    <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528678894043</t>
+    <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702842712402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723844528198</t>
+    <t xml:space="preserve">14.9723854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898017883301</t>
+    <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
     <t xml:space="preserve">15.4354496002197</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">16.5159301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072238922119</t>
+    <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
     <t xml:space="preserve">16.8246383666992</t>
@@ -641,28 +641,28 @@
     <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267395019531</t>
+    <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.0495624542236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636772155762</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810916900635</t>
+    <t xml:space="preserve">15.2810935974121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549680709839</t>
+    <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321441650391</t>
+    <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919057846069</t>
+    <t xml:space="preserve">13.8919067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522144317627</t>
+    <t xml:space="preserve">14.2522106170654</t>
   </si>
   <si>
     <t xml:space="preserve">13.9319381713867</t>
@@ -671,40 +671,40 @@
     <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.45152759552</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721458435059</t>
+    <t xml:space="preserve">14.1721448898315</t>
   </si>
   <si>
     <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315952301025</t>
+    <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
     <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518705368042</t>
+    <t xml:space="preserve">13.8518686294556</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.291389465332</t>
+    <t xml:space="preserve">13.2913885116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123497009277</t>
+    <t xml:space="preserve">14.4123525619507</t>
   </si>
   <si>
     <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.131254196167</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">13.0511827468872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711151123047</t>
+    <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
     <t xml:space="preserve">12.8910455703735</t>
@@ -725,40 +725,40 @@
     <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302225112915</t>
+    <t xml:space="preserve">11.9302234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.6900186538696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903615951538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704292297363</t>
+    <t xml:space="preserve">12.170428276062</t>
   </si>
   <si>
     <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896747589111</t>
+    <t xml:space="preserve">11.2896757125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498109817505</t>
+    <t xml:space="preserve">11.4498100280762</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
@@ -770,121 +770,121 @@
     <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.20960521698</t>
+    <t xml:space="preserve">11.2096042633057</t>
   </si>
   <si>
     <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288507461548</t>
+    <t xml:space="preserve">10.3288497924805</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889879226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089183807373</t>
+    <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487812042236</t>
+    <t xml:space="preserve">10.2487831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687145233154</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
     <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102920532227</t>
+    <t xml:space="preserve">12.010293006897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493270874023</t>
+    <t xml:space="preserve">12.8493280410767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990161895752</t>
+    <t xml:space="preserve">12.5990171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.348705291748</t>
+    <t xml:space="preserve">12.3487043380737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.681206703186</t>
+    <t xml:space="preserve">11.6812057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315185546875</t>
+    <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.181830406189</t>
+    <t xml:space="preserve">12.1818313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321413040161</t>
+    <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155801773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.932765007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830768585205</t>
+    <t xml:space="preserve">13.1830778121948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4333877563477</t>
+    <t xml:space="preserve">13.4333868026733</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162010192871</t>
+    <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
     <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683849334717</t>
+    <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
     <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518218994141</t>
+    <t xml:space="preserve">14.8518180847168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346351623535</t>
+    <t xml:space="preserve">14.4346332550049</t>
   </si>
   <si>
     <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352569580078</t>
+    <t xml:space="preserve">14.9352588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186948776245</t>
+    <t xml:space="preserve">15.0186977386475</t>
   </si>
   <si>
     <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015071868896</t>
+    <t xml:space="preserve">14.601508140564</t>
   </si>
   <si>
     <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0174493789673</t>
+    <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837015151978</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255252838135</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444791793823</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
     <t xml:space="preserve">13.9931058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093151092529</t>
+    <t xml:space="preserve">13.9093160629272</t>
   </si>
   <si>
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
     <t xml:space="preserve">13.6579418182373</t>
@@ -935,61 +935,61 @@
     <t xml:space="preserve">14.3282699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634340286255</t>
+    <t xml:space="preserve">14.6634349822998</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958524703979</t>
+    <t xml:space="preserve">14.4958515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985990524292</t>
+    <t xml:space="preserve">14.9985961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472257614136</t>
+    <t xml:space="preserve">14.7472248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148063659668</t>
+    <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
     <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337621688843</t>
+    <t xml:space="preserve">15.33376121521</t>
   </si>
   <si>
     <t xml:space="preserve">15.417552947998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499742507935</t>
+    <t xml:space="preserve">15.2499704360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851345062256</t>
+    <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
     <t xml:space="preserve">15.6689291000366</t>
   </si>
   <si>
-    <t xml:space="preserve">15.920298576355</t>
+    <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0040912628174</t>
+    <t xml:space="preserve">16.004093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878829956055</t>
+    <t xml:space="preserve">16.0878810882568</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794055938721</t>
+    <t xml:space="preserve">16.2794075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923503875732</t>
+    <t xml:space="preserve">16.1923484802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.1052932739258</t>
@@ -998,40 +998,40 @@
     <t xml:space="preserve">16.0182361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311828613281</t>
+    <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829610824585</t>
+    <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405731201172</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.627628326416</t>
+    <t xml:space="preserve">16.6276264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146854400635</t>
+    <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8017406463623</t>
+    <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1499633789062</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">17.585241317749</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6299057006836</t>
+    <t xml:space="preserve">18.6299076080322</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240718841553</t>
+    <t xml:space="preserve">17.3240737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111270904541</t>
+    <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4697246551514</t>
+    <t xml:space="preserve">18.4697265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.2886505126953</t>
@@ -1094,34 +1094,34 @@
     <t xml:space="preserve">17.6548843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021961212158</t>
+    <t xml:space="preserve">17.2021942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2927341461182</t>
+    <t xml:space="preserve">17.2927322387695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778919219971</t>
+    <t xml:space="preserve">16.4778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157417297363</t>
+    <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441257476807</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2062797546387</t>
+    <t xml:space="preserve">16.20627784729</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">15.9346656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8400440216064</t>
+    <t xml:space="preserve">16.8400421142578</t>
   </si>
   <si>
     <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873558044434</t>
+    <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
     <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535905838013</t>
+    <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819755554199</t>
+    <t xml:space="preserve">15.4819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">14.3955211639404</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239080429077</t>
+    <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3049840927124</t>
+    <t xml:space="preserve">14.3049831390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901428222656</t>
+    <t xml:space="preserve">13.4901418685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1278,6 +1278,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -63051,7 +63054,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63077,7 +63080,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63103,7 +63106,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63129,7 +63132,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63155,7 +63158,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63181,7 +63184,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63207,7 +63210,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63233,7 +63236,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63259,7 +63262,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63285,7 +63288,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63311,7 +63314,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63363,7 +63366,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63389,7 +63392,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63415,7 +63418,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63441,7 +63444,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63467,7 +63470,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63493,7 +63496,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63519,7 +63522,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63545,7 +63548,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63571,7 +63574,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63597,7 +63600,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63623,7 +63626,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63649,7 +63652,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63675,7 +63678,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63701,7 +63704,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63727,7 +63730,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63753,7 +63756,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63779,7 +63782,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63805,7 +63808,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63831,7 +63834,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63857,7 +63860,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63883,7 +63886,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63909,7 +63912,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63935,7 +63938,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63961,7 +63964,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63987,7 +63990,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64013,7 +64016,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64039,7 +64042,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64065,7 +64068,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64091,7 +64094,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64117,7 +64120,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64143,7 +64146,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64169,7 +64172,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64195,7 +64198,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64221,7 +64224,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64247,7 +64250,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64273,7 +64276,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64299,7 +64302,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64325,7 +64328,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64351,7 +64354,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64377,7 +64380,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64403,7 +64406,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64429,7 +64432,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64455,7 +64458,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64481,7 +64484,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64507,7 +64510,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64533,7 +64536,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64559,7 +64562,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64585,7 +64588,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64611,7 +64614,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64637,7 +64640,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64663,7 +64666,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64689,7 +64692,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64715,7 +64718,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64741,7 +64744,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64767,7 +64770,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64793,7 +64796,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64819,7 +64822,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64845,7 +64848,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64871,7 +64874,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64897,7 +64900,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64923,7 +64926,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64949,7 +64952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64975,7 +64978,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65001,7 +65004,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65027,7 +65030,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65053,7 +65056,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65079,7 +65082,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65105,7 +65108,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65131,7 +65134,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65157,7 +65160,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65183,7 +65186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65209,7 +65212,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65235,7 +65238,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65261,7 +65264,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65287,7 +65290,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65313,7 +65316,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65339,7 +65342,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65365,7 +65368,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65391,7 +65394,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65417,7 +65420,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65443,7 +65446,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65469,7 +65472,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65495,7 +65498,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65521,7 +65524,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65547,7 +65550,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65573,7 +65576,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65599,7 +65602,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65625,7 +65628,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65651,7 +65654,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65677,7 +65680,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65703,7 +65706,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65729,7 +65732,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65755,7 +65758,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65781,7 +65784,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65807,7 +65810,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65833,7 +65836,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65859,7 +65862,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65885,7 +65888,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65911,7 +65914,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65937,7 +65940,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65963,7 +65966,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65989,7 +65992,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66015,7 +66018,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66041,7 +66044,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66067,7 +66070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66093,7 +66096,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66119,7 +66122,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66145,7 +66148,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66171,7 +66174,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66197,7 +66200,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66223,7 +66226,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66249,7 +66252,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66275,7 +66278,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66301,7 +66304,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66327,7 +66330,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66353,7 +66356,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66379,7 +66382,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66405,7 +66408,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66431,7 +66434,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66457,7 +66460,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66483,7 +66486,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66509,7 +66512,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66517,7 +66520,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6437847222</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>832</v>
@@ -66535,9 +66538,35 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.4772222222</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>535</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499223709106</t>
+    <t xml:space="preserve">13.149920463562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8577032089233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716144561768</t>
+    <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
     <t xml:space="preserve">12.523736000061</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167770385742</t>
+    <t xml:space="preserve">12.5167789459229</t>
   </si>
   <si>
     <t xml:space="preserve">12.175853729248</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809129714966</t>
+    <t xml:space="preserve">11.1809110641479</t>
   </si>
   <si>
     <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462326049805</t>
+    <t xml:space="preserve">9.91462421417236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280223846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.0885639190674</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">10.3112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060224533081</t>
+    <t xml:space="preserve">10.5060234069824</t>
   </si>
   <si>
     <t xml:space="preserve">10.4990644454956</t>
@@ -95,85 +95,85 @@
     <t xml:space="preserve">10.4364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451740264893</t>
+    <t xml:space="preserve">10.6451759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147512435913</t>
+    <t xml:space="preserve">10.714750289917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843284606934</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826856613159</t>
+    <t xml:space="preserve">11.3826837539673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331596374512</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549816131592</t>
+    <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148024559021</t>
+    <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193706512451</t>
+    <t xml:space="preserve">12.4193687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628894805908</t>
+    <t xml:space="preserve">12.6628866195679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411935806274</t>
+    <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933103561401</t>
+    <t xml:space="preserve">12.5933122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150062561035</t>
+    <t xml:space="preserve">12.3150091171265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506162643433</t>
+    <t xml:space="preserve">12.0506181716919</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583961486816</t>
+    <t xml:space="preserve">11.758394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227880477905</t>
+    <t xml:space="preserve">12.0227861404419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.984130859375</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163705825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407119750977</t>
+    <t xml:space="preserve">11.940710067749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045286178589</t>
+    <t xml:space="preserve">11.9045267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670288085938</t>
+    <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788726806641</t>
+    <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
     <t xml:space="preserve">11.2893991470337</t>
@@ -191,61 +191,61 @@
     <t xml:space="preserve">11.8683433532715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321580886841</t>
+    <t xml:space="preserve">11.8321590423584</t>
   </si>
   <si>
     <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.0854463577271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578140258789</t>
+    <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939992904663</t>
+    <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025531768799</t>
+    <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275535583496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953157424927</t>
+    <t xml:space="preserve">12.2953128814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196542739868</t>
+    <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643905639648</t>
+    <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466238021851</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
     <t xml:space="preserve">12.7729425430298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755706787109</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091278076172</t>
+    <t xml:space="preserve">12.8091287612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.243335723877</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
     <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604396820068</t>
+    <t xml:space="preserve">13.4604368209839</t>
   </si>
   <si>
     <t xml:space="preserve">13.388069152832</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">13.4025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453200340271</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242534637451</t>
+    <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689907073975</t>
+    <t xml:space="preserve">13.5689888000488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5545167922974</t>
+    <t xml:space="preserve">13.554518699646</t>
   </si>
   <si>
     <t xml:space="preserve">13.496621131897</t>
@@ -275,46 +275,46 @@
     <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459648132324</t>
+    <t xml:space="preserve">13.4459638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387292861938</t>
+    <t xml:space="preserve">13.4387302398682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071504592896</t>
+    <t xml:space="preserve">13.2071495056152</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288618087769</t>
+    <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814935684204</t>
+    <t xml:space="preserve">12.881495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985975265503</t>
+    <t xml:space="preserve">13.0985994338989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104433059692</t>
+    <t xml:space="preserve">12.9104423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262308120728</t>
+    <t xml:space="preserve">13.0262317657471</t>
   </si>
   <si>
     <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845311164856</t>
+    <t xml:space="preserve">12.845308303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275482177734</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439956665039</t>
+    <t xml:space="preserve">12.7439966201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189924240112</t>
+    <t xml:space="preserve">13.0189952850342</t>
   </si>
   <si>
     <t xml:space="preserve">12.657154083252</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">12.2446575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012357711792</t>
+    <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143970489502</t>
+    <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.070972442627</t>
@@ -338,148 +338,148 @@
     <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466339111328</t>
+    <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782098770142</t>
+    <t xml:space="preserve">12.0782117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913692474365</t>
+    <t xml:space="preserve">11.9913682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986066818237</t>
+    <t xml:space="preserve">11.998607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479465484619</t>
+    <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722898483276</t>
+    <t xml:space="preserve">12.1722869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551839828491</t>
+    <t xml:space="preserve">11.9551830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696588516235</t>
+    <t xml:space="preserve">11.9696578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768953323364</t>
+    <t xml:space="preserve">11.9768934249878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597904205322</t>
+    <t xml:space="preserve">11.7597923278809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505784988403</t>
+    <t xml:space="preserve">12.1505794525146</t>
   </si>
   <si>
     <t xml:space="preserve">12.2301816940308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229471206665</t>
+    <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554155349731</t>
+    <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054828643799</t>
+    <t xml:space="preserve">12.3054847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805170059204</t>
+    <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
     <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880176544189</t>
+    <t xml:space="preserve">12.3880186080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180326461792</t>
+    <t xml:space="preserve">12.4180307388306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756025314331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.830717086792</t>
+    <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158437728882</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807834625244</t>
+    <t xml:space="preserve">12.9807825088501</t>
   </si>
   <si>
     <t xml:space="preserve">12.9732809066772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881542205811</t>
+    <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657793045044</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432649612427</t>
+    <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
     <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682336807251</t>
+    <t xml:space="preserve">12.8682327270508</t>
   </si>
   <si>
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083402633667</t>
+    <t xml:space="preserve">13.1083383560181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933332443237</t>
+    <t xml:space="preserve">13.0933351516724</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559494018555</t>
+    <t xml:space="preserve">13.3559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809181213379</t>
+    <t xml:space="preserve">13.2809190750122</t>
   </si>
   <si>
     <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735473632812</t>
+    <t xml:space="preserve">13.5735483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435342788696</t>
+    <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">13.2358961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383514404297</t>
+    <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205883026123</t>
+    <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685029983521</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.318434715271</t>
+    <t xml:space="preserve">13.318431854248</t>
   </si>
   <si>
     <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683664321899</t>
+    <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
     <t xml:space="preserve">13.5060176849365</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">13.6560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185684204102</t>
+    <t xml:space="preserve">13.6185674667358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061513900757</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810499191284</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687694549561</t>
+    <t xml:space="preserve">14.0687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6935997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485786437988</t>
+    <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159774780273</t>
+    <t xml:space="preserve">13.415976524353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562196731567</t>
+    <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
     <t xml:space="preserve">14.0312519073486</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">13.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986478805542</t>
+    <t xml:space="preserve">13.7986488342285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087432861328</t>
+    <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
     <t xml:space="preserve">14.631519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013734817505</t>
+    <t xml:space="preserve">14.3013715744019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616512298584</t>
+    <t xml:space="preserve">14.6165142059326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915483474731</t>
+    <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
     <t xml:space="preserve">14.9991846084595</t>
@@ -545,43 +545,43 @@
     <t xml:space="preserve">15.0066871643066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9916801452637</t>
+    <t xml:space="preserve">14.991678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766759872437</t>
+    <t xml:space="preserve">14.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691715240479</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465253829956</t>
+    <t xml:space="preserve">14.6465263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941345214844</t>
+    <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390237808228</t>
+    <t xml:space="preserve">14.6390218734741</t>
   </si>
   <si>
     <t xml:space="preserve">15.1567535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606951713562</t>
+    <t xml:space="preserve">15.606954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568862915039</t>
+    <t xml:space="preserve">15.4568881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570209503174</t>
+    <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572883605957</t>
+    <t xml:space="preserve">16.3572864532471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574230194092</t>
+    <t xml:space="preserve">16.6574192047119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576904296875</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073547363281</t>
+    <t xml:space="preserve">16.5073528289795</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072200775146</t>
+    <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0571537017822</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528659820557</t>
+    <t xml:space="preserve">16.0528678894043</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702861785889</t>
@@ -617,115 +617,115 @@
     <t xml:space="preserve">14.9723854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898027420044</t>
+    <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
     <t xml:space="preserve">15.4354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.744158744812</t>
+    <t xml:space="preserve">15.7441577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159282684326</t>
+    <t xml:space="preserve">16.5159301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072219848633</t>
+    <t xml:space="preserve">16.2072238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8246402740479</t>
+    <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.898512840271</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267414093018</t>
+    <t xml:space="preserve">15.1267395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495624542236</t>
+    <t xml:space="preserve">15.0495634078979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636781692505</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810945510864</t>
+    <t xml:space="preserve">15.2810955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549690246582</t>
+    <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321441650391</t>
+    <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
     <t xml:space="preserve">13.8919038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522115707397</t>
+    <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319372177124</t>
+    <t xml:space="preserve">13.931939125061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.771800994873</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515256881714</t>
+    <t xml:space="preserve">13.45152759552</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721448898315</t>
+    <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.611665725708</t>
+    <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120067596436</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518705368042</t>
+    <t xml:space="preserve">13.8518695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113218307495</t>
+    <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123497009277</t>
+    <t xml:space="preserve">14.4123506546021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714580535889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312532424927</t>
+    <t xml:space="preserve">13.131254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511846542358</t>
+    <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711151123047</t>
+    <t xml:space="preserve">12.9711132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810977935791</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309083938599</t>
+    <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106349945068</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903596878052</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704292297363</t>
+    <t xml:space="preserve">12.170428276062</t>
   </si>
   <si>
     <t xml:space="preserve">11.1295375823975</t>
@@ -755,37 +755,37 @@
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498100280762</t>
+    <t xml:space="preserve">11.4498119354248</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298805236816</t>
+    <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
     <t xml:space="preserve">11.3697423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.20960521698</t>
+    <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288516998291</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889879226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089183807373</t>
+    <t xml:space="preserve">10.4089202880859</t>
   </si>
   <si>
     <t xml:space="preserve">10.2487831115723</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700853347778</t>
+    <t xml:space="preserve">11.7700843811035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102920532227</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">12.5990171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3487043380737</t>
+    <t xml:space="preserve">12.348705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137090682983</t>
+    <t xml:space="preserve">11.0137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315166473389</t>
+    <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
     <t xml:space="preserve">12.181830406189</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9327659606934</t>
+    <t xml:space="preserve">12.932765007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830768585205</t>
+    <t xml:space="preserve">13.1830778121948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4333877563477</t>
+    <t xml:space="preserve">13.4333868026733</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499507904053</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.76589012146</t>
+    <t xml:space="preserve">12.7658910751343</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683839797974</t>
+    <t xml:space="preserve">14.7683849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180711746216</t>
+    <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518199920654</t>
+    <t xml:space="preserve">14.8518209457397</t>
   </si>
   <si>
     <t xml:space="preserve">14.4346351623535</t>
@@ -866,145 +866,145 @@
     <t xml:space="preserve">14.9352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186948776245</t>
+    <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849451065063</t>
+    <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015071868896</t>
+    <t xml:space="preserve">14.6015090942383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511972427368</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843242645264</t>
+    <t xml:space="preserve">14.1843233108521</t>
   </si>
   <si>
     <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837005615234</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671375274658</t>
+    <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002616882324</t>
+    <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677612304688</t>
+    <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741519927979</t>
+    <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444791793823</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.9931058883667</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4120607376099</t>
+    <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
     <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606874465942</t>
+    <t xml:space="preserve">14.1606864929199</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903602600098</t>
+    <t xml:space="preserve">13.4903593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282709121704</t>
+    <t xml:space="preserve">14.3282699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634340286255</t>
+    <t xml:space="preserve">14.6634349822998</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958505630493</t>
+    <t xml:space="preserve">14.4958515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985980987549</t>
+    <t xml:space="preserve">14.9985971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472257614136</t>
+    <t xml:space="preserve">14.7472276687622</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148063659668</t>
+    <t xml:space="preserve">14.9148082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661825180054</t>
+    <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33376121521</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
     <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499732971191</t>
+    <t xml:space="preserve">15.2499704360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823907852173</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851354598999</t>
+    <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689281463623</t>
+    <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9202995300293</t>
+    <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0040912628174</t>
+    <t xml:space="preserve">16.004093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878829956055</t>
+    <t xml:space="preserve">16.0878810882568</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794075012207</t>
+    <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923484802246</t>
+    <t xml:space="preserve">16.1923503875732</t>
   </si>
   <si>
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0182361602783</t>
+    <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311800003052</t>
+    <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700162887573</t>
+    <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6276302337646</t>
+    <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7146835327148</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.801736831665</t>
+    <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5852394104004</t>
+    <t xml:space="preserve">17.585241317749</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299057006836</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557971954346</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.933464050293</t>
+    <t xml:space="preserve">17.9334621429443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240718841553</t>
+    <t xml:space="preserve">17.3240737915039</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111289978027</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359622955322</t>
+    <t xml:space="preserve">17.8359603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264965057373</t>
+    <t xml:space="preserve">17.9264984130859</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738063812256</t>
+    <t xml:space="preserve">17.4738101959229</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116580963135</t>
+    <t xml:space="preserve">17.1116561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305839538574</t>
+    <t xml:space="preserve">16.9305820465088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5684280395508</t>
+    <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2927341461182</t>
@@ -1115,7 +1115,10 @@
     <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.296817779541</t>
+    <t xml:space="preserve">15.8441276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
     <t xml:space="preserve">16.20627784729</t>
@@ -1130,28 +1133,28 @@
     <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589660644531</t>
+    <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663049697876</t>
+    <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
     <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819774627686</t>
+    <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955211639404</t>
+    <t xml:space="preserve">14.3955202102661</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5806798934937</t>
+    <t xml:space="preserve">13.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">14.1239080429077</t>
@@ -1163,16 +1166,16 @@
     <t xml:space="preserve">13.3996057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090667724609</t>
+    <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901418685913</t>
+    <t xml:space="preserve">13.4901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333690643311</t>
+    <t xml:space="preserve">14.0333700180054</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1181,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456705093384</t>
+    <t xml:space="preserve">14.5456695556641</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967765808105</t>
+    <t xml:space="preserve">13.9967775344849</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1202,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.447883605957</t>
+    <t xml:space="preserve">13.4478826522827</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.081955909729</t>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1223,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716025352478</t>
+    <t xml:space="preserve">12.7160263061523</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1232,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330610275269</t>
+    <t xml:space="preserve">12.5330619812012</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1275,9 +1278,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -44750,7 +44750,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44776,7 +44776,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44828,7 +44828,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44854,7 +44854,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44880,7 +44880,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44906,7 +44906,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44932,7 +44932,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44958,7 +44958,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44984,7 +44984,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45010,7 +45010,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45036,7 +45036,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45062,7 +45062,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45088,7 +45088,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45114,7 +45114,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45140,7 +45140,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45166,7 +45166,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45192,7 +45192,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45218,7 +45218,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45244,7 +45244,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45270,7 +45270,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45296,7 +45296,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45322,7 +45322,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45348,7 +45348,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45374,7 +45374,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45426,7 +45426,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45452,7 +45452,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45712,7 +45712,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45946,7 +45946,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45972,7 +45972,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45998,7 +45998,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46024,7 +46024,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46050,7 +46050,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46076,7 +46076,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46102,7 +46102,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46128,7 +46128,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46154,7 +46154,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46180,7 +46180,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46206,7 +46206,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46232,7 +46232,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46258,7 +46258,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46336,7 +46336,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46362,7 +46362,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46544,7 +46544,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46570,7 +46570,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46596,7 +46596,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46622,7 +46622,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46648,7 +46648,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46674,7 +46674,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46700,7 +46700,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46726,7 +46726,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46752,7 +46752,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46778,7 +46778,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46804,7 +46804,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46830,7 +46830,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46856,7 +46856,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46882,7 +46882,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46908,7 +46908,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46934,7 +46934,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46960,7 +46960,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46986,7 +46986,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47012,7 +47012,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47038,7 +47038,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47064,7 +47064,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47116,7 +47116,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47142,7 +47142,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47168,7 +47168,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47194,7 +47194,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47220,7 +47220,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47246,7 +47246,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47272,7 +47272,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47298,7 +47298,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47324,7 +47324,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47350,7 +47350,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47376,7 +47376,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47402,7 +47402,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47506,7 +47506,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47532,7 +47532,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47558,7 +47558,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47584,7 +47584,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47610,7 +47610,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47636,7 +47636,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47662,7 +47662,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47688,7 +47688,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47714,7 +47714,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47766,7 +47766,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47792,7 +47792,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47818,7 +47818,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47844,7 +47844,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47870,7 +47870,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47896,7 +47896,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47922,7 +47922,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48000,7 +48000,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48026,7 +48026,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48052,7 +48052,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48078,7 +48078,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48104,7 +48104,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48130,7 +48130,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48156,7 +48156,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48182,7 +48182,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48234,7 +48234,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48260,7 +48260,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48286,7 +48286,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48338,7 +48338,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48598,7 +48598,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48624,7 +48624,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48650,7 +48650,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48676,7 +48676,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48702,7 +48702,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48728,7 +48728,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48754,7 +48754,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48780,7 +48780,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48806,7 +48806,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48832,7 +48832,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48858,7 +48858,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48884,7 +48884,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48910,7 +48910,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48936,7 +48936,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48962,7 +48962,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48988,7 +48988,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49014,7 +49014,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49040,7 +49040,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49066,7 +49066,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49092,7 +49092,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49118,7 +49118,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49144,7 +49144,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49170,7 +49170,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49196,7 +49196,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49222,7 +49222,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49248,7 +49248,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49274,7 +49274,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49300,7 +49300,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49326,7 +49326,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49352,7 +49352,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49378,7 +49378,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49404,7 +49404,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49430,7 +49430,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49456,7 +49456,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49482,7 +49482,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49508,7 +49508,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49534,7 +49534,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49560,7 +49560,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49586,7 +49586,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49612,7 +49612,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49638,7 +49638,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49664,7 +49664,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49690,7 +49690,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49716,7 +49716,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49742,7 +49742,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49768,7 +49768,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49794,7 +49794,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49820,7 +49820,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49846,7 +49846,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49872,7 +49872,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49898,7 +49898,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49924,7 +49924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49950,7 +49950,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49976,7 +49976,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50002,7 +50002,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50028,7 +50028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50054,7 +50054,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50080,7 +50080,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50106,7 +50106,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50132,7 +50132,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50158,7 +50158,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50184,7 +50184,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50210,7 +50210,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50236,7 +50236,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50262,7 +50262,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50288,7 +50288,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50314,7 +50314,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50340,7 +50340,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50366,7 +50366,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50392,7 +50392,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50418,7 +50418,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50444,7 +50444,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50470,7 +50470,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50496,7 +50496,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50522,7 +50522,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50548,7 +50548,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50574,7 +50574,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50600,7 +50600,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50626,7 +50626,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50652,7 +50652,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50678,7 +50678,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50704,7 +50704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50730,7 +50730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50756,7 +50756,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50782,7 +50782,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50808,7 +50808,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50834,7 +50834,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50860,7 +50860,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50886,7 +50886,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50912,7 +50912,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50938,7 +50938,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50964,7 +50964,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50990,7 +50990,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51016,7 +51016,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51042,7 +51042,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51068,7 +51068,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51094,7 +51094,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51120,7 +51120,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51146,7 +51146,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51172,7 +51172,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51198,7 +51198,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51224,7 +51224,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51250,7 +51250,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51276,7 +51276,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51302,7 +51302,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51328,7 +51328,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51354,7 +51354,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51380,7 +51380,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51406,7 +51406,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51432,7 +51432,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51458,7 +51458,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51484,7 +51484,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51510,7 +51510,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51536,7 +51536,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51562,7 +51562,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51588,7 +51588,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51614,7 +51614,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51640,7 +51640,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51666,7 +51666,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51692,7 +51692,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51718,7 +51718,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51744,7 +51744,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51770,7 +51770,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51796,7 +51796,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51822,7 +51822,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51848,7 +51848,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51874,7 +51874,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51900,7 +51900,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51926,7 +51926,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51952,7 +51952,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51978,7 +51978,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52004,7 +52004,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52030,7 +52030,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52056,7 +52056,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52082,7 +52082,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52108,7 +52108,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52134,7 +52134,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52160,7 +52160,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52186,7 +52186,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52212,7 +52212,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52238,7 +52238,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52264,7 +52264,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52290,7 +52290,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52316,7 +52316,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52342,7 +52342,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52368,7 +52368,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52394,7 +52394,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52420,7 +52420,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52446,7 +52446,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52472,7 +52472,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52498,7 +52498,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52524,7 +52524,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52550,7 +52550,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52576,7 +52576,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52602,7 +52602,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52628,7 +52628,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52654,7 +52654,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52680,7 +52680,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52706,7 +52706,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52732,7 +52732,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52758,7 +52758,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52784,7 +52784,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52810,7 +52810,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52836,7 +52836,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52862,7 +52862,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52888,7 +52888,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52914,7 +52914,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52940,7 +52940,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52966,7 +52966,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -52992,7 +52992,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53018,7 +53018,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53044,7 +53044,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53070,7 +53070,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53096,7 +53096,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53122,7 +53122,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53148,7 +53148,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53174,7 +53174,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53200,7 +53200,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53226,7 +53226,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53252,7 +53252,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53278,7 +53278,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53304,7 +53304,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53330,7 +53330,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53356,7 +53356,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53382,7 +53382,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53408,7 +53408,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53434,7 +53434,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53460,7 +53460,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53486,7 +53486,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53512,7 +53512,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53538,7 +53538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53564,7 +53564,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53590,7 +53590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53616,7 +53616,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53642,7 +53642,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53668,7 +53668,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53694,7 +53694,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53720,7 +53720,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53746,7 +53746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53772,7 +53772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53798,7 +53798,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53824,7 +53824,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53850,7 +53850,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53876,7 +53876,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53902,7 +53902,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53928,7 +53928,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53954,7 +53954,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53980,7 +53980,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54006,7 +54006,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54032,7 +54032,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54058,7 +54058,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54084,7 +54084,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54110,7 +54110,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54136,7 +54136,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54162,7 +54162,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54188,7 +54188,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54214,7 +54214,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54240,7 +54240,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54266,7 +54266,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54292,7 +54292,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54318,7 +54318,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54344,7 +54344,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54370,7 +54370,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54396,7 +54396,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54422,7 +54422,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54448,7 +54448,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54474,7 +54474,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54500,7 +54500,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54526,7 +54526,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54552,7 +54552,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54578,7 +54578,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54604,7 +54604,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54630,7 +54630,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54656,7 +54656,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54682,7 +54682,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54708,7 +54708,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54734,7 +54734,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54760,7 +54760,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54786,7 +54786,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54812,7 +54812,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54838,7 +54838,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54864,7 +54864,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54890,7 +54890,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54916,7 +54916,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54942,7 +54942,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54968,7 +54968,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -54994,7 +54994,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55020,7 +55020,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55046,7 +55046,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55072,7 +55072,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55098,7 +55098,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55124,7 +55124,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55150,7 +55150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55176,7 +55176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55202,7 +55202,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55228,7 +55228,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55254,7 +55254,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55280,7 +55280,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55306,7 +55306,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55332,7 +55332,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55358,7 +55358,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55384,7 +55384,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55410,7 +55410,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55436,7 +55436,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55462,7 +55462,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55488,7 +55488,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55514,7 +55514,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55540,7 +55540,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55566,7 +55566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55592,7 +55592,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55618,7 +55618,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55644,7 +55644,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55670,7 +55670,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55696,7 +55696,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55722,7 +55722,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55748,7 +55748,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55774,7 +55774,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55800,7 +55800,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55826,7 +55826,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55852,7 +55852,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55878,7 +55878,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55904,7 +55904,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55930,7 +55930,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55956,7 +55956,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55982,7 +55982,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56008,7 +56008,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56034,7 +56034,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56060,7 +56060,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56086,7 +56086,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56112,7 +56112,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56138,7 +56138,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56164,7 +56164,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56190,7 +56190,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56216,7 +56216,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56242,7 +56242,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56268,7 +56268,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56294,7 +56294,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56320,7 +56320,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56346,7 +56346,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56372,7 +56372,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56398,7 +56398,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56424,7 +56424,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56450,7 +56450,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56476,7 +56476,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56502,7 +56502,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56528,7 +56528,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56554,7 +56554,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56580,7 +56580,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56606,7 +56606,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56632,7 +56632,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56658,7 +56658,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56684,7 +56684,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56710,7 +56710,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56736,7 +56736,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56762,7 +56762,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56788,7 +56788,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56814,7 +56814,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56840,7 +56840,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56866,7 +56866,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56892,7 +56892,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56918,7 +56918,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56944,7 +56944,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56970,7 +56970,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -56996,7 +56996,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57022,7 +57022,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57048,7 +57048,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57074,7 +57074,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57100,7 +57100,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57126,7 +57126,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57152,7 +57152,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57178,7 +57178,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57204,7 +57204,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57230,7 +57230,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57256,7 +57256,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57282,7 +57282,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57308,7 +57308,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57334,7 +57334,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57360,7 +57360,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57386,7 +57386,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57412,7 +57412,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57438,7 +57438,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57464,7 +57464,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57490,7 +57490,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57516,7 +57516,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57542,7 +57542,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57568,7 +57568,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57594,7 +57594,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57620,7 +57620,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57646,7 +57646,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57672,7 +57672,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57698,7 +57698,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57724,7 +57724,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57750,7 +57750,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57776,7 +57776,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57802,7 +57802,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57828,7 +57828,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57854,7 +57854,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57880,7 +57880,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57906,7 +57906,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57932,7 +57932,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57958,7 +57958,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57984,7 +57984,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58010,7 +58010,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58036,7 +58036,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58062,7 +58062,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58088,7 +58088,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58114,7 +58114,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58140,7 +58140,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58166,7 +58166,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58192,7 +58192,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58218,7 +58218,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58244,7 +58244,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58270,7 +58270,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58296,7 +58296,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58322,7 +58322,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58348,7 +58348,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58374,7 +58374,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58400,7 +58400,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58426,7 +58426,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58452,7 +58452,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58478,7 +58478,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58504,7 +58504,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58530,7 +58530,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58556,7 +58556,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58582,7 +58582,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58608,7 +58608,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58634,7 +58634,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58660,7 +58660,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58686,7 +58686,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58712,7 +58712,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58738,7 +58738,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58764,7 +58764,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58790,7 +58790,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58816,7 +58816,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58842,7 +58842,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58868,7 +58868,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58894,7 +58894,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58920,7 +58920,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58946,7 +58946,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58972,7 +58972,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -58998,7 +58998,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59024,7 +59024,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59050,7 +59050,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59076,7 +59076,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59102,7 +59102,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59128,7 +59128,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59154,7 +59154,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59180,7 +59180,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59206,7 +59206,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59232,7 +59232,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59258,7 +59258,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59284,7 +59284,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59310,7 +59310,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59336,7 +59336,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59362,7 +59362,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59388,7 +59388,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59414,7 +59414,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59440,7 +59440,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59466,7 +59466,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59492,7 +59492,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59518,7 +59518,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59544,7 +59544,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59570,7 +59570,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59596,7 +59596,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59622,7 +59622,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59648,7 +59648,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59674,7 +59674,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59700,7 +59700,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59726,7 +59726,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59752,7 +59752,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59778,7 +59778,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59804,7 +59804,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59830,7 +59830,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59856,7 +59856,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59882,7 +59882,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59908,7 +59908,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59934,7 +59934,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59960,7 +59960,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59986,7 +59986,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60012,7 +60012,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60038,7 +60038,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60064,7 +60064,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60090,7 +60090,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60116,7 +60116,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60142,7 +60142,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60168,7 +60168,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60194,7 +60194,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60220,7 +60220,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60246,7 +60246,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60272,7 +60272,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60298,7 +60298,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60324,7 +60324,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60350,7 +60350,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60376,7 +60376,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60402,7 +60402,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60428,7 +60428,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60454,7 +60454,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60480,7 +60480,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60506,7 +60506,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60532,7 +60532,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60558,7 +60558,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60584,7 +60584,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60610,7 +60610,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60636,7 +60636,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60662,7 +60662,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60688,7 +60688,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60714,7 +60714,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60740,7 +60740,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60766,7 +60766,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60792,7 +60792,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60818,7 +60818,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60844,7 +60844,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60870,7 +60870,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60896,7 +60896,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60922,7 +60922,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60948,7 +60948,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60974,7 +60974,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61000,7 +61000,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61026,7 +61026,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61052,7 +61052,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61078,7 +61078,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61104,7 +61104,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61130,7 +61130,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61156,7 +61156,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61182,7 +61182,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61208,7 +61208,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61234,7 +61234,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61260,7 +61260,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61286,7 +61286,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61312,7 +61312,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61338,7 +61338,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61364,7 +61364,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61390,7 +61390,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61416,7 +61416,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61442,7 +61442,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61468,7 +61468,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61494,7 +61494,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61520,7 +61520,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61546,7 +61546,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61572,7 +61572,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61598,7 +61598,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61624,7 +61624,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61650,7 +61650,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61676,7 +61676,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61702,7 +61702,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61728,7 +61728,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61754,7 +61754,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61780,7 +61780,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61806,7 +61806,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61832,7 +61832,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61858,7 +61858,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61884,7 +61884,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61910,7 +61910,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61936,7 +61936,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61962,7 +61962,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -61988,7 +61988,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62014,7 +62014,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62040,7 +62040,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62066,7 +62066,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62092,7 +62092,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62118,7 +62118,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62144,7 +62144,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62170,7 +62170,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62196,7 +62196,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62222,7 +62222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62248,7 +62248,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62274,7 +62274,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62300,7 +62300,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62326,7 +62326,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62352,7 +62352,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62378,7 +62378,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62404,7 +62404,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62430,7 +62430,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62456,7 +62456,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62482,7 +62482,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62508,7 +62508,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62534,7 +62534,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62560,7 +62560,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62586,7 +62586,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62612,7 +62612,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62638,7 +62638,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62664,7 +62664,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62690,7 +62690,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62716,7 +62716,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62742,7 +62742,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62768,7 +62768,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62794,7 +62794,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62820,7 +62820,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62846,7 +62846,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62872,7 +62872,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62898,7 +62898,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62924,7 +62924,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62950,7 +62950,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62976,7 +62976,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63002,7 +63002,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63028,7 +63028,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63054,7 +63054,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63340,7 +63340,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66676,7 +66676,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6859259259</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>17464</v>
@@ -66697,6 +66697,32 @@
         <v>441</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6866087963</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>10689</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194976806641</t>
+    <t xml:space="preserve">13.219500541687</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149920463562</t>
+    <t xml:space="preserve">13.1499242782593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577032089233</t>
+    <t xml:space="preserve">12.8577013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716163635254</t>
+    <t xml:space="preserve">12.8716154098511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.523736000061</t>
+    <t xml:space="preserve">12.5237340927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167789459229</t>
+    <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.175853729248</t>
+    <t xml:space="preserve">12.1758518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279724121094</t>
+    <t xml:space="preserve">11.8279733657837</t>
   </si>
   <si>
     <t xml:space="preserve">11.1809110641479</t>
@@ -74,145 +74,145 @@
     <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280223846436</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885639190674</t>
+    <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112096786499</t>
+    <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060234069824</t>
+    <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990644454956</t>
+    <t xml:space="preserve">10.4990634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364471435547</t>
+    <t xml:space="preserve">10.4364452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451759338379</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.714750289917</t>
+    <t xml:space="preserve">10.7147493362427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773694992065</t>
+    <t xml:space="preserve">10.7773685455322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1322088241577</t>
+    <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826837539673</t>
+    <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331577301025</t>
+    <t xml:space="preserve">11.6331586837769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905916213989</t>
+    <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549797058105</t>
+    <t xml:space="preserve">12.1549816131592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193687438965</t>
+    <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.6628866195679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150091171265</t>
+    <t xml:space="preserve">12.3150081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506181716919</t>
+    <t xml:space="preserve">12.0506191253662</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758394241333</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227861404419</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.984130859375</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163705825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.940710067749</t>
+    <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045267105103</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670278549194</t>
+    <t xml:space="preserve">11.7670269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065050125122</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788717269897</t>
+    <t xml:space="preserve">11.5788726806641</t>
   </si>
   <si>
     <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426874160767</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979511260986</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512384414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683433532715</t>
+    <t xml:space="preserve">11.8683452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321590423584</t>
+    <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130786895752</t>
+    <t xml:space="preserve">12.0130796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854463577271</t>
+    <t xml:space="preserve">12.0854473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578149795532</t>
+    <t xml:space="preserve">12.1578140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939973831177</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025512695312</t>
+    <t xml:space="preserve">12.3025531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275535583496</t>
+    <t xml:space="preserve">12.0275526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953128814697</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
     <t xml:space="preserve">12.4472856521606</t>
@@ -224,28 +224,28 @@
     <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.9466257095337</t>
   </si>
   <si>
     <t xml:space="preserve">12.7729425430298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755725860596</t>
+    <t xml:space="preserve">12.9755716323853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538612365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091287612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433347702026</t>
+    <t xml:space="preserve">13.2433338165283</t>
   </si>
   <si>
     <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604368209839</t>
+    <t xml:space="preserve">13.4604396820068</t>
   </si>
   <si>
     <t xml:space="preserve">13.388069152832</t>
@@ -254,85 +254,85 @@
     <t xml:space="preserve">13.4025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532012939453</t>
+    <t xml:space="preserve">13.4532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242544174194</t>
+    <t xml:space="preserve">13.4242553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
     <t xml:space="preserve">13.5689888000488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554518699646</t>
+    <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
     <t xml:space="preserve">13.496621131897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518857955933</t>
+    <t xml:space="preserve">13.3518877029419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459638595581</t>
+    <t xml:space="preserve">13.4459629058838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387302398682</t>
+    <t xml:space="preserve">13.4387273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071495056152</t>
+    <t xml:space="preserve">13.2071514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038595199585</t>
+    <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288599014282</t>
+    <t xml:space="preserve">13.2288618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881495475769</t>
+    <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
     <t xml:space="preserve">13.0985994338989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262317657471</t>
+    <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347827911377</t>
+    <t xml:space="preserve">13.134783744812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845308303833</t>
+    <t xml:space="preserve">12.8453102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275463104248</t>
+    <t xml:space="preserve">13.1275472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439966201782</t>
+    <t xml:space="preserve">12.7439947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189952850342</t>
+    <t xml:space="preserve">13.0189914703369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012348175049</t>
+    <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334745407104</t>
+    <t xml:space="preserve">11.9334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143951416016</t>
+    <t xml:space="preserve">12.1143932342529</t>
   </si>
   <si>
-    <t xml:space="preserve">12.070972442627</t>
+    <t xml:space="preserve">12.0709714889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.0492630004883</t>
@@ -344,43 +344,43 @@
     <t xml:space="preserve">12.0782117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913682937622</t>
+    <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.998607635498</t>
+    <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722869873047</t>
+    <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551830291748</t>
+    <t xml:space="preserve">11.9551849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696578979492</t>
+    <t xml:space="preserve">11.9696598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768934249878</t>
+    <t xml:space="preserve">11.9768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597923278809</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301816940308</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229461669922</t>
+    <t xml:space="preserve">12.2229452133179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554145812988</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054847717285</t>
+    <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.3805160522461</t>
@@ -398,70 +398,70 @@
     <t xml:space="preserve">12.3129854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180307388306</t>
+    <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307161331177</t>
+    <t xml:space="preserve">12.8307151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158428192139</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807825088501</t>
+    <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732809066772</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881532669067</t>
+    <t xml:space="preserve">12.6881523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657783508301</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.943265914917</t>
+    <t xml:space="preserve">12.9432668685913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308498382568</t>
+    <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682327270508</t>
+    <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083383560181</t>
+    <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933351516724</t>
+    <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559513092041</t>
+    <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
     <t xml:space="preserve">13.2809190750122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.430983543396</t>
+    <t xml:space="preserve">13.4309825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735483169556</t>
+    <t xml:space="preserve">13.5735464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435333251953</t>
+    <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358961105347</t>
+    <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234809875488</t>
+    <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2058849334717</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.318431854248</t>
+    <t xml:space="preserve">13.3184328079224</t>
   </si>
   <si>
     <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683673858643</t>
+    <t xml:space="preserve">13.1683664321899</t>
   </si>
   <si>
     <t xml:space="preserve">13.5060176849365</t>
@@ -488,46 +488,46 @@
     <t xml:space="preserve">13.6560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185674667358</t>
+    <t xml:space="preserve">13.6185693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061504364014</t>
+    <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810508728027</t>
+    <t xml:space="preserve">13.5810518264771</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6935997009277</t>
+    <t xml:space="preserve">13.6936016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485805511475</t>
+    <t xml:space="preserve">13.6485815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.415976524353</t>
+    <t xml:space="preserve">13.4159784317017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312509536743</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459915161133</t>
+    <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986488342285</t>
+    <t xml:space="preserve">13.7986478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087423324585</t>
+    <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631519317627</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
     <t xml:space="preserve">14.3013715744019</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991846084595</t>
+    <t xml:space="preserve">14.9991836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066871643066</t>
+    <t xml:space="preserve">15.006688117981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991678237915</t>
+    <t xml:space="preserve">14.991681098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766731262207</t>
+    <t xml:space="preserve">14.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691696166992</t>
+    <t xml:space="preserve">14.9691677093506</t>
   </si>
   <si>
     <t xml:space="preserve">14.6465263366699</t>
@@ -560,40 +560,40 @@
     <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567535400391</t>
+    <t xml:space="preserve">15.1567525863647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606954574585</t>
+    <t xml:space="preserve">15.606951713562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568881988525</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
     <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572864532471</t>
+    <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574192047119</t>
+    <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076221466064</t>
+    <t xml:space="preserve">17.1076240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.957555770874</t>
+    <t xml:space="preserve">16.9575595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073528289795</t>
+    <t xml:space="preserve">16.5073509216309</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571537017822</t>
+    <t xml:space="preserve">16.0571556091309</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528678894043</t>
+    <t xml:space="preserve">16.052864074707</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702861785889</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354496002197</t>
+    <t xml:space="preserve">15.4354515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441577911377</t>
+    <t xml:space="preserve">15.7441596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159301757812</t>
+    <t xml:space="preserve">16.5159320831299</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072238922119</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">15.1267395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.0495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636762619019</t>
+    <t xml:space="preserve">14.6636791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810955047607</t>
+    <t xml:space="preserve">15.2810945510864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549671173096</t>
+    <t xml:space="preserve">14.3549680709839</t>
   </si>
   <si>
     <t xml:space="preserve">14.4321451187134</t>
@@ -659,76 +659,76 @@
     <t xml:space="preserve">13.8919038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522125244141</t>
+    <t xml:space="preserve">14.2522106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319400787354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7718000411987</t>
+    <t xml:space="preserve">13.7717990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">13.45152759552</t>
+    <t xml:space="preserve">13.4515256881714</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917333602905</t>
+    <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116647720337</t>
+    <t xml:space="preserve">13.611665725708</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120058059692</t>
+    <t xml:space="preserve">14.0120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518695831299</t>
+    <t xml:space="preserve">13.8518686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113208770752</t>
+    <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
     <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123506546021</t>
+    <t xml:space="preserve">14.4123525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920763015747</t>
+    <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.131254196167</t>
+    <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711132049561</t>
+    <t xml:space="preserve">12.9711151123047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910455703735</t>
+    <t xml:space="preserve">12.8910446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109769821167</t>
+    <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
     <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907035827637</t>
+    <t xml:space="preserve">12.4907026290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508417129517</t>
+    <t xml:space="preserve">12.650842666626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106359481812</t>
   </si>
   <si>
     <t xml:space="preserve">11.9302225112915</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
     <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.170428276062</t>
+    <t xml:space="preserve">12.1704292297363</t>
   </si>
   <si>
     <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896738052368</t>
+    <t xml:space="preserve">11.2896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498119354248</t>
+    <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099481582642</t>
+    <t xml:space="preserve">11.6099472045898</t>
   </si>
   <si>
     <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096061706543</t>
+    <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9693994522095</t>
+    <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494689941406</t>
+    <t xml:space="preserve">11.0494680404663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491250991821</t>
+    <t xml:space="preserve">10.6491241455078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288507461548</t>
+    <t xml:space="preserve">10.3288497924805</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889879226685</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700843811035</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102920532227</t>
+    <t xml:space="preserve">12.0102910995483</t>
   </si>
   <si>
     <t xml:space="preserve">12.8493280410767</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.181830406189</t>
+    <t xml:space="preserve">12.1818313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321422576904</t>
+    <t xml:space="preserve">12.4321413040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155801773071</t>
+    <t xml:space="preserve">12.5155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.932765007019</t>
+    <t xml:space="preserve">12.9327659606934</t>
   </si>
   <si>
     <t xml:space="preserve">13.1830778121948</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">13.4333868026733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499507904053</t>
+    <t xml:space="preserve">13.3499517440796</t>
   </si>
   <si>
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7658910751343</t>
+    <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
     <t xml:space="preserve">14.7683849334717</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518209457397</t>
+    <t xml:space="preserve">14.8518190383911</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346351623535</t>
+    <t xml:space="preserve">14.4346332550049</t>
   </si>
   <si>
     <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352569580078</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186958312988</t>
+    <t xml:space="preserve">15.0186967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.684947013855</t>
+    <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015090942383</t>
+    <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
     <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174474716187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837015151978</t>
+    <t xml:space="preserve">13.6837005615234</t>
   </si>
   <si>
     <t xml:space="preserve">13.7671365737915</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931058883667</t>
+    <t xml:space="preserve">13.9931049346924</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903593063354</t>
+    <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
     <t xml:space="preserve">14.3282699584961</t>
@@ -944,31 +944,31 @@
     <t xml:space="preserve">14.9985971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472276687622</t>
+    <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148082733154</t>
+    <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
     <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175519943237</t>
+    <t xml:space="preserve">15.417552947998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499704360962</t>
+    <t xml:space="preserve">15.2499713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
     <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668927192688</t>
+    <t xml:space="preserve">15.6689291000366</t>
   </si>
   <si>
     <t xml:space="preserve">15.9203014373779</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794055938721</t>
+    <t xml:space="preserve">16.2794075012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.1923503875732</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441286087036</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664588928223</t>
+    <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405731201172</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8017406463623</t>
+    <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499614715576</t>
+    <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.585241317749</t>
+    <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299057006836</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557991027832</t>
+    <t xml:space="preserve">18.4557952880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886505126953</t>
+    <t xml:space="preserve">18.2886486053467</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359603881836</t>
+    <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9264984130859</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738101959229</t>
+    <t xml:space="preserve">17.4738082885742</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778938293457</t>
+    <t xml:space="preserve">16.4778919219971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.8441257476807</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873558044434</t>
+    <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
     <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535886764526</t>
+    <t xml:space="preserve">15.753589630127</t>
   </si>
   <si>
     <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955202102661</t>
+    <t xml:space="preserve">14.3955221176147</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580680847168</t>
+    <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239080429077</t>
+    <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996057510376</t>
+    <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
     <t xml:space="preserve">13.4901428222656</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333700180054</t>
+    <t xml:space="preserve">14.0333690643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1278,6 +1278,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -63054,7 +63057,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63080,7 +63083,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63106,7 +63109,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63132,7 +63135,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63158,7 +63161,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63184,7 +63187,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63210,7 +63213,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63236,7 +63239,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63262,7 +63265,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63288,7 +63291,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63314,7 +63317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63366,7 +63369,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63392,7 +63395,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63418,7 +63421,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63444,7 +63447,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63470,7 +63473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63496,7 +63499,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63522,7 +63525,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63548,7 +63551,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63574,7 +63577,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63600,7 +63603,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63626,7 +63629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63652,7 +63655,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63678,7 +63681,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63704,7 +63707,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63730,7 +63733,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63756,7 +63759,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63782,7 +63785,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63808,7 +63811,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63834,7 +63837,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63860,7 +63863,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63886,7 +63889,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63912,7 +63915,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63938,7 +63941,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63964,7 +63967,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63990,7 +63993,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64016,7 +64019,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64042,7 +64045,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64068,7 +64071,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64094,7 +64097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64120,7 +64123,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64146,7 +64149,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64172,7 +64175,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64198,7 +64201,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64224,7 +64227,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64250,7 +64253,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64276,7 +64279,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64302,7 +64305,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64328,7 +64331,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64354,7 +64357,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64380,7 +64383,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64406,7 +64409,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64432,7 +64435,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64458,7 +64461,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64484,7 +64487,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64510,7 +64513,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64536,7 +64539,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64562,7 +64565,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64588,7 +64591,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64614,7 +64617,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64640,7 +64643,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64666,7 +64669,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64692,7 +64695,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64718,7 +64721,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64744,7 +64747,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64770,7 +64773,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64796,7 +64799,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64822,7 +64825,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64848,7 +64851,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64874,7 +64877,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64900,7 +64903,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64926,7 +64929,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64952,7 +64955,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64978,7 +64981,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65004,7 +65007,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65030,7 +65033,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65056,7 +65059,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65082,7 +65085,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65108,7 +65111,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65134,7 +65137,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65160,7 +65163,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65186,7 +65189,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65212,7 +65215,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65238,7 +65241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65264,7 +65267,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65290,7 +65293,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65316,7 +65319,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65342,7 +65345,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65368,7 +65371,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65394,7 +65397,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65420,7 +65423,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65446,7 +65449,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65472,7 +65475,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65498,7 +65501,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65524,7 +65527,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65550,7 +65553,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65576,7 +65579,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65602,7 +65605,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65628,7 +65631,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65654,7 +65657,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65680,7 +65683,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65706,7 +65709,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65732,7 +65735,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65758,7 +65761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65784,7 +65787,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65810,7 +65813,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65836,7 +65839,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65862,7 +65865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65888,7 +65891,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65914,7 +65917,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65940,7 +65943,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65966,7 +65969,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65992,7 +65995,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66018,7 +66021,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66044,7 +66047,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66070,7 +66073,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66096,7 +66099,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66122,7 +66125,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66148,7 +66151,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66174,7 +66177,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66200,7 +66203,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66226,7 +66229,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66252,7 +66255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66278,7 +66281,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66304,7 +66307,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66330,7 +66333,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66356,7 +66359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66382,7 +66385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66408,7 +66411,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66434,7 +66437,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66460,7 +66463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66486,7 +66489,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66512,7 +66515,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66538,7 +66541,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66564,7 +66567,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66590,7 +66593,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66616,7 +66619,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66642,7 +66645,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66668,7 +66671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66694,7 +66697,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66702,7 +66705,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6866087963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>10689</v>
@@ -66720,9 +66723,35 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6786574074</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>2464</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>438</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.219500541687</t>
+    <t xml:space="preserve">13.2194986343384</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499242782593</t>
+    <t xml:space="preserve">13.149923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8577003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237340927124</t>
+    <t xml:space="preserve">12.523736000061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8020401000977</t>
+    <t xml:space="preserve">12.802041053772</t>
   </si>
   <si>
     <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758518218994</t>
+    <t xml:space="preserve">12.1758546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279733657837</t>
+    <t xml:space="preserve">11.8279705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809110641479</t>
+    <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
     <t xml:space="preserve">10.5755987167358</t>
@@ -80,85 +80,85 @@
     <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885648727417</t>
+    <t xml:space="preserve">10.0885639190674</t>
   </si>
   <si>
     <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060224533081</t>
+    <t xml:space="preserve">10.5060234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364452362061</t>
+    <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451740264893</t>
+    <t xml:space="preserve">10.6451759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147493362427</t>
+    <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843265533447</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773685455322</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826847076416</t>
+    <t xml:space="preserve">11.3826837539673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549816131592</t>
+    <t xml:space="preserve">12.1549806594849</t>
   </si>
   <si>
     <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193696975708</t>
+    <t xml:space="preserve">12.4193716049194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628866195679</t>
+    <t xml:space="preserve">12.6628856658936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411935806274</t>
+    <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933113098145</t>
+    <t xml:space="preserve">12.5933122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150081634521</t>
+    <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506191253662</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583951950073</t>
+    <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227870941162</t>
+    <t xml:space="preserve">12.0227861404419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236061096191</t>
+    <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.984130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407110214233</t>
@@ -170,46 +170,46 @@
     <t xml:space="preserve">11.7670269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788726806641</t>
+    <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
     <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426864624023</t>
+    <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979520797729</t>
+    <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
     <t xml:space="preserve">11.6512384414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683452606201</t>
+    <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.832160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
     <t xml:space="preserve">12.0854473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578140258789</t>
+    <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.193998336792</t>
+    <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025531768799</t>
+    <t xml:space="preserve">12.3025503158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275526046753</t>
+    <t xml:space="preserve">12.0275545120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.295313835144</t>
@@ -218,121 +218,121 @@
     <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196552276611</t>
+    <t xml:space="preserve">12.5196561813354</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466257095337</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729425430298</t>
+    <t xml:space="preserve">12.7729444503784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755716323853</t>
+    <t xml:space="preserve">12.9755706787109</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091287612915</t>
+    <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.2433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157024383545</t>
+    <t xml:space="preserve">13.3157014846802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604396820068</t>
+    <t xml:space="preserve">13.4604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.388069152832</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
     <t xml:space="preserve">13.4025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242553710938</t>
+    <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328073501587</t>
+    <t xml:space="preserve">13.5328063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689888000488</t>
+    <t xml:space="preserve">13.5689907073975</t>
   </si>
   <si>
     <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.496621131897</t>
+    <t xml:space="preserve">13.4966201782227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518877029419</t>
+    <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459629058838</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071514129639</t>
+    <t xml:space="preserve">13.2071485519409</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288618087769</t>
+    <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
     <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985994338989</t>
+    <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104404449463</t>
+    <t xml:space="preserve">12.9104423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262308120728</t>
+    <t xml:space="preserve">13.0262298583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134783744812</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.845308303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275472640991</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439947128296</t>
+    <t xml:space="preserve">12.7439966201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189914703369</t>
+    <t xml:space="preserve">13.0189952850342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571550369263</t>
+    <t xml:space="preserve">12.657154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446565628052</t>
+    <t xml:space="preserve">12.2446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012357711792</t>
+    <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143932342529</t>
+    <t xml:space="preserve">12.1143941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709714889526</t>
+    <t xml:space="preserve">12.070972442627</t>
   </si>
   <si>
     <t xml:space="preserve">12.0492630004883</t>
@@ -341,40 +341,40 @@
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782117843628</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
     <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986066818237</t>
+    <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479475021362</t>
+    <t xml:space="preserve">11.9479465484619</t>
   </si>
   <si>
     <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551849365234</t>
+    <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696598052979</t>
+    <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768962860107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597904205322</t>
+    <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
     <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301826477051</t>
+    <t xml:space="preserve">12.2301836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229452133179</t>
+    <t xml:space="preserve">12.2229480743408</t>
   </si>
   <si>
     <t xml:space="preserve">12.1554155349731</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132905960083</t>
+    <t xml:space="preserve">12.1329069137573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880176544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129854202271</t>
+    <t xml:space="preserve">12.3129873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180326461792</t>
+    <t xml:space="preserve">12.4180335998535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756034851074</t>
+    <t xml:space="preserve">12.5756025314331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307151794434</t>
+    <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158418655396</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807844161987</t>
+    <t xml:space="preserve">12.980785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732799530029</t>
+    <t xml:space="preserve">12.9732789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881523132324</t>
+    <t xml:space="preserve">12.6881542205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.9657773971558</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682346343994</t>
+    <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845724105835</t>
+    <t xml:space="preserve">12.8457250595093</t>
   </si>
   <si>
     <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933322906494</t>
+    <t xml:space="preserve">13.0933332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809190750122</t>
+    <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">13.4309825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735464096069</t>
+    <t xml:space="preserve">13.5735483169556</t>
   </si>
   <si>
     <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358980178833</t>
+    <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
     <t xml:space="preserve">13.1383533477783</t>
@@ -467,43 +467,43 @@
     <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934669494629</t>
+    <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685010910034</t>
+    <t xml:space="preserve">13.4685029983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184328079224</t>
+    <t xml:space="preserve">13.318431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434005737305</t>
+    <t xml:space="preserve">13.2434024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683664321899</t>
+    <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060176849365</t>
+    <t xml:space="preserve">13.5060167312622</t>
   </si>
   <si>
     <t xml:space="preserve">13.6560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185693740845</t>
+    <t xml:space="preserve">13.6185684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061513900757</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810518264771</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687675476074</t>
+    <t xml:space="preserve">14.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6935997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485815048218</t>
+    <t xml:space="preserve">13.6485786437988</t>
   </si>
   <si>
     <t xml:space="preserve">13.4159784317017</t>
@@ -512,67 +512,67 @@
     <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312509536743</t>
+    <t xml:space="preserve">14.0312519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609975814819</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459924697876</t>
+    <t xml:space="preserve">13.4459896087646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986478805542</t>
+    <t xml:space="preserve">13.7986497879028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087413787842</t>
+    <t xml:space="preserve">14.0087394714355</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013715744019</t>
+    <t xml:space="preserve">14.3013725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165142059326</t>
+    <t xml:space="preserve">14.6165132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915454864502</t>
+    <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
     <t xml:space="preserve">14.9991836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.006688117981</t>
+    <t xml:space="preserve">15.0066862106323</t>
   </si>
   <si>
     <t xml:space="preserve">14.991681098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766721725464</t>
+    <t xml:space="preserve">14.976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691677093506</t>
+    <t xml:space="preserve">14.9691715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941354751587</t>
+    <t xml:space="preserve">14.8941373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390228271484</t>
+    <t xml:space="preserve">14.6390237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567525863647</t>
+    <t xml:space="preserve">15.1567516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606951713562</t>
+    <t xml:space="preserve">15.606954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568872451782</t>
+    <t xml:space="preserve">15.4568853378296</t>
   </si>
   <si>
-    <t xml:space="preserve">15.757022857666</t>
+    <t xml:space="preserve">15.7570209503174</t>
   </si>
   <si>
     <t xml:space="preserve">16.3572883605957</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576885223389</t>
+    <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076240539551</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575595855713</t>
+    <t xml:space="preserve">16.9575538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073509216309</t>
+    <t xml:space="preserve">16.5073528289795</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
@@ -602,31 +602,31 @@
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571556091309</t>
+    <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.052864074707</t>
+    <t xml:space="preserve">16.0528678894043</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723854064941</t>
+    <t xml:space="preserve">14.9723863601685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898036956787</t>
+    <t xml:space="preserve">15.5897998809814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354515075684</t>
+    <t xml:space="preserve">15.4354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441596984863</t>
+    <t xml:space="preserve">15.7441577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159320831299</t>
+    <t xml:space="preserve">16.5159301757812</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072238922119</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985137939453</t>
+    <t xml:space="preserve">15.8985118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267395019531</t>
+    <t xml:space="preserve">15.1267414093018</t>
   </si>
   <si>
     <t xml:space="preserve">15.0495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636791229248</t>
+    <t xml:space="preserve">14.6636772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810945510864</t>
+    <t xml:space="preserve">15.2810935974121</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549680709839</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">13.8919038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522106170654</t>
+    <t xml:space="preserve">14.2522144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319400787354</t>
+    <t xml:space="preserve">13.931939125061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7717990875244</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515256881714</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.611665725708</t>
+    <t xml:space="preserve">13.6116628646851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315942764282</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">14.0120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518686294556</t>
+    <t xml:space="preserve">13.8518705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113218307495</t>
+    <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.291389465332</t>
+    <t xml:space="preserve">13.2913885116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123525619507</t>
+    <t xml:space="preserve">14.4123506546021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714580535889</t>
   </si>
   <si>
     <t xml:space="preserve">13.1312532424927</t>
@@ -713,31 +713,31 @@
     <t xml:space="preserve">12.9711151123047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910446166992</t>
+    <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810977935791</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
     <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.650842666626</t>
+    <t xml:space="preserve">12.6508407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106359481812</t>
+    <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302225112915</t>
+    <t xml:space="preserve">11.9302234649658</t>
   </si>
   <si>
     <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707702636719</t>
+    <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.33056640625</t>
@@ -752,34 +752,34 @@
     <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896747589111</t>
+    <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
     <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099472045898</t>
+    <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298795700073</t>
+    <t xml:space="preserve">11.529878616333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.369743347168</t>
+    <t xml:space="preserve">11.3697423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.20960521698</t>
+    <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9694004058838</t>
+    <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491241455078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288497924805</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889879226685</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">10.0085773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687135696411</t>
+    <t xml:space="preserve">10.1687145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102910995483</t>
+    <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
     <t xml:space="preserve">12.8493280410767</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818313598633</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321413040161</t>
+    <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9327659606934</t>
+    <t xml:space="preserve">12.932765007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830778121948</t>
+    <t xml:space="preserve">13.1830768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4333868026733</t>
+    <t xml:space="preserve">13.4333877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499517440796</t>
+    <t xml:space="preserve">13.3499507904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.0162019729614</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518190383911</t>
+    <t xml:space="preserve">14.8518228530884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346332550049</t>
+    <t xml:space="preserve">14.4346351623535</t>
   </si>
   <si>
     <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352579116821</t>
+    <t xml:space="preserve">14.9352560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186967849731</t>
+    <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849460601807</t>
+    <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511962890625</t>
+    <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843242645264</t>
+    <t xml:space="preserve">14.1843214035034</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0174474716187</t>
+    <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837005615234</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
     <t xml:space="preserve">13.7671365737915</t>
@@ -899,16 +899,16 @@
     <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255233764648</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
     <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931049346924</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796432495117</t>
+    <t xml:space="preserve">14.579644203186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606864929199</t>
+    <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">14.3282699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634349822998</t>
+    <t xml:space="preserve">14.6634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958515167236</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985971450806</t>
+    <t xml:space="preserve">14.9985990524292</t>
   </si>
   <si>
     <t xml:space="preserve">14.7472257614136</t>
@@ -950,25 +950,25 @@
     <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661806106567</t>
+    <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
     <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.417552947998</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499713897705</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823888778687</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
     <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689291000366</t>
+    <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
     <t xml:space="preserve">15.9203014373779</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">16.004093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878810882568</t>
+    <t xml:space="preserve">16.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794075012207</t>
+    <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.1923503875732</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570705413818</t>
+    <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405731201172</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8017387390137</t>
+    <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5852394104004</t>
+    <t xml:space="preserve">17.585241317749</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299057006836</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557952880859</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886486053467</t>
+    <t xml:space="preserve">18.2886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359622955322</t>
+    <t xml:space="preserve">17.8359603881836</t>
   </si>
   <si>
     <t xml:space="preserve">17.9264984130859</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738082885742</t>
+    <t xml:space="preserve">17.4738101959229</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116580963135</t>
+    <t xml:space="preserve">17.1116561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305839538574</t>
+    <t xml:space="preserve">16.9305820465088</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778919219971</t>
+    <t xml:space="preserve">16.4778938293457</t>
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441257476807</t>
+    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873538970947</t>
+    <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.753589630127</t>
+    <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955221176147</t>
+    <t xml:space="preserve">14.3955202102661</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5806798934937</t>
+    <t xml:space="preserve">13.580680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239070892334</t>
+    <t xml:space="preserve">14.1239080429077</t>
   </si>
   <si>
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996047973633</t>
+    <t xml:space="preserve">13.3996057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090667724609</t>
+    <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
     <t xml:space="preserve">13.4901428222656</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333690643311</t>
+    <t xml:space="preserve">14.0333700180054</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456705093384</t>
+    <t xml:space="preserve">14.5456695556641</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967765808105</t>
+    <t xml:space="preserve">13.9967775344849</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.447883605957</t>
+    <t xml:space="preserve">13.4478826522827</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.081955909729</t>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716025352478</t>
+    <t xml:space="preserve">12.7160263061523</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330610275269</t>
+    <t xml:space="preserve">12.5330619812012</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1278,9 +1278,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -1341,6 +1338,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6999998092651</t>
   </si>
 </sst>
 </file>
@@ -63057,7 +63057,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63083,7 +63083,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63109,7 +63109,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63135,7 +63135,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63161,7 +63161,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63187,7 +63187,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63213,7 +63213,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63239,7 +63239,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63265,7 +63265,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63291,7 +63291,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63317,7 +63317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63369,7 +63369,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63395,7 +63395,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63421,7 +63421,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63447,7 +63447,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63473,7 +63473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63499,7 +63499,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63525,7 +63525,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63551,7 +63551,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63577,7 +63577,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63603,7 +63603,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63629,7 +63629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63655,7 +63655,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63681,7 +63681,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63707,7 +63707,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63733,7 +63733,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63759,7 +63759,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63785,7 +63785,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63811,7 +63811,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63837,7 +63837,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63863,7 +63863,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63889,7 +63889,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63915,7 +63915,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63941,7 +63941,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63967,7 +63967,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63993,7 +63993,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64019,7 +64019,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64045,7 +64045,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64071,7 +64071,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64097,7 +64097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64123,7 +64123,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64149,7 +64149,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64175,7 +64175,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64201,7 +64201,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64227,7 +64227,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64253,7 +64253,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64279,7 +64279,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64305,7 +64305,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64331,7 +64331,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64357,7 +64357,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64383,7 +64383,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64409,7 +64409,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64435,7 +64435,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64461,7 +64461,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64487,7 +64487,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64513,7 +64513,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64539,7 +64539,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64565,7 +64565,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64591,7 +64591,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64617,7 +64617,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64643,7 +64643,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64669,7 +64669,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64695,7 +64695,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64721,7 +64721,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64747,7 +64747,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64773,7 +64773,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64799,7 +64799,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64825,7 +64825,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64851,7 +64851,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64877,7 +64877,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64903,7 +64903,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64929,7 +64929,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64955,7 +64955,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64981,7 +64981,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65007,7 +65007,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65033,7 +65033,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65059,7 +65059,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65085,7 +65085,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65111,7 +65111,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65137,7 +65137,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65163,7 +65163,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65189,7 +65189,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65215,7 +65215,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65241,7 +65241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65267,7 +65267,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65293,7 +65293,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65319,7 +65319,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65345,7 +65345,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65371,7 +65371,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65397,7 +65397,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65423,7 +65423,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65449,7 +65449,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65475,7 +65475,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65501,7 +65501,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65527,7 +65527,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65553,7 +65553,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65579,7 +65579,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65605,7 +65605,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65631,7 +65631,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65657,7 +65657,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65683,7 +65683,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65709,7 +65709,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65735,7 +65735,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65761,7 +65761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65787,7 +65787,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65813,7 +65813,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65839,7 +65839,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65865,7 +65865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65891,7 +65891,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65917,7 +65917,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65943,7 +65943,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65969,7 +65969,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65995,7 +65995,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66021,7 +66021,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66047,7 +66047,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66073,7 +66073,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66099,7 +66099,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66125,7 +66125,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66151,7 +66151,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66177,7 +66177,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66203,7 +66203,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66229,7 +66229,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66255,7 +66255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66281,7 +66281,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66307,7 +66307,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66333,7 +66333,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66359,7 +66359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66385,7 +66385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66411,7 +66411,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66437,7 +66437,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66463,7 +66463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66489,7 +66489,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66515,7 +66515,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66541,7 +66541,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66567,7 +66567,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66593,7 +66593,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66619,7 +66619,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66645,7 +66645,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66671,7 +66671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66697,7 +66697,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66723,7 +66723,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66731,7 +66731,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6786574074</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>2464</v>
@@ -66749,9 +66749,35 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6277199074</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,40 +44,40 @@
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149923324585</t>
+    <t xml:space="preserve">13.149920463562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577003479004</t>
+    <t xml:space="preserve">12.857702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716144561768</t>
+    <t xml:space="preserve">12.8716154098511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.523736000061</t>
+    <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.802041053772</t>
+    <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167770385742</t>
+    <t xml:space="preserve">12.5167798995972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758546829224</t>
+    <t xml:space="preserve">12.1758527755737</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809129714966</t>
+    <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755987167358</t>
+    <t xml:space="preserve">10.5755996704102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462326049805</t>
+    <t xml:space="preserve">9.91462421417236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280033111572</t>
   </si>
   <si>
     <t xml:space="preserve">10.0885639190674</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060234069824</t>
+    <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
     <t xml:space="preserve">10.4990644454956</t>
@@ -95,88 +95,88 @@
     <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451759338379</t>
+    <t xml:space="preserve">10.6451730728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826837539673</t>
+    <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331577301025</t>
+    <t xml:space="preserve">11.6331586837769</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480236053467</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193716049194</t>
+    <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628856658936</t>
+    <t xml:space="preserve">12.6628866195679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933094024658</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506162643433</t>
+    <t xml:space="preserve">12.0506181716919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114646911621</t>
+    <t xml:space="preserve">11.9114637374878</t>
   </si>
   <si>
     <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227861404419</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.984130859375</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407110214233</t>
+    <t xml:space="preserve">11.9407119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045276641846</t>
+    <t xml:space="preserve">11.9045257568359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670269012451</t>
+    <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065040588379</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788717269897</t>
+    <t xml:space="preserve">11.5788707733154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893991470337</t>
+    <t xml:space="preserve">11.2893981933594</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426874160767</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512384414673</t>
+    <t xml:space="preserve">11.6512393951416</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">11.832160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130786895752</t>
+    <t xml:space="preserve">12.0130796432495</t>
   </si>
   <si>
     <t xml:space="preserve">12.0854473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578149795532</t>
+    <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
     <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025503158569</t>
+    <t xml:space="preserve">12.3025493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275545120239</t>
+    <t xml:space="preserve">12.0275535583496</t>
   </si>
   <si>
     <t xml:space="preserve">12.295313835144</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196561813354</t>
+    <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643896102905</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">12.7729444503784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755706787109</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538612365723</t>
+    <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433338165283</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157014846802</t>
+    <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880701065063</t>
+    <t xml:space="preserve">13.388069152832</t>
   </si>
   <si>
     <t xml:space="preserve">13.4025440216064</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242544174194</t>
+    <t xml:space="preserve">13.4242563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.532808303833</t>
   </si>
   <si>
     <t xml:space="preserve">13.5689907073975</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966201782227</t>
+    <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518857955933</t>
+    <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459648132324</t>
+    <t xml:space="preserve">13.4459629058838</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387273788452</t>
@@ -284,40 +284,40 @@
     <t xml:space="preserve">13.2071485519409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038604736328</t>
+    <t xml:space="preserve">13.5038595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288599014282</t>
+    <t xml:space="preserve">13.2288618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814945220947</t>
+    <t xml:space="preserve">12.8814964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985984802246</t>
+    <t xml:space="preserve">13.098596572876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262298583984</t>
+    <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347827911377</t>
+    <t xml:space="preserve">13.1347818374634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845308303833</t>
+    <t xml:space="preserve">12.845311164856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275463104248</t>
+    <t xml:space="preserve">13.1275434494019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439966201782</t>
+    <t xml:space="preserve">12.7439975738525</t>
   </si>
   <si>
     <t xml:space="preserve">13.0189952850342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571531295776</t>
   </si>
   <si>
     <t xml:space="preserve">12.2446556091309</t>
@@ -326,22 +326,22 @@
     <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334735870361</t>
+    <t xml:space="preserve">11.9334754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143941879272</t>
+    <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492630004883</t>
+    <t xml:space="preserve">12.0492639541626</t>
   </si>
   <si>
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782108306885</t>
+    <t xml:space="preserve">12.0782089233398</t>
   </si>
   <si>
     <t xml:space="preserve">11.9913692474365</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479465484619</t>
+    <t xml:space="preserve">11.9479484558105</t>
   </si>
   <si>
     <t xml:space="preserve">12.172287940979</t>
@@ -362,64 +362,64 @@
     <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768962860107</t>
+    <t xml:space="preserve">11.9768943786621</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.150577545166</t>
+    <t xml:space="preserve">12.1505794525146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229480743408</t>
+    <t xml:space="preserve">12.2229471206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554155349731</t>
+    <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805160522461</t>
+    <t xml:space="preserve">12.3805170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329069137573</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880176544189</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428647994995</t>
+    <t xml:space="preserve">12.0428657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129873275757</t>
+    <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180335998535</t>
+    <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307161331177</t>
+    <t xml:space="preserve">12.8307151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158428192139</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.980785369873</t>
+    <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732789993286</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881542205811</t>
+    <t xml:space="preserve">12.6881523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657773971558</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
     <t xml:space="preserve">12.9432668685913</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457250595093</t>
+    <t xml:space="preserve">12.8457231521606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083402633667</t>
+    <t xml:space="preserve">13.1083393096924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933332443237</t>
+    <t xml:space="preserve">13.093334197998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559503555298</t>
+    <t xml:space="preserve">13.3559522628784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435342788696</t>
+    <t xml:space="preserve">13.5435352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.235897064209</t>
+    <t xml:space="preserve">13.2358961105347</t>
   </si>
   <si>
     <t xml:space="preserve">13.1383533477783</t>
@@ -464,37 +464,37 @@
     <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058849334717</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685029983521</t>
+    <t xml:space="preserve">13.4684991836548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.318431854248</t>
+    <t xml:space="preserve">13.318434715271</t>
   </si>
   <si>
     <t xml:space="preserve">13.2434024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683673858643</t>
+    <t xml:space="preserve">13.1683683395386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060167312622</t>
+    <t xml:space="preserve">13.5060176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185684204102</t>
+    <t xml:space="preserve">13.6185674667358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061504364014</t>
+    <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810508728027</t>
+    <t xml:space="preserve">13.5810489654541</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687685012817</t>
@@ -503,94 +503,94 @@
     <t xml:space="preserve">13.6935997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485786437988</t>
+    <t xml:space="preserve">13.6485795974731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4159784317017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562177658081</t>
+    <t xml:space="preserve">13.9562187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609956741333</t>
+    <t xml:space="preserve">13.4609966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459896087646</t>
+    <t xml:space="preserve">13.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986488342285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087394714355</t>
+    <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315183639526</t>
+    <t xml:space="preserve">14.6315174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013725280762</t>
+    <t xml:space="preserve">14.3013706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165132522583</t>
+    <t xml:space="preserve">14.616512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915445327759</t>
+    <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991836547852</t>
+    <t xml:space="preserve">14.9991817474365</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991681098938</t>
+    <t xml:space="preserve">14.9916801452637</t>
   </si>
   <si>
     <t xml:space="preserve">14.976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691715240479</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465272903442</t>
+    <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941373825073</t>
+    <t xml:space="preserve">14.8941383361816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390237808228</t>
+    <t xml:space="preserve">14.6390218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567506790161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606954574585</t>
+    <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568853378296</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570209503174</t>
+    <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572883605957</t>
+    <t xml:space="preserve">16.3572864532471</t>
   </si>
   <si>
     <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076221466064</t>
+    <t xml:space="preserve">17.1076240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575538635254</t>
+    <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
     <t xml:space="preserve">16.5073528289795</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528678894043</t>
+    <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702861785889</t>
+    <t xml:space="preserve">16.6702842712402</t>
   </si>
   <si>
     <t xml:space="preserve">14.9723863601685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5897998809814</t>
+    <t xml:space="preserve">15.5898027420044</t>
   </si>
   <si>
     <t xml:space="preserve">15.4354496002197</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">15.8985118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267414093018</t>
+    <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
     <t xml:space="preserve">15.0495615005493</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">14.6636772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810935974121</t>
+    <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549680709839</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
     <t xml:space="preserve">14.2522144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515266418457</t>
+    <t xml:space="preserve">13.45152759552</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116628646851</t>
+    <t xml:space="preserve">13.6116638183594</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315942764282</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2913885116577</t>
+    <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123506546021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920763015747</t>
+    <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312532424927</t>
+    <t xml:space="preserve">13.131254196167</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109769821167</t>
+    <t xml:space="preserve">12.8109788894653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309103012085</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907035827637</t>
+    <t xml:space="preserve">12.490701675415</t>
   </si>
   <si>
     <t xml:space="preserve">12.6508407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302234649658</t>
+    <t xml:space="preserve">11.9302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.690016746521</t>
   </si>
   <si>
     <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.33056640625</t>
+    <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
@@ -752,31 +752,31 @@
     <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896738052368</t>
+    <t xml:space="preserve">11.2896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498109817505</t>
+    <t xml:space="preserve">11.4498119354248</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.529878616333</t>
+    <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
     <t xml:space="preserve">11.3697423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096061706543</t>
+    <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
     <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494689941406</t>
+    <t xml:space="preserve">11.0494680404663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491241455078</t>
+    <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
     <t xml:space="preserve">10.3288507461548</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">10.4889879226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089202880859</t>
+    <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487812042236</t>
   </si>
   <si>
     <t xml:space="preserve">10.0085773468018</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">10.1687145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700853347778</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102920532227</t>
+    <t xml:space="preserve">12.010293006897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493280410767</t>
+    <t xml:space="preserve">12.8493270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990171432495</t>
+    <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
     <t xml:space="preserve">12.348705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137100219727</t>
+    <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
     <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315176010132</t>
+    <t xml:space="preserve">11.9315185546875</t>
   </si>
   <si>
     <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321422576904</t>
+    <t xml:space="preserve">12.4321413040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155801773071</t>
+    <t xml:space="preserve">12.5155792236328</t>
   </si>
   <si>
     <t xml:space="preserve">12.932765007019</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">13.4333877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499507904053</t>
+    <t xml:space="preserve">13.3499517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162019729614</t>
+    <t xml:space="preserve">13.0162010192871</t>
   </si>
   <si>
     <t xml:space="preserve">12.76589012146</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">14.7683849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180721282959</t>
+    <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518228530884</t>
+    <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
     <t xml:space="preserve">14.4346351623535</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186958312988</t>
+    <t xml:space="preserve">15.0186948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.684947013855</t>
+    <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511972427368</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843214035034</t>
+    <t xml:space="preserve">14.1843233108521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174493789673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837015151978</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002626419067</t>
+    <t xml:space="preserve">13.6002616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677593231201</t>
+    <t xml:space="preserve">14.2677602767944</t>
   </si>
   <si>
     <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255243301392</t>
+    <t xml:space="preserve">13.8255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.244478225708</t>
+    <t xml:space="preserve">14.2444791793823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.993106842041</t>
+    <t xml:space="preserve">13.9931058883667</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.657940864563</t>
+    <t xml:space="preserve">13.6579418182373</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903602600098</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">14.3282699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634330749512</t>
+    <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148073196411</t>
+    <t xml:space="preserve">14.9148063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
     <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175519943237</t>
+    <t xml:space="preserve">15.417552947998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499723434448</t>
+    <t xml:space="preserve">15.2499742507935</t>
   </si>
   <si>
     <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668927192688</t>
+    <t xml:space="preserve">15.6689291000366</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9203014373779</t>
+    <t xml:space="preserve">15.920298576355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.018238067627</t>
+    <t xml:space="preserve">16.0182361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311819076538</t>
+    <t xml:space="preserve">15.9311828613281</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441286087036</t>
+    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829591751099</t>
+    <t xml:space="preserve">15.5829610824585</t>
   </si>
   <si>
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664588928223</t>
+    <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405731201172</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146835327148</t>
+    <t xml:space="preserve">16.7146854400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499614715576</t>
+    <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758491516113</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">18.6299057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.107572555542</t>
+    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557991027832</t>
+    <t xml:space="preserve">18.4557971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.759349822998</t>
+    <t xml:space="preserve">17.7593517303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9334621429443</t>
+    <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111289978027</t>
+    <t xml:space="preserve">17.4111270904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.4697246551514</t>
@@ -1070,10 +1070,7 @@
     <t xml:space="preserve">18.2886505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1075744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8359603881836</t>
+    <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9264984130859</t>
@@ -1085,7 +1082,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738101959229</t>
+    <t xml:space="preserve">17.4738082885742</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1109,19 +1106,19 @@
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778938293457</t>
+    <t xml:space="preserve">16.4778919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157398223877</t>
+    <t xml:space="preserve">16.1157417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.8441257476807</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.20627784729</t>
+    <t xml:space="preserve">16.2062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1133,28 +1130,28 @@
     <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589679718018</t>
+    <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630506515503</t>
+    <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535886764526</t>
+    <t xml:space="preserve">15.7535905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819765090942</t>
+    <t xml:space="preserve">15.4819755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955202102661</t>
+    <t xml:space="preserve">14.3955211639404</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580680847168</t>
+    <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
     <t xml:space="preserve">14.1239080429077</t>
@@ -1163,7 +1160,7 @@
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996057510376</t>
+    <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090658187866</t>
@@ -1175,7 +1172,7 @@
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333700180054</t>
+    <t xml:space="preserve">14.0333690643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -43609,7 +43606,7 @@
         <v>20</v>
       </c>
       <c r="G1613" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43635,7 +43632,7 @@
         <v>20</v>
       </c>
       <c r="G1614" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43687,7 +43684,7 @@
         <v>20</v>
       </c>
       <c r="G1616" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43713,7 +43710,7 @@
         <v>20</v>
       </c>
       <c r="G1617" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43739,7 +43736,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43765,7 +43762,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1619" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43791,7 +43788,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1620" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43817,7 +43814,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1621" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43843,7 +43840,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43869,7 +43866,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43895,7 +43892,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43921,7 +43918,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43947,7 +43944,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43973,7 +43970,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43999,7 +43996,7 @@
         <v>20</v>
       </c>
       <c r="G1628" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44025,7 +44022,7 @@
         <v>20</v>
       </c>
       <c r="G1629" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44051,7 +44048,7 @@
         <v>20</v>
       </c>
       <c r="G1630" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44077,7 +44074,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1631" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44103,7 +44100,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44129,7 +44126,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1633" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44155,7 +44152,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1634" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44181,7 +44178,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44207,7 +44204,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44233,7 +44230,7 @@
         <v>19.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44259,7 +44256,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44285,7 +44282,7 @@
         <v>19.5</v>
       </c>
       <c r="G1639" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44311,7 +44308,7 @@
         <v>19</v>
       </c>
       <c r="G1640" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44337,7 +44334,7 @@
         <v>19</v>
       </c>
       <c r="G1641" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44363,7 +44360,7 @@
         <v>19</v>
       </c>
       <c r="G1642" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44389,7 +44386,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44415,7 +44412,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44441,7 +44438,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1645" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44467,7 +44464,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1646" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44493,7 +44490,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1647" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44519,7 +44516,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1648" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44545,7 +44542,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44571,7 +44568,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44597,7 +44594,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44623,7 +44620,7 @@
         <v>19</v>
       </c>
       <c r="G1652" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44649,7 +44646,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44675,7 +44672,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1654" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44701,7 +44698,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44727,7 +44724,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44753,7 +44750,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44779,7 +44776,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44805,7 +44802,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44831,7 +44828,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44857,7 +44854,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44883,7 +44880,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44909,7 +44906,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44935,7 +44932,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44961,7 +44958,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44987,7 +44984,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45013,7 +45010,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45039,7 +45036,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45065,7 +45062,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45091,7 +45088,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45117,7 +45114,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45143,7 +45140,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45169,7 +45166,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45195,7 +45192,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45221,7 +45218,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45247,7 +45244,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45273,7 +45270,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45299,7 +45296,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45325,7 +45322,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45351,7 +45348,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45377,7 +45374,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45403,7 +45400,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45429,7 +45426,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45455,7 +45452,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45481,7 +45478,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1685" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45507,7 +45504,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45533,7 +45530,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45559,7 +45556,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1688" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45585,7 +45582,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1689" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45611,7 +45608,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45637,7 +45634,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1691" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45663,7 +45660,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1692" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45689,7 +45686,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1693" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45715,7 +45712,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45741,7 +45738,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1695" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45767,7 +45764,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45793,7 +45790,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1697" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45819,7 +45816,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45845,7 +45842,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45871,7 +45868,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45897,7 +45894,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1701" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45923,7 +45920,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45949,7 +45946,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45975,7 +45972,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46001,7 +45998,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46027,7 +46024,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46053,7 +46050,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46079,7 +46076,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46105,7 +46102,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46131,7 +46128,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46157,7 +46154,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46183,7 +46180,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46209,7 +46206,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46235,7 +46232,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46261,7 +46258,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46287,7 +46284,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1716" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46313,7 +46310,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46339,7 +46336,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46365,7 +46362,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46391,7 +46388,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46417,7 +46414,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1721" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46443,7 +46440,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46469,7 +46466,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46495,7 +46492,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46521,7 +46518,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1725" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46547,7 +46544,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46573,7 +46570,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46599,7 +46596,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46625,7 +46622,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46651,7 +46648,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46677,7 +46674,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46703,7 +46700,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46729,7 +46726,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46755,7 +46752,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46781,7 +46778,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46807,7 +46804,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46833,7 +46830,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46859,7 +46856,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46885,7 +46882,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46911,7 +46908,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46937,7 +46934,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46963,7 +46960,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46989,7 +46986,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47015,7 +47012,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47041,7 +47038,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47067,7 +47064,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47093,7 +47090,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1747" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47119,7 +47116,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47145,7 +47142,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47171,7 +47168,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47197,7 +47194,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47223,7 +47220,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47249,7 +47246,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47275,7 +47272,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47301,7 +47298,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47327,7 +47324,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47353,7 +47350,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47379,7 +47376,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47405,7 +47402,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47431,7 +47428,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1760" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47457,7 +47454,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47483,7 +47480,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1762" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47509,7 +47506,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47535,7 +47532,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47561,7 +47558,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47587,7 +47584,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47613,7 +47610,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47639,7 +47636,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47665,7 +47662,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47691,7 +47688,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47717,7 +47714,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47743,7 +47740,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1772" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47769,7 +47766,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47795,7 +47792,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47821,7 +47818,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47847,7 +47844,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47873,7 +47870,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47899,7 +47896,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47925,7 +47922,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47951,7 +47948,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47977,7 +47974,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48003,7 +48000,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48029,7 +48026,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48055,7 +48052,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48081,7 +48078,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48107,7 +48104,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48133,7 +48130,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48159,7 +48156,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48185,7 +48182,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48211,7 +48208,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48237,7 +48234,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48263,7 +48260,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48289,7 +48286,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48315,7 +48312,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48341,7 +48338,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48367,7 +48364,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48393,7 +48390,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1797" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48419,7 +48416,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48445,7 +48442,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1799" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48471,7 +48468,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48497,7 +48494,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1801" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48523,7 +48520,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48549,7 +48546,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48575,7 +48572,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48601,7 +48598,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48627,7 +48624,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48653,7 +48650,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48679,7 +48676,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48705,7 +48702,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48731,7 +48728,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48757,7 +48754,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48783,7 +48780,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48809,7 +48806,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48835,7 +48832,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48861,7 +48858,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48887,7 +48884,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48913,7 +48910,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48939,7 +48936,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48965,7 +48962,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48991,7 +48988,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49017,7 +49014,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49043,7 +49040,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49069,7 +49066,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49095,7 +49092,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49121,7 +49118,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49147,7 +49144,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49173,7 +49170,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49199,7 +49196,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49225,7 +49222,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49251,7 +49248,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49277,7 +49274,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49303,7 +49300,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49329,7 +49326,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49355,7 +49352,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49381,7 +49378,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49407,7 +49404,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49433,7 +49430,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49459,7 +49456,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49485,7 +49482,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49511,7 +49508,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49537,7 +49534,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49563,7 +49560,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49589,7 +49586,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49615,7 +49612,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49641,7 +49638,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49667,7 +49664,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49693,7 +49690,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49719,7 +49716,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49745,7 +49742,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49771,7 +49768,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49797,7 +49794,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49823,7 +49820,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49849,7 +49846,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49875,7 +49872,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49901,7 +49898,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49927,7 +49924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49953,7 +49950,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49979,7 +49976,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50005,7 +50002,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50031,7 +50028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50057,7 +50054,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50083,7 +50080,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50109,7 +50106,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50135,7 +50132,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50161,7 +50158,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50187,7 +50184,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50213,7 +50210,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50239,7 +50236,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50265,7 +50262,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50291,7 +50288,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50317,7 +50314,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50343,7 +50340,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50369,7 +50366,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50395,7 +50392,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50421,7 +50418,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50447,7 +50444,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50473,7 +50470,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50499,7 +50496,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50525,7 +50522,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50551,7 +50548,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50577,7 +50574,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50603,7 +50600,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50629,7 +50626,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50655,7 +50652,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50681,7 +50678,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50707,7 +50704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50733,7 +50730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50759,7 +50756,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50785,7 +50782,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50811,7 +50808,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50837,7 +50834,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50863,7 +50860,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50889,7 +50886,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50915,7 +50912,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50941,7 +50938,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50967,7 +50964,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50993,7 +50990,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51019,7 +51016,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51045,7 +51042,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51071,7 +51068,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51097,7 +51094,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51123,7 +51120,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51149,7 +51146,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51175,7 +51172,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51201,7 +51198,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51227,7 +51224,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51253,7 +51250,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51279,7 +51276,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51305,7 +51302,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51331,7 +51328,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51357,7 +51354,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51383,7 +51380,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51409,7 +51406,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51435,7 +51432,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51461,7 +51458,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51487,7 +51484,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51513,7 +51510,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51539,7 +51536,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51565,7 +51562,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51591,7 +51588,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51617,7 +51614,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51643,7 +51640,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51669,7 +51666,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51695,7 +51692,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51721,7 +51718,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51747,7 +51744,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51773,7 +51770,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51799,7 +51796,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51825,7 +51822,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51851,7 +51848,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51877,7 +51874,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51903,7 +51900,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51929,7 +51926,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51955,7 +51952,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51981,7 +51978,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52007,7 +52004,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52033,7 +52030,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52059,7 +52056,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52085,7 +52082,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52111,7 +52108,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52137,7 +52134,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52163,7 +52160,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52189,7 +52186,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52215,7 +52212,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52241,7 +52238,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52267,7 +52264,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52293,7 +52290,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52319,7 +52316,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52345,7 +52342,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52371,7 +52368,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52397,7 +52394,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52423,7 +52420,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52449,7 +52446,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52475,7 +52472,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52501,7 +52498,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52527,7 +52524,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52553,7 +52550,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52579,7 +52576,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52605,7 +52602,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52631,7 +52628,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52657,7 +52654,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52683,7 +52680,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52709,7 +52706,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52735,7 +52732,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52761,7 +52758,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52787,7 +52784,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52813,7 +52810,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52839,7 +52836,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52865,7 +52862,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52891,7 +52888,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52917,7 +52914,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52943,7 +52940,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52969,7 +52966,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -52995,7 +52992,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53021,7 +53018,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53047,7 +53044,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53073,7 +53070,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53099,7 +53096,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53125,7 +53122,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53151,7 +53148,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53177,7 +53174,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53203,7 +53200,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53229,7 +53226,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53255,7 +53252,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53281,7 +53278,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53307,7 +53304,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53333,7 +53330,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53359,7 +53356,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53385,7 +53382,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53411,7 +53408,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53437,7 +53434,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53463,7 +53460,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53489,7 +53486,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53515,7 +53512,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53541,7 +53538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53567,7 +53564,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53593,7 +53590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53619,7 +53616,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53645,7 +53642,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53671,7 +53668,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53697,7 +53694,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53723,7 +53720,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53749,7 +53746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53775,7 +53772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53801,7 +53798,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53827,7 +53824,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53853,7 +53850,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53879,7 +53876,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53905,7 +53902,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53931,7 +53928,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53957,7 +53954,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53983,7 +53980,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54009,7 +54006,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54035,7 +54032,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54061,7 +54058,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54087,7 +54084,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54113,7 +54110,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54139,7 +54136,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54165,7 +54162,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54191,7 +54188,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54217,7 +54214,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54243,7 +54240,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54269,7 +54266,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54295,7 +54292,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54321,7 +54318,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54347,7 +54344,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54373,7 +54370,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54399,7 +54396,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54425,7 +54422,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54451,7 +54448,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54477,7 +54474,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54503,7 +54500,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54529,7 +54526,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54555,7 +54552,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54581,7 +54578,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54607,7 +54604,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54633,7 +54630,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54659,7 +54656,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54685,7 +54682,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54711,7 +54708,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54737,7 +54734,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54763,7 +54760,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54789,7 +54786,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54815,7 +54812,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54841,7 +54838,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54867,7 +54864,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54893,7 +54890,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54919,7 +54916,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54945,7 +54942,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54971,7 +54968,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -54997,7 +54994,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55023,7 +55020,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55049,7 +55046,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55075,7 +55072,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55101,7 +55098,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55127,7 +55124,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55153,7 +55150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55179,7 +55176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55205,7 +55202,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55231,7 +55228,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55257,7 +55254,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55283,7 +55280,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55309,7 +55306,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55335,7 +55332,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55361,7 +55358,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55387,7 +55384,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55413,7 +55410,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55439,7 +55436,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55465,7 +55462,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55491,7 +55488,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55517,7 +55514,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55543,7 +55540,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55569,7 +55566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55595,7 +55592,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55621,7 +55618,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55647,7 +55644,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55673,7 +55670,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55699,7 +55696,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55725,7 +55722,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55751,7 +55748,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55777,7 +55774,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55803,7 +55800,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55829,7 +55826,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55855,7 +55852,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55881,7 +55878,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55907,7 +55904,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55933,7 +55930,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55959,7 +55956,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55985,7 +55982,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56011,7 +56008,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56037,7 +56034,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56063,7 +56060,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56089,7 +56086,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56115,7 +56112,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56141,7 +56138,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56167,7 +56164,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56193,7 +56190,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56219,7 +56216,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56245,7 +56242,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56271,7 +56268,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56297,7 +56294,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56323,7 +56320,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56349,7 +56346,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56375,7 +56372,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56401,7 +56398,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56427,7 +56424,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56453,7 +56450,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56479,7 +56476,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56505,7 +56502,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56531,7 +56528,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56557,7 +56554,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56583,7 +56580,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56609,7 +56606,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56635,7 +56632,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56661,7 +56658,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56687,7 +56684,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56713,7 +56710,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56739,7 +56736,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56765,7 +56762,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56791,7 +56788,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56817,7 +56814,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56843,7 +56840,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56869,7 +56866,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56895,7 +56892,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56921,7 +56918,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56947,7 +56944,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56973,7 +56970,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -56999,7 +56996,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57025,7 +57022,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57051,7 +57048,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57077,7 +57074,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57103,7 +57100,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57129,7 +57126,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57155,7 +57152,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57181,7 +57178,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57207,7 +57204,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57233,7 +57230,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57259,7 +57256,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57285,7 +57282,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57311,7 +57308,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57337,7 +57334,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57363,7 +57360,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57389,7 +57386,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57415,7 +57412,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57441,7 +57438,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57467,7 +57464,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57493,7 +57490,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57519,7 +57516,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57545,7 +57542,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57571,7 +57568,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57597,7 +57594,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57623,7 +57620,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57649,7 +57646,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57675,7 +57672,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57701,7 +57698,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57727,7 +57724,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57753,7 +57750,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57779,7 +57776,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57805,7 +57802,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57831,7 +57828,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57857,7 +57854,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57883,7 +57880,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57909,7 +57906,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57935,7 +57932,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57961,7 +57958,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57987,7 +57984,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58013,7 +58010,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58039,7 +58036,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58065,7 +58062,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58091,7 +58088,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58117,7 +58114,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58143,7 +58140,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58169,7 +58166,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58195,7 +58192,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58221,7 +58218,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58247,7 +58244,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58273,7 +58270,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58299,7 +58296,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58325,7 +58322,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58351,7 +58348,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58377,7 +58374,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58403,7 +58400,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58429,7 +58426,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58455,7 +58452,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58481,7 +58478,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58507,7 +58504,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58533,7 +58530,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58559,7 +58556,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58585,7 +58582,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58611,7 +58608,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58637,7 +58634,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58663,7 +58660,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58689,7 +58686,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58715,7 +58712,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58741,7 +58738,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58767,7 +58764,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58793,7 +58790,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58819,7 +58816,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58845,7 +58842,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58871,7 +58868,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58897,7 +58894,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58923,7 +58920,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58949,7 +58946,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58975,7 +58972,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59001,7 +58998,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59027,7 +59024,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59053,7 +59050,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59079,7 +59076,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59105,7 +59102,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59131,7 +59128,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59157,7 +59154,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59183,7 +59180,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59209,7 +59206,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59235,7 +59232,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59261,7 +59258,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59287,7 +59284,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59313,7 +59310,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59339,7 +59336,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59365,7 +59362,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59391,7 +59388,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59417,7 +59414,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59443,7 +59440,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59469,7 +59466,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59495,7 +59492,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59521,7 +59518,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59547,7 +59544,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59573,7 +59570,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59599,7 +59596,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59625,7 +59622,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59651,7 +59648,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59677,7 +59674,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59703,7 +59700,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59729,7 +59726,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59755,7 +59752,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59781,7 +59778,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59807,7 +59804,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59833,7 +59830,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59859,7 +59856,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59885,7 +59882,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59911,7 +59908,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59937,7 +59934,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59963,7 +59960,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59989,7 +59986,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60015,7 +60012,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60041,7 +60038,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60067,7 +60064,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60093,7 +60090,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60119,7 +60116,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60145,7 +60142,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60171,7 +60168,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60197,7 +60194,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60223,7 +60220,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60249,7 +60246,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60275,7 +60272,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60301,7 +60298,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60327,7 +60324,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60353,7 +60350,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60379,7 +60376,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60405,7 +60402,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60431,7 +60428,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60457,7 +60454,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60483,7 +60480,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60509,7 +60506,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60535,7 +60532,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60561,7 +60558,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60587,7 +60584,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60613,7 +60610,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60639,7 +60636,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60665,7 +60662,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60691,7 +60688,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60717,7 +60714,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60743,7 +60740,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60769,7 +60766,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60795,7 +60792,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60821,7 +60818,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60847,7 +60844,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60873,7 +60870,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60899,7 +60896,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60925,7 +60922,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60951,7 +60948,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60977,7 +60974,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61003,7 +61000,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61029,7 +61026,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61055,7 +61052,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61081,7 +61078,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61107,7 +61104,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61133,7 +61130,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61159,7 +61156,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61185,7 +61182,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61211,7 +61208,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61237,7 +61234,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61263,7 +61260,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61289,7 +61286,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61315,7 +61312,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61341,7 +61338,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61367,7 +61364,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61393,7 +61390,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61419,7 +61416,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61445,7 +61442,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61471,7 +61468,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61497,7 +61494,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61523,7 +61520,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61549,7 +61546,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61575,7 +61572,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61601,7 +61598,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61627,7 +61624,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61653,7 +61650,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61679,7 +61676,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61705,7 +61702,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61731,7 +61728,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61757,7 +61754,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61783,7 +61780,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61809,7 +61806,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61835,7 +61832,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61861,7 +61858,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61887,7 +61884,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61913,7 +61910,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61939,7 +61936,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61965,7 +61962,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -61991,7 +61988,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62017,7 +62014,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62043,7 +62040,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62069,7 +62066,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62095,7 +62092,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62121,7 +62118,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62147,7 +62144,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62173,7 +62170,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62199,7 +62196,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62225,7 +62222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62251,7 +62248,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62277,7 +62274,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62303,7 +62300,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62329,7 +62326,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62355,7 +62352,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62381,7 +62378,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62407,7 +62404,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62433,7 +62430,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62459,7 +62456,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62485,7 +62482,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62511,7 +62508,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62537,7 +62534,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62563,7 +62560,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62589,7 +62586,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62615,7 +62612,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62641,7 +62638,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62667,7 +62664,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62693,7 +62690,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62719,7 +62716,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62745,7 +62742,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62771,7 +62768,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62797,7 +62794,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62823,7 +62820,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62849,7 +62846,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62875,7 +62872,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62901,7 +62898,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62927,7 +62924,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62953,7 +62950,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62979,7 +62976,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63005,7 +63002,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63031,7 +63028,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63057,7 +63054,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63083,7 +63080,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63109,7 +63106,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63135,7 +63132,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63161,7 +63158,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63187,7 +63184,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63213,7 +63210,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63239,7 +63236,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63265,7 +63262,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63291,7 +63288,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63317,7 +63314,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63343,7 +63340,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63369,7 +63366,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63395,7 +63392,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63421,7 +63418,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63447,7 +63444,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63473,7 +63470,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63499,7 +63496,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63525,7 +63522,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63551,7 +63548,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63577,7 +63574,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63603,7 +63600,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63629,7 +63626,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63655,7 +63652,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63681,7 +63678,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63707,7 +63704,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63733,7 +63730,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63759,7 +63756,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63785,7 +63782,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63811,7 +63808,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63837,7 +63834,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63863,7 +63860,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63889,7 +63886,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63915,7 +63912,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63941,7 +63938,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63967,7 +63964,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63993,7 +63990,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64019,7 +64016,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64045,7 +64042,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64071,7 +64068,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64097,7 +64094,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64123,7 +64120,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64149,7 +64146,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64175,7 +64172,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64201,7 +64198,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64227,7 +64224,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64253,7 +64250,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64279,7 +64276,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64305,7 +64302,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64331,7 +64328,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64357,7 +64354,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64383,7 +64380,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64409,7 +64406,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64435,7 +64432,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64461,7 +64458,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64487,7 +64484,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64513,7 +64510,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64539,7 +64536,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64565,7 +64562,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64591,7 +64588,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64617,7 +64614,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64643,7 +64640,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64669,7 +64666,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64695,7 +64692,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64721,7 +64718,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64747,7 +64744,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64773,7 +64770,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64799,7 +64796,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64825,7 +64822,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64851,7 +64848,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64877,7 +64874,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64903,7 +64900,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64929,7 +64926,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64955,7 +64952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64981,7 +64978,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65007,7 +65004,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65033,7 +65030,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65059,7 +65056,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65085,7 +65082,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65111,7 +65108,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65137,7 +65134,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65163,7 +65160,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65189,7 +65186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65215,7 +65212,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65241,7 +65238,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65267,7 +65264,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65293,7 +65290,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65319,7 +65316,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65345,7 +65342,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65371,7 +65368,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65397,7 +65394,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65423,7 +65420,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65449,7 +65446,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65475,7 +65472,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65501,7 +65498,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65527,7 +65524,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65553,7 +65550,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65579,7 +65576,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65605,7 +65602,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65631,7 +65628,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65657,7 +65654,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65683,7 +65680,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65709,7 +65706,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65735,7 +65732,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65761,7 +65758,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65787,7 +65784,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65813,7 +65810,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65839,7 +65836,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65865,7 +65862,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65891,7 +65888,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65917,7 +65914,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65943,7 +65940,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65969,7 +65966,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65995,7 +65992,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66021,7 +66018,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66047,7 +66044,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66073,7 +66070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66099,7 +66096,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66125,7 +66122,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66151,7 +66148,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66177,7 +66174,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66203,7 +66200,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66229,7 +66226,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66255,7 +66252,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66281,7 +66278,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66307,7 +66304,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66333,7 +66330,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66359,7 +66356,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66385,7 +66382,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66411,7 +66408,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66437,7 +66434,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66463,7 +66460,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66489,7 +66486,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66515,7 +66512,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66541,7 +66538,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66567,7 +66564,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66593,7 +66590,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66619,7 +66616,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66645,7 +66642,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66671,7 +66668,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66697,7 +66694,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66723,7 +66720,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66749,7 +66746,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66757,7 +66754,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6277199074</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>1850</v>
@@ -66775,9 +66772,35 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2504" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.691087963</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>1334</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194976806641</t>
+    <t xml:space="preserve">13.2194986343384</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499214172363</t>
+    <t xml:space="preserve">13.1499223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8577003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237350463867</t>
+    <t xml:space="preserve">12.5237369537354</t>
   </si>
   <si>
     <t xml:space="preserve">12.802041053772</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">12.5167789459229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758527755737</t>
+    <t xml:space="preserve">12.1758518218994</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809139251709</t>
+    <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
     <t xml:space="preserve">10.5755987167358</t>
@@ -77,73 +77,73 @@
     <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280319213867</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.088565826416</t>
+    <t xml:space="preserve">10.0885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112077713013</t>
+    <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060253143311</t>
+    <t xml:space="preserve">10.5060234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364471435547</t>
+    <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">10.714750289917</t>
+    <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843284606934</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1322078704834</t>
+    <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826856613159</t>
+    <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331577301025</t>
+    <t xml:space="preserve">11.6331586837769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905906677246</t>
+    <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549816131592</t>
+    <t xml:space="preserve">12.1549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480236053467</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193706512451</t>
+    <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628894805908</t>
+    <t xml:space="preserve">12.6628875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411935806274</t>
+    <t xml:space="preserve">12.9411945343018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150091171265</t>
+    <t xml:space="preserve">12.3150081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506172180176</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114637374878</t>
+    <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
     <t xml:space="preserve">11.7583951950073</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.984130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163715362549</t>
+    <t xml:space="preserve">11.7163705825806</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045267105103</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670288085938</t>
+    <t xml:space="preserve">11.7670269012451</t>
   </si>
   <si>
     <t xml:space="preserve">11.5065040588379</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289400100708</t>
+    <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979520797729</t>
+    <t xml:space="preserve">11.3979530334473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683452606201</t>
+    <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
     <t xml:space="preserve">11.8321599960327</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.0854482650757</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939992904663</t>
+    <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
     <t xml:space="preserve">12.3025512695312</t>
@@ -221,49 +221,49 @@
     <t xml:space="preserve">12.5196561813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643905639648</t>
+    <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466257095337</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729434967041</t>
+    <t xml:space="preserve">12.7729444503784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755725860596</t>
+    <t xml:space="preserve">12.9755716323853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538602828979</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.243335723877</t>
+    <t xml:space="preserve">13.2433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157043457031</t>
+    <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604387283325</t>
+    <t xml:space="preserve">13.4604396820068</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880681991577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025449752808</t>
+    <t xml:space="preserve">13.4025430679321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.4531993865967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242544174194</t>
+    <t xml:space="preserve">13.4242553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328073501587</t>
+    <t xml:space="preserve">13.5328063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689907073975</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
     <t xml:space="preserve">13.5545177459717</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">13.4966220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518877029419</t>
+    <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459657669067</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387283325195</t>
+    <t xml:space="preserve">13.4387292861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071514129639</t>
+    <t xml:space="preserve">13.2071504592896</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288618087769</t>
+    <t xml:space="preserve">13.2288608551025</t>
   </si>
   <si>
     <t xml:space="preserve">12.881495475769</t>
@@ -296,52 +296,52 @@
     <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104433059692</t>
   </si>
   <si>
     <t xml:space="preserve">13.0262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134783744812</t>
+    <t xml:space="preserve">13.1347818374634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845311164856</t>
+    <t xml:space="preserve">12.8453102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275463104248</t>
+    <t xml:space="preserve">13.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439947128296</t>
+    <t xml:space="preserve">12.7439975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189933776855</t>
+    <t xml:space="preserve">13.0189943313599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446565628052</t>
+    <t xml:space="preserve">12.2446584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012348175049</t>
+    <t xml:space="preserve">12.2012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143932342529</t>
+    <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709733963013</t>
+    <t xml:space="preserve">12.070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.049262046814</t>
+    <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466329574585</t>
+    <t xml:space="preserve">11.8466339111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782108306885</t>
+    <t xml:space="preserve">12.0782098770142</t>
   </si>
   <si>
     <t xml:space="preserve">11.9913692474365</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">11.998607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479475021362</t>
+    <t xml:space="preserve">11.9479484558105</t>
   </si>
   <si>
     <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551849365234</t>
+    <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696598052979</t>
+    <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768953323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
     <t xml:space="preserve">12.1505784988403</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229471206665</t>
+    <t xml:space="preserve">12.2229452133179</t>
   </si>
   <si>
     <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054838180542</t>
+    <t xml:space="preserve">12.3054847717285</t>
   </si>
   <si>
     <t xml:space="preserve">12.3805160522461</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">12.1329050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880195617676</t>
+    <t xml:space="preserve">12.3880186080933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428647994995</t>
+    <t xml:space="preserve">12.0428657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180307388306</t>
+    <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
     <t xml:space="preserve">12.830717086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158428192139</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807844161987</t>
+    <t xml:space="preserve">12.9807834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732809066772</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657764434814</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432668685913</t>
+    <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308507919312</t>
+    <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682346343994</t>
+    <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457221984863</t>
+    <t xml:space="preserve">12.8457231521606</t>
   </si>
   <si>
     <t xml:space="preserve">13.1083393096924</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">13.0933332443237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559522628784</t>
+    <t xml:space="preserve">13.3559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809181213379</t>
+    <t xml:space="preserve">13.2809190750122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309854507446</t>
+    <t xml:space="preserve">13.4309825897217</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735492706299</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358980178833</t>
+    <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383514404297</t>
+    <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058839797974</t>
+    <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934659957886</t>
@@ -476,61 +476,61 @@
     <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434024810791</t>
+    <t xml:space="preserve">13.2434015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683664321899</t>
+    <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060176849365</t>
+    <t xml:space="preserve">13.5060186386108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185684204102</t>
+    <t xml:space="preserve">13.6185655593872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.80615234375</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810508728027</t>
+    <t xml:space="preserve">13.5810499191284</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687694549561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936025619507</t>
+    <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485815048218</t>
+    <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
     <t xml:space="preserve">13.415979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562177658081</t>
+    <t xml:space="preserve">13.9562196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312528610229</t>
+    <t xml:space="preserve">14.0312509536743</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609975814819</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459915161133</t>
+    <t xml:space="preserve">13.445990562439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986488342285</t>
+    <t xml:space="preserve">13.7986497879028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087413787842</t>
+    <t xml:space="preserve">14.0087404251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631516456604</t>
+    <t xml:space="preserve">14.631519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013715744019</t>
+    <t xml:space="preserve">14.3013725280762</t>
   </si>
   <si>
     <t xml:space="preserve">14.616512298584</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991807937622</t>
+    <t xml:space="preserve">14.9991817474365</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066871643066</t>
@@ -548,61 +548,61 @@
     <t xml:space="preserve">14.991678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766750335693</t>
+    <t xml:space="preserve">14.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691696166992</t>
+    <t xml:space="preserve">14.9691705703735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
     <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390228271484</t>
+    <t xml:space="preserve">14.6390199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568872451782</t>
+    <t xml:space="preserve">15.4568891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570247650146</t>
+    <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
     <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574192047119</t>
+    <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576866149902</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076221466064</t>
+    <t xml:space="preserve">17.1076240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9575576782227</t>
+    <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073547363281</t>
+    <t xml:space="preserve">16.5073528289795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074893951416</t>
+    <t xml:space="preserve">16.8074913024902</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571556091309</t>
+    <t xml:space="preserve">16.0571517944336</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615760803223</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702861785889</t>
+    <t xml:space="preserve">16.6702842712402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723863601685</t>
+    <t xml:space="preserve">14.9723834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898027420044</t>
+    <t xml:space="preserve">15.589804649353</t>
   </si>
   <si>
     <t xml:space="preserve">15.4354486465454</t>
   </si>
   <si>
-    <t xml:space="preserve">15.744158744812</t>
+    <t xml:space="preserve">15.7441568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159320831299</t>
+    <t xml:space="preserve">16.5159282684326</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072238922119</t>
@@ -635,40 +635,40 @@
     <t xml:space="preserve">16.8246402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985118865967</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
     <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495624542236</t>
+    <t xml:space="preserve">15.0495634078979</t>
   </si>
   <si>
     <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810935974121</t>
+    <t xml:space="preserve">15.2810916900635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549661636353</t>
+    <t xml:space="preserve">14.3549690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321451187134</t>
+    <t xml:space="preserve">14.4321441650391</t>
   </si>
   <si>
     <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522144317627</t>
+    <t xml:space="preserve">14.2522134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319381713867</t>
+    <t xml:space="preserve">13.931939125061</t>
   </si>
   <si>
     <t xml:space="preserve">13.771800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515266418457</t>
+    <t xml:space="preserve">13.4515256881714</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -677,34 +677,34 @@
     <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116647720337</t>
+    <t xml:space="preserve">13.6116619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315942764282</t>
+    <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">14.0120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518714904785</t>
+    <t xml:space="preserve">13.8518695831299</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113199234009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2913885116577</t>
+    <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123506546021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312532424927</t>
+    <t xml:space="preserve">13.131254196167</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810977935791</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309093475342</t>
+    <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907026290894</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302234649658</t>
+    <t xml:space="preserve">11.9302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900157928467</t>
+    <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
     <t xml:space="preserve">12.5707712173462</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903615951538</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704301834106</t>
+    <t xml:space="preserve">12.1704292297363</t>
   </si>
   <si>
     <t xml:space="preserve">11.1295375823975</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099481582642</t>
+    <t xml:space="preserve">11.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">11.529878616333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.369743347168</t>
+    <t xml:space="preserve">11.3697423934937</t>
   </si>
   <si>
     <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9693994522095</t>
+    <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491241455078</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">10.3288516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889888763428</t>
+    <t xml:space="preserve">10.4889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089193344116</t>
+    <t xml:space="preserve">10.4089202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085763931274</t>
+    <t xml:space="preserve">10.0085773468018</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687145233154</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">12.8493280410767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990171432495</t>
+    <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.348705291748</t>
+    <t xml:space="preserve">12.3487062454224</t>
   </si>
   <si>
     <t xml:space="preserve">11.0137100219727</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">11.6812076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315195083618</t>
+    <t xml:space="preserve">11.9315185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818294525146</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321413040161</t>
@@ -845,25 +845,25 @@
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7658910751343</t>
+    <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683849334717</t>
+    <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180711746216</t>
+    <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
     <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346361160278</t>
+    <t xml:space="preserve">14.4346351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021308898926</t>
+    <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352588653564</t>
+    <t xml:space="preserve">14.9352560043335</t>
   </si>
   <si>
     <t xml:space="preserve">15.0186958312988</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.601508140564</t>
+    <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
     <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843214035034</t>
   </si>
   <si>
     <t xml:space="preserve">14.017448425293</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671356201172</t>
+    <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002626419067</t>
+    <t xml:space="preserve">13.6002635955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.2677602767944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741510391235</t>
+    <t xml:space="preserve">13.5741519927979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255233764648</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444801330566</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093141555786</t>
@@ -917,64 +917,64 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796432495117</t>
+    <t xml:space="preserve">14.579644203186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606874465942</t>
+    <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6579418182373</t>
+    <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282709121704</t>
+    <t xml:space="preserve">14.3282690048218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634359359741</t>
+    <t xml:space="preserve">14.6634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958515167236</t>
+    <t xml:space="preserve">14.4958534240723</t>
   </si>
   <si>
     <t xml:space="preserve">14.9985980987549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472248077393</t>
+    <t xml:space="preserve">14.7472267150879</t>
   </si>
   <si>
     <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661806106567</t>
+    <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
     <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175539016724</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499713897705</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823888778687</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
     <t xml:space="preserve">15.5851354598999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689291000366</t>
+    <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
     <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923484802246</t>
+    <t xml:space="preserve">16.1923503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1052951812744</t>
+    <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
     <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311828613281</t>
+    <t xml:space="preserve">15.9311809539795</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700162887573</t>
+    <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
     <t xml:space="preserve">15.8441276550293</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088506698608</t>
+    <t xml:space="preserve">15.4088487625122</t>
   </si>
   <si>
     <t xml:space="preserve">16.3664588928223</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146835327148</t>
+    <t xml:space="preserve">16.7146854400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.97585105896</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6299076080322</t>
+    <t xml:space="preserve">18.6299057006836</t>
   </si>
   <si>
     <t xml:space="preserve">18.107572555542</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557952880859</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886524200439</t>
+    <t xml:space="preserve">18.2886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">17.8359603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264965057373</t>
+    <t xml:space="preserve">17.9264984130859</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738082885742</t>
+    <t xml:space="preserve">17.4738101959229</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901418685913</t>
+    <t xml:space="preserve">13.4901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
@@ -1338,6 +1338,12 @@
   </si>
   <si>
     <t xml:space="preserve">11.6999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -66780,19 +66786,19 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6017939815</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>100</v>
+        <v>1334</v>
       </c>
       <c r="C2505" t="n">
-        <v>11.6999998092651</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="D2505" t="n">
         <v>11.6999998092651</v>
       </c>
       <c r="E2505" t="n">
-        <v>11.6999998092651</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="F2505" t="n">
         <v>11.6999998092651</v>
@@ -66801,6 +66807,84 @@
         <v>441</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.5782638889</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>10150</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>443</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194986343384</t>
+    <t xml:space="preserve">13.2194995880127</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499223709106</t>
+    <t xml:space="preserve">13.1499214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577003479004</t>
+    <t xml:space="preserve">12.8577032089233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716144561768</t>
+    <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237369537354</t>
+    <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.802041053772</t>
+    <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167789459229</t>
+    <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758518218994</t>
+    <t xml:space="preserve">12.1758527755737</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279724121094</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755987167358</t>
+    <t xml:space="preserve">10.5755977630615</t>
   </si>
   <si>
     <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280223846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.0885639190674</t>
@@ -86,25 +86,25 @@
     <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060234069824</t>
+    <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990644454956</t>
+    <t xml:space="preserve">10.4990653991699</t>
   </si>
   <si>
     <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451730728149</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147512435913</t>
+    <t xml:space="preserve">10.7147521972656</t>
   </si>
   <si>
     <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773694992065</t>
+    <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.132209777832</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480226516724</t>
+    <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
     <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628875732422</t>
+    <t xml:space="preserve">12.6628866195679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411945343018</t>
+    <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
     <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150081634521</t>
+    <t xml:space="preserve">12.3150053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506162643433</t>
+    <t xml:space="preserve">12.0506191253662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114646911621</t>
+    <t xml:space="preserve">11.9114618301392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583951950073</t>
+    <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227861404419</t>
@@ -155,49 +155,49 @@
     <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.984130859375</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407110214233</t>
+    <t xml:space="preserve">11.9407119750977</t>
   </si>
   <si>
     <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670269012451</t>
+    <t xml:space="preserve">11.7670288085938</t>
   </si>
   <si>
     <t xml:space="preserve">11.5065040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788717269897</t>
+    <t xml:space="preserve">11.5788726806641</t>
   </si>
   <si>
     <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426874160767</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979530334473</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512403488159</t>
+    <t xml:space="preserve">11.6512393951416</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.8321590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130786895752</t>
+    <t xml:space="preserve">12.0130796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854482650757</t>
+    <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578149795532</t>
@@ -212,106 +212,106 @@
     <t xml:space="preserve">12.0275526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
     <t xml:space="preserve">12.447286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196561813354</t>
+    <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.9466257095337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729444503784</t>
+    <t xml:space="preserve">12.7729425430298</t>
   </si>
   <si>
     <t xml:space="preserve">12.9755716323853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538602828979</t>
+    <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091278076172</t>
+    <t xml:space="preserve">12.8091259002686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433338165283</t>
+    <t xml:space="preserve">13.2433366775513</t>
   </si>
   <si>
     <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604396820068</t>
+    <t xml:space="preserve">13.4604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880681991577</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025430679321</t>
+    <t xml:space="preserve">13.4025421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4531993865967</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242553710938</t>
+    <t xml:space="preserve">13.4242534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.532808303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689897537231</t>
+    <t xml:space="preserve">13.5689907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5545177459717</t>
+    <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966220855713</t>
+    <t xml:space="preserve">13.496621131897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518867492676</t>
+    <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
     <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387292861938</t>
+    <t xml:space="preserve">13.4387283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071504592896</t>
+    <t xml:space="preserve">13.2071495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038595199585</t>
+    <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288608551025</t>
+    <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881495475769</t>
+    <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
     <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104433059692</t>
+    <t xml:space="preserve">12.9104413986206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262317657471</t>
+    <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.134783744812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.8453092575073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275444030762</t>
+    <t xml:space="preserve">13.1275453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439975738525</t>
+    <t xml:space="preserve">12.7439947128296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0189943313599</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">12.6571559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446584701538</t>
+    <t xml:space="preserve">12.2446575164795</t>
   </si>
   <si>
     <t xml:space="preserve">12.2012367248535</t>
@@ -332,64 +332,64 @@
     <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.070972442627</t>
+    <t xml:space="preserve">12.0709743499756</t>
   </si>
   <si>
     <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466339111328</t>
+    <t xml:space="preserve">11.8466320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782098770142</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
     <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.998607635498</t>
+    <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479484558105</t>
+    <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.172287940979</t>
+    <t xml:space="preserve">12.1722898483276</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696588516235</t>
+    <t xml:space="preserve">11.9696598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768953323364</t>
+    <t xml:space="preserve">11.9768934249878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597904205322</t>
+    <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505784988403</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301826477051</t>
+    <t xml:space="preserve">12.2301836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229452133179</t>
+    <t xml:space="preserve">12.2229471206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554155349731</t>
+    <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054847717285</t>
+    <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
     <t xml:space="preserve">12.0428657531738</t>
@@ -401,55 +401,55 @@
     <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756034851074</t>
+    <t xml:space="preserve">12.5756025314331</t>
   </si>
   <si>
     <t xml:space="preserve">12.830717086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158418655396</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807834625244</t>
+    <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881532669067</t>
+    <t xml:space="preserve">12.6881542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657783508301</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.943265914917</t>
+    <t xml:space="preserve">12.9432668685913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308498382568</t>
+    <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682336807251</t>
+    <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457231521606</t>
+    <t xml:space="preserve">12.845721244812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083393096924</t>
+    <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933332443237</t>
+    <t xml:space="preserve">13.093334197998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559513092041</t>
+    <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809190750122</t>
+    <t xml:space="preserve">13.2809171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.4309844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735492706299</t>
+    <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
     <t xml:space="preserve">13.5435342788696</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
+    <t xml:space="preserve">13.1383543014526</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058849334717</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934659957886</t>
+    <t xml:space="preserve">13.3934669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4685010910034</t>
@@ -476,100 +476,100 @@
     <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434015274048</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683673858643</t>
+    <t xml:space="preserve">13.1683664321899</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060186386108</t>
+    <t xml:space="preserve">13.5060176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560850143433</t>
+    <t xml:space="preserve">13.6560831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185655593872</t>
+    <t xml:space="preserve">13.6185684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061504364014</t>
+    <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810499191284</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687694549561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936006546021</t>
+    <t xml:space="preserve">13.6935987472534</t>
   </si>
   <si>
     <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.415979385376</t>
+    <t xml:space="preserve">13.415976524353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562196731567</t>
+    <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312509536743</t>
+    <t xml:space="preserve">14.0312528610229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609956741333</t>
+    <t xml:space="preserve">13.4609975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.445990562439</t>
+    <t xml:space="preserve">13.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986507415771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087404251099</t>
+    <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631519317627</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013725280762</t>
+    <t xml:space="preserve">14.3013715744019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616512298584</t>
+    <t xml:space="preserve">14.6165132522583</t>
   </si>
   <si>
     <t xml:space="preserve">14.6915454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991817474365</t>
+    <t xml:space="preserve">14.9991846084595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066871643066</t>
+    <t xml:space="preserve">15.006688117981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991678237915</t>
+    <t xml:space="preserve">14.9916820526123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766731262207</t>
+    <t xml:space="preserve">14.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691705703735</t>
+    <t xml:space="preserve">14.9691686630249</t>
   </si>
   <si>
     <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941354751587</t>
+    <t xml:space="preserve">14.8941373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390199661255</t>
+    <t xml:space="preserve">14.6390237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567544937134</t>
+    <t xml:space="preserve">15.1567554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069526672363</t>
+    <t xml:space="preserve">15.6069536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568891525269</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
     <t xml:space="preserve">15.757022857666</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574211120605</t>
+    <t xml:space="preserve">16.6574230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576885223389</t>
+    <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076240539551</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.957555770874</t>
+    <t xml:space="preserve">16.9575576782227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073528289795</t>
+    <t xml:space="preserve">16.5073547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074913024902</t>
+    <t xml:space="preserve">16.807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571517944336</t>
+    <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615760803223</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702842712402</t>
+    <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723834991455</t>
+    <t xml:space="preserve">14.9723863601685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.589804649353</t>
+    <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354486465454</t>
+    <t xml:space="preserve">15.435450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441568374634</t>
+    <t xml:space="preserve">15.7441596984863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5159282684326</t>
@@ -632,43 +632,43 @@
     <t xml:space="preserve">16.2072238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8246402740479</t>
+    <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985137939453</t>
+    <t xml:space="preserve">15.898512840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267404556274</t>
+    <t xml:space="preserve">15.1267395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.049560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636762619019</t>
+    <t xml:space="preserve">14.6636781692505</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810916900635</t>
+    <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549690246582</t>
+    <t xml:space="preserve">14.3549680709839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321441650391</t>
+    <t xml:space="preserve">14.4321460723877</t>
   </si>
   <si>
     <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522134780884</t>
+    <t xml:space="preserve">14.2522115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.771800994873</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515256881714</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -677,34 +677,34 @@
     <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116619110107</t>
+    <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315952301025</t>
+    <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120048522949</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518695831299</t>
+    <t xml:space="preserve">13.8518686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113199234009</t>
+    <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123506546021</t>
+    <t xml:space="preserve">14.4123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920763015747</t>
+    <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714580535889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.131254196167</t>
+    <t xml:space="preserve">13.1312522888184</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
@@ -713,22 +713,22 @@
     <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109769821167</t>
+    <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
     <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106340408325</t>
+    <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
     <t xml:space="preserve">11.9302225112915</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
@@ -755,46 +755,46 @@
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498109817505</t>
+    <t xml:space="preserve">11.4498100280762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099491119385</t>
+    <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.529878616333</t>
+    <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096061706543</t>
+    <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
     <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494689941406</t>
+    <t xml:space="preserve">11.0494680404663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491241455078</t>
+    <t xml:space="preserve">10.6491260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288516998291</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889869689941</t>
+    <t xml:space="preserve">10.4889879226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089202880859</t>
+    <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
     <t xml:space="preserve">10.2487812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687145233154</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
     <t xml:space="preserve">11.7700862884521</t>
@@ -809,25 +809,25 @@
     <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3487062454224</t>
+    <t xml:space="preserve">12.348705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137100219727</t>
+    <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6812076568604</t>
+    <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315185546875</t>
+    <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
     <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321413040161</t>
+    <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155801773071</t>
+    <t xml:space="preserve">12.5155792236328</t>
   </si>
   <si>
     <t xml:space="preserve">12.932765007019</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683839797974</t>
+    <t xml:space="preserve">14.7683849334717</t>
   </si>
   <si>
     <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518218994141</t>
+    <t xml:space="preserve">14.8518190383911</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346351623535</t>
+    <t xml:space="preserve">14.4346332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021318435669</t>
+    <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352598190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.684947013855</t>
+    <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843214035034</t>
+    <t xml:space="preserve">14.1843233108521</t>
   </si>
   <si>
     <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837015151978</t>
+    <t xml:space="preserve">13.6837005615234</t>
   </si>
   <si>
     <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002635955811</t>
+    <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.2677602767944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741519927979</t>
+    <t xml:space="preserve">13.5741510391235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255243301392</t>
+    <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.244478225708</t>
+    <t xml:space="preserve">14.2444772720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
     <t xml:space="preserve">13.993106842041</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">14.579644203186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.657940864563</t>
+    <t xml:space="preserve">13.6579418182373</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282690048218</t>
+    <t xml:space="preserve">14.3282709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634330749512</t>
+    <t xml:space="preserve">14.6634359359741</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958534240723</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985980987549</t>
+    <t xml:space="preserve">14.9985971450806</t>
   </si>
   <si>
     <t xml:space="preserve">14.7472267150879</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337621688843</t>
+    <t xml:space="preserve">15.3337631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175519943237</t>
+    <t xml:space="preserve">15.4175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499723434448</t>
+    <t xml:space="preserve">15.2499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823879241943</t>
   </si>
   <si>
     <t xml:space="preserve">15.5851354598999</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9203014373779</t>
+    <t xml:space="preserve">15.9203033447266</t>
   </si>
   <si>
     <t xml:space="preserve">16.0040912628174</t>
@@ -989,49 +989,49 @@
     <t xml:space="preserve">16.1923503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1052932739258</t>
+    <t xml:space="preserve">16.1052951812744</t>
   </si>
   <si>
     <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311809539795</t>
+    <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700143814087</t>
+    <t xml:space="preserve">15.6700162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088487625122</t>
+    <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664588928223</t>
+    <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.627628326416</t>
+    <t xml:space="preserve">16.6276302337646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146854400635</t>
+    <t xml:space="preserve">16.7146816253662</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8017406463623</t>
+    <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499614715576</t>
+    <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
     <t xml:space="preserve">16.97585105896</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557991027832</t>
+    <t xml:space="preserve">18.4557952880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111270904541</t>
+    <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4697246551514</t>
+    <t xml:space="preserve">18.4697265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.2886505126953</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359603881836</t>
+    <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9264984130859</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738101959229</t>
+    <t xml:space="preserve">17.4738082885742</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">17.6548843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021961212158</t>
+    <t xml:space="preserve">17.2021942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2927341461182</t>
+    <t xml:space="preserve">17.2927322387695</t>
   </si>
   <si>
     <t xml:space="preserve">16.4778938293457</t>
@@ -1127,52 +1127,52 @@
     <t xml:space="preserve">15.9346656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8400440216064</t>
+    <t xml:space="preserve">16.8400421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589679718018</t>
+    <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873558044434</t>
+    <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630506515503</t>
+    <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
     <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819765090942</t>
+    <t xml:space="preserve">15.4819774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955202102661</t>
+    <t xml:space="preserve">14.3955211639404</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580680847168</t>
+    <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239080429077</t>
+    <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3049840927124</t>
+    <t xml:space="preserve">14.3049831390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996057510376</t>
+    <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901428222656</t>
+    <t xml:space="preserve">13.4901418685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333700180054</t>
+    <t xml:space="preserve">14.0333690643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1275,6 +1275,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -63060,7 +63063,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63086,7 +63089,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63112,7 +63115,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63138,7 +63141,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63164,7 +63167,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63190,7 +63193,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63216,7 +63219,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63242,7 +63245,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63268,7 +63271,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63294,7 +63297,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63320,7 +63323,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63372,7 +63375,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63398,7 +63401,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63424,7 +63427,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63450,7 +63453,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63476,7 +63479,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63502,7 +63505,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63528,7 +63531,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63554,7 +63557,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63580,7 +63583,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63606,7 +63609,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63632,7 +63635,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63658,7 +63661,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63684,7 +63687,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63710,7 +63713,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63736,7 +63739,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63762,7 +63765,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63788,7 +63791,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63814,7 +63817,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63840,7 +63843,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63866,7 +63869,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63892,7 +63895,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63918,7 +63921,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63944,7 +63947,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63970,7 +63973,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -63996,7 +63999,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64022,7 +64025,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64048,7 +64051,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64074,7 +64077,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64100,7 +64103,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64126,7 +64129,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64152,7 +64155,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64178,7 +64181,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64204,7 +64207,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64230,7 +64233,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64256,7 +64259,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64282,7 +64285,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64308,7 +64311,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64334,7 +64337,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64360,7 +64363,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64386,7 +64389,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64412,7 +64415,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64438,7 +64441,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64464,7 +64467,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64490,7 +64493,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64516,7 +64519,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64542,7 +64545,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64568,7 +64571,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64594,7 +64597,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64620,7 +64623,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64646,7 +64649,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64672,7 +64675,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64698,7 +64701,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64724,7 +64727,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64750,7 +64753,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64776,7 +64779,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64802,7 +64805,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64828,7 +64831,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64854,7 +64857,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64880,7 +64883,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64906,7 +64909,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64932,7 +64935,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64958,7 +64961,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64984,7 +64987,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65010,7 +65013,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65036,7 +65039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65062,7 +65065,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65088,7 +65091,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65114,7 +65117,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65140,7 +65143,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65166,7 +65169,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65192,7 +65195,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65218,7 +65221,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65244,7 +65247,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65270,7 +65273,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65296,7 +65299,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65322,7 +65325,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65348,7 +65351,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65374,7 +65377,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65400,7 +65403,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65426,7 +65429,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65452,7 +65455,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65478,7 +65481,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65504,7 +65507,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65530,7 +65533,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65556,7 +65559,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65582,7 +65585,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65608,7 +65611,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65634,7 +65637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65660,7 +65663,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65686,7 +65689,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65712,7 +65715,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65738,7 +65741,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65764,7 +65767,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65790,7 +65793,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65816,7 +65819,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65842,7 +65845,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65868,7 +65871,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65894,7 +65897,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65920,7 +65923,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65946,7 +65949,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65972,7 +65975,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -65998,7 +66001,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66024,7 +66027,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66050,7 +66053,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66076,7 +66079,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66102,7 +66105,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66128,7 +66131,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66154,7 +66157,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66180,7 +66183,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66206,7 +66209,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66232,7 +66235,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66258,7 +66261,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66284,7 +66287,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66310,7 +66313,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66336,7 +66339,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66362,7 +66365,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66388,7 +66391,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66414,7 +66417,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66440,7 +66443,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66466,7 +66469,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66492,7 +66495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66518,7 +66521,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66544,7 +66547,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66570,7 +66573,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66596,7 +66599,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66622,7 +66625,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66648,7 +66651,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66674,7 +66677,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66700,7 +66703,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66726,7 +66729,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66752,7 +66755,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66778,7 +66781,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2504" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -66804,7 +66807,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -66830,7 +66833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -66856,7 +66859,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -66864,7 +66867,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.5782638889</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>10150</v>
@@ -66882,9 +66885,35 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2508" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6823842593</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>5835</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G2509" t="s">
         <v>443</v>
       </c>
-      <c r="H2508" t="s">
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194995880127</t>
+    <t xml:space="preserve">13.219500541687</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149923324585</t>
+    <t xml:space="preserve">13.149920463562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8576993942261</t>
   </si>
   <si>
     <t xml:space="preserve">12.8716154098511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237350463867</t>
+    <t xml:space="preserve">12.523736000061</t>
   </si>
   <si>
     <t xml:space="preserve">12.802041053772</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">12.5167789459229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758527755737</t>
+    <t xml:space="preserve">12.175853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827974319458</t>
+    <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809120178223</t>
+    <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
     <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462230682373</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280319213867</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
     <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112096786499</t>
+    <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060224533081</t>
+    <t xml:space="preserve">10.5060214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
     <t xml:space="preserve">10.4364461898804</t>
@@ -101,73 +101,73 @@
     <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843284606934</t>
+    <t xml:space="preserve">10.7843294143677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773685455322</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826847076416</t>
+    <t xml:space="preserve">11.3826856613159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
     <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549787521362</t>
+    <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480226516724</t>
+    <t xml:space="preserve">12.148021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193706512451</t>
+    <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.6628875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933103561401</t>
+    <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150053024292</t>
+    <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506172180176</t>
+    <t xml:space="preserve">12.0506181716919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114637374878</t>
+    <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583961486816</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227870941162</t>
+    <t xml:space="preserve">12.0227880477905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236051559448</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
     <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045276641846</t>
+    <t xml:space="preserve">11.9045267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670288085938</t>
+    <t xml:space="preserve">11.7670269012451</t>
   </si>
   <si>
     <t xml:space="preserve">11.5065040588379</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893981933594</t>
+    <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979530334473</t>
+    <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512384414673</t>
+    <t xml:space="preserve">11.6512393951416</t>
   </si>
   <si>
     <t xml:space="preserve">11.7236070632935</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">11.8683452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321590423584</t>
+    <t xml:space="preserve">11.8321580886841</t>
   </si>
   <si>
     <t xml:space="preserve">12.0130786895752</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">12.1578149795532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939964294434</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025531768799</t>
+    <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275535583496</t>
@@ -218,67 +218,67 @@
     <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196542739868</t>
+    <t xml:space="preserve">12.5196561813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643896102905</t>
+    <t xml:space="preserve">12.6643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.946626663208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729434967041</t>
+    <t xml:space="preserve">12.7729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">12.9755716323853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538640975952</t>
+    <t xml:space="preserve">12.9538602828979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091259002686</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157033920288</t>
+    <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
     <t xml:space="preserve">13.388069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025449752808</t>
+    <t xml:space="preserve">13.4025430679321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.4531993865967</t>
   </si>
   <si>
     <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.532808303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689916610718</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554518699646</t>
+    <t xml:space="preserve">13.5545177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966201782227</t>
+    <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459667205811</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387273788452</t>
@@ -287,37 +287,37 @@
     <t xml:space="preserve">13.2071504592896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038614273071</t>
+    <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288608551025</t>
+    <t xml:space="preserve">13.2288618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814926147461</t>
+    <t xml:space="preserve">12.881495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985975265503</t>
+    <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104413986206</t>
+    <t xml:space="preserve">12.9104423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262308120728</t>
+    <t xml:space="preserve">13.0262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845311164856</t>
+    <t xml:space="preserve">12.8453092575073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275453567505</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439947128296</t>
+    <t xml:space="preserve">12.7439956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189952850342</t>
+    <t xml:space="preserve">13.0189943313599</t>
   </si>
   <si>
     <t xml:space="preserve">12.6571531295776</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">12.2446565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012376785278</t>
+    <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334754943848</t>
+    <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143951416016</t>
+    <t xml:space="preserve">12.1143941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709743499756</t>
+    <t xml:space="preserve">12.0709714889526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492639541626</t>
+    <t xml:space="preserve">12.049262046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782117843628</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
     <t xml:space="preserve">11.9913682937622</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479484558105</t>
+    <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
     <t xml:space="preserve">12.1722888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551849365234</t>
+    <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696588516235</t>
+    <t xml:space="preserve">11.9696578979492</t>
   </si>
   <si>
     <t xml:space="preserve">11.9768953323364</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.1505784988403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
     <t xml:space="preserve">12.2229471206665</t>
@@ -389,97 +389,97 @@
     <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132905960083</t>
+    <t xml:space="preserve">12.1329050064087</t>
   </si>
   <si>
     <t xml:space="preserve">12.3880186080933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428667068481</t>
+    <t xml:space="preserve">12.0428657531738</t>
   </si>
   <si>
     <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180326461792</t>
+    <t xml:space="preserve">12.4180316925049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756025314331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307161331177</t>
+    <t xml:space="preserve">12.830717086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158418655396</t>
+    <t xml:space="preserve">13.1158409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807834625244</t>
+    <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732789993286</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881542205811</t>
+    <t xml:space="preserve">12.6881523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657783508301</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308498382568</t>
+    <t xml:space="preserve">13.1308517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682327270508</t>
+    <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845724105835</t>
+    <t xml:space="preserve">12.8457231521606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083383560181</t>
+    <t xml:space="preserve">13.1083393096924</t>
   </si>
   <si>
     <t xml:space="preserve">13.093334197998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559484481812</t>
+    <t xml:space="preserve">13.3559513092041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309844970703</t>
+    <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435352325439</t>
+    <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
+    <t xml:space="preserve">13.138352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205883026123</t>
+    <t xml:space="preserve">13.2058839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934669494629</t>
+    <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685001373291</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.318434715271</t>
+    <t xml:space="preserve">13.3184328079224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434005737305</t>
+    <t xml:space="preserve">13.2434024810791</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683664321899</t>
@@ -494,46 +494,46 @@
     <t xml:space="preserve">13.6185674667358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061513900757</t>
+    <t xml:space="preserve">13.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810489654541</t>
+    <t xml:space="preserve">13.5810518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687704086304</t>
+    <t xml:space="preserve">14.0687665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">13.6485795974731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159784317017</t>
+    <t xml:space="preserve">13.415979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562177658081</t>
+    <t xml:space="preserve">13.9562168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312528610229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609956741333</t>
+    <t xml:space="preserve">13.460994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.445990562439</t>
+    <t xml:space="preserve">13.4459896087646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986488342285</t>
+    <t xml:space="preserve">13.7986497879028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087423324585</t>
+    <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631519317627</t>
+    <t xml:space="preserve">14.6315202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013725280762</t>
+    <t xml:space="preserve">14.3013715744019</t>
   </si>
   <si>
     <t xml:space="preserve">14.616512298584</t>
@@ -542,52 +542,52 @@
     <t xml:space="preserve">14.6915473937988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991836547852</t>
+    <t xml:space="preserve">14.9991827011108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066900253296</t>
+    <t xml:space="preserve">15.0066862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991681098938</t>
+    <t xml:space="preserve">14.991678237915</t>
   </si>
   <si>
     <t xml:space="preserve">14.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691686630249</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
     <t xml:space="preserve">14.6465272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941373825073</t>
+    <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567554473877</t>
+    <t xml:space="preserve">15.1567516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069498062134</t>
+    <t xml:space="preserve">15.6069536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568862915039</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.757022857666</t>
+    <t xml:space="preserve">15.7570209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572864532471</t>
+    <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574192047119</t>
+    <t xml:space="preserve">16.6574230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.707893371582</t>
+    <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576866149902</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076221466064</t>
@@ -596,49 +596,49 @@
     <t xml:space="preserve">16.9575576782227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073566436768</t>
+    <t xml:space="preserve">16.5073547363281</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
   </si>
   <si>
+    <t xml:space="preserve">16.2072200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0571537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3615741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6702823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9723863601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898027420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4354486465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.744158744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5159320831299</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571517944336</t>
+    <t xml:space="preserve">16.8246402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.052864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6702861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9723834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.589804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4354515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7441549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5159282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8246383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.898512840271</t>
+    <t xml:space="preserve">15.898509979248</t>
   </si>
   <si>
     <t xml:space="preserve">15.1267404556274</t>
@@ -656,49 +656,49 @@
     <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321451187134</t>
+    <t xml:space="preserve">14.4321460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919048309326</t>
+    <t xml:space="preserve">13.8919038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522106170654</t>
+    <t xml:space="preserve">14.2522144317627</t>
   </si>
   <si>
     <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.771800994873</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
     <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917324066162</t>
+    <t xml:space="preserve">13.6917314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721448898315</t>
+    <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116647720337</t>
+    <t xml:space="preserve">13.6116628646851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315942764282</t>
+    <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120058059692</t>
+    <t xml:space="preserve">14.0120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518695831299</t>
+    <t xml:space="preserve">13.8518705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113208770752</t>
+    <t xml:space="preserve">13.2113199234009</t>
   </si>
   <si>
     <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123506546021</t>
+    <t xml:space="preserve">14.4123497009277</t>
   </si>
   <si>
     <t xml:space="preserve">14.0920753479004</t>
@@ -710,43 +710,43 @@
     <t xml:space="preserve">13.131254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511827468872</t>
+    <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
     <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910455703735</t>
+    <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810977935791</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309103012085</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907035827637</t>
+    <t xml:space="preserve">12.4907026290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.6508407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106359481812</t>
+    <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302234649658</t>
+    <t xml:space="preserve">11.9302215576172</t>
   </si>
   <si>
     <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.33056640625</t>
+    <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903596878052</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704292297363</t>
@@ -758,49 +758,49 @@
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498100280762</t>
+    <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099491119385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298795700073</t>
+    <t xml:space="preserve">11.529878616333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
     <t xml:space="preserve">11.20960521698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9694004058838</t>
+    <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.049467086792</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288497924805</t>
+    <t xml:space="preserve">10.3288516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889879226685</t>
+    <t xml:space="preserve">10.4889869689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085763931274</t>
+    <t xml:space="preserve">10.0085773468018</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700853347778</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102920532227</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3487043380737</t>
+    <t xml:space="preserve">12.3487062454224</t>
   </si>
   <si>
     <t xml:space="preserve">11.0137100219727</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315176010132</t>
+    <t xml:space="preserve">11.9315185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818313598633</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321422576904</t>
+    <t xml:space="preserve">12.4321403503418</t>
   </si>
   <si>
     <t xml:space="preserve">12.5155792236328</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">13.1830768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4333868026733</t>
+    <t xml:space="preserve">13.4333877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3499517440796</t>
+    <t xml:space="preserve">13.3499507904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.0162019729614</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518180847168</t>
+    <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346342086792</t>
+    <t xml:space="preserve">14.4346361160278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021299362183</t>
+    <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352588653564</t>
+    <t xml:space="preserve">14.9352560043335</t>
   </si>
   <si>
     <t xml:space="preserve">15.0186958312988</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015090942383</t>
+    <t xml:space="preserve">14.601508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511972427368</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843223571777</t>
   </si>
   <si>
     <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837024688721</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
     <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002616882324</t>
+    <t xml:space="preserve">13.6002635955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.2677593231201</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">13.5741519927979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255233764648</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
     <t xml:space="preserve">14.2444791793823</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931058883667</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093160629272</t>
+    <t xml:space="preserve">13.9093141555786</t>
   </si>
   <si>
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606864929199</t>
+    <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6579418182373</t>
+    <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903612136841</t>
+    <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
     <t xml:space="preserve">14.3282699584961</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958505630493</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
     <t xml:space="preserve">14.9985980987549</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">14.9148073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661806106567</t>
+    <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33376121521</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175519943237</t>
+    <t xml:space="preserve">15.4175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499704360962</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823879241943</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851354598999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6689291000366</t>
+    <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
     <t xml:space="preserve">15.9203014373779</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878810882568</t>
+    <t xml:space="preserve">16.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794075012207</t>
+    <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.1923503875732</t>
@@ -995,52 +995,52 @@
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0182361602783</t>
+    <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311800003052</t>
+    <t xml:space="preserve">15.9311809539795</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700162887573</t>
+    <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441286087036</t>
+    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088497161865</t>
+    <t xml:space="preserve">15.4088487625122</t>
   </si>
   <si>
     <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405731201172</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146835327148</t>
+    <t xml:space="preserve">16.7146854400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.801736831665</t>
+    <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758491516113</t>
+    <t xml:space="preserve">16.97585105896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.585241317749</t>
+    <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299057006836</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557971954346</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111289978027</t>
+    <t xml:space="preserve">17.4111270904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.4697246551514</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359622955322</t>
+    <t xml:space="preserve">17.8359603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264965057373</t>
+    <t xml:space="preserve">17.9264984130859</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738063812256</t>
+    <t xml:space="preserve">17.4738101959229</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116580963135</t>
+    <t xml:space="preserve">17.1116561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305839538574</t>
+    <t xml:space="preserve">16.9305820465088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5684280395508</t>
+    <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2927341461182</t>
@@ -1118,10 +1118,7 @@
     <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.296817779541</t>
+    <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
     <t xml:space="preserve">16.20627784729</t>
@@ -1136,28 +1133,28 @@
     <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589660644531</t>
+    <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663049697876</t>
+    <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
     <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819774627686</t>
+    <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955211639404</t>
+    <t xml:space="preserve">14.3955202102661</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5806798934937</t>
+    <t xml:space="preserve">13.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">14.1239080429077</t>
@@ -1169,16 +1166,16 @@
     <t xml:space="preserve">13.3996057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090667724609</t>
+    <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901418685913</t>
+    <t xml:space="preserve">13.4901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333690643311</t>
+    <t xml:space="preserve">14.0333700180054</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -1187,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456705093384</t>
+    <t xml:space="preserve">14.5456695556641</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967765808105</t>
+    <t xml:space="preserve">13.9967775344849</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1208,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.447883605957</t>
+    <t xml:space="preserve">13.4478826522827</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.081955909729</t>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1229,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716025352478</t>
+    <t xml:space="preserve">12.7160263061523</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1238,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330610275269</t>
+    <t xml:space="preserve">12.5330619812012</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1281,9 +1278,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -1353,6 +1347,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5</t>
   </si>
 </sst>
 </file>
@@ -44765,7 +44762,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44791,7 +44788,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44843,7 +44840,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44869,7 +44866,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44895,7 +44892,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44921,7 +44918,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44947,7 +44944,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44973,7 +44970,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44999,7 +44996,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45025,7 +45022,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45051,7 +45048,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45077,7 +45074,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45103,7 +45100,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45129,7 +45126,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45155,7 +45152,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45181,7 +45178,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45207,7 +45204,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45233,7 +45230,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45259,7 +45256,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45285,7 +45282,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45311,7 +45308,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45337,7 +45334,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45363,7 +45360,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45389,7 +45386,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45441,7 +45438,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45467,7 +45464,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45727,7 +45724,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45961,7 +45958,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45987,7 +45984,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46013,7 +46010,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46039,7 +46036,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46065,7 +46062,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46091,7 +46088,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46117,7 +46114,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46143,7 +46140,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46169,7 +46166,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46195,7 +46192,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46221,7 +46218,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46247,7 +46244,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46273,7 +46270,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46351,7 +46348,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46377,7 +46374,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46559,7 +46556,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46585,7 +46582,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46611,7 +46608,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46637,7 +46634,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46663,7 +46660,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46689,7 +46686,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46715,7 +46712,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46741,7 +46738,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46767,7 +46764,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46793,7 +46790,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46819,7 +46816,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46845,7 +46842,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46871,7 +46868,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46897,7 +46894,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46923,7 +46920,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46949,7 +46946,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46975,7 +46972,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47001,7 +46998,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47027,7 +47024,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47053,7 +47050,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47079,7 +47076,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47131,7 +47128,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47157,7 +47154,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47183,7 +47180,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47209,7 +47206,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47235,7 +47232,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47261,7 +47258,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47287,7 +47284,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47313,7 +47310,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47339,7 +47336,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47365,7 +47362,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47391,7 +47388,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47417,7 +47414,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47521,7 +47518,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47547,7 +47544,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47573,7 +47570,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47599,7 +47596,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47625,7 +47622,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47651,7 +47648,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47677,7 +47674,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47703,7 +47700,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47729,7 +47726,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47781,7 +47778,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47807,7 +47804,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47833,7 +47830,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47859,7 +47856,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47885,7 +47882,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47911,7 +47908,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47937,7 +47934,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48015,7 +48012,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48041,7 +48038,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48067,7 +48064,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48093,7 +48090,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48119,7 +48116,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48145,7 +48142,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48171,7 +48168,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48197,7 +48194,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48249,7 +48246,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48275,7 +48272,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48301,7 +48298,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48353,7 +48350,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48613,7 +48610,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48639,7 +48636,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48665,7 +48662,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48691,7 +48688,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48717,7 +48714,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48743,7 +48740,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48769,7 +48766,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48795,7 +48792,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48821,7 +48818,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48847,7 +48844,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48873,7 +48870,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48899,7 +48896,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48925,7 +48922,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48951,7 +48948,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48977,7 +48974,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49003,7 +49000,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49029,7 +49026,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49055,7 +49052,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49081,7 +49078,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49107,7 +49104,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49133,7 +49130,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49159,7 +49156,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49185,7 +49182,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49211,7 +49208,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49237,7 +49234,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49263,7 +49260,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49289,7 +49286,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49315,7 +49312,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49341,7 +49338,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49367,7 +49364,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49393,7 +49390,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49419,7 +49416,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49445,7 +49442,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49471,7 +49468,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49497,7 +49494,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49523,7 +49520,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49549,7 +49546,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49575,7 +49572,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49601,7 +49598,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49627,7 +49624,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49653,7 +49650,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49679,7 +49676,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49705,7 +49702,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49731,7 +49728,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49757,7 +49754,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49783,7 +49780,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49809,7 +49806,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49835,7 +49832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49861,7 +49858,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49887,7 +49884,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49913,7 +49910,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49939,7 +49936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49965,7 +49962,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49991,7 +49988,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50017,7 +50014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50043,7 +50040,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50069,7 +50066,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50095,7 +50092,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50121,7 +50118,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50147,7 +50144,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50173,7 +50170,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50199,7 +50196,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50225,7 +50222,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50251,7 +50248,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50277,7 +50274,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50303,7 +50300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50329,7 +50326,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50355,7 +50352,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50381,7 +50378,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50407,7 +50404,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50433,7 +50430,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50459,7 +50456,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50485,7 +50482,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50511,7 +50508,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50537,7 +50534,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50563,7 +50560,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50589,7 +50586,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50615,7 +50612,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50641,7 +50638,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50667,7 +50664,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50693,7 +50690,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50719,7 +50716,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50745,7 +50742,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50771,7 +50768,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50797,7 +50794,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50823,7 +50820,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50849,7 +50846,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50875,7 +50872,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50901,7 +50898,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50927,7 +50924,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50953,7 +50950,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50979,7 +50976,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51005,7 +51002,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51031,7 +51028,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51057,7 +51054,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51083,7 +51080,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51109,7 +51106,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51135,7 +51132,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51161,7 +51158,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51187,7 +51184,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51213,7 +51210,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51239,7 +51236,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51265,7 +51262,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51291,7 +51288,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51317,7 +51314,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51343,7 +51340,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51369,7 +51366,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51395,7 +51392,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51421,7 +51418,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51447,7 +51444,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51473,7 +51470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51499,7 +51496,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51525,7 +51522,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51551,7 +51548,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51577,7 +51574,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51603,7 +51600,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51629,7 +51626,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51655,7 +51652,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51681,7 +51678,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51707,7 +51704,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51733,7 +51730,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51759,7 +51756,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51785,7 +51782,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51811,7 +51808,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51837,7 +51834,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51863,7 +51860,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51889,7 +51886,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51915,7 +51912,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51941,7 +51938,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51967,7 +51964,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51993,7 +51990,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52019,7 +52016,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52045,7 +52042,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52071,7 +52068,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52097,7 +52094,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52123,7 +52120,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52149,7 +52146,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52175,7 +52172,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52201,7 +52198,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52227,7 +52224,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52253,7 +52250,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52279,7 +52276,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52305,7 +52302,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52331,7 +52328,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52357,7 +52354,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52383,7 +52380,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52409,7 +52406,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52435,7 +52432,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52461,7 +52458,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52487,7 +52484,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52513,7 +52510,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52539,7 +52536,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52565,7 +52562,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52591,7 +52588,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52617,7 +52614,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52643,7 +52640,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52669,7 +52666,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52695,7 +52692,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52721,7 +52718,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52747,7 +52744,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52773,7 +52770,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52799,7 +52796,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52825,7 +52822,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52851,7 +52848,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52877,7 +52874,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52903,7 +52900,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52929,7 +52926,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52955,7 +52952,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52981,7 +52978,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53007,7 +53004,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53033,7 +53030,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53059,7 +53056,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53085,7 +53082,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53111,7 +53108,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53137,7 +53134,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53163,7 +53160,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53189,7 +53186,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53215,7 +53212,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53241,7 +53238,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53267,7 +53264,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53293,7 +53290,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53319,7 +53316,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53345,7 +53342,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53371,7 +53368,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53397,7 +53394,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53423,7 +53420,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53449,7 +53446,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53475,7 +53472,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53501,7 +53498,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53527,7 +53524,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53553,7 +53550,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53579,7 +53576,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53605,7 +53602,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53631,7 +53628,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53657,7 +53654,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53683,7 +53680,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53709,7 +53706,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53735,7 +53732,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53761,7 +53758,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53787,7 +53784,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53813,7 +53810,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53839,7 +53836,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53865,7 +53862,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53891,7 +53888,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53917,7 +53914,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53943,7 +53940,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53969,7 +53966,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53995,7 +53992,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54021,7 +54018,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54047,7 +54044,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54073,7 +54070,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54099,7 +54096,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54125,7 +54122,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54151,7 +54148,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54177,7 +54174,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54203,7 +54200,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54229,7 +54226,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54255,7 +54252,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54281,7 +54278,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54307,7 +54304,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54333,7 +54330,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54359,7 +54356,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54385,7 +54382,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54411,7 +54408,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54437,7 +54434,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54463,7 +54460,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54489,7 +54486,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54515,7 +54512,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54541,7 +54538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54567,7 +54564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54593,7 +54590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54619,7 +54616,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54645,7 +54642,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54671,7 +54668,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54697,7 +54694,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54723,7 +54720,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54749,7 +54746,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54775,7 +54772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54801,7 +54798,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54827,7 +54824,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54853,7 +54850,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54879,7 +54876,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54905,7 +54902,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54931,7 +54928,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54957,7 +54954,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54983,7 +54980,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55009,7 +55006,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55035,7 +55032,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55061,7 +55058,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55087,7 +55084,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55113,7 +55110,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55139,7 +55136,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55165,7 +55162,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55191,7 +55188,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55217,7 +55214,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55243,7 +55240,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55269,7 +55266,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55295,7 +55292,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55321,7 +55318,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55347,7 +55344,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55373,7 +55370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55399,7 +55396,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55425,7 +55422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55451,7 +55448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55477,7 +55474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55503,7 +55500,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55529,7 +55526,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55555,7 +55552,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55581,7 +55578,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55607,7 +55604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55633,7 +55630,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55659,7 +55656,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55685,7 +55682,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55711,7 +55708,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55737,7 +55734,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55763,7 +55760,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55789,7 +55786,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55815,7 +55812,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55841,7 +55838,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55867,7 +55864,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55893,7 +55890,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55919,7 +55916,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55945,7 +55942,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55971,7 +55968,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55997,7 +55994,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56023,7 +56020,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56049,7 +56046,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56075,7 +56072,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56101,7 +56098,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56127,7 +56124,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56153,7 +56150,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56179,7 +56176,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56205,7 +56202,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56231,7 +56228,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56257,7 +56254,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56283,7 +56280,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56309,7 +56306,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56335,7 +56332,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56361,7 +56358,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56387,7 +56384,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56413,7 +56410,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56439,7 +56436,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56465,7 +56462,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56491,7 +56488,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56517,7 +56514,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56543,7 +56540,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56569,7 +56566,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56595,7 +56592,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56621,7 +56618,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56647,7 +56644,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56673,7 +56670,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56699,7 +56696,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56725,7 +56722,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56751,7 +56748,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56777,7 +56774,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56803,7 +56800,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56829,7 +56826,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56855,7 +56852,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56881,7 +56878,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56907,7 +56904,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56933,7 +56930,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56959,7 +56956,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56985,7 +56982,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57011,7 +57008,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57037,7 +57034,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57063,7 +57060,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57089,7 +57086,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57115,7 +57112,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57141,7 +57138,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57167,7 +57164,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57193,7 +57190,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57219,7 +57216,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57245,7 +57242,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57271,7 +57268,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57297,7 +57294,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57323,7 +57320,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57349,7 +57346,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57375,7 +57372,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57401,7 +57398,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57427,7 +57424,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57453,7 +57450,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57479,7 +57476,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57505,7 +57502,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57531,7 +57528,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57557,7 +57554,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57583,7 +57580,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57609,7 +57606,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57635,7 +57632,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57661,7 +57658,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57687,7 +57684,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57713,7 +57710,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57739,7 +57736,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57765,7 +57762,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57791,7 +57788,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57817,7 +57814,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57843,7 +57840,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57869,7 +57866,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57895,7 +57892,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57921,7 +57918,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57947,7 +57944,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57973,7 +57970,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57999,7 +57996,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58025,7 +58022,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58051,7 +58048,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58077,7 +58074,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58103,7 +58100,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58129,7 +58126,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58155,7 +58152,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58181,7 +58178,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58207,7 +58204,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58233,7 +58230,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58259,7 +58256,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58285,7 +58282,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58311,7 +58308,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58337,7 +58334,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58363,7 +58360,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58389,7 +58386,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58415,7 +58412,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58441,7 +58438,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58467,7 +58464,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58493,7 +58490,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58519,7 +58516,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58545,7 +58542,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58571,7 +58568,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58597,7 +58594,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58623,7 +58620,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58649,7 +58646,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58675,7 +58672,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58701,7 +58698,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58727,7 +58724,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58753,7 +58750,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58779,7 +58776,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58805,7 +58802,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58831,7 +58828,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58857,7 +58854,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58883,7 +58880,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58909,7 +58906,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58935,7 +58932,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58961,7 +58958,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58987,7 +58984,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59013,7 +59010,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59039,7 +59036,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59065,7 +59062,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59091,7 +59088,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59117,7 +59114,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59143,7 +59140,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59169,7 +59166,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59195,7 +59192,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59221,7 +59218,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59247,7 +59244,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59273,7 +59270,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59299,7 +59296,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59325,7 +59322,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59351,7 +59348,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59377,7 +59374,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59403,7 +59400,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59429,7 +59426,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59455,7 +59452,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59481,7 +59478,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59507,7 +59504,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59533,7 +59530,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59559,7 +59556,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59585,7 +59582,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59611,7 +59608,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59637,7 +59634,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59663,7 +59660,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59689,7 +59686,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59715,7 +59712,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59741,7 +59738,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59767,7 +59764,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59793,7 +59790,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59819,7 +59816,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59845,7 +59842,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59871,7 +59868,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59897,7 +59894,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59923,7 +59920,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59949,7 +59946,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59975,7 +59972,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60001,7 +59998,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60027,7 +60024,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60053,7 +60050,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60079,7 +60076,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60105,7 +60102,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60131,7 +60128,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60157,7 +60154,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60183,7 +60180,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60209,7 +60206,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60235,7 +60232,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60261,7 +60258,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60287,7 +60284,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60313,7 +60310,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60339,7 +60336,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60365,7 +60362,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60391,7 +60388,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60417,7 +60414,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60443,7 +60440,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60469,7 +60466,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60495,7 +60492,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60521,7 +60518,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60547,7 +60544,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60573,7 +60570,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60599,7 +60596,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60625,7 +60622,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60651,7 +60648,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60677,7 +60674,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60703,7 +60700,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60729,7 +60726,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60755,7 +60752,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60781,7 +60778,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60807,7 +60804,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60833,7 +60830,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60859,7 +60856,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60885,7 +60882,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60911,7 +60908,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60937,7 +60934,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60963,7 +60960,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60989,7 +60986,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61015,7 +61012,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61041,7 +61038,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61067,7 +61064,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61093,7 +61090,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61119,7 +61116,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61145,7 +61142,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61171,7 +61168,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61197,7 +61194,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61223,7 +61220,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61249,7 +61246,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61275,7 +61272,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61301,7 +61298,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61327,7 +61324,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61353,7 +61350,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61379,7 +61376,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61405,7 +61402,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61431,7 +61428,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61457,7 +61454,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61483,7 +61480,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61509,7 +61506,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61535,7 +61532,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61561,7 +61558,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61587,7 +61584,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61613,7 +61610,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61639,7 +61636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61665,7 +61662,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61691,7 +61688,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61717,7 +61714,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61743,7 +61740,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61769,7 +61766,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61795,7 +61792,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61821,7 +61818,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61847,7 +61844,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61873,7 +61870,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61899,7 +61896,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61925,7 +61922,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61951,7 +61948,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61977,7 +61974,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62003,7 +62000,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62029,7 +62026,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62055,7 +62052,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62081,7 +62078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62107,7 +62104,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62133,7 +62130,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62159,7 +62156,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62185,7 +62182,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62211,7 +62208,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62237,7 +62234,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62263,7 +62260,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62289,7 +62286,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62315,7 +62312,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62341,7 +62338,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62367,7 +62364,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62393,7 +62390,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62419,7 +62416,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62445,7 +62442,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62471,7 +62468,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62497,7 +62494,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62523,7 +62520,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62549,7 +62546,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62575,7 +62572,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62601,7 +62598,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62627,7 +62624,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62653,7 +62650,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62679,7 +62676,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62705,7 +62702,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62731,7 +62728,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62757,7 +62754,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62783,7 +62780,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62809,7 +62806,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62835,7 +62832,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62861,7 +62858,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62887,7 +62884,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62913,7 +62910,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62939,7 +62936,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62965,7 +62962,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62991,7 +62988,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63017,7 +63014,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63043,7 +63040,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63069,7 +63066,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63095,7 +63092,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63121,7 +63118,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63147,7 +63144,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63173,7 +63170,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63199,7 +63196,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63225,7 +63222,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63251,7 +63248,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63277,7 +63274,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63303,7 +63300,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63329,7 +63326,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63355,7 +63352,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63381,7 +63378,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63407,7 +63404,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63433,7 +63430,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63459,7 +63456,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63485,7 +63482,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63511,7 +63508,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63537,7 +63534,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63563,7 +63560,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63589,7 +63586,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63615,7 +63612,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63641,7 +63638,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63667,7 +63664,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63693,7 +63690,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63719,7 +63716,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63745,7 +63742,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63771,7 +63768,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63797,7 +63794,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63823,7 +63820,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63849,7 +63846,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63875,7 +63872,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63901,7 +63898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63927,7 +63924,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63953,7 +63950,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63979,7 +63976,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64005,7 +64002,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64031,7 +64028,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64057,7 +64054,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64083,7 +64080,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64109,7 +64106,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64135,7 +64132,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64161,7 +64158,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64187,7 +64184,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64213,7 +64210,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64239,7 +64236,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64265,7 +64262,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64291,7 +64288,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64317,7 +64314,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64343,7 +64340,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64369,7 +64366,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64395,7 +64392,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64421,7 +64418,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64447,7 +64444,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64473,7 +64470,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64499,7 +64496,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64525,7 +64522,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64551,7 +64548,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64577,7 +64574,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64603,7 +64600,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64629,7 +64626,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64655,7 +64652,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64681,7 +64678,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64707,7 +64704,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64733,7 +64730,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64759,7 +64756,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64785,7 +64782,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64811,7 +64808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64837,7 +64834,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64863,7 +64860,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64889,7 +64886,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64915,7 +64912,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64941,7 +64938,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64967,7 +64964,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64993,7 +64990,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65019,7 +65016,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65045,7 +65042,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65071,7 +65068,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65097,7 +65094,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65123,7 +65120,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65149,7 +65146,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65175,7 +65172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65201,7 +65198,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65227,7 +65224,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65253,7 +65250,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65279,7 +65276,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65305,7 +65302,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65331,7 +65328,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65357,7 +65354,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65383,7 +65380,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65409,7 +65406,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65435,7 +65432,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65461,7 +65458,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65487,7 +65484,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65513,7 +65510,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65539,7 +65536,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65565,7 +65562,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65591,7 +65588,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65617,7 +65614,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65643,7 +65640,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65669,7 +65666,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65695,7 +65692,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65721,7 +65718,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65747,7 +65744,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65773,7 +65770,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65799,7 +65796,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65825,7 +65822,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65851,7 +65848,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65877,7 +65874,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65903,7 +65900,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65929,7 +65926,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65955,7 +65952,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65981,7 +65978,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66007,7 +66004,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66033,7 +66030,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66059,7 +66056,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66085,7 +66082,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66111,7 +66108,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66137,7 +66134,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66163,7 +66160,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66189,7 +66186,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66215,7 +66212,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66241,7 +66238,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66267,7 +66264,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66293,7 +66290,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66319,7 +66316,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66345,7 +66342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66371,7 +66368,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66397,7 +66394,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66423,7 +66420,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66449,7 +66446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66475,7 +66472,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66501,7 +66498,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66527,7 +66524,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66553,7 +66550,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66579,7 +66576,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66605,7 +66602,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66631,7 +66628,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66657,7 +66654,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66683,7 +66680,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66709,7 +66706,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66735,7 +66732,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66761,7 +66758,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66787,7 +66784,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2504" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -66813,7 +66810,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -66839,7 +66836,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -66865,7 +66862,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -66891,7 +66888,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -66917,7 +66914,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2509" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -66943,7 +66940,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2510" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -66951,7 +66948,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.5275</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>200</v>
@@ -66969,9 +66966,35 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2511" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6517708333</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194995880127</t>
+    <t xml:space="preserve">13.2194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499214172363</t>
+    <t xml:space="preserve">13.149923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577003479004</t>
+    <t xml:space="preserve">12.8577013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716163635254</t>
+    <t xml:space="preserve">12.8716154098511</t>
   </si>
   <si>
     <t xml:space="preserve">12.523736000061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.802041053772</t>
+    <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167789459229</t>
+    <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758527755737</t>
+    <t xml:space="preserve">12.175853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279733657837</t>
+    <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809120178223</t>
+    <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755987167358</t>
+    <t xml:space="preserve">10.5755996704102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280128479004</t>
+    <t xml:space="preserve">9.39280223846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112077713013</t>
+    <t xml:space="preserve">10.311206817627</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364452362061</t>
+    <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
     <t xml:space="preserve">10.6451749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147493362427</t>
+    <t xml:space="preserve">10.7147521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843284606934</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1322088241577</t>
+    <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826856613159</t>
+    <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331577301025</t>
+    <t xml:space="preserve">11.6331596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905906677246</t>
+    <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
     <t xml:space="preserve">12.1549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480255126953</t>
+    <t xml:space="preserve">12.148024559021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4193696975708</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">12.5933122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150091171265</t>
+    <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0506153106689</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583951950073</t>
+    <t xml:space="preserve">11.7583961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227861404419</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841327667236</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163705825806</t>
@@ -170,145 +170,145 @@
     <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065040588379</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289400100708</t>
+    <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.542688369751</t>
+    <t xml:space="preserve">11.5426864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979530334473</t>
+    <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512384414673</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.832160949707</t>
   </si>
   <si>
     <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854482650757</t>
+    <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578140258789</t>
+    <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939992904663</t>
+    <t xml:space="preserve">12.1939973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025522232056</t>
+    <t xml:space="preserve">12.3025503158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275535583496</t>
+    <t xml:space="preserve">12.0275526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953128814697</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472875595093</t>
+    <t xml:space="preserve">12.447286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196561813354</t>
+    <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643896102905</t>
+    <t xml:space="preserve">12.6643915176392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466257095337</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729434967041</t>
+    <t xml:space="preserve">12.7729425430298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755735397339</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538612365723</t>
+    <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091287612915</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.243335723877</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
     <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604368209839</t>
   </si>
   <si>
     <t xml:space="preserve">13.388069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025459289551</t>
+    <t xml:space="preserve">13.4025430679321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532012939453</t>
+    <t xml:space="preserve">13.453200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242534637451</t>
+    <t xml:space="preserve">13.4242553710938</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689907073975</t>
+    <t xml:space="preserve">13.5689916610718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5545167922974</t>
+    <t xml:space="preserve">13.554518699646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966230392456</t>
+    <t xml:space="preserve">13.4966220855713</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459657669067</t>
+    <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071485519409</t>
+    <t xml:space="preserve">13.2071504592896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038585662842</t>
+    <t xml:space="preserve">13.5038614273071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288618087769</t>
+    <t xml:space="preserve">13.2288608551025</t>
   </si>
   <si>
     <t xml:space="preserve">12.881495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985994338989</t>
+    <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104413986206</t>
+    <t xml:space="preserve">12.9104423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262317657471</t>
+    <t xml:space="preserve">13.0262327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.134783744812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453092575073</t>
+    <t xml:space="preserve">12.8453102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275424957275</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
     <t xml:space="preserve">12.7439956665039</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">13.0189943313599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571531295776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012348175049</t>
+    <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334745407104</t>
@@ -332,61 +332,61 @@
     <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709733963013</t>
+    <t xml:space="preserve">12.070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492630004883</t>
+    <t xml:space="preserve">12.049262046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782098770142</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913673400879</t>
+    <t xml:space="preserve">11.9913702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986057281494</t>
+    <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722888946533</t>
+    <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551830291748</t>
+    <t xml:space="preserve">11.9551849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696578979492</t>
+    <t xml:space="preserve">11.9696598052979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.150580406189</t>
+    <t xml:space="preserve">12.1505794525146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301826477051</t>
+    <t xml:space="preserve">12.2301836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229461669922</t>
+    <t xml:space="preserve">12.2229471206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054828643799</t>
+    <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805160522461</t>
+    <t xml:space="preserve">12.3805170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
     <t xml:space="preserve">12.3880186080933</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129854202271</t>
+    <t xml:space="preserve">12.3129873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180316925049</t>
+    <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307151794434</t>
+    <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
     <t xml:space="preserve">13.1158437728882</t>
@@ -413,55 +413,55 @@
     <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732780456543</t>
+    <t xml:space="preserve">12.9732809066772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881523132324</t>
+    <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657764434814</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.943265914917</t>
+    <t xml:space="preserve">12.9432668685913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308498382568</t>
+    <t xml:space="preserve">13.1308507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682355880737</t>
+    <t xml:space="preserve">12.8682346343994</t>
   </si>
   <si>
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083383560181</t>
+    <t xml:space="preserve">13.1083393096924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933332443237</t>
+    <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559494018555</t>
+    <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
     <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309844970703</t>
+    <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435342788696</t>
+    <t xml:space="preserve">13.5435352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383543014526</t>
+    <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234809875488</t>
+    <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
     <t xml:space="preserve">13.2058839797974</t>
@@ -470,73 +470,73 @@
     <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685020446777</t>
+    <t xml:space="preserve">13.4685029983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184328079224</t>
+    <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434005737305</t>
+    <t xml:space="preserve">13.2433996200562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683673858643</t>
+    <t xml:space="preserve">13.1683654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060176849365</t>
+    <t xml:space="preserve">13.5060195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560831069946</t>
+    <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185674667358</t>
+    <t xml:space="preserve">13.6185684204102</t>
   </si>
   <si>
     <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810518264771</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687685012817</t>
+    <t xml:space="preserve">14.0687704086304</t>
   </si>
   <si>
     <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485805511475</t>
+    <t xml:space="preserve">13.6485824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159774780273</t>
+    <t xml:space="preserve">13.415979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562177658081</t>
+    <t xml:space="preserve">13.9562168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312528610229</t>
+    <t xml:space="preserve">14.0312519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609966278076</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
     <t xml:space="preserve">13.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986469268799</t>
+    <t xml:space="preserve">13.7986478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087423324585</t>
+    <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631519317627</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
     <t xml:space="preserve">14.3013725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616512298584</t>
+    <t xml:space="preserve">14.6165142059326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915464401245</t>
+    <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
     <t xml:space="preserve">14.9991817474365</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">14.976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691696166992</t>
+    <t xml:space="preserve">14.9691705703735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941354751587</t>
+    <t xml:space="preserve">14.8941335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390247344971</t>
+    <t xml:space="preserve">14.6390218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567525863647</t>
   </si>
   <si>
     <t xml:space="preserve">15.6069526672363</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574192047119</t>
+    <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.7078876495361</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076221466064</t>
+    <t xml:space="preserve">17.1076202392578</t>
   </si>
   <si>
     <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073547363281</t>
+    <t xml:space="preserve">16.5073528289795</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
@@ -602,73 +602,73 @@
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571537017822</t>
+    <t xml:space="preserve">16.0571556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615760803223</t>
+    <t xml:space="preserve">16.3615779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528659820557</t>
+    <t xml:space="preserve">16.0528678894043</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723854064941</t>
+    <t xml:space="preserve">14.9723834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898008346558</t>
+    <t xml:space="preserve">15.5898017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.435450553894</t>
+    <t xml:space="preserve">15.4354515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.744158744812</t>
+    <t xml:space="preserve">15.7441596984863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5159301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8246402740479</t>
+    <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985137939453</t>
+    <t xml:space="preserve">15.8985118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267385482788</t>
+    <t xml:space="preserve">15.1267414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.049560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636781692505</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810935974121</t>
+    <t xml:space="preserve">15.2810916900635</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321460723877</t>
+    <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919057846069</t>
   </si>
   <si>
     <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">13.771800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515256881714</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917333602905</t>
+    <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.1721448898315</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315942764282</t>
+    <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120058059692</t>
+    <t xml:space="preserve">14.0120067596436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518695831299</t>
+    <t xml:space="preserve">13.8518705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113208770752</t>
+    <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
     <t xml:space="preserve">13.2913885116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123487472534</t>
+    <t xml:space="preserve">14.4123516082764</t>
   </si>
   <si>
     <t xml:space="preserve">14.0920753479004</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511837005615</t>
+    <t xml:space="preserve">13.0511827468872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9711151123047</t>
@@ -713,34 +713,34 @@
     <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109769821167</t>
+    <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309083938599</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.490704536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106340408325</t>
+    <t xml:space="preserve">12.4106349945068</t>
   </si>
   <si>
     <t xml:space="preserve">11.9302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.6900186538696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.3305673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704301834106</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498100280762</t>
+    <t xml:space="preserve">11.4498119354248</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
@@ -761,46 +761,46 @@
     <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.3697443008423</t>
   </si>
   <si>
     <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9693994522095</t>
+    <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494689941406</t>
+    <t xml:space="preserve">11.0494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491250991821</t>
+    <t xml:space="preserve">10.6491241455078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288516998291</t>
+    <t xml:space="preserve">10.3288497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889869689941</t>
+    <t xml:space="preserve">10.4889879226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487812042236</t>
+    <t xml:space="preserve">10.2487840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700872421265</t>
+    <t xml:space="preserve">11.7700862884521</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493280410767</t>
+    <t xml:space="preserve">12.849328994751</t>
   </si>
   <si>
     <t xml:space="preserve">12.5990171432495</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">12.348705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137100219727</t>
+    <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6812076568604</t>
+    <t xml:space="preserve">11.6812057495117</t>
   </si>
   <si>
     <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.181830406189</t>
+    <t xml:space="preserve">12.1818313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321403503418</t>
+    <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
     <t xml:space="preserve">12.5155792236328</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518199920654</t>
+    <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346361160278</t>
+    <t xml:space="preserve">14.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021318435669</t>
+    <t xml:space="preserve">15.1021327972412</t>
   </si>
   <si>
     <t xml:space="preserve">14.9352560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186939239502</t>
+    <t xml:space="preserve">15.0186948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849460601807</t>
+    <t xml:space="preserve">14.6849451065063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.601508140564</t>
+    <t xml:space="preserve">14.6015062332153</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511981964111</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843242645264</t>
+    <t xml:space="preserve">14.1843223571777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0174474716187</t>
+    <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837015151978</t>
@@ -887,25 +887,25 @@
     <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002635955811</t>
+    <t xml:space="preserve">13.6002616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677612304688</t>
+    <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741529464722</t>
+    <t xml:space="preserve">13.5741500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255243301392</t>
+    <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444791793823</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093151092529</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796432495117</t>
+    <t xml:space="preserve">14.579644203186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606874465942</t>
+    <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6579399108887</t>
+    <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903602600098</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">14.3282699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634349822998</t>
+    <t xml:space="preserve">14.6634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958524703979</t>
+    <t xml:space="preserve">14.4958515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985980987549</t>
+    <t xml:space="preserve">14.9986000061035</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472267150879</t>
+    <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148073196411</t>
+    <t xml:space="preserve">14.9148082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661825180054</t>
   </si>
   <si>
     <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175539016724</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499723434448</t>
+    <t xml:space="preserve">15.2499713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851354598999</t>
+    <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
     <t xml:space="preserve">15.668927192688</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0040912628174</t>
+    <t xml:space="preserve">16.004093170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.018238067627</t>
+    <t xml:space="preserve">16.0182361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311809539795</t>
+    <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
@@ -1001,37 +1001,37 @@
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441276550293</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829591751099</t>
+    <t xml:space="preserve">15.5829610824585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4088487625122</t>
+    <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664588928223</t>
+    <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405712127686</t>
+    <t xml:space="preserve">16.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146854400635</t>
+    <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8887939453125</t>
+    <t xml:space="preserve">16.8887920379639</t>
   </si>
   <si>
     <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499614715576</t>
+    <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.97585105896</t>
+    <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
     <t xml:space="preserve">17.585241317749</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557991027832</t>
+    <t xml:space="preserve">18.4557971954346</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240718841553</t>
+    <t xml:space="preserve">17.3240737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111270904541</t>
+    <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
     <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886524200439</t>
+    <t xml:space="preserve">18.2886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8359603881836</t>
+    <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264965057373</t>
+    <t xml:space="preserve">17.9264984130859</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1106,16 +1106,19 @@
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778938293457</t>
+    <t xml:space="preserve">16.4778919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157398223877</t>
+    <t xml:space="preserve">16.1157417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8441257476807</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.20627784729</t>
+    <t xml:space="preserve">16.2062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1127,28 +1130,28 @@
     <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589679718018</t>
+    <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630506515503</t>
+    <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535886764526</t>
+    <t xml:space="preserve">15.7535905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819765090942</t>
+    <t xml:space="preserve">15.4819755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955202102661</t>
+    <t xml:space="preserve">14.3955211639404</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580680847168</t>
+    <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
     <t xml:space="preserve">14.1239080429077</t>
@@ -1157,19 +1160,19 @@
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996057510376</t>
+    <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901418685913</t>
+    <t xml:space="preserve">13.4901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0333700180054</t>
+    <t xml:space="preserve">14.0333690643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.1797409057617</t>
@@ -44762,7 +44765,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44788,7 +44791,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44840,7 +44843,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44866,7 +44869,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44892,7 +44895,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44918,7 +44921,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44944,7 +44947,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44970,7 +44973,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44996,7 +44999,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45022,7 +45025,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45048,7 +45051,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45074,7 +45077,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45100,7 +45103,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45126,7 +45129,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45152,7 +45155,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45178,7 +45181,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45204,7 +45207,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45230,7 +45233,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45256,7 +45259,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45282,7 +45285,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45308,7 +45311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45334,7 +45337,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45360,7 +45363,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45386,7 +45389,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45438,7 +45441,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45464,7 +45467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45724,7 +45727,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45958,7 +45961,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45984,7 +45987,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46010,7 +46013,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46036,7 +46039,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46062,7 +46065,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46088,7 +46091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46114,7 +46117,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46140,7 +46143,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46166,7 +46169,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46192,7 +46195,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46218,7 +46221,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46244,7 +46247,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46270,7 +46273,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46348,7 +46351,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46374,7 +46377,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46556,7 +46559,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46582,7 +46585,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46608,7 +46611,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46634,7 +46637,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46660,7 +46663,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46686,7 +46689,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46712,7 +46715,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46738,7 +46741,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46764,7 +46767,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46790,7 +46793,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46816,7 +46819,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46842,7 +46845,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46868,7 +46871,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46894,7 +46897,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46920,7 +46923,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46946,7 +46949,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46972,7 +46975,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46998,7 +47001,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47024,7 +47027,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47050,7 +47053,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47076,7 +47079,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47128,7 +47131,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47154,7 +47157,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47180,7 +47183,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47206,7 +47209,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47232,7 +47235,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47258,7 +47261,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47284,7 +47287,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47310,7 +47313,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47336,7 +47339,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47362,7 +47365,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47388,7 +47391,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47414,7 +47417,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47518,7 +47521,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47544,7 +47547,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47570,7 +47573,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47596,7 +47599,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47622,7 +47625,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47648,7 +47651,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47674,7 +47677,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47700,7 +47703,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47726,7 +47729,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47778,7 +47781,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47804,7 +47807,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47830,7 +47833,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47856,7 +47859,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47882,7 +47885,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47908,7 +47911,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47934,7 +47937,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48012,7 +48015,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48038,7 +48041,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48064,7 +48067,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48090,7 +48093,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48116,7 +48119,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48142,7 +48145,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48168,7 +48171,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48194,7 +48197,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48246,7 +48249,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48272,7 +48275,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48298,7 +48301,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48350,7 +48353,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48610,7 +48613,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48636,7 +48639,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48662,7 +48665,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48688,7 +48691,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48714,7 +48717,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48740,7 +48743,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48766,7 +48769,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48792,7 +48795,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48818,7 +48821,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48844,7 +48847,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48870,7 +48873,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48896,7 +48899,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48922,7 +48925,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48948,7 +48951,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48974,7 +48977,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49000,7 +49003,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49026,7 +49029,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49052,7 +49055,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49078,7 +49081,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49104,7 +49107,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49130,7 +49133,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49156,7 +49159,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49182,7 +49185,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49208,7 +49211,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49234,7 +49237,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49260,7 +49263,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49286,7 +49289,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49312,7 +49315,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49338,7 +49341,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49364,7 +49367,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49390,7 +49393,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49416,7 +49419,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49442,7 +49445,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49468,7 +49471,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49494,7 +49497,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49520,7 +49523,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49546,7 +49549,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49572,7 +49575,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49598,7 +49601,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49624,7 +49627,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49650,7 +49653,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49676,7 +49679,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49702,7 +49705,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49728,7 +49731,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49754,7 +49757,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49780,7 +49783,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49806,7 +49809,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49832,7 +49835,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49858,7 +49861,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49884,7 +49887,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49910,7 +49913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49936,7 +49939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49962,7 +49965,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49988,7 +49991,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50014,7 +50017,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50040,7 +50043,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50066,7 +50069,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50092,7 +50095,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50118,7 +50121,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50144,7 +50147,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50170,7 +50173,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50196,7 +50199,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50222,7 +50225,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50248,7 +50251,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50274,7 +50277,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50300,7 +50303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50326,7 +50329,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50352,7 +50355,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50378,7 +50381,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50404,7 +50407,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50430,7 +50433,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50456,7 +50459,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50482,7 +50485,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50508,7 +50511,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50534,7 +50537,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50560,7 +50563,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50586,7 +50589,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50612,7 +50615,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50638,7 +50641,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50664,7 +50667,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50690,7 +50693,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50716,7 +50719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50742,7 +50745,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50768,7 +50771,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50794,7 +50797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50820,7 +50823,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50846,7 +50849,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50872,7 +50875,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50898,7 +50901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50924,7 +50927,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50950,7 +50953,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50976,7 +50979,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51002,7 +51005,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51028,7 +51031,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51054,7 +51057,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51080,7 +51083,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51106,7 +51109,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51132,7 +51135,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51158,7 +51161,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51184,7 +51187,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51210,7 +51213,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51236,7 +51239,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51262,7 +51265,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51288,7 +51291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51314,7 +51317,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51340,7 +51343,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51366,7 +51369,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51392,7 +51395,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51418,7 +51421,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51444,7 +51447,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51470,7 +51473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51496,7 +51499,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51522,7 +51525,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51548,7 +51551,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51574,7 +51577,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51600,7 +51603,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51626,7 +51629,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51652,7 +51655,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51678,7 +51681,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51704,7 +51707,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51730,7 +51733,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51756,7 +51759,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51782,7 +51785,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51808,7 +51811,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51834,7 +51837,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51860,7 +51863,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51886,7 +51889,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51912,7 +51915,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51938,7 +51941,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51964,7 +51967,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51990,7 +51993,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52016,7 +52019,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52042,7 +52045,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52068,7 +52071,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52094,7 +52097,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52120,7 +52123,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52146,7 +52149,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52172,7 +52175,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52198,7 +52201,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52224,7 +52227,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52250,7 +52253,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52276,7 +52279,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52302,7 +52305,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52328,7 +52331,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52354,7 +52357,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52380,7 +52383,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52406,7 +52409,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52432,7 +52435,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52458,7 +52461,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52484,7 +52487,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52510,7 +52513,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52536,7 +52539,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52562,7 +52565,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52588,7 +52591,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52614,7 +52617,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52640,7 +52643,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52666,7 +52669,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52692,7 +52695,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52718,7 +52721,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52744,7 +52747,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52770,7 +52773,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52796,7 +52799,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52822,7 +52825,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52848,7 +52851,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52874,7 +52877,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52900,7 +52903,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52926,7 +52929,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52952,7 +52955,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52978,7 +52981,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53004,7 +53007,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53030,7 +53033,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53056,7 +53059,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53082,7 +53085,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53108,7 +53111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53134,7 +53137,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53160,7 +53163,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53186,7 +53189,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53212,7 +53215,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53238,7 +53241,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53264,7 +53267,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53290,7 +53293,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53316,7 +53319,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53342,7 +53345,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53368,7 +53371,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53394,7 +53397,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53420,7 +53423,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53446,7 +53449,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53472,7 +53475,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53498,7 +53501,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53524,7 +53527,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53550,7 +53553,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53576,7 +53579,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53602,7 +53605,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53628,7 +53631,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53654,7 +53657,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53680,7 +53683,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53706,7 +53709,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53732,7 +53735,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53758,7 +53761,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53784,7 +53787,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53810,7 +53813,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53836,7 +53839,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53862,7 +53865,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53888,7 +53891,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53914,7 +53917,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53940,7 +53943,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53966,7 +53969,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53992,7 +53995,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54018,7 +54021,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54044,7 +54047,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54070,7 +54073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54096,7 +54099,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54122,7 +54125,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54148,7 +54151,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54174,7 +54177,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54200,7 +54203,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54226,7 +54229,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54252,7 +54255,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54278,7 +54281,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54304,7 +54307,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54330,7 +54333,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54356,7 +54359,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54382,7 +54385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54408,7 +54411,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54434,7 +54437,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54460,7 +54463,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54486,7 +54489,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54512,7 +54515,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54538,7 +54541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54564,7 +54567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54590,7 +54593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54616,7 +54619,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54642,7 +54645,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54668,7 +54671,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54694,7 +54697,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54720,7 +54723,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54746,7 +54749,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54772,7 +54775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54798,7 +54801,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54824,7 +54827,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54850,7 +54853,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54876,7 +54879,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54902,7 +54905,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54928,7 +54931,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54954,7 +54957,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54980,7 +54983,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55006,7 +55009,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55032,7 +55035,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55058,7 +55061,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55084,7 +55087,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55110,7 +55113,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55136,7 +55139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55162,7 +55165,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55188,7 +55191,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55214,7 +55217,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55240,7 +55243,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55266,7 +55269,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55292,7 +55295,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55318,7 +55321,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55344,7 +55347,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55370,7 +55373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55396,7 +55399,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55422,7 +55425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55448,7 +55451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55474,7 +55477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55500,7 +55503,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55526,7 +55529,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55552,7 +55555,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55578,7 +55581,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55604,7 +55607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55630,7 +55633,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55656,7 +55659,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55682,7 +55685,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55708,7 +55711,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55734,7 +55737,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55760,7 +55763,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55786,7 +55789,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55812,7 +55815,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55838,7 +55841,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55864,7 +55867,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55890,7 +55893,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55916,7 +55919,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55942,7 +55945,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55968,7 +55971,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55994,7 +55997,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56020,7 +56023,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56046,7 +56049,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56072,7 +56075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56098,7 +56101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56124,7 +56127,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56150,7 +56153,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56176,7 +56179,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56202,7 +56205,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56228,7 +56231,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56254,7 +56257,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56280,7 +56283,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56306,7 +56309,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56332,7 +56335,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56358,7 +56361,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56384,7 +56387,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56410,7 +56413,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56436,7 +56439,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56462,7 +56465,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56488,7 +56491,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56514,7 +56517,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56540,7 +56543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56566,7 +56569,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56592,7 +56595,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56618,7 +56621,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56644,7 +56647,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56670,7 +56673,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56696,7 +56699,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56722,7 +56725,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56748,7 +56751,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56774,7 +56777,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56800,7 +56803,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56826,7 +56829,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56852,7 +56855,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56878,7 +56881,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56904,7 +56907,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56930,7 +56933,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56956,7 +56959,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56982,7 +56985,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57008,7 +57011,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57034,7 +57037,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57060,7 +57063,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57086,7 +57089,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57112,7 +57115,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57138,7 +57141,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57164,7 +57167,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57190,7 +57193,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57216,7 +57219,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57242,7 +57245,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57268,7 +57271,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57294,7 +57297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57320,7 +57323,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57346,7 +57349,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57372,7 +57375,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57398,7 +57401,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57424,7 +57427,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57450,7 +57453,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57476,7 +57479,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57502,7 +57505,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57528,7 +57531,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57554,7 +57557,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57580,7 +57583,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57606,7 +57609,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57632,7 +57635,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57658,7 +57661,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57684,7 +57687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57710,7 +57713,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57736,7 +57739,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57762,7 +57765,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57788,7 +57791,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57814,7 +57817,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57840,7 +57843,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57866,7 +57869,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57892,7 +57895,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57918,7 +57921,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57944,7 +57947,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57970,7 +57973,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57996,7 +57999,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58022,7 +58025,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58048,7 +58051,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58074,7 +58077,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58100,7 +58103,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58126,7 +58129,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58152,7 +58155,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58178,7 +58181,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58204,7 +58207,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58230,7 +58233,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58256,7 +58259,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58282,7 +58285,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58308,7 +58311,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58334,7 +58337,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58360,7 +58363,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58386,7 +58389,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58412,7 +58415,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58438,7 +58441,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58464,7 +58467,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58490,7 +58493,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58516,7 +58519,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58542,7 +58545,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58568,7 +58571,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58594,7 +58597,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58620,7 +58623,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58646,7 +58649,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58672,7 +58675,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58698,7 +58701,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58724,7 +58727,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58750,7 +58753,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58776,7 +58779,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58802,7 +58805,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58828,7 +58831,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58854,7 +58857,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58880,7 +58883,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58906,7 +58909,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58932,7 +58935,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58958,7 +58961,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58984,7 +58987,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59010,7 +59013,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59036,7 +59039,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59062,7 +59065,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59088,7 +59091,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59114,7 +59117,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59140,7 +59143,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59166,7 +59169,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59192,7 +59195,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59218,7 +59221,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59244,7 +59247,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59270,7 +59273,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59296,7 +59299,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59322,7 +59325,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59348,7 +59351,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59374,7 +59377,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59400,7 +59403,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59426,7 +59429,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59452,7 +59455,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59478,7 +59481,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59504,7 +59507,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59530,7 +59533,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59556,7 +59559,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59582,7 +59585,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59608,7 +59611,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59634,7 +59637,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59660,7 +59663,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59686,7 +59689,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59712,7 +59715,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59738,7 +59741,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59764,7 +59767,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59790,7 +59793,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59816,7 +59819,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59842,7 +59845,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59868,7 +59871,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59894,7 +59897,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59920,7 +59923,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59946,7 +59949,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59972,7 +59975,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -59998,7 +60001,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60024,7 +60027,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60050,7 +60053,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60076,7 +60079,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60102,7 +60105,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60128,7 +60131,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60154,7 +60157,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60180,7 +60183,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60206,7 +60209,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60232,7 +60235,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60258,7 +60261,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60284,7 +60287,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60310,7 +60313,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60336,7 +60339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60362,7 +60365,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60388,7 +60391,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60414,7 +60417,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60440,7 +60443,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60466,7 +60469,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60492,7 +60495,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60518,7 +60521,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60544,7 +60547,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60570,7 +60573,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60596,7 +60599,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60622,7 +60625,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60648,7 +60651,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60674,7 +60677,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60700,7 +60703,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60726,7 +60729,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60752,7 +60755,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60778,7 +60781,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60804,7 +60807,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60830,7 +60833,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60856,7 +60859,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60882,7 +60885,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60908,7 +60911,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60934,7 +60937,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60960,7 +60963,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60986,7 +60989,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61012,7 +61015,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61038,7 +61041,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61064,7 +61067,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61090,7 +61093,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61116,7 +61119,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61142,7 +61145,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61168,7 +61171,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61194,7 +61197,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61220,7 +61223,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61246,7 +61249,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61272,7 +61275,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61298,7 +61301,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61324,7 +61327,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61350,7 +61353,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61376,7 +61379,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61402,7 +61405,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61428,7 +61431,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61454,7 +61457,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61480,7 +61483,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61506,7 +61509,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61532,7 +61535,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61558,7 +61561,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61584,7 +61587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61610,7 +61613,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61636,7 +61639,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61662,7 +61665,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61688,7 +61691,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61714,7 +61717,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61740,7 +61743,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61766,7 +61769,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61792,7 +61795,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61818,7 +61821,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61844,7 +61847,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61870,7 +61873,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61896,7 +61899,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61922,7 +61925,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61948,7 +61951,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61974,7 +61977,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62000,7 +62003,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62026,7 +62029,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62052,7 +62055,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62078,7 +62081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62104,7 +62107,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62130,7 +62133,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62156,7 +62159,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62182,7 +62185,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62208,7 +62211,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62234,7 +62237,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62260,7 +62263,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62286,7 +62289,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62312,7 +62315,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62338,7 +62341,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62364,7 +62367,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62390,7 +62393,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62416,7 +62419,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62442,7 +62445,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62468,7 +62471,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62494,7 +62497,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62520,7 +62523,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62546,7 +62549,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62572,7 +62575,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62598,7 +62601,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62624,7 +62627,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62650,7 +62653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62676,7 +62679,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62702,7 +62705,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62728,7 +62731,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62754,7 +62757,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62780,7 +62783,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62806,7 +62809,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62832,7 +62835,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62858,7 +62861,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62884,7 +62887,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62910,7 +62913,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62936,7 +62939,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62962,7 +62965,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62988,7 +62991,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63014,7 +63017,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63040,7 +63043,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63066,7 +63069,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63092,7 +63095,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63118,7 +63121,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63144,7 +63147,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63170,7 +63173,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63196,7 +63199,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63222,7 +63225,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63248,7 +63251,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63274,7 +63277,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63300,7 +63303,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63326,7 +63329,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63352,7 +63355,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63378,7 +63381,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63404,7 +63407,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63430,7 +63433,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63456,7 +63459,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63482,7 +63485,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63508,7 +63511,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63534,7 +63537,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63560,7 +63563,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63586,7 +63589,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63612,7 +63615,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63638,7 +63641,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63664,7 +63667,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63690,7 +63693,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63716,7 +63719,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63742,7 +63745,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63768,7 +63771,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63794,7 +63797,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63820,7 +63823,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63846,7 +63849,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63872,7 +63875,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63898,7 +63901,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63924,7 +63927,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63950,7 +63953,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63976,7 +63979,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64002,7 +64005,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64028,7 +64031,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64054,7 +64057,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64080,7 +64083,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64106,7 +64109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64132,7 +64135,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64158,7 +64161,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64184,7 +64187,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64210,7 +64213,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64236,7 +64239,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64262,7 +64265,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64288,7 +64291,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64314,7 +64317,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64340,7 +64343,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64366,7 +64369,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64392,7 +64395,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64418,7 +64421,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64444,7 +64447,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64470,7 +64473,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64496,7 +64499,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64522,7 +64525,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64548,7 +64551,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64574,7 +64577,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64600,7 +64603,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64626,7 +64629,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64652,7 +64655,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64678,7 +64681,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64704,7 +64707,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64730,7 +64733,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64756,7 +64759,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64782,7 +64785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64808,7 +64811,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64834,7 +64837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64860,7 +64863,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64886,7 +64889,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64912,7 +64915,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64938,7 +64941,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64964,7 +64967,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64990,7 +64993,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65016,7 +65019,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65042,7 +65045,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65068,7 +65071,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65094,7 +65097,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65120,7 +65123,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65146,7 +65149,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65172,7 +65175,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65198,7 +65201,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65224,7 +65227,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65250,7 +65253,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65276,7 +65279,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65302,7 +65305,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65328,7 +65331,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65354,7 +65357,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65380,7 +65383,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65406,7 +65409,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65432,7 +65435,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65458,7 +65461,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65484,7 +65487,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65510,7 +65513,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65536,7 +65539,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65562,7 +65565,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65588,7 +65591,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65614,7 +65617,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65640,7 +65643,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65666,7 +65669,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65692,7 +65695,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65718,7 +65721,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65744,7 +65747,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65770,7 +65773,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65796,7 +65799,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65822,7 +65825,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65848,7 +65851,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65874,7 +65877,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65900,7 +65903,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65926,7 +65929,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65952,7 +65955,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65978,7 +65981,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66004,7 +66007,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66030,7 +66033,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66056,7 +66059,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66082,7 +66085,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66108,7 +66111,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66134,7 +66137,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66160,7 +66163,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66186,7 +66189,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66212,7 +66215,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66238,7 +66241,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66264,7 +66267,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66290,7 +66293,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66316,7 +66319,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66342,7 +66345,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66368,7 +66371,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66394,7 +66397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66420,7 +66423,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66446,7 +66449,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66472,7 +66475,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66498,7 +66501,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66524,7 +66527,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66550,7 +66553,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66576,7 +66579,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66602,7 +66605,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66628,7 +66631,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66654,7 +66657,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66680,7 +66683,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66706,7 +66709,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66732,7 +66735,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66758,7 +66761,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66784,7 +66787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2504" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -66810,7 +66813,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -66836,7 +66839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -66862,7 +66865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -66888,7 +66891,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -66914,7 +66917,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2509" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -66940,7 +66943,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2510" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -66966,7 +66969,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2511" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -66992,7 +66995,7 @@
         <v>11.5</v>
       </c>
       <c r="G2512" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67018,7 +67021,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67044,7 +67047,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2514" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67070,7 +67073,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2515" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67096,7 +67099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67104,7 +67107,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.5830439815</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>120</v>
@@ -67122,9 +67125,35 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2517" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6807986111</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>3570</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194976806641</t>
+    <t xml:space="preserve">13.2194986343384</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">12.8577013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716173171997</t>
   </si>
   <si>
     <t xml:space="preserve">12.523736000061</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.175853729248</t>
+    <t xml:space="preserve">12.1758546829224</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809129714966</t>
+    <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755996704102</t>
+    <t xml:space="preserve">10.5755968093872</t>
   </si>
   <si>
     <t xml:space="preserve">9.91462326049805</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.311206817627</t>
+    <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060224533081</t>
+    <t xml:space="preserve">10.5060234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990644454956</t>
+    <t xml:space="preserve">10.4990653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364461898804</t>
+    <t xml:space="preserve">10.4364452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147521972656</t>
+    <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
@@ -110,76 +110,76 @@
     <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826847076416</t>
+    <t xml:space="preserve">11.3826856613159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331596374512</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905897140503</t>
+    <t xml:space="preserve">11.8905916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148024559021</t>
+    <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193696975708</t>
+    <t xml:space="preserve">12.4193687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628885269165</t>
+    <t xml:space="preserve">12.6628856658936</t>
   </si>
   <si>
     <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150062561035</t>
+    <t xml:space="preserve">12.3150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506153106689</t>
+    <t xml:space="preserve">12.0506172180176</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583961486816</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.9841327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163696289062</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045276641846</t>
+    <t xml:space="preserve">11.9045257568359</t>
   </si>
   <si>
     <t xml:space="preserve">11.7670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065040588379</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893991470337</t>
+    <t xml:space="preserve">11.289400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426864624023</t>
+    <t xml:space="preserve">11.542688369751</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979511260986</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">11.832160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130786895752</t>
+    <t xml:space="preserve">12.0130796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.08544921875</t>
+    <t xml:space="preserve">12.0854482650757</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939973831177</t>
+    <t xml:space="preserve">12.1939992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025503158569</t>
+    <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275526046753</t>
+    <t xml:space="preserve">12.0275545120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.295313835144</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643915176392</t>
+    <t xml:space="preserve">12.6643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466247558594</t>
+    <t xml:space="preserve">12.9466276168823</t>
   </si>
   <si>
     <t xml:space="preserve">12.7729425430298</t>
@@ -242,85 +242,85 @@
     <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157024383545</t>
+    <t xml:space="preserve">13.3157014846802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604368209839</t>
+    <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.388069152832</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025430679321</t>
+    <t xml:space="preserve">13.4025440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.453200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242553710938</t>
+    <t xml:space="preserve">13.4242534637451</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689916610718</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.554518699646</t>
+    <t xml:space="preserve">13.5545148849487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966220855713</t>
+    <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459648132324</t>
+    <t xml:space="preserve">13.4459657669067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387283325195</t>
+    <t xml:space="preserve">13.4387264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071504592896</t>
+    <t xml:space="preserve">13.2071495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038614273071</t>
+    <t xml:space="preserve">13.5038585662842</t>
   </si>
   <si>
     <t xml:space="preserve">13.2288608551025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881495475769</t>
+    <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985984802246</t>
+    <t xml:space="preserve">13.098596572876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104423522949</t>
+    <t xml:space="preserve">12.9104433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262327194214</t>
+    <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134783744812</t>
+    <t xml:space="preserve">13.1347818374634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.845311164856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275463104248</t>
+    <t xml:space="preserve">13.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439956665039</t>
+    <t xml:space="preserve">12.7439975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189943313599</t>
+    <t xml:space="preserve">13.0189952850342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571531295776</t>
+    <t xml:space="preserve">12.657154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446565628052</t>
+    <t xml:space="preserve">12.2446584701538</t>
   </si>
   <si>
     <t xml:space="preserve">12.2012357711792</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143951416016</t>
+    <t xml:space="preserve">12.1143960952759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.070972442627</t>
+    <t xml:space="preserve">12.0709743499756</t>
   </si>
   <si>
-    <t xml:space="preserve">12.049262046814</t>
+    <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466329574585</t>
+    <t xml:space="preserve">11.8466320037842</t>
   </si>
   <si>
     <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913702011108</t>
+    <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
     <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479475021362</t>
+    <t xml:space="preserve">11.9479465484619</t>
   </si>
   <si>
     <t xml:space="preserve">12.172287940979</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">11.9551849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696598052979</t>
+    <t xml:space="preserve">11.9696578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768934249878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597894668579</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301816940308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229471206665</t>
+    <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
     <t xml:space="preserve">12.1554155349731</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">12.3805170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132905960083</t>
+    <t xml:space="preserve">12.1329069137573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428647994995</t>
+    <t xml:space="preserve">12.0428667068481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129873275757</t>
+    <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
     <t xml:space="preserve">12.4180326461792</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158437728882</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
     <t xml:space="preserve">12.9807844161987</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">12.9732809066772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881532669067</t>
+    <t xml:space="preserve">12.6881523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657783508301</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432668685913</t>
+    <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308507919312</t>
+    <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">12.8682346343994</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083393096924</t>
+    <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
     <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3559503555298</t>
+    <t xml:space="preserve">13.3559494018555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809181213379</t>
+    <t xml:space="preserve">13.2809171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.430983543396</t>
+    <t xml:space="preserve">13.4309825897217</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435352325439</t>
+    <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
+    <t xml:space="preserve">13.1383543014526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2058839797974</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685029983521</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
     <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433996200562</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683654785156</t>
+    <t xml:space="preserve">13.1683692932129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060195922852</t>
+    <t xml:space="preserve">13.5060176849365</t>
   </si>
   <si>
     <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185684204102</t>
+    <t xml:space="preserve">13.6185665130615</t>
   </si>
   <si>
     <t xml:space="preserve">13.8061513900757</t>
@@ -497,31 +497,31 @@
     <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687704086304</t>
+    <t xml:space="preserve">14.0687694549561</t>
   </si>
   <si>
     <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485824584961</t>
+    <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.415979385376</t>
+    <t xml:space="preserve">13.4159784317017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562168121338</t>
+    <t xml:space="preserve">13.9562187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312528610229</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459915161133</t>
+    <t xml:space="preserve">13.445990562439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986478805542</t>
+    <t xml:space="preserve">13.7986469268799</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087413787842</t>
@@ -533,43 +533,43 @@
     <t xml:space="preserve">14.3013725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165142059326</t>
+    <t xml:space="preserve">14.616512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991817474365</t>
+    <t xml:space="preserve">14.9991827011108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066871643066</t>
+    <t xml:space="preserve">15.006688117981</t>
   </si>
   <si>
     <t xml:space="preserve">14.9916791915894</t>
   </si>
   <si>
-    <t xml:space="preserve">14.976674079895</t>
+    <t xml:space="preserve">14.9766750335693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691705703735</t>
+    <t xml:space="preserve">14.9691715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465253829956</t>
+    <t xml:space="preserve">14.6465272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941335678101</t>
+    <t xml:space="preserve">14.894136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567525863647</t>
+    <t xml:space="preserve">15.1567516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069526672363</t>
+    <t xml:space="preserve">15.6069536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568872451782</t>
+    <t xml:space="preserve">15.4568853378296</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570209503174</t>
@@ -581,46 +581,46 @@
     <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078876495361</t>
+    <t xml:space="preserve">17.707893371582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076202392578</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
     <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073528289795</t>
+    <t xml:space="preserve">16.5073547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074893951416</t>
+    <t xml:space="preserve">16.8074913024902</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571556091309</t>
+    <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528678894043</t>
+    <t xml:space="preserve">16.052864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702861785889</t>
+    <t xml:space="preserve">16.6702880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723834991455</t>
+    <t xml:space="preserve">14.9723854064941</t>
   </si>
   <si>
     <t xml:space="preserve">15.5898017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354515075684</t>
+    <t xml:space="preserve">15.4354524612427</t>
   </si>
   <si>
     <t xml:space="preserve">15.7441596984863</t>
@@ -632,55 +632,55 @@
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985118865967</t>
+    <t xml:space="preserve">15.8985109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267414093018</t>
+    <t xml:space="preserve">15.1267395019531</t>
   </si>
   <si>
     <t xml:space="preserve">15.049560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636762619019</t>
+    <t xml:space="preserve">14.6636753082275</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810916900635</t>
+    <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549671173096</t>
+    <t xml:space="preserve">14.3549680709839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321451187134</t>
+    <t xml:space="preserve">14.4321460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919057846069</t>
+    <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522125244141</t>
+    <t xml:space="preserve">14.2522115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319381713867</t>
+    <t xml:space="preserve">13.9319372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.771800994873</t>
+    <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
     <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917324066162</t>
+    <t xml:space="preserve">13.6917314529419</t>
   </si>
   <si>
     <t xml:space="preserve">14.1721448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116647720337</t>
+    <t xml:space="preserve">13.6116628646851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120067596436</t>
+    <t xml:space="preserve">14.0120077133179</t>
   </si>
   <si>
     <t xml:space="preserve">13.8518705368042</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2913885116577</t>
+    <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123516082764</t>
+    <t xml:space="preserve">14.4123506546021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312532424927</t>
+    <t xml:space="preserve">13.1312522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511827468872</t>
+    <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711151123047</t>
+    <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
     <t xml:space="preserve">12.810977935791</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.490704536438</t>
+    <t xml:space="preserve">12.4907026290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508417129517</t>
+    <t xml:space="preserve">12.6508407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106359481812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302225112915</t>
+    <t xml:space="preserve">11.9302234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900186538696</t>
+    <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707721710205</t>
+    <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.3305673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903596878052</t>
+    <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704301834106</t>
@@ -749,61 +749,61 @@
     <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896738052368</t>
+    <t xml:space="preserve">11.2896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498119354248</t>
+    <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099481582642</t>
+    <t xml:space="preserve">11.6099472045898</t>
   </si>
   <si>
     <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697443008423</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
     <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9694004058838</t>
+    <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494699478149</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491241455078</t>
+    <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288497924805</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889879226685</t>
+    <t xml:space="preserve">10.4889869689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487840652466</t>
+    <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
     <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687135696411</t>
+    <t xml:space="preserve">10.1687145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.849328994751</t>
+    <t xml:space="preserve">12.8493280410767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5990171432495</t>
+    <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
     <t xml:space="preserve">12.348705291748</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6812057495117</t>
+    <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9315176010132</t>
+    <t xml:space="preserve">11.9315185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818313598633</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321422576904</t>
+    <t xml:space="preserve">12.4321413040161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5155792236328</t>
@@ -842,67 +842,67 @@
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.76589012146</t>
+    <t xml:space="preserve">12.7658910751343</t>
   </si>
   <si>
     <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180711746216</t>
+    <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
     <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346342086792</t>
+    <t xml:space="preserve">14.4346332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021327972412</t>
+    <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186948776245</t>
+    <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849451065063</t>
+    <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015062332153</t>
+    <t xml:space="preserve">14.6015071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511962890625</t>
+    <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843223571777</t>
+    <t xml:space="preserve">14.1843233108521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837015151978</t>
+    <t xml:space="preserve">13.6837005615234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671365737915</t>
+    <t xml:space="preserve">13.7671375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002616882324</t>
+    <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741500854492</t>
+    <t xml:space="preserve">13.5741519927979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255233764648</t>
+    <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
     <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417335510254</t>
   </si>
   <si>
     <t xml:space="preserve">13.993106842041</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
@@ -926,43 +926,43 @@
     <t xml:space="preserve">13.4903602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282699584961</t>
+    <t xml:space="preserve">14.3282709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634330749512</t>
+    <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8310174942017</t>
+    <t xml:space="preserve">14.8310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958515167236</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9986000061035</t>
+    <t xml:space="preserve">14.9985971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472257614136</t>
+    <t xml:space="preserve">14.7472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148082733154</t>
+    <t xml:space="preserve">14.9148063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661825180054</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337621688843</t>
+    <t xml:space="preserve">15.3337631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175519943237</t>
+    <t xml:space="preserve">15.4175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499713897705</t>
+    <t xml:space="preserve">15.2499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823888778687</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851345062256</t>
   </si>
   <si>
     <t xml:space="preserve">15.668927192688</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878829956055</t>
+    <t xml:space="preserve">16.0878849029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923503875732</t>
+    <t xml:space="preserve">16.1923484802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0182361602783</t>
+    <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700143814087</t>
+    <t xml:space="preserve">15.6700162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829610824585</t>
+    <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405731201172</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8887920379639</t>
+    <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">16.8017387390137</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.585241317749</t>
+    <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.6299057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.107572555542</t>
+    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557971954346</t>
+    <t xml:space="preserve">18.4557952880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1055,19 +1055,16 @@
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4697246551514</t>
+    <t xml:space="preserve">18.4697265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.2886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
     <t xml:space="preserve">17.8359622955322</t>
@@ -1091,34 +1088,34 @@
     <t xml:space="preserve">17.6548843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021961212158</t>
+    <t xml:space="preserve">17.2021942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2927341461182</t>
+    <t xml:space="preserve">17.2927322387695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778919219971</t>
+    <t xml:space="preserve">16.4778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157417297363</t>
+    <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441257476807</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2062797546387</t>
+    <t xml:space="preserve">16.20627784729</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1127,22 +1124,22 @@
     <t xml:space="preserve">15.9346656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8400440216064</t>
+    <t xml:space="preserve">16.8400421142578</t>
   </si>
   <si>
     <t xml:space="preserve">16.6589660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3873558044434</t>
+    <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
     <t xml:space="preserve">15.6630516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535905838013</t>
+    <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819755554199</t>
+    <t xml:space="preserve">15.4819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">14.3955211639404</t>
@@ -1154,19 +1151,19 @@
     <t xml:space="preserve">13.5806798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1239080429077</t>
+    <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3049840927124</t>
+    <t xml:space="preserve">14.3049831390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.3996047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901428222656</t>
+    <t xml:space="preserve">13.4901418685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
@@ -1181,13 +1178,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1202,13 +1199,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1223,7 +1220,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1275,6 +1272,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -43621,7 +43621,7 @@
         <v>20</v>
       </c>
       <c r="G1613" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43647,7 +43647,7 @@
         <v>20</v>
       </c>
       <c r="G1614" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43699,7 +43699,7 @@
         <v>20</v>
       </c>
       <c r="G1616" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43725,7 +43725,7 @@
         <v>20</v>
       </c>
       <c r="G1617" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43751,7 +43751,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43777,7 +43777,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1619" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43803,7 +43803,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1620" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43829,7 +43829,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1621" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43855,7 +43855,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43881,7 +43881,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43907,7 +43907,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43933,7 +43933,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43959,7 +43959,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43985,7 +43985,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44011,7 +44011,7 @@
         <v>20</v>
       </c>
       <c r="G1628" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44037,7 +44037,7 @@
         <v>20</v>
       </c>
       <c r="G1629" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44063,7 +44063,7 @@
         <v>20</v>
       </c>
       <c r="G1630" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44089,7 +44089,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1631" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44115,7 +44115,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44141,7 +44141,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1633" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44167,7 +44167,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1634" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44193,7 +44193,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44219,7 +44219,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44245,7 +44245,7 @@
         <v>19.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44271,7 +44271,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44297,7 +44297,7 @@
         <v>19.5</v>
       </c>
       <c r="G1639" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44323,7 +44323,7 @@
         <v>19</v>
       </c>
       <c r="G1640" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44349,7 +44349,7 @@
         <v>19</v>
       </c>
       <c r="G1641" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44375,7 +44375,7 @@
         <v>19</v>
       </c>
       <c r="G1642" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44401,7 +44401,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44427,7 +44427,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44453,7 +44453,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1645" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44479,7 +44479,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1646" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44505,7 +44505,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1647" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44531,7 +44531,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1648" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44557,7 +44557,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44583,7 +44583,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44609,7 +44609,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44635,7 +44635,7 @@
         <v>19</v>
       </c>
       <c r="G1652" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44661,7 +44661,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44687,7 +44687,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1654" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44713,7 +44713,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44739,7 +44739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44765,7 +44765,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44791,7 +44791,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44817,7 +44817,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44843,7 +44843,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44869,7 +44869,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44895,7 +44895,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44921,7 +44921,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44947,7 +44947,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44973,7 +44973,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44999,7 +44999,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45025,7 +45025,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45051,7 +45051,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45077,7 +45077,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45103,7 +45103,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45129,7 +45129,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45155,7 +45155,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45181,7 +45181,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45207,7 +45207,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45233,7 +45233,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45259,7 +45259,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45285,7 +45285,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45311,7 +45311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45337,7 +45337,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45363,7 +45363,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45389,7 +45389,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45415,7 +45415,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45441,7 +45441,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45467,7 +45467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45493,7 +45493,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1685" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45519,7 +45519,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45545,7 +45545,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45571,7 +45571,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1688" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45597,7 +45597,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1689" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45623,7 +45623,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45649,7 +45649,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1691" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45675,7 +45675,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1692" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45701,7 +45701,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1693" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45727,7 +45727,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45753,7 +45753,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1695" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45779,7 +45779,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45805,7 +45805,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1697" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45831,7 +45831,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45857,7 +45857,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45883,7 +45883,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45909,7 +45909,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1701" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45935,7 +45935,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45961,7 +45961,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45987,7 +45987,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46013,7 +46013,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46039,7 +46039,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46065,7 +46065,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46091,7 +46091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46117,7 +46117,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46143,7 +46143,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46169,7 +46169,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46195,7 +46195,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46221,7 +46221,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46247,7 +46247,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46273,7 +46273,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46299,7 +46299,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1716" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46325,7 +46325,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46351,7 +46351,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46377,7 +46377,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46403,7 +46403,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46429,7 +46429,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1721" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46455,7 +46455,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46481,7 +46481,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46507,7 +46507,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46533,7 +46533,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1725" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46559,7 +46559,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46585,7 +46585,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46611,7 +46611,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46637,7 +46637,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46663,7 +46663,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46689,7 +46689,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46715,7 +46715,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46741,7 +46741,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46767,7 +46767,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46793,7 +46793,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46819,7 +46819,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46845,7 +46845,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46871,7 +46871,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46897,7 +46897,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46923,7 +46923,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46949,7 +46949,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46975,7 +46975,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47001,7 +47001,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47027,7 +47027,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47053,7 +47053,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47079,7 +47079,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47105,7 +47105,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1747" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47131,7 +47131,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47157,7 +47157,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47183,7 +47183,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47209,7 +47209,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47235,7 +47235,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47261,7 +47261,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47287,7 +47287,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47313,7 +47313,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47339,7 +47339,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47365,7 +47365,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47391,7 +47391,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47417,7 +47417,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47443,7 +47443,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1760" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47469,7 +47469,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47495,7 +47495,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1762" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47521,7 +47521,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47547,7 +47547,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47573,7 +47573,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47599,7 +47599,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47625,7 +47625,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47651,7 +47651,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47677,7 +47677,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47703,7 +47703,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47729,7 +47729,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47755,7 +47755,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1772" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47781,7 +47781,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47807,7 +47807,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47833,7 +47833,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47859,7 +47859,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47885,7 +47885,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47911,7 +47911,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47937,7 +47937,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47963,7 +47963,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47989,7 +47989,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48015,7 +48015,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48041,7 +48041,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48067,7 +48067,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48093,7 +48093,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48119,7 +48119,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48145,7 +48145,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48171,7 +48171,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48197,7 +48197,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48223,7 +48223,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48249,7 +48249,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48275,7 +48275,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48301,7 +48301,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48327,7 +48327,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48353,7 +48353,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48379,7 +48379,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48405,7 +48405,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1797" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48431,7 +48431,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48457,7 +48457,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1799" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48483,7 +48483,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48509,7 +48509,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1801" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48535,7 +48535,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48561,7 +48561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48587,7 +48587,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48613,7 +48613,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48639,7 +48639,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48665,7 +48665,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48691,7 +48691,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48717,7 +48717,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48743,7 +48743,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48769,7 +48769,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48795,7 +48795,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48821,7 +48821,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48847,7 +48847,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48873,7 +48873,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48899,7 +48899,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48925,7 +48925,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48951,7 +48951,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48977,7 +48977,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49003,7 +49003,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49029,7 +49029,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49055,7 +49055,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49081,7 +49081,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49107,7 +49107,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49133,7 +49133,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49159,7 +49159,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49185,7 +49185,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49211,7 +49211,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49237,7 +49237,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49263,7 +49263,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49289,7 +49289,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49315,7 +49315,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49341,7 +49341,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49367,7 +49367,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49393,7 +49393,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49419,7 +49419,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49445,7 +49445,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49471,7 +49471,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49497,7 +49497,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49523,7 +49523,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49549,7 +49549,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49575,7 +49575,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49601,7 +49601,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49627,7 +49627,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49653,7 +49653,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49679,7 +49679,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49705,7 +49705,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49731,7 +49731,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49757,7 +49757,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49783,7 +49783,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49809,7 +49809,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49835,7 +49835,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49861,7 +49861,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49887,7 +49887,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49913,7 +49913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49939,7 +49939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49965,7 +49965,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49991,7 +49991,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50017,7 +50017,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50043,7 +50043,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50069,7 +50069,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50095,7 +50095,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50121,7 +50121,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50147,7 +50147,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50173,7 +50173,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50199,7 +50199,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50225,7 +50225,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50251,7 +50251,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50277,7 +50277,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50303,7 +50303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50329,7 +50329,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50355,7 +50355,7 @@
         <v>15.5</v>
       </c>
       <c r="G1872" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50381,7 +50381,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1873" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50407,7 +50407,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1874" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50433,7 +50433,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1875" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50459,7 +50459,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50485,7 +50485,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50511,7 +50511,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1878" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50537,7 +50537,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1879" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50563,7 +50563,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50589,7 +50589,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50615,7 +50615,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50641,7 +50641,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1883" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50667,7 +50667,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50693,7 +50693,7 @@
         <v>15</v>
       </c>
       <c r="G1885" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50719,7 +50719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50745,7 +50745,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50771,7 +50771,7 @@
         <v>15</v>
       </c>
       <c r="G1888" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50797,7 +50797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50823,7 +50823,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50849,7 +50849,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50875,7 +50875,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50901,7 +50901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50927,7 +50927,7 @@
         <v>15</v>
       </c>
       <c r="G1894" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50953,7 +50953,7 @@
         <v>15</v>
       </c>
       <c r="G1895" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50979,7 +50979,7 @@
         <v>15</v>
       </c>
       <c r="G1896" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51005,7 +51005,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51031,7 +51031,7 @@
         <v>15</v>
       </c>
       <c r="G1898" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51057,7 +51057,7 @@
         <v>15</v>
       </c>
       <c r="G1899" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51083,7 +51083,7 @@
         <v>15</v>
       </c>
       <c r="G1900" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51109,7 +51109,7 @@
         <v>15</v>
       </c>
       <c r="G1901" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51135,7 +51135,7 @@
         <v>15</v>
       </c>
       <c r="G1902" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51161,7 +51161,7 @@
         <v>15</v>
       </c>
       <c r="G1903" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51187,7 +51187,7 @@
         <v>15</v>
       </c>
       <c r="G1904" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51213,7 +51213,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1905" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51239,7 +51239,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51265,7 +51265,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1907" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51291,7 +51291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51317,7 +51317,7 @@
         <v>15</v>
       </c>
       <c r="G1909" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51343,7 +51343,7 @@
         <v>15</v>
       </c>
       <c r="G1910" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51369,7 +51369,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51395,7 +51395,7 @@
         <v>15</v>
       </c>
       <c r="G1912" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51421,7 +51421,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51447,7 +51447,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51473,7 +51473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1915" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51499,7 +51499,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51525,7 +51525,7 @@
         <v>15</v>
       </c>
       <c r="G1917" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51551,7 +51551,7 @@
         <v>15</v>
       </c>
       <c r="G1918" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51577,7 +51577,7 @@
         <v>15</v>
       </c>
       <c r="G1919" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51603,7 +51603,7 @@
         <v>15</v>
       </c>
       <c r="G1920" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51629,7 +51629,7 @@
         <v>15</v>
       </c>
       <c r="G1921" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51655,7 +51655,7 @@
         <v>15</v>
       </c>
       <c r="G1922" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51681,7 +51681,7 @@
         <v>15</v>
       </c>
       <c r="G1923" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51707,7 +51707,7 @@
         <v>15</v>
       </c>
       <c r="G1924" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51733,7 +51733,7 @@
         <v>15</v>
       </c>
       <c r="G1925" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51759,7 +51759,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51785,7 +51785,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51811,7 +51811,7 @@
         <v>15</v>
       </c>
       <c r="G1928" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51837,7 +51837,7 @@
         <v>15</v>
       </c>
       <c r="G1929" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51863,7 +51863,7 @@
         <v>15</v>
       </c>
       <c r="G1930" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51889,7 +51889,7 @@
         <v>15</v>
       </c>
       <c r="G1931" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51915,7 +51915,7 @@
         <v>15</v>
       </c>
       <c r="G1932" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51941,7 +51941,7 @@
         <v>15</v>
       </c>
       <c r="G1933" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51967,7 +51967,7 @@
         <v>15</v>
       </c>
       <c r="G1934" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51993,7 +51993,7 @@
         <v>15</v>
       </c>
       <c r="G1935" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52019,7 +52019,7 @@
         <v>15</v>
       </c>
       <c r="G1936" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52045,7 +52045,7 @@
         <v>15</v>
       </c>
       <c r="G1937" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52071,7 +52071,7 @@
         <v>15</v>
       </c>
       <c r="G1938" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52097,7 +52097,7 @@
         <v>15</v>
       </c>
       <c r="G1939" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52123,7 +52123,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1940" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52149,7 +52149,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52175,7 +52175,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52201,7 +52201,7 @@
         <v>15</v>
       </c>
       <c r="G1943" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52227,7 +52227,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52253,7 +52253,7 @@
         <v>15</v>
       </c>
       <c r="G1945" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52279,7 +52279,7 @@
         <v>15</v>
       </c>
       <c r="G1946" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52305,7 +52305,7 @@
         <v>15</v>
       </c>
       <c r="G1947" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52331,7 +52331,7 @@
         <v>15</v>
       </c>
       <c r="G1948" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52357,7 +52357,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52383,7 +52383,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52409,7 +52409,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52435,7 +52435,7 @@
         <v>15</v>
       </c>
       <c r="G1952" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52461,7 +52461,7 @@
         <v>15</v>
       </c>
       <c r="G1953" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52487,7 +52487,7 @@
         <v>15</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52513,7 +52513,7 @@
         <v>15</v>
       </c>
       <c r="G1955" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52539,7 +52539,7 @@
         <v>15</v>
       </c>
       <c r="G1956" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52565,7 +52565,7 @@
         <v>15</v>
       </c>
       <c r="G1957" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52591,7 +52591,7 @@
         <v>15</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52617,7 +52617,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52643,7 +52643,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52669,7 +52669,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1961" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52695,7 +52695,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52721,7 +52721,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52747,7 +52747,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52773,7 +52773,7 @@
         <v>15</v>
       </c>
       <c r="G1965" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52799,7 +52799,7 @@
         <v>15</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -52825,7 +52825,7 @@
         <v>15</v>
       </c>
       <c r="G1967" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -52851,7 +52851,7 @@
         <v>15</v>
       </c>
       <c r="G1968" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -52877,7 +52877,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -52903,7 +52903,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -52929,7 +52929,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -52955,7 +52955,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -52981,7 +52981,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1973" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53007,7 +53007,7 @@
         <v>15</v>
       </c>
       <c r="G1974" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53033,7 +53033,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53059,7 +53059,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53085,7 +53085,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53111,7 +53111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53137,7 +53137,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53163,7 +53163,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53189,7 +53189,7 @@
         <v>14.5</v>
       </c>
       <c r="G1981" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53215,7 +53215,7 @@
         <v>14.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53241,7 +53241,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53267,7 +53267,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53293,7 +53293,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1985" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53319,7 +53319,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1986" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53345,7 +53345,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53371,7 +53371,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53397,7 +53397,7 @@
         <v>14.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53423,7 +53423,7 @@
         <v>14.5</v>
       </c>
       <c r="G1990" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53449,7 +53449,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53475,7 +53475,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1992" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53501,7 +53501,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1993" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53527,7 +53527,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1994" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53553,7 +53553,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53579,7 +53579,7 @@
         <v>15</v>
       </c>
       <c r="G1996" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53605,7 +53605,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53631,7 +53631,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53657,7 +53657,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53683,7 +53683,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2000" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53709,7 +53709,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53735,7 +53735,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2002" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53761,7 +53761,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53787,7 +53787,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2004" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53813,7 +53813,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -53839,7 +53839,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2006" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -53865,7 +53865,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -53891,7 +53891,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2008" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -53917,7 +53917,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2009" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -53943,7 +53943,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -53969,7 +53969,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -53995,7 +53995,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54021,7 +54021,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2013" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54047,7 +54047,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2014" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54073,7 +54073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54099,7 +54099,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54125,7 +54125,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54151,7 +54151,7 @@
         <v>14.5</v>
       </c>
       <c r="G2018" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54177,7 +54177,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2019" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54203,7 +54203,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54229,7 +54229,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2021" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54255,7 +54255,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2022" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54281,7 +54281,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54307,7 +54307,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54333,7 +54333,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54359,7 +54359,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54385,7 +54385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2027" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54411,7 +54411,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54437,7 +54437,7 @@
         <v>14.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54463,7 +54463,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2030" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54489,7 +54489,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54515,7 +54515,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2032" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54541,7 +54541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54567,7 +54567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2034" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54593,7 +54593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2035" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54619,7 +54619,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2036" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54645,7 +54645,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2037" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54671,7 +54671,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54697,7 +54697,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54723,7 +54723,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54749,7 +54749,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54775,7 +54775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2042" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54801,7 +54801,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -54827,7 +54827,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -54853,7 +54853,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -54879,7 +54879,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -54905,7 +54905,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -54931,7 +54931,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -54957,7 +54957,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -54983,7 +54983,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2050" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55009,7 +55009,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55035,7 +55035,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55061,7 +55061,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55087,7 +55087,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2054" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55113,7 +55113,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55139,7 +55139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55165,7 +55165,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55191,7 +55191,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55217,7 +55217,7 @@
         <v>15</v>
       </c>
       <c r="G2059" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55243,7 +55243,7 @@
         <v>15</v>
       </c>
       <c r="G2060" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55269,7 +55269,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2061" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55295,7 +55295,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55321,7 +55321,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55347,7 +55347,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2064" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55373,7 +55373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2065" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55399,7 +55399,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2066" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55425,7 +55425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2067" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55451,7 +55451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55477,7 +55477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2069" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55503,7 +55503,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2070" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55529,7 +55529,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55555,7 +55555,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2072" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55581,7 +55581,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55607,7 +55607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2074" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55633,7 +55633,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55659,7 +55659,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2076" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55685,7 +55685,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55711,7 +55711,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55737,7 +55737,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55763,7 +55763,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2080" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55789,7 +55789,7 @@
         <v>14</v>
       </c>
       <c r="G2081" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55815,7 +55815,7 @@
         <v>14.5</v>
       </c>
       <c r="G2082" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -55841,7 +55841,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -55867,7 +55867,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2084" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -55893,7 +55893,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2085" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -55919,7 +55919,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -55945,7 +55945,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -55971,7 +55971,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2088" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -55997,7 +55997,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2089" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56023,7 +56023,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56049,7 +56049,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56075,7 +56075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56101,7 +56101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2093" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56127,7 +56127,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56153,7 +56153,7 @@
         <v>14</v>
       </c>
       <c r="G2095" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56179,7 +56179,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2096" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56205,7 +56205,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2097" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56231,7 +56231,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56257,7 +56257,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56283,7 +56283,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56309,7 +56309,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56335,7 +56335,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56361,7 +56361,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2103" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56387,7 +56387,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56413,7 +56413,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56439,7 +56439,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56465,7 +56465,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56491,7 +56491,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2108" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56517,7 +56517,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56543,7 +56543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2110" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56569,7 +56569,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2111" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56595,7 +56595,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56621,7 +56621,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2113" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56647,7 +56647,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2114" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56673,7 +56673,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2115" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56699,7 +56699,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56725,7 +56725,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56751,7 +56751,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56777,7 +56777,7 @@
         <v>14</v>
       </c>
       <c r="G2119" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56803,7 +56803,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -56829,7 +56829,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -56855,7 +56855,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2122" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -56881,7 +56881,7 @@
         <v>14</v>
       </c>
       <c r="G2123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -56907,7 +56907,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -56933,7 +56933,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2125" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -56959,7 +56959,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2126" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -56985,7 +56985,7 @@
         <v>14</v>
       </c>
       <c r="G2127" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57011,7 +57011,7 @@
         <v>14</v>
       </c>
       <c r="G2128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57037,7 +57037,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2129" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57063,7 +57063,7 @@
         <v>14</v>
       </c>
       <c r="G2130" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57089,7 +57089,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2131" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57115,7 +57115,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57141,7 +57141,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57167,7 +57167,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57193,7 +57193,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57219,7 +57219,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2136" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57245,7 +57245,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57271,7 +57271,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57297,7 +57297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2139" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57323,7 +57323,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57349,7 +57349,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2141" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57375,7 +57375,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2142" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57401,7 +57401,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57427,7 +57427,7 @@
         <v>14</v>
       </c>
       <c r="G2144" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57453,7 +57453,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2145" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57479,7 +57479,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57505,7 +57505,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2147" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57531,7 +57531,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2148" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57557,7 +57557,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57583,7 +57583,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57609,7 +57609,7 @@
         <v>14</v>
       </c>
       <c r="G2151" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57635,7 +57635,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57661,7 +57661,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2153" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57687,7 +57687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2154" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57713,7 +57713,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57739,7 +57739,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57765,7 +57765,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57791,7 +57791,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57817,7 +57817,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2159" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -57843,7 +57843,7 @@
         <v>14</v>
       </c>
       <c r="G2160" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -57869,7 +57869,7 @@
         <v>14</v>
       </c>
       <c r="G2161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -57895,7 +57895,7 @@
         <v>14</v>
       </c>
       <c r="G2162" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -57921,7 +57921,7 @@
         <v>14</v>
       </c>
       <c r="G2163" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -57947,7 +57947,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -57973,7 +57973,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2165" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -57999,7 +57999,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58025,7 +58025,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58051,7 +58051,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2168" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58077,7 +58077,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58103,7 +58103,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2170" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58129,7 +58129,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58155,7 +58155,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58181,7 +58181,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2173" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58207,7 +58207,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2174" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58233,7 +58233,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2175" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58259,7 +58259,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58285,7 +58285,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2177" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58311,7 +58311,7 @@
         <v>15</v>
       </c>
       <c r="G2178" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58337,7 +58337,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58363,7 +58363,7 @@
         <v>15</v>
       </c>
       <c r="G2180" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58389,7 +58389,7 @@
         <v>15</v>
       </c>
       <c r="G2181" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58415,7 +58415,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58441,7 +58441,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58467,7 +58467,7 @@
         <v>15</v>
       </c>
       <c r="G2184" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58493,7 +58493,7 @@
         <v>15</v>
       </c>
       <c r="G2185" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58519,7 +58519,7 @@
         <v>15</v>
       </c>
       <c r="G2186" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58545,7 +58545,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58571,7 +58571,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2188" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58597,7 +58597,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2189" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58623,7 +58623,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2190" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58649,7 +58649,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58675,7 +58675,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58701,7 +58701,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58727,7 +58727,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58753,7 +58753,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2195" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58779,7 +58779,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2196" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58805,7 +58805,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -58831,7 +58831,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -58857,7 +58857,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -58883,7 +58883,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -58909,7 +58909,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2201" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -58935,7 +58935,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -58961,7 +58961,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -58987,7 +58987,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59013,7 +59013,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59039,7 +59039,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59065,7 +59065,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59091,7 +59091,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59117,7 +59117,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2209" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59143,7 +59143,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59169,7 +59169,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2211" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59195,7 +59195,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59221,7 +59221,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59247,7 +59247,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59273,7 +59273,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59299,7 +59299,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59325,7 +59325,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59351,7 +59351,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59377,7 +59377,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2219" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59403,7 +59403,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2220" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59429,7 +59429,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2221" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59455,7 +59455,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59481,7 +59481,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2223" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59507,7 +59507,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59533,7 +59533,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2225" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59559,7 +59559,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2226" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59585,7 +59585,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59611,7 +59611,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2228" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59637,7 +59637,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59663,7 +59663,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2230" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59689,7 +59689,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2231" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59715,7 +59715,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2232" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59741,7 +59741,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59767,7 +59767,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2234" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59793,7 +59793,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59819,7 +59819,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2236" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -59845,7 +59845,7 @@
         <v>15</v>
       </c>
       <c r="G2237" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -59871,7 +59871,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -59897,7 +59897,7 @@
         <v>15</v>
       </c>
       <c r="G2239" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -59923,7 +59923,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2240" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -59949,7 +59949,7 @@
         <v>14.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -59975,7 +59975,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60001,7 +60001,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60027,7 +60027,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2244" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60053,7 +60053,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60079,7 +60079,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2246" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60105,7 +60105,7 @@
         <v>14.5</v>
       </c>
       <c r="G2247" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60131,7 +60131,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60157,7 +60157,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60183,7 +60183,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2250" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60209,7 +60209,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60235,7 +60235,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60261,7 +60261,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2253" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60287,7 +60287,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60313,7 +60313,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2255" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60339,7 +60339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2256" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60365,7 +60365,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2257" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60391,7 +60391,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60417,7 +60417,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60443,7 +60443,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2260" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60469,7 +60469,7 @@
         <v>14</v>
       </c>
       <c r="G2261" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60495,7 +60495,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60521,7 +60521,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60547,7 +60547,7 @@
         <v>14.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60573,7 +60573,7 @@
         <v>14.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60599,7 +60599,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2266" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60625,7 +60625,7 @@
         <v>14</v>
       </c>
       <c r="G2267" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60651,7 +60651,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2268" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60677,7 +60677,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60703,7 +60703,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2270" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60729,7 +60729,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60755,7 +60755,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2272" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60781,7 +60781,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60807,7 +60807,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2274" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -60833,7 +60833,7 @@
         <v>14.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -60859,7 +60859,7 @@
         <v>14.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -60885,7 +60885,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -60911,7 +60911,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -60937,7 +60937,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2279" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -60963,7 +60963,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2280" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -60989,7 +60989,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2281" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61015,7 +61015,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61041,7 +61041,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61067,7 +61067,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61093,7 +61093,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61119,7 +61119,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61145,7 +61145,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2287" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61171,7 +61171,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61197,7 +61197,7 @@
         <v>14.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61223,7 +61223,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61249,7 +61249,7 @@
         <v>14.5</v>
       </c>
       <c r="G2291" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61275,7 +61275,7 @@
         <v>14.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61301,7 +61301,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61327,7 +61327,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2294" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61353,7 +61353,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61379,7 +61379,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61405,7 +61405,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2297" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61431,7 +61431,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2298" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61457,7 +61457,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61483,7 +61483,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61509,7 +61509,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61535,7 +61535,7 @@
         <v>15</v>
       </c>
       <c r="G2302" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61561,7 +61561,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2303" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61587,7 +61587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61613,7 +61613,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2305" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61639,7 +61639,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61665,7 +61665,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2307" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61691,7 +61691,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2308" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61717,7 +61717,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2309" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61743,7 +61743,7 @@
         <v>15</v>
       </c>
       <c r="G2310" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61769,7 +61769,7 @@
         <v>15</v>
       </c>
       <c r="G2311" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61795,7 +61795,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -61821,7 +61821,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2313" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -61847,7 +61847,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2314" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -61873,7 +61873,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -61899,7 +61899,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2316" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -61925,7 +61925,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -61951,7 +61951,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -61977,7 +61977,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62003,7 +62003,7 @@
         <v>15</v>
       </c>
       <c r="G2320" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62029,7 +62029,7 @@
         <v>15</v>
       </c>
       <c r="G2321" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62055,7 +62055,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62081,7 +62081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62107,7 +62107,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62133,7 +62133,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2325" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62159,7 +62159,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2326" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62185,7 +62185,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2327" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62211,7 +62211,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2328" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62237,7 +62237,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2329" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62263,7 +62263,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2330" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62289,7 +62289,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2331" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62315,7 +62315,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62341,7 +62341,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62367,7 +62367,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2334" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62393,7 +62393,7 @@
         <v>15</v>
       </c>
       <c r="G2335" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62419,7 +62419,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62445,7 +62445,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2337" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62471,7 +62471,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2338" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62497,7 +62497,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2339" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62523,7 +62523,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62549,7 +62549,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62575,7 +62575,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62601,7 +62601,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62627,7 +62627,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62653,7 +62653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62679,7 +62679,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2346" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62705,7 +62705,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2347" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62731,7 +62731,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62757,7 +62757,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62783,7 +62783,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62809,7 +62809,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2351" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -62835,7 +62835,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -62861,7 +62861,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2353" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -62887,7 +62887,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -62913,7 +62913,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -62939,7 +62939,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2356" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -62965,7 +62965,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -62991,7 +62991,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2358" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63017,7 +63017,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63043,7 +63043,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63069,7 +63069,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63355,7 +63355,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2372" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67133,7 +67133,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6807986111</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>3570</v>
@@ -67154,6 +67154,32 @@
         <v>445</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6849768519</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>2980</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>446</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194976806641</t>
+    <t xml:space="preserve">13.2194986343384</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
@@ -47,61 +47,61 @@
     <t xml:space="preserve">13.1499214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.8577003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237340927124</t>
+    <t xml:space="preserve">12.5237350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8020391464233</t>
+    <t xml:space="preserve">12.802041053772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167779922485</t>
+    <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758508682251</t>
+    <t xml:space="preserve">12.1758518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279705047607</t>
+    <t xml:space="preserve">11.827974319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1809120178223</t>
+    <t xml:space="preserve">11.1809110641479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755996704102</t>
+    <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462230682373</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
     <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885639190674</t>
+    <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112077713013</t>
+    <t xml:space="preserve">10.3112087249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364452362061</t>
+    <t xml:space="preserve">10.4364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
     <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
@@ -110,70 +110,70 @@
     <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826847076416</t>
+    <t xml:space="preserve">11.3826856613159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331605911255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905897140503</t>
+    <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
     <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480226516724</t>
+    <t xml:space="preserve">12.148024559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193696975708</t>
+    <t xml:space="preserve">12.4193687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628885269165</t>
+    <t xml:space="preserve">12.6628875732422</t>
   </si>
   <si>
     <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933103561401</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506181716919</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758397102356</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227861404419</t>
+    <t xml:space="preserve">12.0227880477905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236080169678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.9841327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045257568359</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670278549194</t>
+    <t xml:space="preserve">11.7670288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065040588379</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788717269897</t>
+    <t xml:space="preserve">11.5788707733154</t>
   </si>
   <si>
     <t xml:space="preserve">11.2893991470337</t>
@@ -182,37 +182,37 @@
     <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979511260986</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512384414673</t>
+    <t xml:space="preserve">11.6512403488159</t>
   </si>
   <si>
     <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321599960327</t>
+    <t xml:space="preserve">11.8321590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854482650757</t>
+    <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578149795532</t>
+    <t xml:space="preserve">12.1578140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939973831177</t>
+    <t xml:space="preserve">12.1939992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025503158569</t>
+    <t xml:space="preserve">12.3025522232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275535583496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
     <t xml:space="preserve">12.447286605835</t>
@@ -221,58 +221,58 @@
     <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643896102905</t>
+    <t xml:space="preserve">12.6643886566162</t>
   </si>
   <si>
     <t xml:space="preserve">12.9466238021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729444503784</t>
+    <t xml:space="preserve">12.7729425430298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755725860596</t>
+    <t xml:space="preserve">12.9755735397339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091268539429</t>
+    <t xml:space="preserve">12.8091259002686</t>
   </si>
   <si>
     <t xml:space="preserve">13.243335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157005310059</t>
+    <t xml:space="preserve">13.3157033920288</t>
   </si>
   <si>
     <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880710601807</t>
+    <t xml:space="preserve">13.388069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025421142578</t>
+    <t xml:space="preserve">13.4025449752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453200340271</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242553710938</t>
+    <t xml:space="preserve">13.4242534637451</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689888000488</t>
+    <t xml:space="preserve">13.5689907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5545167922974</t>
+    <t xml:space="preserve">13.5545148849487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966220855713</t>
+    <t xml:space="preserve">13.4966201782227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518886566162</t>
+    <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4459629058838</t>
@@ -287,43 +287,43 @@
     <t xml:space="preserve">13.5038614273071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288608551025</t>
+    <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881495475769</t>
+    <t xml:space="preserve">12.8814926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985994338989</t>
+    <t xml:space="preserve">13.098596572876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104433059692</t>
+    <t xml:space="preserve">12.9104413986206</t>
   </si>
   <si>
     <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.8453121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275463104248</t>
+    <t xml:space="preserve">13.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439966201782</t>
+    <t xml:space="preserve">12.7439956665039</t>
   </si>
   <si>
     <t xml:space="preserve">13.0189933776855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.657154083252</t>
+    <t xml:space="preserve">12.6571550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012367248535</t>
+    <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334735870361</t>
@@ -332,31 +332,31 @@
     <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709733963013</t>
+    <t xml:space="preserve">12.0709743499756</t>
   </si>
   <si>
     <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466339111328</t>
+    <t xml:space="preserve">11.8466320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782098770142</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913682937622</t>
+    <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
     <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479465484619</t>
+    <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.172287940979</t>
+    <t xml:space="preserve">12.1722888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551849365234</t>
+    <t xml:space="preserve">11.9551839828491</t>
   </si>
   <si>
     <t xml:space="preserve">11.9696588516235</t>
@@ -365,49 +365,49 @@
     <t xml:space="preserve">11.9768953323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597904205322</t>
+    <t xml:space="preserve">11.7597894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505784988403</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229471206665</t>
+    <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554164886475</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054847717285</t>
+    <t xml:space="preserve">12.3054828643799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3805160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132905960083</t>
+    <t xml:space="preserve">12.1329050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
     <t xml:space="preserve">12.0428647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180335998535</t>
+    <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307161331177</t>
+    <t xml:space="preserve">12.830717086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158437728882</t>
+    <t xml:space="preserve">13.1158447265625</t>
   </si>
   <si>
     <t xml:space="preserve">12.9807844161987</t>
@@ -416,40 +416,40 @@
     <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881523132324</t>
+    <t xml:space="preserve">12.6881542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657773971558</t>
+    <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432649612427</t>
+    <t xml:space="preserve">12.9432668685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682346343994</t>
+    <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457231521606</t>
+    <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
     <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093334197998</t>
+    <t xml:space="preserve">13.0933313369751</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809181213379</t>
+    <t xml:space="preserve">13.2809162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5735492706299</t>
+    <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
     <t xml:space="preserve">13.5435333251953</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.138352394104</t>
+    <t xml:space="preserve">13.1383514404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205883026123</t>
+    <t xml:space="preserve">13.2058820724487</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934669494629</t>
@@ -473,73 +473,73 @@
     <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184328079224</t>
+    <t xml:space="preserve">13.318434715271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434015274048</t>
+    <t xml:space="preserve">13.2434024810791</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060176849365</t>
+    <t xml:space="preserve">13.5060186386108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560850143433</t>
+    <t xml:space="preserve">13.6560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185674667358</t>
+    <t xml:space="preserve">13.6185684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8061504364014</t>
+    <t xml:space="preserve">13.8061532974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810518264771</t>
+    <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687685012817</t>
+    <t xml:space="preserve">14.0687694549561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485805511475</t>
+    <t xml:space="preserve">13.6485795974731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159784317017</t>
+    <t xml:space="preserve">13.415979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562187194824</t>
+    <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609966278076</t>
+    <t xml:space="preserve">13.4609975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459915161133</t>
+    <t xml:space="preserve">13.4459934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986488342285</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315202713013</t>
+    <t xml:space="preserve">14.6315174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013734817505</t>
+    <t xml:space="preserve">14.3013715744019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165103912354</t>
+    <t xml:space="preserve">14.6165113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915445327759</t>
+    <t xml:space="preserve">14.6915464401245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991827011108</t>
+    <t xml:space="preserve">14.9991817474365</t>
   </si>
   <si>
     <t xml:space="preserve">15.0066862106323</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">14.991681098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.976674079895</t>
+    <t xml:space="preserve">14.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691705703735</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
     <t xml:space="preserve">14.6465253829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941383361816</t>
+    <t xml:space="preserve">14.8941345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390228271484</t>
+    <t xml:space="preserve">14.6390199661255</t>
   </si>
   <si>
     <t xml:space="preserve">15.1567516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.606951713562</t>
+    <t xml:space="preserve">15.6069536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568891525269</t>
+    <t xml:space="preserve">15.4568872451782</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570209503174</t>
@@ -578,157 +578,157 @@
     <t xml:space="preserve">16.3572902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574230194092</t>
+    <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076240539551</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.957555770874</t>
+    <t xml:space="preserve">16.9575576782227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073528289795</t>
+    <t xml:space="preserve">16.5073566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.807487487793</t>
+    <t xml:space="preserve">16.8074893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072219848633</t>
+    <t xml:space="preserve">16.207218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571556091309</t>
+    <t xml:space="preserve">16.0571537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615779876709</t>
+    <t xml:space="preserve">16.3615741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0528678894043</t>
+    <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702842712402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723854064941</t>
+    <t xml:space="preserve">14.9723863601685</t>
   </si>
   <si>
     <t xml:space="preserve">15.5898036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354496002197</t>
+    <t xml:space="preserve">15.4354524612427</t>
   </si>
   <si>
     <t xml:space="preserve">15.7441577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159320831299</t>
+    <t xml:space="preserve">16.5159282684326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072238922119</t>
+    <t xml:space="preserve">16.2072200775146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985118865967</t>
+    <t xml:space="preserve">15.898512840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267395019531</t>
+    <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495643615723</t>
+    <t xml:space="preserve">15.0495624542236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636772155762</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
     <t xml:space="preserve">15.2810926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549690246582</t>
+    <t xml:space="preserve">14.3549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522134780884</t>
+    <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.931939125061</t>
+    <t xml:space="preserve">13.9319372177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515266418457</t>
+    <t xml:space="preserve">13.4515256881714</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721448898315</t>
+    <t xml:space="preserve">14.1721467971802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116628646851</t>
+    <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
     <t xml:space="preserve">13.5315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120048522949</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518705368042</t>
+    <t xml:space="preserve">13.8518714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113218307495</t>
+    <t xml:space="preserve">13.2113199234009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.291389465332</t>
+    <t xml:space="preserve">13.2913885116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123506546021</t>
+    <t xml:space="preserve">14.4123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920743942261</t>
+    <t xml:space="preserve">14.0920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714590072632</t>
+    <t xml:space="preserve">13.3714580535889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.131254196167</t>
+    <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0511827468872</t>
+    <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971116065979</t>
+    <t xml:space="preserve">12.9711141586304</t>
   </si>
   <si>
     <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109769821167</t>
+    <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309103012085</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106359481812</t>
+    <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
     <t xml:space="preserve">11.9302225112915</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707721710205</t>
+    <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.33056640625</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">12.1704301834106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295366287231</t>
+    <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896747589111</t>
+    <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498119354248</t>
+    <t xml:space="preserve">11.4498100280762</t>
   </si>
   <si>
     <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.529878616333</t>
+    <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3697423934937</t>
+    <t xml:space="preserve">11.369743347168</t>
   </si>
   <si>
     <t xml:space="preserve">11.20960521698</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491241455078</t>
+    <t xml:space="preserve">10.6491250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288516998291</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889879226685</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102910995483</t>
+    <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
     <t xml:space="preserve">12.8493280410767</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">12.3487043380737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137090682983</t>
+    <t xml:space="preserve">11.0137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">11.681206703186</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">11.9315176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1818313598633</t>
+    <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321413040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155782699585</t>
+    <t xml:space="preserve">12.5155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.932765007019</t>
+    <t xml:space="preserve">12.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">13.1830768585205</t>
@@ -845,31 +845,31 @@
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7658891677856</t>
+    <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683839797974</t>
+    <t xml:space="preserve">14.7683849334717</t>
   </si>
   <si>
     <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518218994141</t>
+    <t xml:space="preserve">14.8518199920654</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346351623535</t>
+    <t xml:space="preserve">14.4346361160278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021327972412</t>
+    <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186948776245</t>
+    <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849451065063</t>
+    <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
@@ -878,106 +878,106 @@
     <t xml:space="preserve">14.3511972427368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843223571777</t>
+    <t xml:space="preserve">14.1843233108521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174474716187</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671365737915</t>
+    <t xml:space="preserve">13.7671356201172</t>
   </si>
   <si>
     <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677593231201</t>
+    <t xml:space="preserve">14.2677602767944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741510391235</t>
+    <t xml:space="preserve">13.5741519927979</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.244478225708</t>
+    <t xml:space="preserve">14.2444801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417316436768</t>
+    <t xml:space="preserve">13.7417325973511</t>
   </si>
   <si>
     <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093151092529</t>
+    <t xml:space="preserve">13.9093160629272</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4120626449585</t>
+    <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606874465942</t>
+    <t xml:space="preserve">14.1606864929199</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903602600098</t>
+    <t xml:space="preserve">13.4903612136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282699584961</t>
+    <t xml:space="preserve">14.3282709121704</t>
   </si>
   <si>
     <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8310165405273</t>
+    <t xml:space="preserve">14.831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958515167236</t>
+    <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985990524292</t>
+    <t xml:space="preserve">14.9985980987549</t>
   </si>
   <si>
     <t xml:space="preserve">14.7472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148073196411</t>
+    <t xml:space="preserve">14.9148054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337640762329</t>
+    <t xml:space="preserve">15.33376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.417552947998</t>
+    <t xml:space="preserve">15.4175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499713897705</t>
+    <t xml:space="preserve">15.2499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823879241943</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851373672485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668927192688</t>
+    <t xml:space="preserve">15.6689281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9202995300293</t>
+    <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878829956055</t>
+    <t xml:space="preserve">16.0878849029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">16.1923503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1052932739258</t>
+    <t xml:space="preserve">16.1052951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0182361602783</t>
+    <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311819076538</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">15.7570724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700143814087</t>
+    <t xml:space="preserve">15.6700162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829610824585</t>
+    <t xml:space="preserve">15.5829591751099</t>
   </si>
   <si>
     <t xml:space="preserve">15.4088497161865</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">16.3664608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405731201172</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146835327148</t>
+    <t xml:space="preserve">16.7146854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8887920379639</t>
+    <t xml:space="preserve">16.8887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8017387390137</t>
+    <t xml:space="preserve">16.801736831665</t>
   </si>
   <si>
     <t xml:space="preserve">17.1499633789062</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">17.759349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.933464050293</t>
+    <t xml:space="preserve">17.9334621429443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240737915039</t>
+    <t xml:space="preserve">17.3240718841553</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111289978027</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">17.8359622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9264984130859</t>
+    <t xml:space="preserve">17.9264965057373</t>
   </si>
   <si>
     <t xml:space="preserve">17.7454223632812</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">17.3832721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4738082885742</t>
+    <t xml:space="preserve">17.4738063812256</t>
   </si>
   <si>
     <t xml:space="preserve">18.0170364379883</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1116561889648</t>
+    <t xml:space="preserve">17.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305820465088</t>
+    <t xml:space="preserve">16.9305839538574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5684299468994</t>
+    <t xml:space="preserve">16.5684280395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778919219971</t>
+    <t xml:space="preserve">16.4778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157417297363</t>
+    <t xml:space="preserve">16.1157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441257476807</t>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2968158721924</t>
+    <t xml:space="preserve">16.296817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2062797546387</t>
+    <t xml:space="preserve">16.20627784729</t>
   </si>
   <si>
     <t xml:space="preserve">16.025203704834</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">16.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630516052246</t>
+    <t xml:space="preserve">15.663049697876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535905838013</t>
+    <t xml:space="preserve">15.7535886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819755554199</t>
+    <t xml:space="preserve">15.4819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">14.3955211639404</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3996047973633</t>
+    <t xml:space="preserve">13.3996057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090658187866</t>
+    <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901428222656</t>
+    <t xml:space="preserve">13.4901418685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">14.4541883468628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5456695556641</t>
+    <t xml:space="preserve">14.5456705093384</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9967775344849</t>
+    <t xml:space="preserve">13.9967765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.905294418335</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.6308479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4478826522827</t>
+    <t xml:space="preserve">13.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">13.3564023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0819549560547</t>
+    <t xml:space="preserve">13.081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2649192810059</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.8075075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160263061523</t>
+    <t xml:space="preserve">12.716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.8989906311035</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.6245441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5330619812012</t>
+    <t xml:space="preserve">12.5330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3684206008911</t>
@@ -1278,6 +1278,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.227819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0819549560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9864664077759</t>
@@ -63072,7 +63075,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63098,7 +63101,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63124,7 +63127,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63150,7 +63153,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63176,7 +63179,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63202,7 +63205,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63228,7 +63231,7 @@
         <v>13.5</v>
       </c>
       <c r="G2367" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63254,7 +63257,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63280,7 +63283,7 @@
         <v>13.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63306,7 +63309,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2370" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63332,7 +63335,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2371" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63384,7 +63387,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63410,7 +63413,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63436,7 +63439,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2375" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63462,7 +63465,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63488,7 +63491,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63514,7 +63517,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2378" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63540,7 +63543,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2379" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63566,7 +63569,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63592,7 +63595,7 @@
         <v>13</v>
       </c>
       <c r="G2381" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63618,7 +63621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2382" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63644,7 +63647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63670,7 +63673,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63696,7 +63699,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63722,7 +63725,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63748,7 +63751,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2387" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63774,7 +63777,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2388" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63800,7 +63803,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -63826,7 +63829,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2390" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -63852,7 +63855,7 @@
         <v>13</v>
       </c>
       <c r="G2391" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -63878,7 +63881,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -63904,7 +63907,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -63930,7 +63933,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -63956,7 +63959,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2395" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -63982,7 +63985,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64008,7 +64011,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2397" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64034,7 +64037,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2398" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64060,7 +64063,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2399" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64086,7 +64089,7 @@
         <v>12.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64112,7 +64115,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64138,7 +64141,7 @@
         <v>12.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64164,7 +64167,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64190,7 +64193,7 @@
         <v>12</v>
       </c>
       <c r="G2404" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64216,7 +64219,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2405" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64242,7 +64245,7 @@
         <v>12</v>
       </c>
       <c r="G2406" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64268,7 +64271,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64294,7 +64297,7 @@
         <v>12</v>
       </c>
       <c r="G2408" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64320,7 +64323,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64346,7 +64349,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64372,7 +64375,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64398,7 +64401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64424,7 +64427,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2413" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64450,7 +64453,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2414" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64476,7 +64479,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64502,7 +64505,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64528,7 +64531,7 @@
         <v>12.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64554,7 +64557,7 @@
         <v>12.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64580,7 +64583,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64606,7 +64609,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2420" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64632,7 +64635,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2421" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64658,7 +64661,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64684,7 +64687,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64710,7 +64713,7 @@
         <v>12.5</v>
       </c>
       <c r="G2424" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64736,7 +64739,7 @@
         <v>12.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64762,7 +64765,7 @@
         <v>12.5</v>
       </c>
       <c r="G2426" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64788,7 +64791,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64814,7 +64817,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -64840,7 +64843,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -64866,7 +64869,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2430" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -64892,7 +64895,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2431" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -64918,7 +64921,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2432" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -64944,7 +64947,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -64970,7 +64973,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2434" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -64996,7 +64999,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65022,7 +65025,7 @@
         <v>12.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65048,7 +65051,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65074,7 +65077,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65100,7 +65103,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2439" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65126,7 +65129,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2440" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65152,7 +65155,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65178,7 +65181,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65204,7 +65207,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65230,7 +65233,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2444" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65256,7 +65259,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65282,7 +65285,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2446" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65308,7 +65311,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2447" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65334,7 +65337,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65360,7 +65363,7 @@
         <v>12.5</v>
       </c>
       <c r="G2449" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65386,7 +65389,7 @@
         <v>12.5</v>
       </c>
       <c r="G2450" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65412,7 +65415,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2451" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65438,7 +65441,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2452" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65464,7 +65467,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2453" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65490,7 +65493,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2454" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65516,7 +65519,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2455" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65542,7 +65545,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65568,7 +65571,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65594,7 +65597,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2458" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65620,7 +65623,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2459" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65646,7 +65649,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65672,7 +65675,7 @@
         <v>13</v>
       </c>
       <c r="G2461" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65698,7 +65701,7 @@
         <v>13</v>
       </c>
       <c r="G2462" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65724,7 +65727,7 @@
         <v>13</v>
       </c>
       <c r="G2463" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65750,7 +65753,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65776,7 +65779,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65802,7 +65805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -65828,7 +65831,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2467" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -65854,7 +65857,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -65880,7 +65883,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2469" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -65906,7 +65909,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2470" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -65932,7 +65935,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -65958,7 +65961,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2472" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -65984,7 +65987,7 @@
         <v>12.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66010,7 +66013,7 @@
         <v>12.5</v>
       </c>
       <c r="G2474" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66036,7 +66039,7 @@
         <v>12.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66062,7 +66065,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66088,7 +66091,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66114,7 +66117,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66140,7 +66143,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2479" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66166,7 +66169,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2480" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66192,7 +66195,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66218,7 +66221,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2482" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66244,7 +66247,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66270,7 +66273,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2484" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66296,7 +66299,7 @@
         <v>13</v>
       </c>
       <c r="G2485" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66322,7 +66325,7 @@
         <v>12.5</v>
       </c>
       <c r="G2486" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66348,7 +66351,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66374,7 +66377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66400,7 +66403,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66426,7 +66429,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2490" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66452,7 +66455,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2491" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66478,7 +66481,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2492" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66504,7 +66507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66530,7 +66533,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66556,7 +66559,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66582,7 +66585,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2496" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66608,7 +66611,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66634,7 +66637,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2498" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66660,7 +66663,7 @@
         <v>12</v>
       </c>
       <c r="G2499" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66686,7 +66689,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66712,7 +66715,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66738,7 +66741,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66764,7 +66767,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2503" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66790,7 +66793,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2504" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -66816,7 +66819,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -66842,7 +66845,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -66868,7 +66871,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -66894,7 +66897,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2508" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -66920,7 +66923,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2509" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -66946,7 +66949,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2510" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -66972,7 +66975,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2511" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -66998,7 +67001,7 @@
         <v>11.5</v>
       </c>
       <c r="G2512" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67024,7 +67027,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67050,7 +67053,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2514" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67076,7 +67079,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2515" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67102,7 +67105,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67128,7 +67131,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2517" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67154,7 +67157,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2518" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67180,7 +67183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2519" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67206,7 +67209,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2520" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67232,7 +67235,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2521" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67258,7 +67261,7 @@
         <v>11.5</v>
       </c>
       <c r="G2522" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67284,7 +67287,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2523" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67310,7 +67313,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2524" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67318,7 +67321,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6849421296</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>4772</v>
@@ -67336,7 +67339,7 @@
         <v>11.5</v>
       </c>
       <c r="G2525" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -38,106 +38,106 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194986343384</t>
+    <t xml:space="preserve">13.2194995880127</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1499223709106</t>
+    <t xml:space="preserve">13.1499214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8577013015747</t>
+    <t xml:space="preserve">12.857702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871618270874</t>
+    <t xml:space="preserve">12.8716163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237350463867</t>
+    <t xml:space="preserve">12.523736000061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8020401000977</t>
+    <t xml:space="preserve">12.8020391464233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167779922485</t>
+    <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.1758527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8279724121094</t>
+    <t xml:space="preserve">11.8279733657837</t>
   </si>
   <si>
     <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755977630615</t>
+    <t xml:space="preserve">10.5756006240845</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280223846436</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885629653931</t>
+    <t xml:space="preserve">10.0885639190674</t>
   </si>
   <si>
     <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060234069824</t>
+    <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990644454956</t>
+    <t xml:space="preserve">10.4990634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.4364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451759338379</t>
+    <t xml:space="preserve">10.6451749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147521972656</t>
+    <t xml:space="preserve">10.7147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843294143677</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1322088241577</t>
+    <t xml:space="preserve">11.132209777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.3826856613159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905897140503</t>
+    <t xml:space="preserve">11.8905906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1480236053467</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193696975708</t>
+    <t xml:space="preserve">12.4193706512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628866195679</t>
+    <t xml:space="preserve">12.6628875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411926269531</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933122634888</t>
+    <t xml:space="preserve">12.5933103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150091171265</t>
+    <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0506172180176</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7583961486816</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236080169678</t>
+    <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841318130493</t>
+    <t xml:space="preserve">11.9841327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163696289062</t>
+    <t xml:space="preserve">11.7163705825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407110214233</t>
+    <t xml:space="preserve">11.9407119750977</t>
   </si>
   <si>
     <t xml:space="preserve">11.9045267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7670278549194</t>
+    <t xml:space="preserve">11.7670288085938</t>
   </si>
   <si>
     <t xml:space="preserve">11.5065040588379</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289400100708</t>
+    <t xml:space="preserve">11.2893981933594</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979530334473</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
     <t xml:space="preserve">11.6512403488159</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130777359009</t>
+    <t xml:space="preserve">12.0130796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854482650757</t>
+    <t xml:space="preserve">12.0854473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578149795532</t>
+    <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939992904663</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
     <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275535583496</t>
+    <t xml:space="preserve">12.0275545120239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953147888184</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472856521606</t>
   </si>
   <si>
     <t xml:space="preserve">12.5196552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643896102905</t>
+    <t xml:space="preserve">12.6643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466238021851</t>
+    <t xml:space="preserve">12.9466247558594</t>
   </si>
   <si>
     <t xml:space="preserve">12.7729434967041</t>
@@ -236,52 +236,52 @@
     <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538612365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433338165283</t>
+    <t xml:space="preserve">13.243335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157024383545</t>
+    <t xml:space="preserve">13.3157014846802</t>
   </si>
   <si>
     <t xml:space="preserve">13.4604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880701065063</t>
+    <t xml:space="preserve">13.388069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025430679321</t>
+    <t xml:space="preserve">13.4025449752808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453200340271</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242544174194</t>
+    <t xml:space="preserve">13.4242515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5328063964844</t>
+    <t xml:space="preserve">13.532808303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689916610718</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
     <t xml:space="preserve">13.5545177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.496621131897</t>
+    <t xml:space="preserve">13.4966230392456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3518857955933</t>
+    <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387283325195</t>
+    <t xml:space="preserve">13.4387302398682</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071504592896</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288618087769</t>
+    <t xml:space="preserve">13.2288589477539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814964294434</t>
+    <t xml:space="preserve">12.881495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985984802246</t>
+    <t xml:space="preserve">13.0985975265503</t>
   </si>
   <si>
     <t xml:space="preserve">12.9104423522949</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">13.0262308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347846984863</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.845311164856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1275463104248</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">12.7439956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189933776855</t>
+    <t xml:space="preserve">13.0189943313599</t>
   </si>
   <si>
     <t xml:space="preserve">12.6571531295776</t>
@@ -326,37 +326,37 @@
     <t xml:space="preserve">12.2446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012357711792</t>
+    <t xml:space="preserve">12.2012348175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.9334745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143951416016</t>
+    <t xml:space="preserve">12.1143932342529</t>
   </si>
   <si>
     <t xml:space="preserve">12.0709733963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492639541626</t>
+    <t xml:space="preserve">12.049262046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782117843628</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913692474365</t>
+    <t xml:space="preserve">11.9913702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986066818237</t>
+    <t xml:space="preserve">11.9986057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479475021362</t>
+    <t xml:space="preserve">11.9479484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722869873047</t>
+    <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551849365234</t>
@@ -368,37 +368,37 @@
     <t xml:space="preserve">11.9768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.1505784988403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301826477051</t>
+    <t xml:space="preserve">12.2301816940308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229480743408</t>
+    <t xml:space="preserve">12.2229471206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1554145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054838180542</t>
+    <t xml:space="preserve">12.3054828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805160522461</t>
+    <t xml:space="preserve">12.3805170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428667068481</t>
+    <t xml:space="preserve">12.0428657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129863739014</t>
+    <t xml:space="preserve">12.3129873275757</t>
   </si>
   <si>
     <t xml:space="preserve">12.4180316925049</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">12.5756025314331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.830714225769</t>
+    <t xml:space="preserve">12.8307161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158428192139</t>
+    <t xml:space="preserve">13.1158418655396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807834625244</t>
+    <t xml:space="preserve">12.9807844161987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9732809066772</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">12.9657783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.943265914917</t>
+    <t xml:space="preserve">12.9432668685913</t>
   </si>
   <si>
     <t xml:space="preserve">13.1308498382568</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083402633667</t>
+    <t xml:space="preserve">13.1083374023438</t>
   </si>
   <si>
     <t xml:space="preserve">13.093334197998</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">13.3559522628784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809190750122</t>
+    <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309844970703</t>
+    <t xml:space="preserve">13.4309825897217</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435352325439</t>
+    <t xml:space="preserve">13.5435342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.235897064209</t>
+    <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234790802002</t>
+    <t xml:space="preserve">13.4234800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058849334717</t>
+    <t xml:space="preserve">13.205885887146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934669494629</t>
+    <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685029983521</t>
+    <t xml:space="preserve">13.4685001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3184337615967</t>
+    <t xml:space="preserve">13.318434715271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434015274048</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683673858643</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">13.5060186386108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560831069946</t>
+    <t xml:space="preserve">13.6560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185703277588</t>
+    <t xml:space="preserve">13.6185674667358</t>
   </si>
   <si>
     <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810508728027</t>
+    <t xml:space="preserve">13.5810499191284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687694549561</t>
+    <t xml:space="preserve">14.0687685012817</t>
   </si>
   <si>
     <t xml:space="preserve">13.6936006546021</t>
@@ -509,43 +509,43 @@
     <t xml:space="preserve">13.6485795974731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.415976524353</t>
+    <t xml:space="preserve">13.4159774780273</t>
   </si>
   <si>
     <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312519073486</t>
+    <t xml:space="preserve">14.0312538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609975814819</t>
+    <t xml:space="preserve">13.4609956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459915161133</t>
+    <t xml:space="preserve">13.4459896087646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986488342285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0087413787842</t>
+    <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315183639526</t>
+    <t xml:space="preserve">14.6315174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013744354248</t>
+    <t xml:space="preserve">14.3013706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616512298584</t>
+    <t xml:space="preserve">14.6165103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915464401245</t>
+    <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
     <t xml:space="preserve">14.9991817474365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066862106323</t>
+    <t xml:space="preserve">15.0066843032837</t>
   </si>
   <si>
     <t xml:space="preserve">14.991678237915</t>
@@ -557,37 +557,37 @@
     <t xml:space="preserve">14.9691715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465253829956</t>
+    <t xml:space="preserve">14.6465263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.894136428833</t>
+    <t xml:space="preserve">14.8941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390237808228</t>
+    <t xml:space="preserve">14.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567506790161</t>
   </si>
   <si>
     <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568853378296</t>
+    <t xml:space="preserve">15.4568891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570209503174</t>
+    <t xml:space="preserve">15.7570219039917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572864532471</t>
+    <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574211120605</t>
+    <t xml:space="preserve">16.6574230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078914642334</t>
+    <t xml:space="preserve">17.7078895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2576904296875</t>
+    <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076221466064</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">16.5073547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074913024902</t>
+    <t xml:space="preserve">16.807487487793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072238922119</t>
+    <t xml:space="preserve">16.2072200775146</t>
   </si>
   <si>
     <t xml:space="preserve">16.0571537017822</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">16.0528659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702880859375</t>
+    <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
     <t xml:space="preserve">14.9723863601685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898017883301</t>
+    <t xml:space="preserve">15.5898027420044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354486465454</t>
+    <t xml:space="preserve">15.4354476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441596984863</t>
+    <t xml:space="preserve">15.7441577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159301757812</t>
+    <t xml:space="preserve">16.5159282684326</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072219848633</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985109329224</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267414093018</t>
+    <t xml:space="preserve">15.1267385482788</t>
   </si>
   <si>
     <t xml:space="preserve">15.0495615005493</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919048309326</t>
+    <t xml:space="preserve">13.8919057846069</t>
   </si>
   <si>
     <t xml:space="preserve">14.2522134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319372177124</t>
+    <t xml:space="preserve">13.9319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515266418457</t>
+    <t xml:space="preserve">13.45152759552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917314529419</t>
+    <t xml:space="preserve">13.6917324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1721439361572</t>
+    <t xml:space="preserve">14.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6116638183594</t>
+    <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315952301025</t>
+    <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0120067596436</t>
+    <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
     <t xml:space="preserve">13.8518705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113218307495</t>
+    <t xml:space="preserve">13.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">13.2913885116577</t>
@@ -707,61 +707,61 @@
     <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312522888184</t>
+    <t xml:space="preserve">13.1312532424927</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711151123047</t>
+    <t xml:space="preserve">12.9711132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910455703735</t>
+    <t xml:space="preserve">12.8910465240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.810977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309083938599</t>
+    <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907035827637</t>
+    <t xml:space="preserve">12.4907026290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.6508407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302225112915</t>
+    <t xml:space="preserve">11.9302234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900177001953</t>
+    <t xml:space="preserve">11.690016746521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707712173462</t>
+    <t xml:space="preserve">12.5707721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305673599243</t>
+    <t xml:space="preserve">12.3305654525757</t>
   </si>
   <si>
     <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704301834106</t>
+    <t xml:space="preserve">12.170428276062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295375823975</t>
+    <t xml:space="preserve">11.1295366287231</t>
   </si>
   <si>
     <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498100280762</t>
+    <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099472045898</t>
+    <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
     <t xml:space="preserve">11.5298795700073</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9694004058838</t>
+    <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
     <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491250991821</t>
+    <t xml:space="preserve">10.6491260528564</t>
   </si>
   <si>
     <t xml:space="preserve">10.3288507461548</t>
@@ -794,31 +794,31 @@
     <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085773468018</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687145233154</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.010293006897</t>
+    <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493280410767</t>
+    <t xml:space="preserve">12.8493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.348705291748</t>
+    <t xml:space="preserve">12.3487043380737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137090682983</t>
+    <t xml:space="preserve">11.0137100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.681206703186</t>
+    <t xml:space="preserve">11.6812076568604</t>
   </si>
   <si>
     <t xml:space="preserve">11.9315176010132</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155782699585</t>
   </si>
   <si>
     <t xml:space="preserve">12.932765007019</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">14.7683849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180721282959</t>
+    <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518190383911</t>
+    <t xml:space="preserve">14.8518209457397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4346332550049</t>
+    <t xml:space="preserve">14.4346351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021308898926</t>
+    <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352598190308</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
     <t xml:space="preserve">15.0186958312988</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">14.6849460601807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015071868896</t>
+    <t xml:space="preserve">14.601508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511972427368</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1843233108521</t>
+    <t xml:space="preserve">14.1843242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.017448425293</t>
+    <t xml:space="preserve">14.0174493789673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6837005615234</t>
@@ -905,58 +905,58 @@
     <t xml:space="preserve">13.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444772720337</t>
+    <t xml:space="preserve">14.2444791793823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.993106842041</t>
+    <t xml:space="preserve">13.9931077957153</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093141555786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4120616912842</t>
+    <t xml:space="preserve">14.4120626449585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606864929199</t>
+    <t xml:space="preserve">14.1606884002686</t>
   </si>
   <si>
     <t xml:space="preserve">13.6579418182373</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903602600098</t>
+    <t xml:space="preserve">13.4903593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282709121704</t>
+    <t xml:space="preserve">14.3282718658447</t>
   </si>
   <si>
     <t xml:space="preserve">14.6634359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8310174942017</t>
+    <t xml:space="preserve">14.831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958524703979</t>
+    <t xml:space="preserve">14.4958515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985971450806</t>
+    <t xml:space="preserve">14.9985990524292</t>
   </si>
   <si>
     <t xml:space="preserve">14.7472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148073196411</t>
+    <t xml:space="preserve">14.9148063659668</t>
   </si>
   <si>
     <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337631225586</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
     <t xml:space="preserve">15.4175539016724</t>
@@ -965,25 +965,25 @@
     <t xml:space="preserve">15.2499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823879241943</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851354598999</t>
+    <t xml:space="preserve">15.5851364135742</t>
   </si>
   <si>
     <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9203033447266</t>
+    <t xml:space="preserve">15.9203004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0040912628174</t>
+    <t xml:space="preserve">16.004093170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.0878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4535160064697</t>
+    <t xml:space="preserve">16.4535179138184</t>
   </si>
   <si>
     <t xml:space="preserve">16.2794055938721</t>
@@ -998,34 +998,34 @@
     <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311819076538</t>
+    <t xml:space="preserve">15.9311809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570734024048</t>
   </si>
   <si>
     <t xml:space="preserve">15.6700162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441257476807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5829591751099</t>
+    <t xml:space="preserve">15.5829601287842</t>
   </si>
   <si>
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405712127686</t>
+    <t xml:space="preserve">16.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">16.6276302337646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146816253662</t>
+    <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">16.8017387390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.97585105896</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">17.4111289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4697265625</t>
+    <t xml:space="preserve">18.4697246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2886505126953</t>
+    <t xml:space="preserve">18.2886486053467</t>
   </si>
   <si>
     <t xml:space="preserve">18.1075744628906</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">17.6548843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021942138672</t>
+    <t xml:space="preserve">17.2021961212158</t>
   </si>
   <si>
     <t xml:space="preserve">17.1116580963135</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">16.5684299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2927322387695</t>
+    <t xml:space="preserve">17.2927341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4778938293457</t>
+    <t xml:space="preserve">16.4778919219971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">15.9346656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8400421142578</t>
+    <t xml:space="preserve">16.8400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6589660644531</t>
+    <t xml:space="preserve">16.6589679718018</t>
   </si>
   <si>
     <t xml:space="preserve">16.3873538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630516052246</t>
+    <t xml:space="preserve">15.6630506515503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7535886764526</t>
+    <t xml:space="preserve">15.753589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4819774627686</t>
+    <t xml:space="preserve">15.4819765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3955211639404</t>
+    <t xml:space="preserve">14.3955221176147</t>
   </si>
   <si>
     <t xml:space="preserve">14.4860591888428</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">14.1239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3049831390381</t>
+    <t xml:space="preserve">14.3049840927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.3996047973633</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">13.3090667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4901418685913</t>
+    <t xml:space="preserve">13.4901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.7617559432983</t>
@@ -67451,7 +67451,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6911458333</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>2640</v>
@@ -67472,6 +67472,32 @@
         <v>442</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6491435185</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>446</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194995880127</t>
+    <t xml:space="preserve">13.2194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149923324585</t>
+    <t xml:space="preserve">13.1499223709106</t>
   </si>
   <si>
     <t xml:space="preserve">12.8577013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716154098511</t>
+    <t xml:space="preserve">12.8716173171997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5237369537354</t>
+    <t xml:space="preserve">12.523736000061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.802041053772</t>
+    <t xml:space="preserve">12.8020391464233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167789459229</t>
+    <t xml:space="preserve">12.5167779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1758546829224</t>
+    <t xml:space="preserve">12.1758518218994</t>
   </si>
   <si>
     <t xml:space="preserve">11.8279724121094</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">11.1809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755977630615</t>
+    <t xml:space="preserve">10.5755996704102</t>
   </si>
   <si>
     <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280223846436</t>
+    <t xml:space="preserve">9.39280033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885639190674</t>
+    <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112087249756</t>
+    <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060224533081</t>
+    <t xml:space="preserve">10.5060214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990634918213</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364461898804</t>
+    <t xml:space="preserve">10.4364452362061</t>
   </si>
   <si>
     <t xml:space="preserve">10.6451749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7147512435913</t>
+    <t xml:space="preserve">10.714750289917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.784327507019</t>
+    <t xml:space="preserve">10.7843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773694992065</t>
@@ -110,115 +110,115 @@
     <t xml:space="preserve">11.1322088241577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3826847076416</t>
+    <t xml:space="preserve">11.3826837539673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331577301025</t>
+    <t xml:space="preserve">11.6331586837769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905916213989</t>
+    <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
     <t xml:space="preserve">12.1549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148021697998</t>
+    <t xml:space="preserve">12.1480236053467</t>
   </si>
   <si>
     <t xml:space="preserve">12.4193696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628875732422</t>
+    <t xml:space="preserve">12.6628904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411945343018</t>
+    <t xml:space="preserve">12.9411935806274</t>
   </si>
   <si>
     <t xml:space="preserve">12.5933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150072097778</t>
+    <t xml:space="preserve">12.3150062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0506181716919</t>
+    <t xml:space="preserve">12.0506162643433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758394241333</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227870941162</t>
+    <t xml:space="preserve">12.0227861404419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236061096191</t>
+    <t xml:space="preserve">11.7236070632935</t>
   </si>
   <si>
     <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7163705825806</t>
+    <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
     <t xml:space="preserve">11.9407110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045257568359</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
     <t xml:space="preserve">11.7670288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065040588379</t>
+    <t xml:space="preserve">11.5065031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788707733154</t>
+    <t xml:space="preserve">11.5788717269897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893981933594</t>
+    <t xml:space="preserve">11.2893991470337</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979511260986</t>
+    <t xml:space="preserve">11.3979520797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512384414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683433532715</t>
+    <t xml:space="preserve">11.8683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8321590423584</t>
+    <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854463577271</t>
+    <t xml:space="preserve">12.08544921875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1939992904663</t>
+    <t xml:space="preserve">12.193998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025522232056</t>
+    <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275535583496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953157424927</t>
+    <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196552276611</t>
+    <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643896102905</t>
@@ -227,91 +227,91 @@
     <t xml:space="preserve">12.946626663208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729425430298</t>
+    <t xml:space="preserve">12.7729434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755735397339</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9538621902466</t>
+    <t xml:space="preserve">12.9538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091259002686</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433347702026</t>
+    <t xml:space="preserve">13.2433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157024383545</t>
+    <t xml:space="preserve">13.3157014846802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604377746582</t>
+    <t xml:space="preserve">13.4604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880681991577</t>
+    <t xml:space="preserve">13.3880701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025459289551</t>
+    <t xml:space="preserve">13.4025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.4531993865967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242525100708</t>
+    <t xml:space="preserve">13.4242544174194</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689907073975</t>
+    <t xml:space="preserve">13.5689935684204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5545177459717</t>
+    <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.496621131897</t>
+    <t xml:space="preserve">13.4966220855713</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459638595581</t>
+    <t xml:space="preserve">13.4459657669067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387283325195</t>
+    <t xml:space="preserve">13.4387273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071514129639</t>
+    <t xml:space="preserve">13.2071495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038595199585</t>
+    <t xml:space="preserve">13.5038623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2288599014282</t>
+    <t xml:space="preserve">13.2288589477539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814945220947</t>
+    <t xml:space="preserve">12.881495475769</t>
   </si>
   <si>
     <t xml:space="preserve">13.0985984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104433059692</t>
+    <t xml:space="preserve">12.9104404449463</t>
   </si>
   <si>
     <t xml:space="preserve">13.0262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347818374634</t>
+    <t xml:space="preserve">13.1347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453102111816</t>
+    <t xml:space="preserve">12.845311164856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275472640991</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439937591553</t>
+    <t xml:space="preserve">12.7439975738525</t>
   </si>
   <si>
     <t xml:space="preserve">13.0189933776855</t>
@@ -320,31 +320,31 @@
     <t xml:space="preserve">12.657154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446565628052</t>
   </si>
   <si>
     <t xml:space="preserve">12.2012357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334745407104</t>
+    <t xml:space="preserve">11.9334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143941879272</t>
+    <t xml:space="preserve">12.1143951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709743499756</t>
+    <t xml:space="preserve">12.0709733963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492649078369</t>
+    <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8466320037842</t>
+    <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0782117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913702011108</t>
+    <t xml:space="preserve">11.9913682937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9986066818237</t>
@@ -353,190 +353,190 @@
     <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722869873047</t>
+    <t xml:space="preserve">12.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551839828491</t>
+    <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9696588516235</t>
+    <t xml:space="preserve">11.9696598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768934249878</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505784988403</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301836013794</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229480743408</t>
+    <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554145812988</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3054828643799</t>
+    <t xml:space="preserve">12.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805160522461</t>
+    <t xml:space="preserve">12.3805170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1329050064087</t>
+    <t xml:space="preserve">12.132905960083</t>
   </si>
   <si>
     <t xml:space="preserve">12.3880186080933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428657531738</t>
+    <t xml:space="preserve">12.0428638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3129854202271</t>
+    <t xml:space="preserve">12.3129863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4180316925049</t>
+    <t xml:space="preserve">12.4180307388306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.830717086792</t>
+    <t xml:space="preserve">12.8307151794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9807834625244</t>
+    <t xml:space="preserve">12.9807825088501</t>
   </si>
   <si>
     <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881523132324</t>
+    <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657764434814</t>
+    <t xml:space="preserve">12.9657773971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308498382568</t>
+    <t xml:space="preserve">13.1308488845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8682327270508</t>
+    <t xml:space="preserve">12.8682336807251</t>
   </si>
   <si>
     <t xml:space="preserve">12.845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1083393096924</t>
+    <t xml:space="preserve">13.1083402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093334197998</t>
+    <t xml:space="preserve">13.0933322906494</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809171676636</t>
+    <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.430983543396</t>
+    <t xml:space="preserve">13.4309844970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435352325439</t>
+    <t xml:space="preserve">13.5435333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2358961105347</t>
+    <t xml:space="preserve">13.235897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
+    <t xml:space="preserve">13.138352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234819412231</t>
+    <t xml:space="preserve">13.4234809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205885887146</t>
+    <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934669494629</t>
+    <t xml:space="preserve">13.3934650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685010910034</t>
+    <t xml:space="preserve">13.4685001373291</t>
   </si>
   <si>
     <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434015274048</t>
+    <t xml:space="preserve">13.2433996200562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1683664321899</t>
+    <t xml:space="preserve">13.1683654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5060186386108</t>
+    <t xml:space="preserve">13.5060195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6560840606689</t>
+    <t xml:space="preserve">13.6560850143433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6185674667358</t>
+    <t xml:space="preserve">13.6185665130615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.80615234375</t>
+    <t xml:space="preserve">13.8061494827271</t>
   </si>
   <si>
     <t xml:space="preserve">13.5810508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0687685012817</t>
+    <t xml:space="preserve">14.0687704086304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">13.6485805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159774780273</t>
+    <t xml:space="preserve">13.415979385376</t>
   </si>
   <si>
     <t xml:space="preserve">13.9562177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312528610229</t>
+    <t xml:space="preserve">14.0312519073486</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.445990562439</t>
+    <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7986497879028</t>
+    <t xml:space="preserve">13.7986469268799</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315183639526</t>
+    <t xml:space="preserve">14.6315202713013</t>
   </si>
   <si>
     <t xml:space="preserve">14.3013725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165132522583</t>
+    <t xml:space="preserve">14.6165151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915454864502</t>
+    <t xml:space="preserve">14.6915435791016</t>
   </si>
   <si>
     <t xml:space="preserve">14.9991817474365</t>
@@ -545,28 +545,28 @@
     <t xml:space="preserve">15.0066862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9916801452637</t>
+    <t xml:space="preserve">14.991678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">14.976674079895</t>
+    <t xml:space="preserve">14.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9691686630249</t>
+    <t xml:space="preserve">14.9691696166992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6465263366699</t>
+    <t xml:space="preserve">14.6465282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941345214844</t>
+    <t xml:space="preserve">14.8941373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6390218734741</t>
+    <t xml:space="preserve">14.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1567516326904</t>
+    <t xml:space="preserve">15.1567497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069507598877</t>
+    <t xml:space="preserve">15.6069526672363</t>
   </si>
   <si>
     <t xml:space="preserve">15.4568872451782</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3572864532471</t>
+    <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574192047119</t>
+    <t xml:space="preserve">16.6574230194092</t>
   </si>
   <si>
     <t xml:space="preserve">17.7078895568848</t>
@@ -587,46 +587,46 @@
     <t xml:space="preserve">17.2576904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076221466064</t>
+    <t xml:space="preserve">17.1076240539551</t>
   </si>
   <si>
     <t xml:space="preserve">16.957555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073566436768</t>
+    <t xml:space="preserve">16.5073547363281</t>
   </si>
   <si>
     <t xml:space="preserve">16.8074893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072200775146</t>
+    <t xml:space="preserve">16.2072219848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571537017822</t>
+    <t xml:space="preserve">16.0571556091309</t>
   </si>
   <si>
     <t xml:space="preserve">16.3615760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.052864074707</t>
+    <t xml:space="preserve">16.0528678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702842712402</t>
+    <t xml:space="preserve">16.6702861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723854064941</t>
+    <t xml:space="preserve">14.9723844528198</t>
   </si>
   <si>
     <t xml:space="preserve">15.5898017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354486465454</t>
+    <t xml:space="preserve">15.4354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441577911377</t>
+    <t xml:space="preserve">15.7441596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159301757812</t>
+    <t xml:space="preserve">16.5159320831299</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072238922119</t>
@@ -635,34 +635,34 @@
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.898512840271</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267395019531</t>
+    <t xml:space="preserve">15.1267375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495615005493</t>
+    <t xml:space="preserve">15.0495624542236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6636781692505</t>
+    <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810945510864</t>
+    <t xml:space="preserve">15.2810935974121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549671173096</t>
+    <t xml:space="preserve">14.3549680709839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4321460723877</t>
+    <t xml:space="preserve">14.4321451187134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919048309326</t>
+    <t xml:space="preserve">13.8919057846069</t>
   </si>
   <si>
     <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319381713867</t>
+    <t xml:space="preserve">13.9319400787354</t>
   </si>
   <si>
     <t xml:space="preserve">13.771800994873</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6917333602905</t>
+    <t xml:space="preserve">13.6917314529419</t>
   </si>
   <si>
     <t xml:space="preserve">14.1721448898315</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">13.6116647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5315952301025</t>
+    <t xml:space="preserve">13.5315942764282</t>
   </si>
   <si>
     <t xml:space="preserve">14.0120058059692</t>
@@ -689,49 +689,49 @@
     <t xml:space="preserve">13.8518695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113199234009</t>
+    <t xml:space="preserve">13.2113218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2913885116577</t>
+    <t xml:space="preserve">13.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.092077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3714580535889</t>
+    <t xml:space="preserve">13.3714590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1312522888184</t>
+    <t xml:space="preserve">13.131254196167</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711141586304</t>
+    <t xml:space="preserve">12.9711151123047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8109788894653</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
     <t xml:space="preserve">12.7309093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907026290894</t>
+    <t xml:space="preserve">12.4907035827637</t>
   </si>
   <si>
     <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106359481812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9302234649658</t>
+    <t xml:space="preserve">11.9302215576172</t>
   </si>
   <si>
     <t xml:space="preserve">11.690016746521</t>
@@ -740,49 +740,49 @@
     <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3305654525757</t>
+    <t xml:space="preserve">12.33056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903606414795</t>
+    <t xml:space="preserve">12.0903596878052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704301834106</t>
+    <t xml:space="preserve">12.1704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295375823975</t>
+    <t xml:space="preserve">11.1295385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896738052368</t>
+    <t xml:space="preserve">11.2896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498100280762</t>
+    <t xml:space="preserve">11.4498119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099472045898</t>
+    <t xml:space="preserve">11.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298805236816</t>
+    <t xml:space="preserve">11.529878616333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.369743347168</t>
+    <t xml:space="preserve">11.3697443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2096042633057</t>
+    <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9693994522095</t>
+    <t xml:space="preserve">10.9694004058838</t>
   </si>
   <si>
     <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6491260528564</t>
+    <t xml:space="preserve">10.6491241455078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3288516998291</t>
+    <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889879226685</t>
+    <t xml:space="preserve">10.4889888763428</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089193344116</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085783004761</t>
+    <t xml:space="preserve">10.0085763931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0102920532227</t>
+    <t xml:space="preserve">12.0102910995483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493280410767</t>
+    <t xml:space="preserve">12.849328994751</t>
   </si>
   <si>
     <t xml:space="preserve">12.5990171432495</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">11.0137090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6812057495117</t>
+    <t xml:space="preserve">11.681206703186</t>
   </si>
   <si>
     <t xml:space="preserve">11.9315176010132</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">12.4321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.932765007019</t>
+    <t xml:space="preserve">12.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">13.1830768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.433388710022</t>
+    <t xml:space="preserve">13.4333877563477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499507904053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162010192871</t>
+    <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7658910751343</t>
+    <t xml:space="preserve">12.76589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768383026123</t>
+    <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180721282959</t>
+    <t xml:space="preserve">14.5180711746216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518209457397</t>
+    <t xml:space="preserve">14.8518218994141</t>
   </si>
   <si>
     <t xml:space="preserve">14.4346342086792</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">15.1021308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352569580078</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186958312988</t>
+    <t xml:space="preserve">15.0186967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849460601807</t>
+    <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
     <t xml:space="preserve">14.6015071868896</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">14.0174493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837005615234</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671365737915</t>
+    <t xml:space="preserve">13.7671375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002616882324</t>
+    <t xml:space="preserve">13.6002626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677602767944</t>
+    <t xml:space="preserve">14.2677593231201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5741519927979</t>
+    <t xml:space="preserve">13.5741500854492</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2444791793823</t>
+    <t xml:space="preserve">14.244478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7417325973511</t>
+    <t xml:space="preserve">13.7417335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.993106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9093151092529</t>
+    <t xml:space="preserve">13.9093160629272</t>
   </si>
   <si>
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796432495117</t>
+    <t xml:space="preserve">14.5796422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606874465942</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
@@ -932,79 +932,79 @@
     <t xml:space="preserve">14.3282709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634359359741</t>
+    <t xml:space="preserve">14.6634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.831018447876</t>
+    <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4958524703979</t>
+    <t xml:space="preserve">14.4958515167236</t>
   </si>
   <si>
     <t xml:space="preserve">14.9985980987549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472267150879</t>
+    <t xml:space="preserve">14.7472257614136</t>
   </si>
   <si>
     <t xml:space="preserve">14.9148063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1661815643311</t>
+    <t xml:space="preserve">15.1661806106567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33376121521</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175539016724</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499713897705</t>
+    <t xml:space="preserve">15.2499723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.082389831543</t>
+    <t xml:space="preserve">15.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851373672485</t>
+    <t xml:space="preserve">15.5851345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668927192688</t>
+    <t xml:space="preserve">15.6689291000366</t>
   </si>
   <si>
     <t xml:space="preserve">15.9202995300293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.004093170166</t>
+    <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878810882568</t>
+    <t xml:space="preserve">16.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794055938721</t>
+    <t xml:space="preserve">16.2794075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1923503875732</t>
+    <t xml:space="preserve">16.1923484802246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1052951812744</t>
+    <t xml:space="preserve">16.1052932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.018238067627</t>
+    <t xml:space="preserve">16.0182361602783</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570724487305</t>
+    <t xml:space="preserve">15.7570705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6700162887573</t>
+    <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.844126701355</t>
+    <t xml:space="preserve">15.8441286087036</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">15.4088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3664608001709</t>
+    <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
     <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6276302337646</t>
+    <t xml:space="preserve">16.6276264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7146816253662</t>
+    <t xml:space="preserve">16.7146835327148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8887939453125</t>
@@ -1034,31 +1034,31 @@
     <t xml:space="preserve">17.1499633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.97585105896</t>
+    <t xml:space="preserve">16.9758491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5852394104004</t>
+    <t xml:space="preserve">17.585241317749</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6299057006836</t>
+    <t xml:space="preserve">18.6299076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.107572555542</t>
+    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557952880859</t>
+    <t xml:space="preserve">18.4557971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.759349822998</t>
+    <t xml:space="preserve">17.7593517303467</t>
   </si>
   <si>
     <t xml:space="preserve">17.933464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3240718841553</t>
+    <t xml:space="preserve">17.3240737915039</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111289978027</t>
@@ -1068,9 +1068,6 @@
   </si>
   <si>
     <t xml:space="preserve">18.2886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1075744628906</t>
   </si>
   <si>
     <t xml:space="preserve">17.8359622955322</t>
@@ -1113,6 +1110,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.844126701355</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -43624,7 +43624,7 @@
         <v>20</v>
       </c>
       <c r="G1613" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43650,7 +43650,7 @@
         <v>20</v>
       </c>
       <c r="G1614" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43702,7 +43702,7 @@
         <v>20</v>
       </c>
       <c r="G1616" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43728,7 +43728,7 @@
         <v>20</v>
       </c>
       <c r="G1617" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43754,7 +43754,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43780,7 +43780,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1619" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43806,7 +43806,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1620" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43832,7 +43832,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1621" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43858,7 +43858,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43884,7 +43884,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43910,7 +43910,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43936,7 +43936,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43962,7 +43962,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43988,7 +43988,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44014,7 +44014,7 @@
         <v>20</v>
       </c>
       <c r="G1628" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44040,7 +44040,7 @@
         <v>20</v>
       </c>
       <c r="G1629" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44066,7 +44066,7 @@
         <v>20</v>
       </c>
       <c r="G1630" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44092,7 +44092,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1631" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44118,7 +44118,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44144,7 +44144,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1633" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44170,7 +44170,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1634" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44196,7 +44196,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44222,7 +44222,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44248,7 +44248,7 @@
         <v>19.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44274,7 +44274,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44300,7 +44300,7 @@
         <v>19.5</v>
       </c>
       <c r="G1639" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44326,7 +44326,7 @@
         <v>19</v>
       </c>
       <c r="G1640" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44352,7 +44352,7 @@
         <v>19</v>
       </c>
       <c r="G1641" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44378,7 +44378,7 @@
         <v>19</v>
       </c>
       <c r="G1642" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44404,7 +44404,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44430,7 +44430,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44456,7 +44456,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1645" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44482,7 +44482,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1646" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44508,7 +44508,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1647" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44534,7 +44534,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1648" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44560,7 +44560,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44586,7 +44586,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44612,7 +44612,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44638,7 +44638,7 @@
         <v>19</v>
       </c>
       <c r="G1652" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44664,7 +44664,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44690,7 +44690,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1654" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44716,7 +44716,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44742,7 +44742,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44768,7 +44768,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44820,7 +44820,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45418,7 +45418,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45496,7 +45496,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1685" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45522,7 +45522,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45548,7 +45548,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45574,7 +45574,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1688" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45600,7 +45600,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1689" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45626,7 +45626,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45652,7 +45652,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1691" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45678,7 +45678,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1692" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45704,7 +45704,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1693" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45756,7 +45756,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1695" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45782,7 +45782,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45808,7 +45808,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1697" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45834,7 +45834,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45860,7 +45860,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45886,7 +45886,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45912,7 +45912,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1701" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45938,7 +45938,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46302,7 +46302,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1716" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46328,7 +46328,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46406,7 +46406,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46432,7 +46432,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1721" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46458,7 +46458,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46484,7 +46484,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46510,7 +46510,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46536,7 +46536,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1725" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47108,7 +47108,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1747" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47446,7 +47446,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1760" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47472,7 +47472,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47498,7 +47498,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1762" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47758,7 +47758,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1772" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47966,7 +47966,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47992,7 +47992,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48226,7 +48226,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48252,7 +48252,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48330,7 +48330,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48382,7 +48382,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48408,7 +48408,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1797" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48434,7 +48434,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48460,7 +48460,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1799" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48486,7 +48486,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48512,7 +48512,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1801" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48538,7 +48538,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48564,7 +48564,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48590,7 +48590,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48772,7 +48772,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -67526,7 +67526,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6909837963</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>217</v>
@@ -67547,6 +67547,32 @@
         <v>444</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6665162037</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>1355</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IB.MI.xlsx
+++ b/data/IB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2194986343384</t>
+    <t xml:space="preserve">13.2194995880127</t>
   </si>
   <si>
     <t xml:space="preserve">IB.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">12.8577013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8716163635254</t>
+    <t xml:space="preserve">12.8716144561768</t>
   </si>
   <si>
     <t xml:space="preserve">12.523736000061</t>
@@ -59,154 +59,154 @@
     <t xml:space="preserve">12.8020401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5167779922485</t>
+    <t xml:space="preserve">12.5167770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.175853729248</t>
+    <t xml:space="preserve">12.1758518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827974319458</t>
+    <t xml:space="preserve">11.8279714584351</t>
   </si>
   <si>
     <t xml:space="preserve">11.1809129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5755996704102</t>
+    <t xml:space="preserve">10.5755987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91462421417236</t>
+    <t xml:space="preserve">9.91462326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39280223846436</t>
+    <t xml:space="preserve">9.39280128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0885629653931</t>
+    <t xml:space="preserve">10.0885648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3112096786499</t>
+    <t xml:space="preserve">10.3112077713013</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4990653991699</t>
+    <t xml:space="preserve">10.4990644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364461898804</t>
+    <t xml:space="preserve">10.4364452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6451749801636</t>
+    <t xml:space="preserve">10.6451740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.714750289917</t>
+    <t xml:space="preserve">10.7147521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7843265533447</t>
+    <t xml:space="preserve">10.784327507019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132209777832</t>
+    <t xml:space="preserve">11.1322078704834</t>
   </si>
   <si>
     <t xml:space="preserve">11.3826847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6331586837769</t>
+    <t xml:space="preserve">11.6331577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8905906677246</t>
+    <t xml:space="preserve">11.8905897140503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1549806594849</t>
+    <t xml:space="preserve">12.1549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148024559021</t>
+    <t xml:space="preserve">12.1480226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4193706512451</t>
+    <t xml:space="preserve">12.4193677902222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6628885269165</t>
+    <t xml:space="preserve">12.6628904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9411916732788</t>
+    <t xml:space="preserve">12.9411926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5933113098145</t>
+    <t xml:space="preserve">12.5933132171631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150091171265</t>
+    <t xml:space="preserve">12.3150081634521</t>
   </si>
   <si>
     <t xml:space="preserve">12.0506172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114627838135</t>
+    <t xml:space="preserve">11.9114646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758394241333</t>
+    <t xml:space="preserve">11.7583951950073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227870941162</t>
+    <t xml:space="preserve">12.0227861404419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7236070632935</t>
+    <t xml:space="preserve">11.7236061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.984130859375</t>
+    <t xml:space="preserve">11.9841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">11.7163715362549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9407119750977</t>
+    <t xml:space="preserve">11.940710067749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045267105103</t>
+    <t xml:space="preserve">11.9045276641846</t>
   </si>
   <si>
     <t xml:space="preserve">11.7670288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5065031051636</t>
+    <t xml:space="preserve">11.5065040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788717269897</t>
+    <t xml:space="preserve">11.5788707733154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2893991470337</t>
+    <t xml:space="preserve">11.289400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426874160767</t>
+    <t xml:space="preserve">11.542688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979520797729</t>
+    <t xml:space="preserve">11.3979511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6512393951416</t>
+    <t xml:space="preserve">11.6512403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8683443069458</t>
+    <t xml:space="preserve">11.8683452606201</t>
   </si>
   <si>
     <t xml:space="preserve">11.8321599960327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0130796432495</t>
+    <t xml:space="preserve">12.0130786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0854473114014</t>
+    <t xml:space="preserve">12.0854482650757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1578149795532</t>
+    <t xml:space="preserve">12.1578140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.193998336792</t>
+    <t xml:space="preserve">12.1939992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3025531768799</t>
+    <t xml:space="preserve">12.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275535583496</t>
@@ -215,184 +215,184 @@
     <t xml:space="preserve">12.295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.447286605835</t>
+    <t xml:space="preserve">12.4472875595093</t>
   </si>
   <si>
     <t xml:space="preserve">12.5196542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643915176392</t>
+    <t xml:space="preserve">12.6643886566162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9466257095337</t>
+    <t xml:space="preserve">12.9466238021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7729425430298</t>
+    <t xml:space="preserve">12.7729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9755716323853</t>
+    <t xml:space="preserve">12.9755725860596</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091287612915</t>
+    <t xml:space="preserve">12.8091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433366775513</t>
+    <t xml:space="preserve">13.2433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3157014846802</t>
+    <t xml:space="preserve">13.3157024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4604368209839</t>
+    <t xml:space="preserve">13.4604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880701065063</t>
+    <t xml:space="preserve">13.3880681991577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4025440216064</t>
+    <t xml:space="preserve">13.4025459289551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532022476196</t>
+    <t xml:space="preserve">13.4532012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4242525100708</t>
+    <t xml:space="preserve">13.4242553710938</t>
   </si>
   <si>
     <t xml:space="preserve">13.5328073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5689907073975</t>
+    <t xml:space="preserve">13.5689897537231</t>
   </si>
   <si>
     <t xml:space="preserve">13.5545167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4966230392456</t>
+    <t xml:space="preserve">13.4966249465942</t>
   </si>
   <si>
     <t xml:space="preserve">13.3518867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459648132324</t>
+    <t xml:space="preserve">13.4459638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387264251709</t>
+    <t xml:space="preserve">13.4387283325195</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038595199585</t>
+    <t xml:space="preserve">13.5038604736328</t>
   </si>
   <si>
     <t xml:space="preserve">13.2288599014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8814935684204</t>
+    <t xml:space="preserve">12.8814945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0985994338989</t>
+    <t xml:space="preserve">13.0986003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9104413986206</t>
+    <t xml:space="preserve">12.9104423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0262308120728</t>
+    <t xml:space="preserve">13.0262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1347827911377</t>
+    <t xml:space="preserve">13.134783744812</t>
   </si>
   <si>
     <t xml:space="preserve">12.8453102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1275444030762</t>
+    <t xml:space="preserve">13.1275463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7439956665039</t>
+    <t xml:space="preserve">12.7439966201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0189943313599</t>
+    <t xml:space="preserve">13.0189933776855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571521759033</t>
+    <t xml:space="preserve">12.6571550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2446575164795</t>
+    <t xml:space="preserve">12.2446565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2012357711792</t>
+    <t xml:space="preserve">12.2012338638306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9334735870361</t>
+    <t xml:space="preserve">11.9334754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1143951416016</t>
+    <t xml:space="preserve">12.1143970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709743499756</t>
+    <t xml:space="preserve">12.0709733963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0492639541626</t>
+    <t xml:space="preserve">12.0492630004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.8466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0782117843628</t>
+    <t xml:space="preserve">12.0782108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9913702011108</t>
+    <t xml:space="preserve">11.9913692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9986057281494</t>
+    <t xml:space="preserve">11.9986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1722888946533</t>
+    <t xml:space="preserve">12.1722869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551839828491</t>
+    <t xml:space="preserve">11.9551830291748</t>
   </si>
   <si>
     <t xml:space="preserve">11.9696588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9768943786621</t>
+    <t xml:space="preserve">11.9768953323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597913742065</t>
+    <t xml:space="preserve">11.7597904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1505794525146</t>
+    <t xml:space="preserve">12.150577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2301816940308</t>
+    <t xml:space="preserve">12.2301826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2229480743408</t>
+    <t xml:space="preserve">12.2229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1554145812988</t>
+    <t xml:space="preserve">12.1554155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.3054828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3805170059204</t>
+    <t xml:space="preserve">12.3805150985718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132905960083</t>
+    <t xml:space="preserve">12.1329050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3880186080933</t>
+    <t xml:space="preserve">12.3880195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0428657531738</t>
+    <t xml:space="preserve">12.0428667068481</t>
   </si>
   <si>
     <t xml:space="preserve">12.3129854202271</t>
@@ -401,31 +401,31 @@
     <t xml:space="preserve">12.4180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756025314331</t>
+    <t xml:space="preserve">12.5756015777588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8307180404663</t>
+    <t xml:space="preserve">12.830717086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158437728882</t>
+    <t xml:space="preserve">13.1158428192139</t>
   </si>
   <si>
     <t xml:space="preserve">12.9807834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9732789993286</t>
+    <t xml:space="preserve">12.9732799530029</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9657773971558</t>
+    <t xml:space="preserve">12.9657764434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.943265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1308488845825</t>
+    <t xml:space="preserve">13.1308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">12.8682346343994</t>
@@ -437,46 +437,46 @@
     <t xml:space="preserve">13.1083393096924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093334197998</t>
+    <t xml:space="preserve">13.0933332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.3559503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2809190750122</t>
+    <t xml:space="preserve">13.2809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4309825897217</t>
+    <t xml:space="preserve">13.4309854507446</t>
   </si>
   <si>
     <t xml:space="preserve">13.5735492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5435333251953</t>
+    <t xml:space="preserve">13.5435352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.235897064209</t>
+    <t xml:space="preserve">13.2358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.138352394104</t>
+    <t xml:space="preserve">13.1383533477783</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.205885887146</t>
+    <t xml:space="preserve">13.2058849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3934650421143</t>
+    <t xml:space="preserve">13.3934659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685020446777</t>
+    <t xml:space="preserve">13.4685010910034</t>
   </si>
   <si>
     <t xml:space="preserve">13.3184337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2434024810791</t>
+    <t xml:space="preserve">13.2434005737305</t>
   </si>
   <si>
     <t xml:space="preserve">13.1683664321899</t>
@@ -494,31 +494,31 @@
     <t xml:space="preserve">13.8061513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5810527801514</t>
+    <t xml:space="preserve">13.5810499191284</t>
   </si>
   <si>
     <t xml:space="preserve">14.0687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6936016082764</t>
+    <t xml:space="preserve">13.6935987472534</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6485805511475</t>
+    <t xml:space="preserve">13.6485815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4159784317017</t>
+    <t xml:space="preserve">13.4159774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9562206268311</t>
+    <t xml:space="preserve">13.9562187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0312528610229</t>
+    <t xml:space="preserve">14.0312519073486</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4459896087646</t>
+    <t xml:space="preserve">13.4459924697876</t>
   </si>
   <si>
     <t xml:space="preserve">13.7986488342285</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">14.0087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6315174102783</t>
+    <t xml:space="preserve">14.6315183639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3013725280762</t>
+    <t xml:space="preserve">14.3013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165113449097</t>
+    <t xml:space="preserve">14.616512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915464401245</t>
+    <t xml:space="preserve">14.6915435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9991836547852</t>
+    <t xml:space="preserve">14.9991855621338</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0066862106323</t>
+    <t xml:space="preserve">15.0066871643066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991678237915</t>
+    <t xml:space="preserve">14.991681098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9766721725464</t>
+    <t xml:space="preserve">14.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">14.9691696166992</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">14.6465263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941345214844</t>
+    <t xml:space="preserve">14.8941373825073</t>
   </si>
   <si>
     <t xml:space="preserve">14.6390218734741</t>
@@ -566,46 +566,46 @@
     <t xml:space="preserve">15.1567525863647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6069536209106</t>
+    <t xml:space="preserve">15.6069507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4568881988525</t>
+    <t xml:space="preserve">15.4568891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7570209503174</t>
+    <t xml:space="preserve">15.757022857666</t>
   </si>
   <si>
     <t xml:space="preserve">16.3572883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6574230194092</t>
+    <t xml:space="preserve">16.6574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7078895568848</t>
+    <t xml:space="preserve">17.7078914642334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2576885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1076240539551</t>
+    <t xml:space="preserve">17.1076221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.957555770874</t>
+    <t xml:space="preserve">16.9575538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5073547363281</t>
+    <t xml:space="preserve">16.5073528289795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8074893951416</t>
+    <t xml:space="preserve">16.8074913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072257995605</t>
+    <t xml:space="preserve">16.2072238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0571537017822</t>
+    <t xml:space="preserve">16.0571517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3615760803223</t>
+    <t xml:space="preserve">16.3615741729736</t>
   </si>
   <si>
     <t xml:space="preserve">16.0528659820557</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">14.9723854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898036956787</t>
+    <t xml:space="preserve">15.5898027420044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4354496002197</t>
+    <t xml:space="preserve">15.435450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7441577911377</t>
+    <t xml:space="preserve">15.7441606521606</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5159301757812</t>
+    <t xml:space="preserve">16.5159282684326</t>
   </si>
   <si>
     <t xml:space="preserve">16.8246383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8985118865967</t>
+    <t xml:space="preserve">15.8985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1267385482788</t>
+    <t xml:space="preserve">15.1267404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495634078979</t>
+    <t xml:space="preserve">15.0495615005493</t>
   </si>
   <si>
     <t xml:space="preserve">14.6636762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2810926437378</t>
+    <t xml:space="preserve">15.2810935974121</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549671173096</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">14.432147026062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8919038772583</t>
+    <t xml:space="preserve">13.8919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2522134780884</t>
+    <t xml:space="preserve">14.2522125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319381713867</t>
+    <t xml:space="preserve">13.931939125061</t>
   </si>
   <si>
     <t xml:space="preserve">13.7718000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.45152759552</t>
+    <t xml:space="preserve">13.4515266418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.6917324066162</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">14.0120058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8518705368042</t>
+    <t xml:space="preserve">13.8518695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113208770752</t>
+    <t xml:space="preserve">13.2113199234009</t>
   </si>
   <si>
     <t xml:space="preserve">13.291389465332</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">14.4123497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0920753479004</t>
+    <t xml:space="preserve">14.0920763015747</t>
   </si>
   <si>
     <t xml:space="preserve">13.3714580535889</t>
@@ -707,34 +707,34 @@
     <t xml:space="preserve">13.0511837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9711151123047</t>
+    <t xml:space="preserve">12.9711132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8910465240479</t>
+    <t xml:space="preserve">12.8910455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810977935791</t>
+    <t xml:space="preserve">12.8109769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7309093475342</t>
+    <t xml:space="preserve">12.7309103012085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907026290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6508407592773</t>
+    <t xml:space="preserve">12.6508417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106349945068</t>
+    <t xml:space="preserve">12.4106340408325</t>
   </si>
   <si>
     <t xml:space="preserve">11.9302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.690016746521</t>
+    <t xml:space="preserve">11.6900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5707721710205</t>
+    <t xml:space="preserve">12.5707712173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.3305654525757</t>
@@ -743,34 +743,34 @@
     <t xml:space="preserve">12.0903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704301834106</t>
+    <t xml:space="preserve">12.170428276062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1295385360718</t>
+    <t xml:space="preserve">11.1295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2896747589111</t>
+    <t xml:space="preserve">11.2896738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498119354248</t>
+    <t xml:space="preserve">11.4498109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6099472045898</t>
+    <t xml:space="preserve">11.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">11.5298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.369743347168</t>
+    <t xml:space="preserve">11.3697423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.20960521698</t>
+    <t xml:space="preserve">11.2096061706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.9693994522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0494680404663</t>
+    <t xml:space="preserve">11.0494689941406</t>
   </si>
   <si>
     <t xml:space="preserve">10.6491250991821</t>
@@ -779,40 +779,40 @@
     <t xml:space="preserve">10.3288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889879226685</t>
+    <t xml:space="preserve">10.4889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089193344116</t>
+    <t xml:space="preserve">10.4089202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2487831115723</t>
+    <t xml:space="preserve">10.2487821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0085763931274</t>
+    <t xml:space="preserve">10.0085773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1687126159668</t>
+    <t xml:space="preserve">10.1687135696411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7700862884521</t>
+    <t xml:space="preserve">11.7700853347778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0102920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8493270874023</t>
+    <t xml:space="preserve">12.8493280410767</t>
   </si>
   <si>
     <t xml:space="preserve">12.5990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.348705291748</t>
+    <t xml:space="preserve">12.3487062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0137090682983</t>
+    <t xml:space="preserve">11.0137100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.681206703186</t>
+    <t xml:space="preserve">11.6812076568604</t>
   </si>
   <si>
     <t xml:space="preserve">11.9315185546875</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">12.181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321422576904</t>
+    <t xml:space="preserve">12.4321413040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155792236328</t>
+    <t xml:space="preserve">12.5155801773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.932765007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830768585205</t>
+    <t xml:space="preserve">13.1830778121948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4333877563477</t>
+    <t xml:space="preserve">13.4333868026733</t>
   </si>
   <si>
     <t xml:space="preserve">13.3499507904053</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">13.0162019729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.76589012146</t>
+    <t xml:space="preserve">12.7658910751343</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768385887146</t>
+    <t xml:space="preserve">14.7683839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5180711746216</t>
+    <t xml:space="preserve">14.5180721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8518209457397</t>
+    <t xml:space="preserve">14.8518199920654</t>
   </si>
   <si>
     <t xml:space="preserve">14.4346351623535</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">15.1021318435669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352560043335</t>
+    <t xml:space="preserve">14.9352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0186939239502</t>
+    <t xml:space="preserve">15.0186958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6849460601807</t>
+    <t xml:space="preserve">14.684947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6015062332153</t>
+    <t xml:space="preserve">14.6015090942383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3511953353882</t>
+    <t xml:space="preserve">14.3511962890625</t>
   </si>
   <si>
     <t xml:space="preserve">14.1843233108521</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">14.017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6837005615234</t>
+    <t xml:space="preserve">13.6837015151978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7671375274658</t>
+    <t xml:space="preserve">13.7671365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6002626419067</t>
+    <t xml:space="preserve">13.6002635955811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2677593231201</t>
+    <t xml:space="preserve">14.2677602767944</t>
   </si>
   <si>
     <t xml:space="preserve">13.5741519927979</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">13.7417316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9931077957153</t>
+    <t xml:space="preserve">13.9931058883667</t>
   </si>
   <si>
     <t xml:space="preserve">13.9093141555786</t>
@@ -914,70 +914,70 @@
     <t xml:space="preserve">14.4120616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579644203186</t>
+    <t xml:space="preserve">14.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1606884002686</t>
+    <t xml:space="preserve">14.1606864929199</t>
   </si>
   <si>
     <t xml:space="preserve">13.657940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903602600098</t>
+    <t xml:space="preserve">13.4903593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3282699584961</t>
+    <t xml:space="preserve">14.3282690048218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6634330749512</t>
+    <t xml:space="preserve">14.6634349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8310165405273</t>
+    <t xml:space="preserve">14.8310174942017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4958524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9985980987549</t>
+    <t xml:space="preserve">14.9985971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7472257614136</t>
+    <t xml:space="preserve">14.7472276687622</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9148073196411</t>
+    <t xml:space="preserve">14.9148092269897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1661815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337631225586</t>
+    <t xml:space="preserve">15.3337621688843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175539016724</t>
+    <t xml:space="preserve">15.4175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2499742507935</t>
+    <t xml:space="preserve">15.2499704360962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0823888778687</t>
+    <t xml:space="preserve">15.082389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5851364135742</t>
+    <t xml:space="preserve">15.5851354598999</t>
   </si>
   <si>
     <t xml:space="preserve">15.668927192688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9202976226807</t>
+    <t xml:space="preserve">15.9203014373779</t>
   </si>
   <si>
     <t xml:space="preserve">16.0040912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0878849029541</t>
+    <t xml:space="preserve">16.0878810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4535140991211</t>
+    <t xml:space="preserve">16.4535160064697</t>
   </si>
   <si>
     <t xml:space="preserve">16.2794055938721</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">16.018238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311828613281</t>
+    <t xml:space="preserve">15.9311809539795</t>
   </si>
   <si>
     <t xml:space="preserve">15.7570724487305</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">15.6700143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8441295623779</t>
+    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
     <t xml:space="preserve">15.5829591751099</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">16.3664588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5405693054199</t>
+    <t xml:space="preserve">16.5405712127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.627628326416</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">16.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1499633789062</t>
+    <t xml:space="preserve">17.1499614715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.97585105896</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">17.5852394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6299076080322</t>
+    <t xml:space="preserve">18.6299057006836</t>
   </si>
   <si>
     <t xml:space="preserve">18.107572555542</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">18.2816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4557971954346</t>
+    <t xml:space="preserve">18.4557991027832</t>
   </si>
   <si>
     <t xml:space="preserve">17.759349822998</t>
@@ -1110,9 +1110,6 @@
   </si>
   <si>
     <t xml:space="preserve">16.1157398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8441276550293</t>
   </si>
   <si>
     <t xml:space="preserve">16.2968158721924</t>
@@ -44765,7 +44762,7 @@
         <v>17.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44791,7 +44788,7 @@
         <v>18</v>
       </c>
       <c r="G1658" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44843,7 +44840,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44869,7 +44866,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44895,7 +44892,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1662" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44921,7 +44918,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1663" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44947,7 +44944,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44973,7 +44970,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44999,7 +44996,7 @@
         <v>18</v>
       </c>
       <c r="G1666" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45025,7 +45022,7 @@
         <v>18</v>
       </c>
       <c r="G1667" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45051,7 +45048,7 @@
         <v>18</v>
       </c>
       <c r="G1668" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45077,7 +45074,7 @@
         <v>18</v>
       </c>
       <c r="G1669" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45103,7 +45100,7 @@
         <v>18</v>
       </c>
       <c r="G1670" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45129,7 +45126,7 @@
         <v>18</v>
       </c>
       <c r="G1671" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45155,7 +45152,7 @@
         <v>18</v>
       </c>
       <c r="G1672" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45181,7 +45178,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1673" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45207,7 +45204,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45233,7 +45230,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1675" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45259,7 +45256,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45285,7 +45282,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45311,7 +45308,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1678" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45337,7 +45334,7 @@
         <v>18</v>
       </c>
       <c r="G1679" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45363,7 +45360,7 @@
         <v>18</v>
       </c>
       <c r="G1680" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45389,7 +45386,7 @@
         <v>18</v>
       </c>
       <c r="G1681" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45441,7 +45438,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45467,7 +45464,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45727,7 +45724,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45961,7 +45958,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45987,7 +45984,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46013,7 +46010,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46039,7 +46036,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46065,7 +46062,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46091,7 +46088,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46117,7 +46114,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46143,7 +46140,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46169,7 +46166,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46195,7 +46192,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1712" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46221,7 +46218,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1713" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46247,7 +46244,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46273,7 +46270,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46351,7 +46348,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46377,7 +46374,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46559,7 +46556,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46585,7 +46582,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1727" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46611,7 +46608,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46637,7 +46634,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46663,7 +46660,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46689,7 +46686,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1731" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46715,7 +46712,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1732" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46741,7 +46738,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46767,7 +46764,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46793,7 +46790,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46819,7 +46816,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46845,7 +46842,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1737" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46871,7 +46868,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46897,7 +46894,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46923,7 +46920,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46949,7 +46946,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46975,7 +46972,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47001,7 +46998,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1743" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47027,7 +47024,7 @@
         <v>18</v>
       </c>
       <c r="G1744" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47053,7 +47050,7 @@
         <v>18</v>
       </c>
       <c r="G1745" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47079,7 +47076,7 @@
         <v>18</v>
       </c>
       <c r="G1746" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47131,7 +47128,7 @@
         <v>18</v>
       </c>
       <c r="G1748" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47157,7 +47154,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1749" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47183,7 +47180,7 @@
         <v>18</v>
       </c>
       <c r="G1750" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47209,7 +47206,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47235,7 +47232,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47261,7 +47258,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47287,7 +47284,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47313,7 +47310,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47339,7 +47336,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47365,7 +47362,7 @@
         <v>18</v>
       </c>
       <c r="G1757" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47391,7 +47388,7 @@
         <v>18</v>
       </c>
       <c r="G1758" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47417,7 +47414,7 @@
         <v>18</v>
       </c>
       <c r="G1759" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47521,7 +47518,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47547,7 +47544,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1764" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47573,7 +47570,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47599,7 +47596,7 @@
         <v>18</v>
       </c>
       <c r="G1766" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47625,7 +47622,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47651,7 +47648,7 @@
         <v>18</v>
       </c>
       <c r="G1768" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47677,7 +47674,7 @@
         <v>18</v>
       </c>
       <c r="G1769" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47703,7 +47700,7 @@
         <v>18</v>
       </c>
       <c r="G1770" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47729,7 +47726,7 @@
         <v>18</v>
       </c>
       <c r="G1771" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47781,7 +47778,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47807,7 +47804,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47833,7 +47830,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47859,7 +47856,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1776" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47885,7 +47882,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47911,7 +47908,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47937,7 +47934,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48015,7 +48012,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48041,7 +48038,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48067,7 +48064,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1784" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48093,7 +48090,7 @@
         <v>18</v>
       </c>
       <c r="G1785" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48119,7 +48116,7 @@
         <v>18</v>
       </c>
       <c r="G1786" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48145,7 +48142,7 @@
         <v>18</v>
       </c>
       <c r="G1787" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48171,7 +48168,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48197,7 +48194,7 @@
         <v>18</v>
       </c>
       <c r="G1789" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48249,7 +48246,7 @@
         <v>17.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48275,7 +48272,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48301,7 +48298,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48353,7 +48350,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48613,7 +48610,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48639,7 +48636,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48665,7 +48662,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48691,7 +48688,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48717,7 +48714,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48743,7 +48740,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1810" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48769,7 +48766,7 @@
         <v>17.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48795,7 +48792,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1812" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48821,7 +48818,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48847,7 +48844,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48873,7 +48870,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48899,7 +48896,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48925,7 +48922,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1817" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48951,7 +48948,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48977,7 +48974,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49003,7 +49000,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49029,7 +49026,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49055,7 +49052,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49081,7 +49078,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49107,7 +49104,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49133,7 +49130,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49159,7 +49156,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49185,7 +49182,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49211,7 +49208,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49237,7 +49234,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49263,7 +49260,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49289,7 +49286,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49315,7 +49312,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49341,7 +49338,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49367,7 +49364,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49393,7 +49390,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1835" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49419,7 +49416,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49445,7 +49442,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49471,7 +49468,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49497,7 +49494,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49523,7 +49520,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49549,7 +49546,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49575,7 +49572,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49601,7 +49598,7 @@
         <v>16</v>
       </c>
       <c r="G1843" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49627,7 +49624,7 @@
         <v>15</v>
       </c>
       <c r="G1844" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49653,7 +49650,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49679,7 +49676,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1846" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49705,7 +49702,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49731,7 +49728,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49757,7 +49754,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1849" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49783,7 +49780,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49809,7 +49806,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49835,7 +49832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49861,7 +49858,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49887,7 +49884,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1854" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49913,7 +49910,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49939,7 +49936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49965,7 +49962,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49991,7 +49988,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1858" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50017,7 +50014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50043,7 +50040,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50069,7 +50066,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50095,7 +50092,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50121,7 +50118,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1863" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50147,7 +50144,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50173,7 +50170,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1865" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50199,7 +50196,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1866" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50225,7 +50222,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1867" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50251,7 +50248,7 @@
         <v>15.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50277,7 +50274,7 @@
         <v>15.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50303,7 +50300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50329,7 +50326,7 @@
         <v>15.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50355,7 +50352,7 @@
         <v>15